--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,7 +1062,6 @@
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3896,7 +3895,7 @@
         </is>
       </c>
       <c r="B25" s="89" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="C25" s="89" t="n">
         <v>7.26</v>
@@ -3993,7 +3992,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>-0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.15</v>
@@ -4090,7 +4089,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.11</v>
@@ -8840,7 +8839,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>3.38</v>
+        <v>2.44</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>3.38</v>
@@ -8937,7 +8936,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>15.09</v>
+        <v>14.75</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>15.09</v>
@@ -9034,7 +9033,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>62.36</v>
+        <v>67.67</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>62.36</v>
@@ -9131,7 +9130,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>62.36</v>
+        <v>67.67</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>62.36</v>
@@ -9385,7 +9384,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>0.07000000000000001</v>
@@ -9482,7 +9481,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>7.11</v>
+        <v>6.41</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>7.11</v>
@@ -9579,7 +9578,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>50.71</v>
+        <v>44.15</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>50.71</v>
@@ -9676,7 +9675,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>42.3</v>
+        <v>38.85</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>42.3</v>
@@ -9930,7 +9929,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>4.39</v>
+        <v>3.41</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>4.39</v>
@@ -10027,7 +10026,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>16.7</v>
+        <v>16.83</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>16.7</v>
@@ -10118,13 +10117,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="inlineStr">
+      <c r="A35" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>16.98</v>
+        <v>63.63</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>16.98</v>
@@ -10215,13 +10214,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>16.98</v>
+        <v>63.63</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>16.98</v>
@@ -11565,7 +11564,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>3.49</v>
+        <v>3.61</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>0.29</v>
@@ -11662,7 +11661,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>9.869999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>6.18</v>
@@ -11759,7 +11758,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>73.19</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>41.54</v>
@@ -11856,7 +11855,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>64.76000000000001</v>
+        <v>65.12</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>49.84</v>
@@ -12110,7 +12109,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>0.98</v>
+        <v>0.54</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>0.76</v>
@@ -12207,7 +12206,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>6.73</v>
+        <v>6.26</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>7.6</v>
@@ -12304,7 +12303,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>57.39</v>
+        <v>42</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>38.72</v>
@@ -12401,7 +12400,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>46.79</v>
+        <v>36.92</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>35.14</v>
@@ -12655,7 +12654,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>5.33</v>
+        <v>5.04</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>4.52</v>
@@ -12752,7 +12751,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>11.35</v>
+        <v>11.04</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>11.24</v>
@@ -12849,7 +12848,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>61.47</v>
+        <v>54.79</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>26.44</v>
@@ -12946,7 +12945,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>56.34</v>
+        <v>51.35</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>34.78</v>
@@ -13039,7 +13038,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RSI2:16.98&lt;=36;ixic:RSI2:16.98&lt;=35</t>
+          <t>今日买报：</t>
         </is>
       </c>
     </row>
@@ -16702,13 +16701,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="97" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="99">
+      <c r="J2" s="98">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16739,13 +16738,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="97" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="98">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16776,13 +16775,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="97" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="98">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16813,13 +16812,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="97" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="98">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16850,13 +16849,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="100" t="n">
+      <c r="H6" s="99" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="98">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16887,13 +16886,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="97" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="98">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16924,13 +16923,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="100" t="n">
+      <c r="H8" s="99" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="98">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16961,13 +16960,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="100" t="n">
+      <c r="H9" s="99" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="98">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16998,13 +16997,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="99" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="100">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17035,13 +17034,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="102" t="n">
+      <c r="H11" s="101" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="102">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17072,13 +17071,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="100" t="n">
+      <c r="H12" s="99" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="100">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17109,13 +17108,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="102" t="n">
+      <c r="H13" s="101" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="102">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17146,13 +17145,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="100" t="n">
+      <c r="H14" s="99" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="100">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17183,13 +17182,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="102" t="n">
+      <c r="H15" s="101" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="102">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17220,13 +17219,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="100" t="n">
+      <c r="H16" s="99" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="100">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17257,13 +17256,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="102" t="n">
+      <c r="H17" s="101" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="102">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17294,13 +17293,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="100" t="n">
+      <c r="H18" s="99" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="100">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17331,13 +17330,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="102" t="n">
+      <c r="H19" s="101" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="102">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17368,13 +17367,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="100" t="n">
+      <c r="H20" s="99" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="100">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17405,13 +17404,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="102" t="n">
+      <c r="H21" s="101" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="103">
+      <c r="J21" s="102">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17440,13 +17439,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="104" t="n">
+      <c r="H22" s="103" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="100">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17475,13 +17474,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="103" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="100">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17510,13 +17509,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="n">
+      <c r="H24" s="99" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="100">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17545,13 +17544,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="100" t="n">
+      <c r="H25" s="99" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="100">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17580,13 +17579,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="100" t="n">
+      <c r="H26" s="99" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="100">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17615,13 +17614,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="100" t="n">
+      <c r="H27" s="99" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="100">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17650,13 +17649,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="104" t="n">
+      <c r="H28" s="103" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="100">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17685,13 +17684,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="105" t="n">
+      <c r="H29" s="104" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="102">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17720,13 +17719,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="104" t="n">
+      <c r="H30" s="103" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="100">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17755,13 +17754,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="105" t="n">
+      <c r="H31" s="104" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="103">
+      <c r="J31" s="102">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17790,13 +17789,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="104" t="n">
+      <c r="H32" s="103" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="100">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17825,13 +17824,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="105" t="n">
+      <c r="H33" s="104" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="102">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17860,13 +17859,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="105" t="n">
+      <c r="H34" s="104" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="102">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17895,13 +17894,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="103" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="100">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17930,13 +17929,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="105" t="n">
+      <c r="H36" s="104" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="103">
+      <c r="J36" s="102">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17965,13 +17964,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="103" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="100">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18000,13 +17999,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="104" t="n">
+      <c r="H38" s="103" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="100">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18035,13 +18034,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="105" t="n">
+      <c r="H39" s="104" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="103">
+      <c r="J39" s="102">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2732,7 +2733,7 @@
         </is>
       </c>
       <c r="B13" s="87" t="n">
-        <v>0</v>
+        <v>33.78</v>
       </c>
       <c r="C13" s="87" t="n">
         <v>15.39</v>
@@ -3993,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.16</v>
@@ -4090,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.45</v>
@@ -8682,9 +8683,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8840,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>2.44</v>
+        <v>3.27</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>2.44</v>
@@ -8937,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.75</v>
+        <v>14.47</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.75</v>
@@ -9034,7 +9035,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>67.67</v>
+        <v>76.59</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>67.67</v>
@@ -9131,7 +9132,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>67.67</v>
+        <v>76.59</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>67.67</v>
@@ -9385,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.57</v>
+        <v>-0.03</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.57</v>
@@ -9482,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>6.41</v>
+        <v>6.34</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>6.41</v>
@@ -9579,7 +9580,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>44.15</v>
+        <v>54.82</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>44.15</v>
@@ -9676,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>38.85</v>
+        <v>45.59</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>38.85</v>
@@ -9930,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>3.41</v>
@@ -10027,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>16.83</v>
+        <v>16.8</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>16.83</v>
@@ -10124,7 +10125,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>63.63</v>
+        <v>72.87</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>63.63</v>
@@ -10221,7 +10222,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>63.63</v>
+        <v>72.87</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>63.63</v>
@@ -10478,7 +10479,7 @@
         <v>-3.21</v>
       </c>
       <c r="C38" s="96" t="n">
-        <v>-2.89</v>
+        <v>-2.93</v>
       </c>
       <c r="D38" s="96" t="n">
         <v>-4.04</v>
@@ -10575,7 +10576,7 @@
         <v>18.39</v>
       </c>
       <c r="C39" s="96" t="n">
-        <v>17.18</v>
+        <v>17.13</v>
       </c>
       <c r="D39" s="96" t="n">
         <v>15.12</v>
@@ -10669,10 +10670,10 @@
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>54.89</v>
+        <v>55.1</v>
       </c>
       <c r="C40" s="96" t="n">
-        <v>60.05</v>
+        <v>59.66</v>
       </c>
       <c r="D40" s="96" t="n">
         <v>46.7</v>
@@ -10766,10 +10767,10 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>53.09</v>
+        <v>53.16</v>
       </c>
       <c r="C41" s="96" t="n">
-        <v>55.77</v>
+        <v>55.52</v>
       </c>
       <c r="D41" s="96" t="n">
         <v>48.02</v>
@@ -11020,7 +11021,7 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="C43" s="96" t="n">
         <v>0.79</v>
@@ -11117,7 +11118,7 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
-        <v>14.93</v>
+        <v>15.01</v>
       </c>
       <c r="C44" s="96" t="n">
         <v>14.24</v>
@@ -11214,7 +11215,7 @@
         </is>
       </c>
       <c r="B45" s="96" t="n">
-        <v>71.48</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="C45" s="96" t="n">
         <v>68.26000000000001</v>
@@ -11311,7 +11312,7 @@
         </is>
       </c>
       <c r="B46" s="96" t="n">
-        <v>64.22</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="C46" s="96" t="n">
         <v>62.04</v>
@@ -11565,7 +11566,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>-1.99</v>
+        <v>-2.43</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>3.61</v>
@@ -11662,7 +11663,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>3.69</v>
+        <v>3.23</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>9.99</v>
@@ -11759,7 +11760,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>36.1</v>
+        <v>34.71</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>73.68000000000001</v>
@@ -11856,7 +11857,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>42.7</v>
+        <v>41.57</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>65.12</v>
@@ -11952,9 +11953,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B52" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C52" s="93" t="inlineStr">
@@ -12110,7 +12111,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>0.54</v>
+        <v>-0.98</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>0.54</v>
@@ -12207,7 +12208,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>6.26</v>
+        <v>5.12</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>6.26</v>
@@ -12298,13 +12299,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="78" t="inlineStr">
+      <c r="A55" s="98" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>42</v>
+        <v>21.68</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>42</v>
@@ -12401,7 +12402,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>36.92</v>
+        <v>26.35</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>36.92</v>
@@ -12655,10 +12656,10 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>3.83</v>
+        <v>3.22</v>
       </c>
       <c r="C58" s="96" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="D58" s="96" t="n">
         <v>4.52</v>
@@ -12752,10 +12753,10 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.31</v>
+        <v>9.66</v>
       </c>
       <c r="C59" s="96" t="n">
-        <v>11.05</v>
+        <v>11.03</v>
       </c>
       <c r="D59" s="96" t="n">
         <v>11.24</v>
@@ -12849,10 +12850,10 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>39.59</v>
+        <v>29</v>
       </c>
       <c r="C60" s="96" t="n">
-        <v>55.05</v>
+        <v>54.46</v>
       </c>
       <c r="D60" s="96" t="n">
         <v>26.44</v>
@@ -12946,10 +12947,10 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>41.82</v>
+        <v>33.63</v>
       </c>
       <c r="C61" s="96" t="n">
-        <v>51.54</v>
+        <v>51.12</v>
       </c>
       <c r="D61" s="96" t="n">
         <v>34.78</v>
@@ -13039,7 +13040,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：fr40:RSI3:21.68&lt;=28</t>
         </is>
       </c>
     </row>
@@ -16702,13 +16703,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="99" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="99">
+      <c r="J2" s="100">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16739,13 +16740,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="100">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16776,13 +16777,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16813,13 +16814,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16850,13 +16851,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="100" t="n">
+      <c r="H6" s="101" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16887,13 +16888,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16924,13 +16925,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="100" t="n">
+      <c r="H8" s="101" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16961,13 +16962,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="100" t="n">
+      <c r="H9" s="101" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16998,13 +16999,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17035,13 +17036,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="102" t="n">
+      <c r="H11" s="103" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="104">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17072,13 +17073,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="100" t="n">
+      <c r="H12" s="101" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="102">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17109,13 +17110,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="102" t="n">
+      <c r="H13" s="103" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="104">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17146,13 +17147,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="100" t="n">
+      <c r="H14" s="101" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="102">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17183,13 +17184,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="102" t="n">
+      <c r="H15" s="103" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="104">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17220,13 +17221,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="100" t="n">
+      <c r="H16" s="101" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="102">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17257,13 +17258,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="102" t="n">
+      <c r="H17" s="103" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="104">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17294,13 +17295,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="100" t="n">
+      <c r="H18" s="101" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="102">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17331,13 +17332,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="102" t="n">
+      <c r="H19" s="103" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="104">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17368,13 +17369,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="100" t="n">
+      <c r="H20" s="101" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="102">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17405,13 +17406,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="102" t="n">
+      <c r="H21" s="103" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="103">
+      <c r="J21" s="104">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17440,13 +17441,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="104" t="n">
+      <c r="H22" s="105" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="102">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17475,13 +17476,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="105" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="102">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17510,13 +17511,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="n">
+      <c r="H24" s="101" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="102">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17545,13 +17546,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="100" t="n">
+      <c r="H25" s="101" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="102">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17580,13 +17581,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="100" t="n">
+      <c r="H26" s="101" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="102">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17615,13 +17616,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="100" t="n">
+      <c r="H27" s="101" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="102">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17650,13 +17651,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="104" t="n">
+      <c r="H28" s="105" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="102">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17685,13 +17686,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="105" t="n">
+      <c r="H29" s="106" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="104">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17720,13 +17721,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="104" t="n">
+      <c r="H30" s="105" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="102">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17755,13 +17756,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="105" t="n">
+      <c r="H31" s="106" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="103">
+      <c r="J31" s="104">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17790,13 +17791,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="104" t="n">
+      <c r="H32" s="105" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="102">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17825,13 +17826,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="105" t="n">
+      <c r="H33" s="106" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="104">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17860,13 +17861,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="105" t="n">
+      <c r="H34" s="106" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="104">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17895,13 +17896,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="105" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="102">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17930,13 +17931,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="105" t="n">
+      <c r="H36" s="106" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="103">
+      <c r="J36" s="104">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17965,13 +17966,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="105" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="102">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18000,13 +18001,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="104" t="n">
+      <c r="H38" s="105" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="102">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18035,13 +18036,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="105" t="n">
+      <c r="H39" s="106" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="103">
+      <c r="J39" s="104">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,6 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3992,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.01</v>
@@ -4089,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.32</v>
@@ -8839,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>3.27</v>
+        <v>4.61</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>3.27</v>
@@ -8936,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.47</v>
+        <v>15.3</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.47</v>
@@ -9027,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>76.59</v>
+        <v>95.63</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>76.59</v>
@@ -9124,13 +9125,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>76.59</v>
+        <v>95.63</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>76.59</v>
@@ -9384,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.03</v>
@@ -9481,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>6.34</v>
+        <v>6.09</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>6.34</v>
@@ -9578,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>54.82</v>
+        <v>62.23</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>54.82</v>
@@ -9675,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>45.59</v>
+        <v>50.28</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>45.59</v>
@@ -9771,9 +9772,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B32" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C32" s="94" t="inlineStr">
@@ -9929,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>4.8</v>
@@ -10026,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>16.8</v>
+        <v>18.26</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>16.8</v>
@@ -10117,13 +10118,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="78" t="inlineStr">
+      <c r="A35" s="97" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>72.87</v>
+        <v>96.08</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>72.87</v>
@@ -10214,13 +10215,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="inlineStr">
+      <c r="A36" s="97" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>72.87</v>
+        <v>96.08</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>72.87</v>
@@ -11406,9 +11407,9 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B47" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B47" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C47" s="93" t="inlineStr">
@@ -11564,7 +11565,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>-0.16</v>
+        <v>0.96</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>-2.43</v>
@@ -11661,7 +11662,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>5.19</v>
+        <v>6.37</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>3.23</v>
@@ -11758,7 +11759,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>45.94</v>
+        <v>50.68</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>34.71</v>
@@ -11855,7 +11856,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>48.26</v>
+        <v>51.37</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>41.57</v>
@@ -12109,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-0.75</v>
+        <v>-0.27</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-0.98</v>
@@ -12206,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>5.62</v>
+        <v>6.14</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>5.12</v>
@@ -12303,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>42.48</v>
+        <v>57.18</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>21.68</v>
@@ -12400,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>37.49</v>
+        <v>47.72</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>26.35</v>
@@ -12496,9 +12497,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C57" s="93" t="inlineStr">
@@ -12654,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>3.98</v>
+        <v>4.24</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>3.15</v>
@@ -12751,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.32</v>
+        <v>10.59</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>9.59</v>
@@ -12848,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>47.82</v>
+        <v>52.84</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>28.17</v>
@@ -12945,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>46.34</v>
+        <v>50.21</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>32.93</v>
@@ -13045,7 +13046,7 @@
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：</t>
+          <t>今日卖报：us500:RSI2:95.63&gt;=91;us500:RSI2:95.63&gt;=85;ixic:RSI2:96.08&gt;=95;ixic:RSI2:96.08&gt;=85</t>
         </is>
       </c>
     </row>
@@ -16701,13 +16702,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="97" t="n">
+      <c r="H2" s="98" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="98">
+      <c r="J2" s="99">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16738,13 +16739,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="97" t="n">
+      <c r="H3" s="98" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="99">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16775,13 +16776,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="97" t="n">
+      <c r="H4" s="98" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="98">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16812,13 +16813,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="97" t="n">
+      <c r="H5" s="98" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="98">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16849,13 +16850,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="99" t="n">
+      <c r="H6" s="100" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16886,13 +16887,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="97" t="n">
+      <c r="H7" s="98" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16923,13 +16924,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="99" t="n">
+      <c r="H8" s="100" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16960,13 +16961,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="99" t="n">
+      <c r="H9" s="100" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16997,13 +16998,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="99" t="n">
+      <c r="H10" s="100" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="100">
+      <c r="J10" s="101">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17034,13 +17035,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="102" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="103">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17071,13 +17072,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="99" t="n">
+      <c r="H12" s="100" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="100">
+      <c r="J12" s="101">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17108,13 +17109,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="101" t="n">
+      <c r="H13" s="102" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="102">
+      <c r="J13" s="103">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17145,13 +17146,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="99" t="n">
+      <c r="H14" s="100" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="100">
+      <c r="J14" s="101">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17182,13 +17183,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="101" t="n">
+      <c r="H15" s="102" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="102">
+      <c r="J15" s="103">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17219,13 +17220,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="99" t="n">
+      <c r="H16" s="100" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="100">
+      <c r="J16" s="101">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17256,13 +17257,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="101" t="n">
+      <c r="H17" s="102" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="102">
+      <c r="J17" s="103">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17293,13 +17294,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="99" t="n">
+      <c r="H18" s="100" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="100">
+      <c r="J18" s="101">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17330,13 +17331,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="101" t="n">
+      <c r="H19" s="102" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="102">
+      <c r="J19" s="103">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17367,13 +17368,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="99" t="n">
+      <c r="H20" s="100" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="100">
+      <c r="J20" s="101">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17404,13 +17405,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="101" t="n">
+      <c r="H21" s="102" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="102">
+      <c r="J21" s="103">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17439,13 +17440,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="103" t="n">
+      <c r="H22" s="104" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="100">
+      <c r="J22" s="101">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17474,13 +17475,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="103" t="n">
+      <c r="H23" s="104" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="100">
+      <c r="J23" s="101">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17509,13 +17510,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="H24" s="100" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="100">
+      <c r="J24" s="101">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17544,13 +17545,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="H25" s="100" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="100">
+      <c r="J25" s="101">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17579,13 +17580,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="99" t="n">
+      <c r="H26" s="100" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="100">
+      <c r="J26" s="101">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17614,13 +17615,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="99" t="n">
+      <c r="H27" s="100" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="100">
+      <c r="J27" s="101">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17649,13 +17650,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="103" t="n">
+      <c r="H28" s="104" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="100">
+      <c r="J28" s="101">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17684,13 +17685,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="104" t="n">
+      <c r="H29" s="105" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="102">
+      <c r="J29" s="103">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17719,13 +17720,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="103" t="n">
+      <c r="H30" s="104" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="100">
+      <c r="J30" s="101">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17754,13 +17755,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="104" t="n">
+      <c r="H31" s="105" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="102">
+      <c r="J31" s="103">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17789,13 +17790,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="103" t="n">
+      <c r="H32" s="104" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="100">
+      <c r="J32" s="101">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17824,13 +17825,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="104" t="n">
+      <c r="H33" s="105" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="102">
+      <c r="J33" s="103">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17859,13 +17860,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="104" t="n">
+      <c r="H34" s="105" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="102">
+      <c r="J34" s="103">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17894,13 +17895,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="103" t="n">
+      <c r="H35" s="104" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="100">
+      <c r="J35" s="101">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17929,13 +17930,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="104" t="n">
+      <c r="H36" s="105" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="102">
+      <c r="J36" s="103">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17964,13 +17965,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="103" t="n">
+      <c r="H37" s="104" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="100">
+      <c r="J37" s="101">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -17999,13 +18000,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="103" t="n">
+      <c r="H38" s="104" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="100">
+      <c r="J38" s="101">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18034,13 +18035,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="104" t="n">
+      <c r="H39" s="105" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="102">
+      <c r="J39" s="103">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.1</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.4</v>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.61</v>
+        <v>3.43</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.61</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>15.3</v>
+        <v>13.72</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>15.3</v>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>95.63</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>95.63</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>95.63</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>95.63</v>
@@ -9227,9 +9227,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B27" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C27" s="94" t="inlineStr">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>0.1</v>
+        <v>-0.31</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>0.1</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>6.09</v>
+        <v>4.84</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>6.09</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>62.23</v>
+        <v>68.58</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>62.23</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>50.28</v>
+        <v>54.32</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>50.28</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>7.3</v>
+        <v>5.58</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>7.3</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>18.26</v>
+        <v>16.55</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>18.26</v>
@@ -10118,13 +10118,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="inlineStr">
+      <c r="A35" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>96.08</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>96.08</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>96.08</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>96.08</v>
@@ -13038,7 +13038,7 @@
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:95.63&gt;=91;us500:RSI2:95.63&gt;=85;ixic:RSI2:96.08&gt;=95;ixic:RSI2:96.08&gt;=85</t>
+          <t>今日卖报：us500:RSI2:93.04&gt;=91;us500:RSI2:93.04&gt;=85;ixic:RSI2:89.26&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6347,152 +6348,152 @@
       </c>
       <c r="B1" s="79" t="inlineStr">
         <is>
+          <t>240610</t>
+        </is>
+      </c>
+      <c r="C1" s="79" t="inlineStr">
+        <is>
           <t>240607</t>
         </is>
       </c>
-      <c r="C1" s="79" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>240606</t>
         </is>
       </c>
-      <c r="D1" s="79" t="inlineStr">
+      <c r="E1" s="79" t="inlineStr">
         <is>
           <t>240605</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="F1" s="79" t="inlineStr">
         <is>
           <t>240604</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>240603</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>240531</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>240530</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="J1" s="79" t="inlineStr">
         <is>
           <t>240529</t>
         </is>
       </c>
-      <c r="J1" s="79" t="inlineStr">
+      <c r="K1" s="79" t="inlineStr">
         <is>
           <t>240528</t>
         </is>
       </c>
-      <c r="K1" s="79" t="inlineStr">
+      <c r="L1" s="79" t="inlineStr">
         <is>
           <t>240527</t>
         </is>
       </c>
-      <c r="L1" s="79" t="inlineStr">
+      <c r="M1" s="79" t="inlineStr">
         <is>
           <t>240524</t>
         </is>
       </c>
-      <c r="M1" s="79" t="inlineStr">
+      <c r="N1" s="79" t="inlineStr">
         <is>
           <t>240523</t>
         </is>
       </c>
-      <c r="N1" s="79" t="inlineStr">
+      <c r="O1" s="79" t="inlineStr">
         <is>
           <t>240522</t>
         </is>
       </c>
-      <c r="O1" s="79" t="inlineStr">
+      <c r="P1" s="79" t="inlineStr">
         <is>
           <t>240521</t>
         </is>
       </c>
-      <c r="P1" s="79" t="inlineStr">
+      <c r="Q1" s="79" t="inlineStr">
         <is>
           <t>240520</t>
         </is>
       </c>
-      <c r="Q1" s="79" t="inlineStr">
+      <c r="R1" s="79" t="inlineStr">
         <is>
           <t>240518</t>
         </is>
       </c>
-      <c r="R1" s="79" t="inlineStr">
+      <c r="S1" s="79" t="inlineStr">
         <is>
           <t>240517</t>
         </is>
       </c>
-      <c r="S1" s="79" t="inlineStr">
+      <c r="T1" s="79" t="inlineStr">
         <is>
           <t>240516</t>
         </is>
       </c>
-      <c r="T1" s="79" t="inlineStr">
+      <c r="U1" s="79" t="inlineStr">
         <is>
           <t>240515</t>
         </is>
       </c>
-      <c r="U1" s="79" t="inlineStr">
+      <c r="V1" s="79" t="inlineStr">
         <is>
           <t>240514</t>
         </is>
       </c>
-      <c r="V1" s="79" t="inlineStr">
+      <c r="W1" s="79" t="inlineStr">
         <is>
           <t>240513</t>
         </is>
       </c>
-      <c r="W1" s="79" t="inlineStr">
+      <c r="X1" s="79" t="inlineStr">
         <is>
           <t>240510</t>
         </is>
       </c>
-      <c r="X1" s="79" t="inlineStr">
+      <c r="Y1" s="79" t="inlineStr">
         <is>
           <t>240509</t>
         </is>
       </c>
-      <c r="Y1" s="79" t="inlineStr">
+      <c r="Z1" s="79" t="inlineStr">
         <is>
           <t>240508</t>
         </is>
       </c>
-      <c r="Z1" s="79" t="inlineStr">
+      <c r="AA1" s="79" t="inlineStr">
         <is>
           <t>240507</t>
         </is>
       </c>
-      <c r="AA1" s="79" t="inlineStr">
+      <c r="AB1" s="79" t="inlineStr">
         <is>
           <t>240506</t>
         </is>
       </c>
-      <c r="AB1" s="79" t="inlineStr">
+      <c r="AC1" s="79" t="inlineStr">
         <is>
           <t>240503</t>
         </is>
       </c>
-      <c r="AC1" s="79" t="inlineStr">
+      <c r="AD1" s="79" t="inlineStr">
         <is>
           <t>240502</t>
         </is>
       </c>
-      <c r="AD1" s="79" t="inlineStr">
+      <c r="AE1" s="79" t="inlineStr">
         <is>
           <t>240501</t>
-        </is>
-      </c>
-      <c r="AE1" s="79" t="inlineStr">
-        <is>
-          <t>240430</t>
         </is>
       </c>
     </row>
@@ -6507,150 +6508,144 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C2" s="94" t="inlineStr">
+      <c r="C2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D2" s="94" t="inlineStr">
+      <c r="E2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E2" s="93" t="inlineStr">
+      <c r="F2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="94" t="inlineStr">
+      <c r="G2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G2" s="94" t="inlineStr">
+      <c r="H2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H2" s="94" t="inlineStr">
+      <c r="I2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I2" s="94" t="inlineStr">
+      <c r="J2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J2" s="94" t="inlineStr">
+      <c r="K2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K2" s="94" t="inlineStr">
+      <c r="L2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L2" s="94" t="inlineStr">
+      <c r="M2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="94" t="inlineStr">
+      <c r="N2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N2" s="93" t="inlineStr">
+      <c r="O2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="P2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="95" t="inlineStr">
+      <c r="Q2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q2" s="95" t="inlineStr">
+      <c r="R2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R2" s="95" t="inlineStr">
+      <c r="S2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S2" s="93" t="inlineStr">
+      <c r="T2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="93" t="inlineStr">
+      <c r="U2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X2" s="95" t="inlineStr">
+      <c r="Y2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z2" s="95" t="inlineStr">
+      <c r="AA2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA2" s="95" t="inlineStr">
+      <c r="AB2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AC2" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AD2" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AE2" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -6663,91 +6658,91 @@
         <v>0.17</v>
       </c>
       <c r="C3" s="96" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D3" s="96" t="n">
         <v>0.71</v>
       </c>
-      <c r="D3" s="96" t="n">
+      <c r="E3" s="96" t="n">
         <v>0.84</v>
       </c>
-      <c r="E3" s="96" t="n">
+      <c r="F3" s="96" t="n">
         <v>1.42</v>
       </c>
-      <c r="F3" s="96" t="n">
+      <c r="G3" s="96" t="n">
         <v>1.29</v>
       </c>
-      <c r="G3" s="96" t="n">
+      <c r="H3" s="96" t="n">
         <v>1.98</v>
       </c>
-      <c r="H3" s="96" t="n">
+      <c r="I3" s="96" t="n">
         <v>2.54</v>
       </c>
-      <c r="I3" s="96" t="n">
+      <c r="J3" s="96" t="n">
         <v>5.18</v>
       </c>
-      <c r="J3" s="96" t="n">
+      <c r="K3" s="96" t="n">
         <v>3.12</v>
       </c>
-      <c r="K3" s="96" t="n">
+      <c r="L3" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="L3" s="96" t="n">
+      <c r="M3" s="96" t="n">
         <v>2.8</v>
       </c>
-      <c r="M3" s="96" t="n">
+      <c r="N3" s="96" t="n">
         <v>4.28</v>
       </c>
-      <c r="N3" s="96" t="n">
+      <c r="O3" s="96" t="n">
         <v>7.03</v>
       </c>
-      <c r="O3" s="96" t="n">
+      <c r="P3" s="96" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="P3" s="96" t="n">
+      <c r="Q3" s="96" t="n">
         <v>8.949999999999999</v>
-      </c>
-      <c r="Q3" s="96" t="n">
-        <v>10.05</v>
       </c>
       <c r="R3" s="96" t="n">
         <v>10.05</v>
       </c>
       <c r="S3" s="96" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="T3" s="96" t="n">
         <v>10.34</v>
       </c>
-      <c r="T3" s="96" t="n">
+      <c r="U3" s="96" t="n">
         <v>11.84</v>
       </c>
-      <c r="U3" s="96" t="n">
+      <c r="V3" s="96" t="n">
         <v>16.42</v>
       </c>
-      <c r="V3" s="96" t="n">
+      <c r="W3" s="96" t="n">
         <v>15.31</v>
       </c>
-      <c r="W3" s="96" t="n">
+      <c r="X3" s="96" t="n">
         <v>13.85</v>
       </c>
-      <c r="X3" s="96" t="n">
+      <c r="Y3" s="96" t="n">
         <v>13.12</v>
       </c>
-      <c r="Y3" s="96" t="n">
+      <c r="Z3" s="96" t="n">
         <v>10.53</v>
       </c>
-      <c r="Z3" s="96" t="n">
+      <c r="AA3" s="96" t="n">
         <v>9.17</v>
       </c>
-      <c r="AA3" s="96" t="n">
+      <c r="AB3" s="96" t="n">
         <v>7.92</v>
       </c>
-      <c r="AB3" s="96" t="n">
-        <v>6.84</v>
-      </c>
       <c r="AC3" s="96" t="n">
-        <v>6.84</v>
+        <v/>
       </c>
       <c r="AD3" s="96" t="n">
-        <v>6.84</v>
+        <v/>
       </c>
       <c r="AE3" s="96" t="n">
-        <v>6.84</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -6760,91 +6755,91 @@
         <v>2.77</v>
       </c>
       <c r="C4" s="96" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D4" s="96" t="n">
         <v>2.57</v>
       </c>
-      <c r="D4" s="96" t="n">
+      <c r="E4" s="96" t="n">
         <v>1.41</v>
       </c>
-      <c r="E4" s="96" t="n">
+      <c r="F4" s="96" t="n">
         <v>1.96</v>
       </c>
-      <c r="F4" s="96" t="n">
+      <c r="G4" s="96" t="n">
         <v>1.61</v>
       </c>
-      <c r="G4" s="96" t="n">
+      <c r="H4" s="96" t="n">
         <v>2.16</v>
       </c>
-      <c r="H4" s="96" t="n">
+      <c r="I4" s="96" t="n">
         <v>1.75</v>
       </c>
-      <c r="I4" s="96" t="n">
+      <c r="J4" s="96" t="n">
         <v>2.62</v>
       </c>
-      <c r="J4" s="96" t="n">
+      <c r="K4" s="96" t="n">
         <v>2.26</v>
       </c>
-      <c r="K4" s="96" t="n">
+      <c r="L4" s="96" t="n">
         <v>2.03</v>
       </c>
-      <c r="L4" s="96" t="n">
+      <c r="M4" s="96" t="n">
         <v>1.49</v>
       </c>
-      <c r="M4" s="96" t="n">
+      <c r="N4" s="96" t="n">
         <v>1.58</v>
       </c>
-      <c r="N4" s="96" t="n">
+      <c r="O4" s="96" t="n">
         <v>2.94</v>
       </c>
-      <c r="O4" s="96" t="n">
+      <c r="P4" s="96" t="n">
         <v>3.39</v>
       </c>
-      <c r="P4" s="96" t="n">
+      <c r="Q4" s="96" t="n">
         <v>3.94</v>
-      </c>
-      <c r="Q4" s="96" t="n">
-        <v>2.64</v>
       </c>
       <c r="R4" s="96" t="n">
         <v>2.64</v>
       </c>
       <c r="S4" s="96" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T4" s="96" t="n">
         <v>2.17</v>
       </c>
-      <c r="T4" s="96" t="n">
+      <c r="U4" s="96" t="n">
         <v>2.41</v>
       </c>
-      <c r="U4" s="96" t="n">
+      <c r="V4" s="96" t="n">
         <v>3.51</v>
       </c>
-      <c r="V4" s="96" t="n">
+      <c r="W4" s="96" t="n">
         <v>3.1</v>
       </c>
-      <c r="W4" s="96" t="n">
+      <c r="X4" s="96" t="n">
         <v>3.35</v>
       </c>
-      <c r="X4" s="96" t="n">
+      <c r="Y4" s="96" t="n">
         <v>3.17</v>
       </c>
-      <c r="Y4" s="96" t="n">
+      <c r="Z4" s="96" t="n">
         <v>2.29</v>
       </c>
-      <c r="Z4" s="96" t="n">
+      <c r="AA4" s="96" t="n">
         <v>3.86</v>
       </c>
-      <c r="AA4" s="96" t="n">
+      <c r="AB4" s="96" t="n">
         <v>4.36</v>
       </c>
-      <c r="AB4" s="96" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AC4" s="96" t="n">
-        <v>2.7</v>
+        <v/>
       </c>
       <c r="AD4" s="96" t="n">
-        <v>2.7</v>
+        <v/>
       </c>
       <c r="AE4" s="96" t="n">
-        <v>2.7</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -6857,91 +6852,91 @@
         <v>36.04</v>
       </c>
       <c r="C5" s="96" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="D5" s="96" t="n">
         <v>35.1</v>
       </c>
-      <c r="D5" s="96" t="n">
+      <c r="E5" s="96" t="n">
         <v>38.55</v>
       </c>
-      <c r="E5" s="96" t="n">
+      <c r="F5" s="96" t="n">
         <v>44.78</v>
       </c>
-      <c r="F5" s="96" t="n">
+      <c r="G5" s="96" t="n">
         <v>40.48</v>
       </c>
-      <c r="G5" s="96" t="n">
+      <c r="H5" s="96" t="n">
         <v>42.44</v>
       </c>
-      <c r="H5" s="96" t="n">
+      <c r="I5" s="96" t="n">
         <v>43.57</v>
       </c>
-      <c r="I5" s="96" t="n">
+      <c r="J5" s="96" t="n">
         <v>48.19</v>
       </c>
-      <c r="J5" s="96" t="n">
+      <c r="K5" s="96" t="n">
         <v>47.82</v>
       </c>
-      <c r="K5" s="96" t="n">
+      <c r="L5" s="96" t="n">
         <v>51.2</v>
       </c>
-      <c r="L5" s="96" t="n">
+      <c r="M5" s="96" t="n">
         <v>42.16</v>
       </c>
-      <c r="M5" s="96" t="n">
+      <c r="N5" s="96" t="n">
         <v>48.56</v>
       </c>
-      <c r="N5" s="96" t="n">
+      <c r="O5" s="96" t="n">
         <v>61.58</v>
       </c>
-      <c r="O5" s="96" t="n">
+      <c r="P5" s="96" t="n">
         <v>61.45</v>
       </c>
-      <c r="P5" s="96" t="n">
+      <c r="Q5" s="96" t="n">
         <v>66.04000000000001</v>
-      </c>
-      <c r="Q5" s="96" t="n">
-        <v>62.75</v>
       </c>
       <c r="R5" s="96" t="n">
         <v>62.75</v>
       </c>
       <c r="S5" s="96" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="T5" s="96" t="n">
         <v>55.52</v>
       </c>
-      <c r="T5" s="96" t="n">
+      <c r="U5" s="96" t="n">
         <v>54.9</v>
       </c>
-      <c r="U5" s="96" t="n">
+      <c r="V5" s="96" t="n">
         <v>63.32</v>
       </c>
-      <c r="V5" s="96" t="n">
+      <c r="W5" s="96" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="W5" s="96" t="n">
+      <c r="X5" s="96" t="n">
         <v>66.23999999999999</v>
       </c>
-      <c r="X5" s="96" t="n">
+      <c r="Y5" s="96" t="n">
         <v>66.2</v>
       </c>
-      <c r="Y5" s="96" t="n">
+      <c r="Z5" s="96" t="n">
         <v>62.04</v>
       </c>
-      <c r="Z5" s="96" t="n">
+      <c r="AA5" s="96" t="n">
         <v>67.69</v>
       </c>
-      <c r="AA5" s="96" t="n">
+      <c r="AB5" s="96" t="n">
         <v>66.69</v>
       </c>
-      <c r="AB5" s="96" t="n">
-        <v>61.06</v>
-      </c>
       <c r="AC5" s="96" t="n">
-        <v>61.06</v>
+        <v/>
       </c>
       <c r="AD5" s="96" t="n">
-        <v>61.06</v>
+        <v/>
       </c>
       <c r="AE5" s="96" t="n">
-        <v>61.06</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6954,91 +6949,91 @@
         <v>20.81</v>
       </c>
       <c r="C6" s="96" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="D6" s="96" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="D6" s="96" t="n">
+      <c r="E6" s="96" t="n">
         <v>18.16</v>
       </c>
-      <c r="E6" s="96" t="n">
+      <c r="F6" s="96" t="n">
         <v>60.74</v>
       </c>
-      <c r="F6" s="96" t="n">
+      <c r="G6" s="96" t="n">
         <v>7.07</v>
       </c>
-      <c r="G6" s="96" t="n">
+      <c r="H6" s="96" t="n">
         <v>12.8</v>
       </c>
-      <c r="H6" s="96" t="n">
+      <c r="I6" s="96" t="n">
         <v>16.77</v>
       </c>
-      <c r="I6" s="96" t="n">
+      <c r="J6" s="96" t="n">
         <v>43.73</v>
       </c>
-      <c r="J6" s="96" t="n">
+      <c r="K6" s="96" t="n">
         <v>40.12</v>
       </c>
-      <c r="K6" s="96" t="n">
+      <c r="L6" s="96" t="n">
         <v>58.99</v>
       </c>
-      <c r="L6" s="96" t="n">
+      <c r="M6" s="96" t="n">
         <v>4.28</v>
       </c>
-      <c r="M6" s="96" t="n">
+      <c r="N6" s="96" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="N6" s="96" t="n">
+      <c r="O6" s="96" t="n">
         <v>54.6</v>
       </c>
-      <c r="O6" s="96" t="n">
+      <c r="P6" s="96" t="n">
         <v>52.98</v>
       </c>
-      <c r="P6" s="96" t="n">
+      <c r="Q6" s="96" t="n">
         <v>90.23999999999999</v>
-      </c>
-      <c r="Q6" s="96" t="n">
-        <v>82.04000000000001</v>
       </c>
       <c r="R6" s="96" t="n">
         <v>82.04000000000001</v>
       </c>
       <c r="S6" s="96" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="T6" s="96" t="n">
         <v>19.58</v>
       </c>
-      <c r="T6" s="96" t="n">
+      <c r="U6" s="96" t="n">
         <v>6.77</v>
       </c>
-      <c r="U6" s="96" t="n">
+      <c r="V6" s="96" t="n">
         <v>38.51</v>
       </c>
-      <c r="V6" s="96" t="n">
+      <c r="W6" s="96" t="n">
         <v>48.36</v>
       </c>
-      <c r="W6" s="96" t="n">
+      <c r="X6" s="96" t="n">
         <v>76.91</v>
       </c>
-      <c r="X6" s="96" t="n">
+      <c r="Y6" s="96" t="n">
         <v>76.67</v>
       </c>
-      <c r="Y6" s="96" t="n">
+      <c r="Z6" s="96" t="n">
         <v>43.06</v>
       </c>
-      <c r="Z6" s="96" t="n">
+      <c r="AA6" s="96" t="n">
         <v>92.95</v>
       </c>
-      <c r="AA6" s="96" t="n">
+      <c r="AB6" s="96" t="n">
         <v>91.06</v>
       </c>
-      <c r="AB6" s="96" t="n">
-        <v>71.68000000000001</v>
-      </c>
       <c r="AC6" s="96" t="n">
-        <v>71.68000000000001</v>
+        <v/>
       </c>
       <c r="AD6" s="96" t="n">
-        <v>71.68000000000001</v>
+        <v/>
       </c>
       <c r="AE6" s="96" t="n">
-        <v>71.68000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -7057,145 +7052,139 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D7" s="95" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E7" s="95" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F7" s="95" t="inlineStr">
+      <c r="G7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G7" s="93" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H7" s="93" t="inlineStr">
+      <c r="I7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I7" s="93" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J7" s="94" t="inlineStr">
+      <c r="K7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K7" s="93" t="inlineStr">
+      <c r="L7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L7" s="94" t="inlineStr">
+      <c r="M7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M7" s="94" t="inlineStr">
+      <c r="N7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N7" s="93" t="inlineStr">
+      <c r="O7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="94" t="inlineStr">
+      <c r="P7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P7" s="94" t="inlineStr">
+      <c r="Q7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q7" s="94" t="inlineStr">
+      <c r="R7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R7" s="94" t="inlineStr">
+      <c r="S7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S7" s="94" t="inlineStr">
+      <c r="T7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T7" s="94" t="inlineStr">
+      <c r="U7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U7" s="94" t="inlineStr">
+      <c r="V7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V7" s="93" t="inlineStr">
+      <c r="W7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W7" s="93" t="inlineStr">
+      <c r="X7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X7" s="95" t="inlineStr">
+      <c r="Y7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y7" s="93" t="inlineStr">
+      <c r="Z7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z7" s="93" t="inlineStr">
+      <c r="AA7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA7" s="95" t="inlineStr">
+      <c r="AB7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB7" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC7" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD7" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE7" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AC7" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AD7" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AE7" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -7208,91 +7197,91 @@
         <v>-8.130000000000001</v>
       </c>
       <c r="C8" s="96" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="D8" s="96" t="n">
         <v>-6.42</v>
       </c>
-      <c r="D8" s="96" t="n">
+      <c r="E8" s="96" t="n">
         <v>-7.37</v>
       </c>
-      <c r="E8" s="96" t="n">
+      <c r="F8" s="96" t="n">
         <v>-7.84</v>
       </c>
-      <c r="F8" s="96" t="n">
+      <c r="G8" s="96" t="n">
         <v>-8.32</v>
       </c>
-      <c r="G8" s="96" t="n">
+      <c r="H8" s="96" t="n">
         <v>-8.859999999999999</v>
       </c>
-      <c r="H8" s="96" t="n">
+      <c r="I8" s="96" t="n">
         <v>-8.050000000000001</v>
       </c>
-      <c r="I8" s="96" t="n">
+      <c r="J8" s="96" t="n">
         <v>-4.83</v>
       </c>
-      <c r="J8" s="96" t="n">
+      <c r="K8" s="96" t="n">
         <v>-7.79</v>
       </c>
-      <c r="K8" s="96" t="n">
+      <c r="L8" s="96" t="n">
         <v>-3.88</v>
       </c>
-      <c r="L8" s="96" t="n">
+      <c r="M8" s="96" t="n">
         <v>-4.88</v>
       </c>
-      <c r="M8" s="96" t="n">
+      <c r="N8" s="96" t="n">
         <v>-2.62</v>
       </c>
-      <c r="N8" s="96" t="n">
+      <c r="O8" s="96" t="n">
         <v>-0.03</v>
       </c>
-      <c r="O8" s="96" t="n">
+      <c r="P8" s="96" t="n">
         <v>-0.86</v>
       </c>
-      <c r="P8" s="96" t="n">
+      <c r="Q8" s="96" t="n">
         <v>-1.28</v>
-      </c>
-      <c r="Q8" s="96" t="n">
-        <v>0.39</v>
       </c>
       <c r="R8" s="96" t="n">
         <v>0.39</v>
       </c>
       <c r="S8" s="96" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="T8" s="96" t="n">
         <v>0.41</v>
       </c>
-      <c r="T8" s="96" t="n">
+      <c r="U8" s="96" t="n">
         <v>3.98</v>
       </c>
-      <c r="U8" s="96" t="n">
+      <c r="V8" s="96" t="n">
         <v>12.34</v>
       </c>
-      <c r="V8" s="96" t="n">
+      <c r="W8" s="96" t="n">
         <v>13.41</v>
       </c>
-      <c r="W8" s="96" t="n">
+      <c r="X8" s="96" t="n">
         <v>11.18</v>
       </c>
-      <c r="X8" s="96" t="n">
+      <c r="Y8" s="96" t="n">
         <v>13.73</v>
       </c>
-      <c r="Y8" s="96" t="n">
+      <c r="Z8" s="96" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="Z8" s="96" t="n">
+      <c r="AA8" s="96" t="n">
         <v>6.13</v>
       </c>
-      <c r="AA8" s="96" t="n">
+      <c r="AB8" s="96" t="n">
         <v>4.23</v>
       </c>
-      <c r="AB8" s="96" t="n">
-        <v>0.22</v>
-      </c>
       <c r="AC8" s="96" t="n">
-        <v>0.22</v>
+        <v/>
       </c>
       <c r="AD8" s="96" t="n">
-        <v>0.22</v>
+        <v/>
       </c>
       <c r="AE8" s="96" t="n">
-        <v>0.22</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -7305,91 +7294,91 @@
         <v>-13.06</v>
       </c>
       <c r="C9" s="96" t="n">
+        <v>-13.06</v>
+      </c>
+      <c r="D9" s="96" t="n">
         <v>-12.13</v>
       </c>
-      <c r="D9" s="96" t="n">
+      <c r="E9" s="96" t="n">
         <v>-12.75</v>
       </c>
-      <c r="E9" s="96" t="n">
+      <c r="F9" s="96" t="n">
         <v>-13.13</v>
       </c>
-      <c r="F9" s="96" t="n">
+      <c r="G9" s="96" t="n">
         <v>-13.31</v>
       </c>
-      <c r="G9" s="96" t="n">
+      <c r="H9" s="96" t="n">
         <v>-13.78</v>
       </c>
-      <c r="H9" s="96" t="n">
+      <c r="I9" s="96" t="n">
         <v>-14.82</v>
       </c>
-      <c r="I9" s="96" t="n">
+      <c r="J9" s="96" t="n">
         <v>-15.4</v>
       </c>
-      <c r="J9" s="96" t="n">
+      <c r="K9" s="96" t="n">
         <v>-15.02</v>
       </c>
-      <c r="K9" s="96" t="n">
+      <c r="L9" s="96" t="n">
         <v>-15.85</v>
       </c>
-      <c r="L9" s="96" t="n">
+      <c r="M9" s="96" t="n">
         <v>-16.49</v>
       </c>
-      <c r="M9" s="96" t="n">
+      <c r="N9" s="96" t="n">
         <v>-16.1</v>
       </c>
-      <c r="N9" s="96" t="n">
+      <c r="O9" s="96" t="n">
         <v>-15.42</v>
       </c>
-      <c r="O9" s="96" t="n">
+      <c r="P9" s="96" t="n">
         <v>-16.06</v>
       </c>
-      <c r="P9" s="96" t="n">
+      <c r="Q9" s="96" t="n">
         <v>-15.06</v>
-      </c>
-      <c r="Q9" s="96" t="n">
-        <v>-16.38</v>
       </c>
       <c r="R9" s="96" t="n">
         <v>-16.38</v>
       </c>
       <c r="S9" s="96" t="n">
+        <v>-16.38</v>
+      </c>
+      <c r="T9" s="96" t="n">
         <v>-17.46</v>
       </c>
-      <c r="T9" s="96" t="n">
+      <c r="U9" s="96" t="n">
         <v>-16.41</v>
       </c>
-      <c r="U9" s="96" t="n">
+      <c r="V9" s="96" t="n">
         <v>-14.55</v>
       </c>
-      <c r="V9" s="96" t="n">
+      <c r="W9" s="96" t="n">
         <v>-14.56</v>
       </c>
-      <c r="W9" s="96" t="n">
+      <c r="X9" s="96" t="n">
         <v>-14.72</v>
       </c>
-      <c r="X9" s="96" t="n">
+      <c r="Y9" s="96" t="n">
         <v>-12.63</v>
       </c>
-      <c r="Y9" s="96" t="n">
+      <c r="Z9" s="96" t="n">
         <v>-14.44</v>
       </c>
-      <c r="Z9" s="96" t="n">
+      <c r="AA9" s="96" t="n">
         <v>-12.06</v>
       </c>
-      <c r="AA9" s="96" t="n">
+      <c r="AB9" s="96" t="n">
         <v>-9.57</v>
       </c>
-      <c r="AB9" s="96" t="n">
-        <v>-11.78</v>
-      </c>
       <c r="AC9" s="96" t="n">
-        <v>-11.78</v>
+        <v/>
       </c>
       <c r="AD9" s="96" t="n">
-        <v>-11.78</v>
+        <v/>
       </c>
       <c r="AE9" s="96" t="n">
-        <v>-11.78</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -7402,91 +7391,91 @@
         <v>42.36</v>
       </c>
       <c r="C10" s="96" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="D10" s="96" t="n">
         <v>46.19</v>
       </c>
-      <c r="D10" s="96" t="n">
+      <c r="E10" s="96" t="n">
         <v>53.41</v>
       </c>
-      <c r="E10" s="96" t="n">
+      <c r="F10" s="96" t="n">
         <v>54.81</v>
       </c>
-      <c r="F10" s="96" t="n">
+      <c r="G10" s="96" t="n">
         <v>52.56</v>
       </c>
-      <c r="G10" s="96" t="n">
+      <c r="H10" s="96" t="n">
         <v>47.27</v>
       </c>
-      <c r="H10" s="96" t="n">
+      <c r="I10" s="96" t="n">
         <v>46.88</v>
       </c>
-      <c r="I10" s="96" t="n">
+      <c r="J10" s="96" t="n">
         <v>40.6</v>
       </c>
-      <c r="J10" s="96" t="n">
+      <c r="K10" s="96" t="n">
         <v>40.87</v>
       </c>
-      <c r="K10" s="96" t="n">
+      <c r="L10" s="96" t="n">
         <v>42.74</v>
       </c>
-      <c r="L10" s="96" t="n">
+      <c r="M10" s="96" t="n">
         <v>34.63</v>
       </c>
-      <c r="M10" s="96" t="n">
+      <c r="N10" s="96" t="n">
         <v>41.69</v>
       </c>
-      <c r="N10" s="96" t="n">
+      <c r="O10" s="96" t="n">
         <v>49.14</v>
       </c>
-      <c r="O10" s="96" t="n">
+      <c r="P10" s="96" t="n">
         <v>44.35</v>
       </c>
-      <c r="P10" s="96" t="n">
+      <c r="Q10" s="96" t="n">
         <v>47.52</v>
-      </c>
-      <c r="Q10" s="96" t="n">
-        <v>48.04</v>
       </c>
       <c r="R10" s="96" t="n">
         <v>48.04</v>
       </c>
       <c r="S10" s="96" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="T10" s="96" t="n">
         <v>43.02</v>
       </c>
-      <c r="T10" s="96" t="n">
+      <c r="U10" s="96" t="n">
         <v>44.48</v>
       </c>
-      <c r="U10" s="96" t="n">
+      <c r="V10" s="96" t="n">
         <v>49.98</v>
       </c>
-      <c r="V10" s="96" t="n">
+      <c r="W10" s="96" t="n">
         <v>51.79</v>
       </c>
-      <c r="W10" s="96" t="n">
+      <c r="X10" s="96" t="n">
         <v>53.57</v>
       </c>
-      <c r="X10" s="96" t="n">
+      <c r="Y10" s="96" t="n">
         <v>59.82</v>
       </c>
-      <c r="Y10" s="96" t="n">
+      <c r="Z10" s="96" t="n">
         <v>52.49</v>
       </c>
-      <c r="Z10" s="96" t="n">
+      <c r="AA10" s="96" t="n">
         <v>56.9</v>
       </c>
-      <c r="AA10" s="96" t="n">
+      <c r="AB10" s="96" t="n">
         <v>61.4</v>
       </c>
-      <c r="AB10" s="96" t="n">
-        <v>57.48</v>
-      </c>
       <c r="AC10" s="96" t="n">
-        <v>57.48</v>
+        <v/>
       </c>
       <c r="AD10" s="96" t="n">
-        <v>57.48</v>
+        <v/>
       </c>
       <c r="AE10" s="96" t="n">
-        <v>57.48</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -7499,91 +7488,91 @@
         <v>34.88</v>
       </c>
       <c r="C11" s="96" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="D11" s="96" t="n">
         <v>43.2</v>
       </c>
-      <c r="D11" s="96" t="n">
+      <c r="E11" s="96" t="n">
         <v>63.28</v>
       </c>
-      <c r="E11" s="96" t="n">
+      <c r="F11" s="96" t="n">
         <v>67.86</v>
       </c>
-      <c r="F11" s="96" t="n">
+      <c r="G11" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="G11" s="96" t="n">
+      <c r="H11" s="96" t="n">
         <v>52.4</v>
       </c>
-      <c r="H11" s="96" t="n">
+      <c r="I11" s="96" t="n">
         <v>51.52</v>
       </c>
-      <c r="I11" s="96" t="n">
+      <c r="J11" s="96" t="n">
         <v>36.71</v>
       </c>
-      <c r="J11" s="96" t="n">
+      <c r="K11" s="96" t="n">
         <v>37.28</v>
       </c>
-      <c r="K11" s="96" t="n">
+      <c r="L11" s="96" t="n">
         <v>40.97</v>
       </c>
-      <c r="L11" s="96" t="n">
+      <c r="M11" s="96" t="n">
         <v>22.47</v>
       </c>
-      <c r="M11" s="96" t="n">
+      <c r="N11" s="96" t="n">
         <v>33.68</v>
       </c>
-      <c r="N11" s="96" t="n">
+      <c r="O11" s="96" t="n">
         <v>50.29</v>
       </c>
-      <c r="O11" s="96" t="n">
+      <c r="P11" s="96" t="n">
         <v>36.98</v>
       </c>
-      <c r="P11" s="96" t="n">
+      <c r="Q11" s="96" t="n">
         <v>44.48</v>
-      </c>
-      <c r="Q11" s="96" t="n">
-        <v>45.72</v>
       </c>
       <c r="R11" s="96" t="n">
         <v>45.72</v>
       </c>
       <c r="S11" s="96" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="T11" s="96" t="n">
         <v>32.12</v>
       </c>
-      <c r="T11" s="96" t="n">
+      <c r="U11" s="96" t="n">
         <v>34.75</v>
       </c>
-      <c r="U11" s="96" t="n">
+      <c r="V11" s="96" t="n">
         <v>45.49</v>
       </c>
-      <c r="V11" s="96" t="n">
+      <c r="W11" s="96" t="n">
         <v>49.31</v>
       </c>
-      <c r="W11" s="96" t="n">
+      <c r="X11" s="96" t="n">
         <v>52.96</v>
       </c>
-      <c r="X11" s="96" t="n">
+      <c r="Y11" s="96" t="n">
         <v>66.12</v>
       </c>
-      <c r="Y11" s="96" t="n">
+      <c r="Z11" s="96" t="n">
         <v>52.12</v>
       </c>
-      <c r="Z11" s="96" t="n">
+      <c r="AA11" s="96" t="n">
         <v>61.76</v>
       </c>
-      <c r="AA11" s="96" t="n">
+      <c r="AB11" s="96" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="AB11" s="96" t="n">
-        <v>66.23999999999999</v>
-      </c>
       <c r="AC11" s="96" t="n">
-        <v>66.23999999999999</v>
+        <v/>
       </c>
       <c r="AD11" s="96" t="n">
-        <v>66.23999999999999</v>
+        <v/>
       </c>
       <c r="AE11" s="96" t="n">
-        <v>66.23999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -7597,150 +7586,144 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D12" s="95" t="inlineStr">
+      <c r="E12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E12" s="95" t="inlineStr">
+      <c r="F12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F12" s="93" t="inlineStr">
+      <c r="G12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G12" s="94" t="inlineStr">
+      <c r="H12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H12" s="93" t="inlineStr">
+      <c r="I12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I12" s="94" t="inlineStr">
+      <c r="J12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J12" s="94" t="inlineStr">
+      <c r="K12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K12" s="94" t="inlineStr">
+      <c r="L12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L12" s="94" t="inlineStr">
+      <c r="M12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="94" t="inlineStr">
+      <c r="N12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="95" t="inlineStr">
+      <c r="O12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O12" s="93" t="inlineStr">
+      <c r="P12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P12" s="95" t="inlineStr">
+      <c r="Q12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q12" s="93" t="inlineStr">
+      <c r="R12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R12" s="93" t="inlineStr">
+      <c r="S12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S12" s="94" t="inlineStr">
+      <c r="T12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T12" s="94" t="inlineStr">
+      <c r="U12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U12" s="93" t="inlineStr">
+      <c r="V12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V12" s="93" t="inlineStr">
+      <c r="W12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W12" s="93" t="inlineStr">
+      <c r="X12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X12" s="95" t="inlineStr">
+      <c r="Y12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y12" s="93" t="inlineStr">
+      <c r="Z12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z12" s="95" t="inlineStr">
+      <c r="AA12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA12" s="95" t="inlineStr">
+      <c r="AB12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AC12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AC12" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AD12" s="93" t="n">
+        <v/>
+      </c>
+      <c r="AE12" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -7753,91 +7736,91 @@
         <v>-1.45</v>
       </c>
       <c r="C13" s="96" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="D13" s="96" t="n">
         <v>1.7</v>
       </c>
-      <c r="D13" s="96" t="n">
+      <c r="E13" s="96" t="n">
         <v>0.05</v>
       </c>
-      <c r="E13" s="96" t="n">
+      <c r="F13" s="96" t="n">
         <v>0.54</v>
       </c>
-      <c r="F13" s="96" t="n">
+      <c r="G13" s="96" t="n">
         <v>-0.84</v>
       </c>
-      <c r="G13" s="96" t="n">
+      <c r="H13" s="96" t="n">
         <v>-1.04</v>
       </c>
-      <c r="H13" s="96" t="n">
+      <c r="I13" s="96" t="n">
         <v>0.34</v>
       </c>
-      <c r="I13" s="96" t="n">
+      <c r="J13" s="96" t="n">
         <v>3.55</v>
       </c>
-      <c r="J13" s="96" t="n">
+      <c r="K13" s="96" t="n">
         <v>0.68</v>
       </c>
-      <c r="K13" s="96" t="n">
+      <c r="L13" s="96" t="n">
         <v>4.52</v>
       </c>
-      <c r="L13" s="96" t="n">
+      <c r="M13" s="96" t="n">
         <v>3.43</v>
       </c>
-      <c r="M13" s="96" t="n">
+      <c r="N13" s="96" t="n">
         <v>5.36</v>
       </c>
-      <c r="N13" s="96" t="n">
+      <c r="O13" s="96" t="n">
         <v>7.16</v>
       </c>
-      <c r="O13" s="96" t="n">
+      <c r="P13" s="96" t="n">
         <v>6.6</v>
       </c>
-      <c r="P13" s="96" t="n">
+      <c r="Q13" s="96" t="n">
         <v>7.42</v>
-      </c>
-      <c r="Q13" s="96" t="n">
-        <v>8</v>
       </c>
       <c r="R13" s="96" t="n">
         <v>8</v>
       </c>
       <c r="S13" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" s="96" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="T13" s="96" t="n">
+      <c r="U13" s="96" t="n">
         <v>10.28</v>
       </c>
-      <c r="U13" s="96" t="n">
+      <c r="V13" s="96" t="n">
         <v>18.75</v>
       </c>
-      <c r="V13" s="96" t="n">
+      <c r="W13" s="96" t="n">
         <v>20</v>
       </c>
-      <c r="W13" s="96" t="n">
+      <c r="X13" s="96" t="n">
         <v>18.2</v>
       </c>
-      <c r="X13" s="96" t="n">
+      <c r="Y13" s="96" t="n">
         <v>20.76</v>
       </c>
-      <c r="Y13" s="96" t="n">
+      <c r="Z13" s="96" t="n">
         <v>17.76</v>
       </c>
-      <c r="Z13" s="96" t="n">
+      <c r="AA13" s="96" t="n">
         <v>16.55</v>
       </c>
-      <c r="AA13" s="96" t="n">
+      <c r="AB13" s="96" t="n">
         <v>12.64</v>
       </c>
-      <c r="AB13" s="96" t="n">
-        <v>8</v>
-      </c>
       <c r="AC13" s="96" t="n">
-        <v>8</v>
+        <v/>
       </c>
       <c r="AD13" s="96" t="n">
-        <v>8</v>
+        <v/>
       </c>
       <c r="AE13" s="96" t="n">
-        <v>8</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -7850,91 +7833,91 @@
         <v>-5.36</v>
       </c>
       <c r="C14" s="96" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="D14" s="96" t="n">
         <v>-2.71</v>
       </c>
-      <c r="D14" s="96" t="n">
+      <c r="E14" s="96" t="n">
         <v>-3.95</v>
       </c>
-      <c r="E14" s="96" t="n">
+      <c r="F14" s="96" t="n">
         <v>-4.29</v>
       </c>
-      <c r="F14" s="96" t="n">
+      <c r="G14" s="96" t="n">
         <v>-5.36</v>
       </c>
-      <c r="G14" s="96" t="n">
+      <c r="H14" s="96" t="n">
         <v>-5.88</v>
       </c>
-      <c r="H14" s="96" t="n">
+      <c r="I14" s="96" t="n">
         <v>-6.46</v>
       </c>
-      <c r="I14" s="96" t="n">
+      <c r="J14" s="96" t="n">
         <v>-5.98</v>
       </c>
-      <c r="J14" s="96" t="n">
+      <c r="K14" s="96" t="n">
         <v>-6.8</v>
       </c>
-      <c r="K14" s="96" t="n">
+      <c r="L14" s="96" t="n">
         <v>-6.65</v>
       </c>
-      <c r="L14" s="96" t="n">
+      <c r="M14" s="96" t="n">
         <v>-6.74</v>
       </c>
-      <c r="M14" s="96" t="n">
+      <c r="N14" s="96" t="n">
         <v>-6.66</v>
       </c>
-      <c r="N14" s="96" t="n">
+      <c r="O14" s="96" t="n">
         <v>-5.77</v>
       </c>
-      <c r="O14" s="96" t="n">
+      <c r="P14" s="96" t="n">
         <v>-6.29</v>
       </c>
-      <c r="P14" s="96" t="n">
+      <c r="Q14" s="96" t="n">
         <v>-5.17</v>
-      </c>
-      <c r="Q14" s="96" t="n">
-        <v>-7.46</v>
       </c>
       <c r="R14" s="96" t="n">
         <v>-7.46</v>
       </c>
       <c r="S14" s="96" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="T14" s="96" t="n">
         <v>-8.01</v>
       </c>
-      <c r="T14" s="96" t="n">
+      <c r="U14" s="96" t="n">
         <v>-8.48</v>
       </c>
-      <c r="U14" s="96" t="n">
+      <c r="V14" s="96" t="n">
         <v>-7.46</v>
       </c>
-      <c r="V14" s="96" t="n">
+      <c r="W14" s="96" t="n">
         <v>-7.83</v>
       </c>
-      <c r="W14" s="96" t="n">
+      <c r="X14" s="96" t="n">
         <v>-7.17</v>
       </c>
-      <c r="X14" s="96" t="n">
+      <c r="Y14" s="96" t="n">
         <v>-6.07</v>
       </c>
-      <c r="Y14" s="96" t="n">
+      <c r="Z14" s="96" t="n">
         <v>-8.23</v>
       </c>
-      <c r="Z14" s="96" t="n">
+      <c r="AA14" s="96" t="n">
         <v>-3.84</v>
       </c>
-      <c r="AA14" s="96" t="n">
+      <c r="AB14" s="96" t="n">
         <v>-2.29</v>
       </c>
-      <c r="AB14" s="96" t="n">
-        <v>-5.14</v>
-      </c>
       <c r="AC14" s="96" t="n">
-        <v>-5.14</v>
+        <v/>
       </c>
       <c r="AD14" s="96" t="n">
-        <v>-5.14</v>
+        <v/>
       </c>
       <c r="AE14" s="96" t="n">
-        <v>-5.14</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -7947,91 +7930,91 @@
         <v>36.04</v>
       </c>
       <c r="C15" s="96" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="D15" s="96" t="n">
         <v>45.9</v>
       </c>
-      <c r="D15" s="96" t="n">
+      <c r="E15" s="96" t="n">
         <v>49.99</v>
       </c>
-      <c r="E15" s="96" t="n">
+      <c r="F15" s="96" t="n">
         <v>53.27</v>
       </c>
-      <c r="F15" s="96" t="n">
+      <c r="G15" s="96" t="n">
         <v>45.55</v>
       </c>
-      <c r="G15" s="96" t="n">
+      <c r="H15" s="96" t="n">
         <v>40.27</v>
       </c>
-      <c r="H15" s="96" t="n">
+      <c r="I15" s="96" t="n">
         <v>42.34</v>
       </c>
-      <c r="I15" s="96" t="n">
+      <c r="J15" s="96" t="n">
         <v>41.64</v>
       </c>
-      <c r="J15" s="96" t="n">
+      <c r="K15" s="96" t="n">
         <v>40.13</v>
       </c>
-      <c r="K15" s="96" t="n">
+      <c r="L15" s="96" t="n">
         <v>45.58</v>
       </c>
-      <c r="L15" s="96" t="n">
+      <c r="M15" s="96" t="n">
         <v>42.02</v>
       </c>
-      <c r="M15" s="96" t="n">
+      <c r="N15" s="96" t="n">
         <v>49.97</v>
       </c>
-      <c r="N15" s="96" t="n">
+      <c r="O15" s="96" t="n">
         <v>57.52</v>
       </c>
-      <c r="O15" s="96" t="n">
+      <c r="P15" s="96" t="n">
         <v>53.49</v>
       </c>
-      <c r="P15" s="96" t="n">
+      <c r="Q15" s="96" t="n">
         <v>57.82</v>
-      </c>
-      <c r="Q15" s="96" t="n">
-        <v>55.35</v>
       </c>
       <c r="R15" s="96" t="n">
         <v>55.35</v>
       </c>
       <c r="S15" s="96" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="T15" s="96" t="n">
         <v>50.41</v>
       </c>
-      <c r="T15" s="96" t="n">
+      <c r="U15" s="96" t="n">
         <v>49.11</v>
       </c>
-      <c r="U15" s="96" t="n">
+      <c r="V15" s="96" t="n">
         <v>53.04</v>
       </c>
-      <c r="V15" s="96" t="n">
+      <c r="W15" s="96" t="n">
         <v>54.16</v>
       </c>
-      <c r="W15" s="96" t="n">
+      <c r="X15" s="96" t="n">
         <v>58.26</v>
       </c>
-      <c r="X15" s="96" t="n">
+      <c r="Y15" s="96" t="n">
         <v>63.59</v>
       </c>
-      <c r="Y15" s="96" t="n">
+      <c r="Z15" s="96" t="n">
         <v>58.08</v>
       </c>
-      <c r="Z15" s="96" t="n">
+      <c r="AA15" s="96" t="n">
         <v>65.04000000000001</v>
       </c>
-      <c r="AA15" s="96" t="n">
+      <c r="AB15" s="96" t="n">
         <v>65.73</v>
       </c>
-      <c r="AB15" s="96" t="n">
-        <v>60.53</v>
-      </c>
       <c r="AC15" s="96" t="n">
-        <v>60.53</v>
+        <v/>
       </c>
       <c r="AD15" s="96" t="n">
-        <v>60.53</v>
+        <v/>
       </c>
       <c r="AE15" s="96" t="n">
-        <v>60.53</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -8044,91 +8027,91 @@
         <v>34.6</v>
       </c>
       <c r="C16" s="96" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D16" s="96" t="n">
         <v>45.5</v>
       </c>
-      <c r="D16" s="96" t="n">
+      <c r="E16" s="96" t="n">
         <v>50.17</v>
       </c>
-      <c r="E16" s="96" t="n">
+      <c r="F16" s="96" t="n">
         <v>53.94</v>
       </c>
-      <c r="F16" s="96" t="n">
+      <c r="G16" s="96" t="n">
         <v>45.12</v>
       </c>
-      <c r="G16" s="96" t="n">
+      <c r="H16" s="96" t="n">
         <v>38.95</v>
       </c>
-      <c r="H16" s="96" t="n">
+      <c r="I16" s="96" t="n">
         <v>41.26</v>
       </c>
-      <c r="I16" s="96" t="n">
+      <c r="J16" s="96" t="n">
         <v>40.45</v>
       </c>
-      <c r="J16" s="96" t="n">
+      <c r="K16" s="96" t="n">
         <v>38.7</v>
       </c>
-      <c r="K16" s="96" t="n">
+      <c r="L16" s="96" t="n">
         <v>44.68</v>
       </c>
-      <c r="L16" s="96" t="n">
+      <c r="M16" s="96" t="n">
         <v>40.58</v>
       </c>
-      <c r="M16" s="96" t="n">
+      <c r="N16" s="96" t="n">
         <v>49.35</v>
       </c>
-      <c r="N16" s="96" t="n">
+      <c r="O16" s="96" t="n">
         <v>57.93</v>
       </c>
-      <c r="O16" s="96" t="n">
+      <c r="P16" s="96" t="n">
         <v>53.35</v>
       </c>
-      <c r="P16" s="96" t="n">
+      <c r="Q16" s="96" t="n">
         <v>58.31</v>
-      </c>
-      <c r="Q16" s="96" t="n">
-        <v>55.51</v>
       </c>
       <c r="R16" s="96" t="n">
         <v>55.51</v>
       </c>
       <c r="S16" s="96" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="T16" s="96" t="n">
         <v>49.87</v>
       </c>
-      <c r="T16" s="96" t="n">
+      <c r="U16" s="96" t="n">
         <v>48.37</v>
       </c>
-      <c r="U16" s="96" t="n">
+      <c r="V16" s="96" t="n">
         <v>52.76</v>
       </c>
-      <c r="V16" s="96" t="n">
+      <c r="W16" s="96" t="n">
         <v>54.01</v>
       </c>
-      <c r="W16" s="96" t="n">
+      <c r="X16" s="96" t="n">
         <v>58.59</v>
       </c>
-      <c r="X16" s="96" t="n">
+      <c r="Y16" s="96" t="n">
         <v>64.56</v>
       </c>
-      <c r="Y16" s="96" t="n">
+      <c r="Z16" s="96" t="n">
         <v>58.56</v>
       </c>
-      <c r="Z16" s="96" t="n">
+      <c r="AA16" s="96" t="n">
         <v>66.42</v>
       </c>
-      <c r="AA16" s="96" t="n">
+      <c r="AB16" s="96" t="n">
         <v>67.2</v>
       </c>
-      <c r="AB16" s="96" t="n">
-        <v>61.68</v>
-      </c>
       <c r="AC16" s="96" t="n">
-        <v>61.68</v>
+        <v/>
       </c>
       <c r="AD16" s="96" t="n">
-        <v>61.68</v>
+        <v/>
       </c>
       <c r="AE16" s="96" t="n">
-        <v>61.68</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -8162,130 +8145,128 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="G17" s="94" t="inlineStr">
+      <c r="G17" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H17" s="94" t="inlineStr">
+      <c r="I17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I17" s="94" t="inlineStr">
+      <c r="J17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J17" s="94" t="inlineStr">
+      <c r="K17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K17" s="94" t="inlineStr">
+      <c r="L17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L17" s="94" t="inlineStr">
+      <c r="M17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M17" s="94" t="inlineStr">
+      <c r="N17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N17" s="93" t="inlineStr">
+      <c r="O17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="93" t="inlineStr">
+      <c r="P17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="93" t="inlineStr">
+      <c r="Q17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q17" s="93" t="inlineStr">
+      <c r="R17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R17" s="93" t="inlineStr">
+      <c r="S17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S17" s="95" t="inlineStr">
+      <c r="T17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T17" s="93" t="inlineStr">
+      <c r="U17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U17" s="93" t="inlineStr">
+      <c r="V17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V17" s="95" t="inlineStr">
+      <c r="W17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W17" s="95" t="inlineStr">
+      <c r="X17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X17" s="93" t="inlineStr">
+      <c r="Y17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y17" s="93" t="inlineStr">
+      <c r="Z17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z17" s="93" t="inlineStr">
+      <c r="AA17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA17" s="95" t="inlineStr">
+      <c r="AB17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB17" s="95" t="inlineStr">
+      <c r="AC17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC17" s="95" t="inlineStr">
+      <c r="AD17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD17" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE17" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE17" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -8298,91 +8279,91 @@
         <v>12.31</v>
       </c>
       <c r="C18" s="96" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="D18" s="96" t="n">
         <v>13.85</v>
       </c>
-      <c r="D18" s="96" t="n">
+      <c r="E18" s="96" t="n">
         <v>12.09</v>
       </c>
-      <c r="E18" s="96" t="n">
+      <c r="F18" s="96" t="n">
         <v>14.12</v>
       </c>
-      <c r="F18" s="96" t="n">
+      <c r="G18" s="96" t="n">
         <v>10.89</v>
       </c>
-      <c r="G18" s="96" t="n">
+      <c r="H18" s="96" t="n">
         <v>8.98</v>
       </c>
-      <c r="H18" s="96" t="n">
+      <c r="I18" s="96" t="n">
         <v>10.41</v>
       </c>
-      <c r="I18" s="96" t="n">
+      <c r="J18" s="96" t="n">
         <v>11.73</v>
       </c>
-      <c r="J18" s="96" t="n">
+      <c r="K18" s="96" t="n">
         <v>12.09</v>
       </c>
-      <c r="K18" s="96" t="n">
+      <c r="L18" s="96" t="n">
         <v>13.18</v>
       </c>
-      <c r="L18" s="96" t="n">
+      <c r="M18" s="96" t="n">
         <v>11.26</v>
       </c>
-      <c r="M18" s="96" t="n">
+      <c r="N18" s="96" t="n">
         <v>12.7</v>
       </c>
-      <c r="N18" s="96" t="n">
+      <c r="O18" s="96" t="n">
         <v>16.32</v>
       </c>
-      <c r="O18" s="96" t="n">
+      <c r="P18" s="96" t="n">
         <v>18.3</v>
       </c>
-      <c r="P18" s="96" t="n">
+      <c r="Q18" s="96" t="n">
         <v>21.54</v>
-      </c>
-      <c r="Q18" s="96" t="n">
-        <v>19.67</v>
       </c>
       <c r="R18" s="96" t="n">
         <v>19.67</v>
       </c>
       <c r="S18" s="96" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="T18" s="96" t="n">
         <v>21.52</v>
-      </c>
-      <c r="T18" s="96" t="n">
-        <v>20.12</v>
       </c>
       <c r="U18" s="96" t="n">
         <v>20.12</v>
       </c>
       <c r="V18" s="96" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="W18" s="96" t="n">
         <v>21.39</v>
       </c>
-      <c r="W18" s="96" t="n">
+      <c r="X18" s="96" t="n">
         <v>19.43</v>
       </c>
-      <c r="X18" s="96" t="n">
+      <c r="Y18" s="96" t="n">
         <v>15.27</v>
       </c>
-      <c r="Y18" s="96" t="n">
+      <c r="Z18" s="96" t="n">
         <v>13.49</v>
       </c>
-      <c r="Z18" s="96" t="n">
+      <c r="AA18" s="96" t="n">
         <v>19.14</v>
       </c>
-      <c r="AA18" s="96" t="n">
+      <c r="AB18" s="96" t="n">
         <v>19.6</v>
       </c>
-      <c r="AB18" s="96" t="n">
+      <c r="AC18" s="96" t="n">
         <v>18.69</v>
       </c>
-      <c r="AC18" s="96" t="n">
+      <c r="AD18" s="96" t="n">
         <v>17.58</v>
       </c>
-      <c r="AD18" s="96" t="n">
-        <v>13.12</v>
-      </c>
       <c r="AE18" s="96" t="n">
-        <v>13.12</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -8395,91 +8376,91 @@
         <v>12.44</v>
       </c>
       <c r="C19" s="96" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="D19" s="96" t="n">
         <v>13.04</v>
       </c>
-      <c r="D19" s="96" t="n">
+      <c r="E19" s="96" t="n">
         <v>11.92</v>
       </c>
-      <c r="E19" s="96" t="n">
+      <c r="F19" s="96" t="n">
         <v>12.96</v>
       </c>
-      <c r="F19" s="96" t="n">
+      <c r="G19" s="96" t="n">
         <v>10.55</v>
       </c>
-      <c r="G19" s="96" t="n">
+      <c r="H19" s="96" t="n">
         <v>7.42</v>
       </c>
-      <c r="H19" s="96" t="n">
+      <c r="I19" s="96" t="n">
         <v>6.97</v>
       </c>
-      <c r="I19" s="96" t="n">
+      <c r="J19" s="96" t="n">
         <v>8.73</v>
       </c>
-      <c r="J19" s="96" t="n">
+      <c r="K19" s="96" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="K19" s="96" t="n">
+      <c r="L19" s="96" t="n">
         <v>7.43</v>
       </c>
-      <c r="L19" s="96" t="n">
+      <c r="M19" s="96" t="n">
         <v>5.98</v>
       </c>
-      <c r="M19" s="96" t="n">
+      <c r="N19" s="96" t="n">
         <v>5.35</v>
       </c>
-      <c r="N19" s="96" t="n">
+      <c r="O19" s="96" t="n">
         <v>8.24</v>
       </c>
-      <c r="O19" s="96" t="n">
+      <c r="P19" s="96" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="P19" s="96" t="n">
+      <c r="Q19" s="96" t="n">
         <v>10.45</v>
-      </c>
-      <c r="Q19" s="96" t="n">
-        <v>12.03</v>
       </c>
       <c r="R19" s="96" t="n">
         <v>12.03</v>
       </c>
       <c r="S19" s="96" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="T19" s="96" t="n">
         <v>8.66</v>
-      </c>
-      <c r="T19" s="96" t="n">
-        <v>5.5</v>
       </c>
       <c r="U19" s="96" t="n">
         <v>5.5</v>
       </c>
       <c r="V19" s="96" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W19" s="96" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="W19" s="96" t="n">
+      <c r="X19" s="96" t="n">
         <v>8.82</v>
       </c>
-      <c r="X19" s="96" t="n">
+      <c r="Y19" s="96" t="n">
         <v>7.76</v>
       </c>
-      <c r="Y19" s="96" t="n">
+      <c r="Z19" s="96" t="n">
         <v>4.58</v>
       </c>
-      <c r="Z19" s="96" t="n">
+      <c r="AA19" s="96" t="n">
         <v>5.18</v>
       </c>
-      <c r="AA19" s="96" t="n">
+      <c r="AB19" s="96" t="n">
         <v>5.14</v>
       </c>
-      <c r="AB19" s="96" t="n">
+      <c r="AC19" s="96" t="n">
         <v>2.83</v>
       </c>
-      <c r="AC19" s="96" t="n">
+      <c r="AD19" s="96" t="n">
         <v>3.07</v>
       </c>
-      <c r="AD19" s="96" t="n">
-        <v>3.09</v>
-      </c>
       <c r="AE19" s="96" t="n">
-        <v>3.09</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -8492,91 +8473,91 @@
         <v>40.59</v>
       </c>
       <c r="C20" s="96" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="D20" s="96" t="n">
         <v>46.68</v>
       </c>
-      <c r="D20" s="96" t="n">
+      <c r="E20" s="96" t="n">
         <v>43.34</v>
       </c>
-      <c r="E20" s="96" t="n">
+      <c r="F20" s="96" t="n">
         <v>44.19</v>
       </c>
-      <c r="F20" s="96" t="n">
+      <c r="G20" s="96" t="n">
         <v>42.15</v>
       </c>
-      <c r="G20" s="96" t="n">
+      <c r="H20" s="96" t="n">
         <v>23.96</v>
       </c>
-      <c r="H20" s="96" t="n">
+      <c r="I20" s="96" t="n">
         <v>27.29</v>
       </c>
-      <c r="I20" s="96" t="n">
+      <c r="J20" s="96" t="n">
         <v>33.69</v>
       </c>
-      <c r="J20" s="96" t="n">
+      <c r="K20" s="96" t="n">
         <v>46.29</v>
       </c>
-      <c r="K20" s="96" t="n">
+      <c r="L20" s="96" t="n">
         <v>46.55</v>
       </c>
-      <c r="L20" s="96" t="n">
+      <c r="M20" s="96" t="n">
         <v>35.92</v>
       </c>
-      <c r="M20" s="96" t="n">
+      <c r="N20" s="96" t="n">
         <v>44.74</v>
       </c>
-      <c r="N20" s="96" t="n">
+      <c r="O20" s="96" t="n">
         <v>60.23</v>
       </c>
-      <c r="O20" s="96" t="n">
+      <c r="P20" s="96" t="n">
         <v>61.59</v>
       </c>
-      <c r="P20" s="96" t="n">
+      <c r="Q20" s="96" t="n">
         <v>89.59999999999999</v>
-      </c>
-      <c r="Q20" s="96" t="n">
-        <v>88.75</v>
       </c>
       <c r="R20" s="96" t="n">
         <v>88.75</v>
       </c>
       <c r="S20" s="96" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="T20" s="96" t="n">
         <v>86.84</v>
-      </c>
-      <c r="T20" s="96" t="n">
-        <v>82.62</v>
       </c>
       <c r="U20" s="96" t="n">
         <v>82.62</v>
       </c>
       <c r="V20" s="96" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="W20" s="96" t="n">
         <v>85.75</v>
       </c>
-      <c r="W20" s="96" t="n">
+      <c r="X20" s="96" t="n">
         <v>83.89</v>
       </c>
-      <c r="X20" s="96" t="n">
+      <c r="Y20" s="96" t="n">
         <v>76.78</v>
       </c>
-      <c r="Y20" s="96" t="n">
+      <c r="Z20" s="96" t="n">
         <v>71.20999999999999</v>
       </c>
-      <c r="Z20" s="96" t="n">
+      <c r="AA20" s="96" t="n">
         <v>83.54000000000001</v>
       </c>
-      <c r="AA20" s="96" t="n">
+      <c r="AB20" s="96" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="AB20" s="96" t="n">
+      <c r="AC20" s="96" t="n">
         <v>90.67</v>
       </c>
-      <c r="AC20" s="96" t="n">
+      <c r="AD20" s="96" t="n">
         <v>88.42</v>
       </c>
-      <c r="AD20" s="96" t="n">
-        <v>82.69</v>
-      </c>
       <c r="AE20" s="96" t="n">
-        <v>82.69</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -8589,91 +8570,91 @@
         <v>52.45</v>
       </c>
       <c r="C21" s="96" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="D21" s="96" t="n">
         <v>54.2</v>
       </c>
-      <c r="D21" s="96" t="n">
+      <c r="E21" s="96" t="n">
         <v>53.51</v>
       </c>
-      <c r="E21" s="96" t="n">
+      <c r="F21" s="96" t="n">
         <v>53.79</v>
       </c>
-      <c r="F21" s="96" t="n">
+      <c r="G21" s="96" t="n">
         <v>53.28</v>
       </c>
-      <c r="G21" s="96" t="n">
+      <c r="H21" s="96" t="n">
         <v>49.13</v>
       </c>
-      <c r="H21" s="96" t="n">
+      <c r="I21" s="96" t="n">
         <v>51.14</v>
       </c>
-      <c r="I21" s="96" t="n">
+      <c r="J21" s="96" t="n">
         <v>54.6</v>
       </c>
-      <c r="J21" s="96" t="n">
+      <c r="K21" s="96" t="n">
         <v>59.95</v>
       </c>
-      <c r="K21" s="96" t="n">
+      <c r="L21" s="96" t="n">
         <v>60.05</v>
       </c>
-      <c r="L21" s="96" t="n">
+      <c r="M21" s="96" t="n">
         <v>57.68</v>
       </c>
-      <c r="M21" s="96" t="n">
+      <c r="N21" s="96" t="n">
         <v>61.81</v>
       </c>
-      <c r="N21" s="96" t="n">
+      <c r="O21" s="96" t="n">
         <v>67.58</v>
       </c>
-      <c r="O21" s="96" t="n">
+      <c r="P21" s="96" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="P21" s="96" t="n">
+      <c r="Q21" s="96" t="n">
         <v>76.20999999999999</v>
-      </c>
-      <c r="Q21" s="96" t="n">
-        <v>75.66</v>
       </c>
       <c r="R21" s="96" t="n">
         <v>75.66</v>
       </c>
       <c r="S21" s="96" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="T21" s="96" t="n">
         <v>74.45999999999999</v>
-      </c>
-      <c r="T21" s="96" t="n">
-        <v>72.23999999999999</v>
       </c>
       <c r="U21" s="96" t="n">
         <v>72.23999999999999</v>
       </c>
       <c r="V21" s="96" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="W21" s="96" t="n">
         <v>73.06</v>
       </c>
-      <c r="W21" s="96" t="n">
+      <c r="X21" s="96" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="X21" s="96" t="n">
+      <c r="Y21" s="96" t="n">
         <v>68.52</v>
       </c>
-      <c r="Y21" s="96" t="n">
+      <c r="Z21" s="96" t="n">
         <v>66.47</v>
       </c>
-      <c r="Z21" s="96" t="n">
+      <c r="AA21" s="96" t="n">
         <v>69.64</v>
       </c>
-      <c r="AA21" s="96" t="n">
+      <c r="AB21" s="96" t="n">
         <v>71.58</v>
       </c>
-      <c r="AB21" s="96" t="n">
+      <c r="AC21" s="96" t="n">
         <v>70.78</v>
       </c>
-      <c r="AC21" s="96" t="n">
+      <c r="AD21" s="96" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="AD21" s="96" t="n">
-        <v>64.43000000000001</v>
-      </c>
       <c r="AE21" s="96" t="n">
-        <v>64.43000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -8702,129 +8683,129 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F22" s="93" t="inlineStr">
+      <c r="F22" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G22" s="93" t="inlineStr">
+      <c r="H22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H22" s="94" t="inlineStr">
+      <c r="I22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I22" s="94" t="inlineStr">
+      <c r="J22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J22" s="93" t="inlineStr">
+      <c r="K22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K22" s="93" t="inlineStr">
+      <c r="L22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="93" t="inlineStr">
+      <c r="M22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="93" t="inlineStr">
+      <c r="N22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="93" t="inlineStr">
+      <c r="O22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="93" t="inlineStr">
+      <c r="P22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="93" t="inlineStr">
+      <c r="Q22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="93" t="inlineStr">
+      <c r="R22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="93" t="inlineStr">
+      <c r="S22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="93" t="inlineStr">
+      <c r="T22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="95" t="inlineStr">
+      <c r="U22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U22" s="95" t="inlineStr">
+      <c r="V22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V22" s="93" t="inlineStr">
+      <c r="W22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W22" s="95" t="inlineStr">
+      <c r="X22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X22" s="95" t="inlineStr">
+      <c r="Y22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y22" s="95" t="inlineStr">
+      <c r="Z22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z22" s="95" t="inlineStr">
+      <c r="AA22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA22" s="95" t="inlineStr">
+      <c r="AB22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB22" s="95" t="inlineStr">
+      <c r="AC22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC22" s="93" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE22" s="94" t="inlineStr">
@@ -8840,94 +8821,94 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="C23" s="96" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="D23" s="96" t="n">
         <v>3.43</v>
       </c>
-      <c r="C23" s="96" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="D23" s="96" t="n">
+      <c r="E23" s="96" t="n">
         <v>4.61</v>
       </c>
-      <c r="E23" s="96" t="n">
+      <c r="F23" s="96" t="n">
         <v>3.27</v>
       </c>
-      <c r="F23" s="96" t="n">
+      <c r="G23" s="96" t="n">
         <v>2.44</v>
       </c>
-      <c r="G23" s="96" t="n">
+      <c r="H23" s="96" t="n">
         <v>3.38</v>
       </c>
-      <c r="H23" s="96" t="n">
+      <c r="I23" s="96" t="n">
         <v>3.09</v>
       </c>
-      <c r="I23" s="96" t="n">
+      <c r="J23" s="96" t="n">
         <v>2.65</v>
       </c>
-      <c r="J23" s="96" t="n">
+      <c r="K23" s="96" t="n">
         <v>3.29</v>
-      </c>
-      <c r="K23" s="96" t="n">
-        <v>4.09</v>
       </c>
       <c r="L23" s="96" t="n">
         <v>4.09</v>
       </c>
       <c r="M23" s="96" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="N23" s="96" t="n">
         <v>3.91</v>
       </c>
-      <c r="N23" s="96" t="n">
+      <c r="O23" s="96" t="n">
         <v>4.51</v>
       </c>
-      <c r="O23" s="96" t="n">
+      <c r="P23" s="96" t="n">
         <v>4.97</v>
       </c>
-      <c r="P23" s="96" t="n">
+      <c r="Q23" s="96" t="n">
         <v>4.31</v>
-      </c>
-      <c r="Q23" s="96" t="n">
-        <v>4.25</v>
       </c>
       <c r="R23" s="96" t="n">
         <v>4.25</v>
       </c>
       <c r="S23" s="96" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T23" s="96" t="n">
         <v>6.33</v>
       </c>
-      <c r="T23" s="96" t="n">
+      <c r="U23" s="96" t="n">
         <v>6.69</v>
       </c>
-      <c r="U23" s="96" t="n">
+      <c r="V23" s="96" t="n">
         <v>4.82</v>
       </c>
-      <c r="V23" s="96" t="n">
+      <c r="W23" s="96" t="n">
         <v>3.81</v>
       </c>
-      <c r="W23" s="96" t="n">
+      <c r="X23" s="96" t="n">
         <v>4.44</v>
       </c>
-      <c r="X23" s="96" t="n">
+      <c r="Y23" s="96" t="n">
         <v>5.27</v>
       </c>
-      <c r="Y23" s="96" t="n">
+      <c r="Z23" s="96" t="n">
         <v>3.3</v>
       </c>
-      <c r="Z23" s="96" t="n">
+      <c r="AA23" s="96" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA23" s="96" t="n">
+      <c r="AB23" s="96" t="n">
         <v>3.66</v>
       </c>
-      <c r="AB23" s="96" t="n">
+      <c r="AC23" s="96" t="n">
         <v>2.66</v>
       </c>
-      <c r="AC23" s="96" t="n">
+      <c r="AD23" s="96" t="n">
         <v>2.22</v>
       </c>
-      <c r="AD23" s="96" t="n">
+      <c r="AE23" s="96" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AE23" s="96" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="24">
@@ -8937,191 +8918,191 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C24" s="96" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="D24" s="96" t="n">
         <v>13.72</v>
       </c>
-      <c r="C24" s="96" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="D24" s="96" t="n">
+      <c r="E24" s="96" t="n">
         <v>15.3</v>
       </c>
-      <c r="E24" s="96" t="n">
+      <c r="F24" s="96" t="n">
         <v>14.47</v>
       </c>
-      <c r="F24" s="96" t="n">
+      <c r="G24" s="96" t="n">
         <v>14.75</v>
       </c>
-      <c r="G24" s="96" t="n">
+      <c r="H24" s="96" t="n">
         <v>15.09</v>
       </c>
-      <c r="H24" s="96" t="n">
+      <c r="I24" s="96" t="n">
         <v>15.08</v>
       </c>
-      <c r="I24" s="96" t="n">
+      <c r="J24" s="96" t="n">
         <v>15.32</v>
       </c>
-      <c r="J24" s="96" t="n">
+      <c r="K24" s="96" t="n">
         <v>16.11</v>
-      </c>
-      <c r="K24" s="96" t="n">
-        <v>15.45</v>
       </c>
       <c r="L24" s="96" t="n">
         <v>15.45</v>
       </c>
       <c r="M24" s="96" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="N24" s="96" t="n">
         <v>15.33</v>
       </c>
-      <c r="N24" s="96" t="n">
+      <c r="O24" s="96" t="n">
         <v>16.62</v>
       </c>
-      <c r="O24" s="96" t="n">
+      <c r="P24" s="96" t="n">
         <v>16.83</v>
       </c>
-      <c r="P24" s="96" t="n">
+      <c r="Q24" s="96" t="n">
         <v>16.65</v>
-      </c>
-      <c r="Q24" s="96" t="n">
-        <v>16.32</v>
       </c>
       <c r="R24" s="96" t="n">
         <v>16.32</v>
       </c>
       <c r="S24" s="96" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="T24" s="96" t="n">
         <v>16.25</v>
       </c>
-      <c r="T24" s="96" t="n">
+      <c r="U24" s="96" t="n">
         <v>16.97</v>
       </c>
-      <c r="U24" s="96" t="n">
+      <c r="V24" s="96" t="n">
         <v>15.38</v>
       </c>
-      <c r="V24" s="96" t="n">
+      <c r="W24" s="96" t="n">
         <v>15.67</v>
       </c>
-      <c r="W24" s="96" t="n">
+      <c r="X24" s="96" t="n">
         <v>15.85</v>
       </c>
-      <c r="X24" s="96" t="n">
+      <c r="Y24" s="96" t="n">
         <v>15.79</v>
       </c>
-      <c r="Y24" s="96" t="n">
+      <c r="Z24" s="96" t="n">
         <v>15.39</v>
       </c>
-      <c r="Z24" s="96" t="n">
+      <c r="AA24" s="96" t="n">
         <v>17.59</v>
       </c>
-      <c r="AA24" s="96" t="n">
+      <c r="AB24" s="96" t="n">
         <v>17.34</v>
       </c>
-      <c r="AB24" s="96" t="n">
+      <c r="AC24" s="96" t="n">
         <v>17.95</v>
       </c>
-      <c r="AC24" s="96" t="n">
+      <c r="AD24" s="96" t="n">
         <v>15.55</v>
       </c>
-      <c r="AD24" s="96" t="n">
+      <c r="AE24" s="96" t="n">
         <v>14.62</v>
       </c>
-      <c r="AE24" s="96" t="n">
-        <v>15.34</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="C25" s="96" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D25" s="96" t="n">
         <v>93.04000000000001</v>
       </c>
-      <c r="C25" s="96" t="n">
-        <v>93.04000000000001</v>
-      </c>
-      <c r="D25" s="96" t="n">
+      <c r="E25" s="96" t="n">
         <v>95.63</v>
       </c>
-      <c r="E25" s="96" t="n">
+      <c r="F25" s="96" t="n">
         <v>76.59</v>
       </c>
-      <c r="F25" s="96" t="n">
+      <c r="G25" s="96" t="n">
         <v>67.67</v>
       </c>
-      <c r="G25" s="96" t="n">
+      <c r="H25" s="96" t="n">
         <v>62.36</v>
       </c>
-      <c r="H25" s="96" t="n">
+      <c r="I25" s="96" t="n">
         <v>8.93</v>
       </c>
-      <c r="I25" s="96" t="n">
+      <c r="J25" s="96" t="n">
         <v>19.05</v>
       </c>
-      <c r="J25" s="96" t="n">
+      <c r="K25" s="96" t="n">
         <v>64.41</v>
-      </c>
-      <c r="K25" s="96" t="n">
-        <v>62.92</v>
       </c>
       <c r="L25" s="96" t="n">
         <v>62.92</v>
       </c>
       <c r="M25" s="96" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="N25" s="96" t="n">
         <v>10.58</v>
       </c>
-      <c r="N25" s="96" t="n">
+      <c r="O25" s="96" t="n">
         <v>42.26</v>
       </c>
-      <c r="O25" s="96" t="n">
+      <c r="P25" s="96" t="n">
         <v>94.03</v>
       </c>
-      <c r="P25" s="96" t="n">
+      <c r="Q25" s="96" t="n">
         <v>86.27</v>
-      </c>
-      <c r="Q25" s="96" t="n">
-        <v>82</v>
       </c>
       <c r="R25" s="96" t="n">
         <v>82</v>
       </c>
       <c r="S25" s="96" t="n">
+        <v>82</v>
+      </c>
+      <c r="T25" s="96" t="n">
         <v>77.56</v>
       </c>
-      <c r="T25" s="96" t="n">
+      <c r="U25" s="96" t="n">
         <v>99.52</v>
       </c>
-      <c r="U25" s="96" t="n">
+      <c r="V25" s="96" t="n">
         <v>97.75</v>
       </c>
-      <c r="V25" s="96" t="n">
+      <c r="W25" s="96" t="n">
         <v>90.59</v>
       </c>
-      <c r="W25" s="96" t="n">
+      <c r="X25" s="96" t="n">
         <v>98.39</v>
       </c>
-      <c r="X25" s="96" t="n">
+      <c r="Y25" s="96" t="n">
         <v>97.72</v>
       </c>
-      <c r="Y25" s="96" t="n">
+      <c r="Z25" s="96" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="Z25" s="96" t="n">
+      <c r="AA25" s="96" t="n">
         <v>93.78</v>
       </c>
-      <c r="AA25" s="96" t="n">
+      <c r="AB25" s="96" t="n">
         <v>92.95</v>
       </c>
-      <c r="AB25" s="96" t="n">
+      <c r="AC25" s="96" t="n">
         <v>85.79000000000001</v>
       </c>
-      <c r="AC25" s="96" t="n">
+      <c r="AD25" s="96" t="n">
         <v>63.58</v>
       </c>
-      <c r="AD25" s="96" t="n">
+      <c r="AE25" s="96" t="n">
         <v>16.62</v>
-      </c>
-      <c r="AE25" s="96" t="n">
-        <v>21.97</v>
       </c>
     </row>
     <row r="26">
@@ -9131,94 +9112,94 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="C26" s="96" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D26" s="96" t="n">
         <v>93.04000000000001</v>
       </c>
-      <c r="C26" s="96" t="n">
-        <v>93.04000000000001</v>
-      </c>
-      <c r="D26" s="96" t="n">
+      <c r="E26" s="96" t="n">
         <v>95.63</v>
       </c>
-      <c r="E26" s="96" t="n">
+      <c r="F26" s="96" t="n">
         <v>76.59</v>
       </c>
-      <c r="F26" s="96" t="n">
+      <c r="G26" s="96" t="n">
         <v>67.67</v>
       </c>
-      <c r="G26" s="96" t="n">
+      <c r="H26" s="96" t="n">
         <v>62.36</v>
       </c>
-      <c r="H26" s="96" t="n">
+      <c r="I26" s="96" t="n">
         <v>8.93</v>
       </c>
-      <c r="I26" s="96" t="n">
+      <c r="J26" s="96" t="n">
         <v>19.05</v>
       </c>
-      <c r="J26" s="96" t="n">
+      <c r="K26" s="96" t="n">
         <v>64.41</v>
-      </c>
-      <c r="K26" s="96" t="n">
-        <v>62.92</v>
       </c>
       <c r="L26" s="96" t="n">
         <v>62.92</v>
       </c>
       <c r="M26" s="96" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="N26" s="96" t="n">
         <v>10.58</v>
       </c>
-      <c r="N26" s="96" t="n">
+      <c r="O26" s="96" t="n">
         <v>42.26</v>
       </c>
-      <c r="O26" s="96" t="n">
+      <c r="P26" s="96" t="n">
         <v>94.03</v>
       </c>
-      <c r="P26" s="96" t="n">
+      <c r="Q26" s="96" t="n">
         <v>86.27</v>
-      </c>
-      <c r="Q26" s="96" t="n">
-        <v>82</v>
       </c>
       <c r="R26" s="96" t="n">
         <v>82</v>
       </c>
       <c r="S26" s="96" t="n">
+        <v>82</v>
+      </c>
+      <c r="T26" s="96" t="n">
         <v>77.56</v>
       </c>
-      <c r="T26" s="96" t="n">
+      <c r="U26" s="96" t="n">
         <v>99.52</v>
       </c>
-      <c r="U26" s="96" t="n">
+      <c r="V26" s="96" t="n">
         <v>97.75</v>
       </c>
-      <c r="V26" s="96" t="n">
+      <c r="W26" s="96" t="n">
         <v>90.59</v>
       </c>
-      <c r="W26" s="96" t="n">
+      <c r="X26" s="96" t="n">
         <v>98.39</v>
       </c>
-      <c r="X26" s="96" t="n">
+      <c r="Y26" s="96" t="n">
         <v>97.72</v>
       </c>
-      <c r="Y26" s="96" t="n">
+      <c r="Z26" s="96" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="Z26" s="96" t="n">
+      <c r="AA26" s="96" t="n">
         <v>93.78</v>
       </c>
-      <c r="AA26" s="96" t="n">
+      <c r="AB26" s="96" t="n">
         <v>92.95</v>
       </c>
-      <c r="AB26" s="96" t="n">
+      <c r="AC26" s="96" t="n">
         <v>85.79000000000001</v>
       </c>
-      <c r="AC26" s="96" t="n">
+      <c r="AD26" s="96" t="n">
         <v>63.58</v>
       </c>
-      <c r="AD26" s="96" t="n">
+      <c r="AE26" s="96" t="n">
         <v>16.62</v>
-      </c>
-      <c r="AE26" s="96" t="n">
-        <v>21.97</v>
       </c>
     </row>
     <row r="27">
@@ -9232,144 +9213,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C27" s="95" t="inlineStr">
+      <c r="C27" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D27" s="93" t="inlineStr">
+      <c r="E27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E27" s="93" t="inlineStr">
+      <c r="F27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F27" s="93" t="inlineStr">
+      <c r="G27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G27" s="93" t="inlineStr">
+      <c r="H27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H27" s="94" t="inlineStr">
+      <c r="I27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I27" s="94" t="inlineStr">
+      <c r="J27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J27" s="94" t="inlineStr">
+      <c r="K27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K27" s="94" t="inlineStr">
+      <c r="L27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L27" s="94" t="inlineStr">
+      <c r="M27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M27" s="94" t="inlineStr">
+      <c r="N27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N27" s="93" t="inlineStr">
+      <c r="O27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O27" s="93" t="inlineStr">
+      <c r="P27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P27" s="93" t="inlineStr">
+      <c r="Q27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q27" s="93" t="inlineStr">
+      <c r="R27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R27" s="93" t="inlineStr">
+      <c r="S27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S27" s="93" t="inlineStr">
+      <c r="T27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="95" t="inlineStr">
+      <c r="U27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U27" s="93" t="inlineStr">
+      <c r="V27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V27" s="93" t="inlineStr">
+      <c r="W27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W27" s="95" t="inlineStr">
+      <c r="X27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X27" s="95" t="inlineStr">
+      <c r="Y27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y27" s="95" t="inlineStr">
+      <c r="Z27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z27" s="95" t="inlineStr">
+      <c r="AA27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA27" s="95" t="inlineStr">
+      <c r="AB27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB27" s="95" t="inlineStr">
+      <c r="AC27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC27" s="95" t="inlineStr">
+      <c r="AD27" s="95" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD27" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE27" s="94" t="inlineStr">
@@ -9385,94 +9366,94 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C28" s="96" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="D28" s="96" t="n">
         <v>-0.31</v>
       </c>
-      <c r="C28" s="96" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="D28" s="96" t="n">
+      <c r="E28" s="96" t="n">
         <v>0.1</v>
       </c>
-      <c r="E28" s="96" t="n">
+      <c r="F28" s="96" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F28" s="96" t="n">
+      <c r="G28" s="96" t="n">
         <v>-0.57</v>
       </c>
-      <c r="G28" s="96" t="n">
+      <c r="H28" s="96" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H28" s="96" t="n">
+      <c r="I28" s="96" t="n">
         <v>-1.23</v>
       </c>
-      <c r="I28" s="96" t="n">
+      <c r="J28" s="96" t="n">
         <v>-1.41</v>
       </c>
-      <c r="J28" s="96" t="n">
+      <c r="K28" s="96" t="n">
         <v>-0.6</v>
-      </c>
-      <c r="K28" s="96" t="n">
-        <v>0.19</v>
       </c>
       <c r="L28" s="96" t="n">
         <v>0.19</v>
       </c>
       <c r="M28" s="96" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N28" s="96" t="n">
         <v>0.3</v>
       </c>
-      <c r="N28" s="96" t="n">
+      <c r="O28" s="96" t="n">
         <v>1.79</v>
       </c>
-      <c r="O28" s="96" t="n">
+      <c r="P28" s="96" t="n">
         <v>2.06</v>
       </c>
-      <c r="P28" s="96" t="n">
+      <c r="Q28" s="96" t="n">
         <v>1.73</v>
-      </c>
-      <c r="Q28" s="96" t="n">
-        <v>2.39</v>
       </c>
       <c r="R28" s="96" t="n">
         <v>2.39</v>
       </c>
       <c r="S28" s="96" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T28" s="96" t="n">
         <v>3.26</v>
       </c>
-      <c r="T28" s="96" t="n">
+      <c r="U28" s="96" t="n">
         <v>3.49</v>
       </c>
-      <c r="U28" s="96" t="n">
+      <c r="V28" s="96" t="n">
         <v>2.41</v>
       </c>
-      <c r="V28" s="96" t="n">
+      <c r="W28" s="96" t="n">
         <v>1.7</v>
       </c>
-      <c r="W28" s="96" t="n">
+      <c r="X28" s="96" t="n">
         <v>2.83</v>
       </c>
-      <c r="X28" s="96" t="n">
+      <c r="Y28" s="96" t="n">
         <v>2.91</v>
       </c>
-      <c r="Y28" s="96" t="n">
+      <c r="Z28" s="96" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z28" s="96" t="n">
+      <c r="AA28" s="96" t="n">
         <v>0.55</v>
       </c>
-      <c r="AA28" s="96" t="n">
+      <c r="AB28" s="96" t="n">
         <v>0.33</v>
       </c>
-      <c r="AB28" s="96" t="n">
+      <c r="AC28" s="96" t="n">
         <v>-0</v>
       </c>
-      <c r="AC28" s="96" t="n">
+      <c r="AD28" s="96" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AD28" s="96" t="n">
+      <c r="AE28" s="96" t="n">
         <v>-1.24</v>
-      </c>
-      <c r="AE28" s="96" t="n">
-        <v>-2.17</v>
       </c>
     </row>
     <row r="29">
@@ -9482,94 +9463,94 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="C29" s="96" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D29" s="96" t="n">
         <v>4.84</v>
       </c>
-      <c r="C29" s="96" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="D29" s="96" t="n">
+      <c r="E29" s="96" t="n">
         <v>6.09</v>
       </c>
-      <c r="E29" s="96" t="n">
+      <c r="F29" s="96" t="n">
         <v>6.34</v>
       </c>
-      <c r="F29" s="96" t="n">
+      <c r="G29" s="96" t="n">
         <v>6.41</v>
       </c>
-      <c r="G29" s="96" t="n">
+      <c r="H29" s="96" t="n">
         <v>7.11</v>
       </c>
-      <c r="H29" s="96" t="n">
+      <c r="I29" s="96" t="n">
         <v>5.71</v>
       </c>
-      <c r="I29" s="96" t="n">
+      <c r="J29" s="96" t="n">
         <v>6.41</v>
       </c>
-      <c r="J29" s="96" t="n">
+      <c r="K29" s="96" t="n">
         <v>7.32</v>
-      </c>
-      <c r="K29" s="96" t="n">
-        <v>7.79</v>
       </c>
       <c r="L29" s="96" t="n">
         <v>7.79</v>
       </c>
       <c r="M29" s="96" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="N29" s="96" t="n">
         <v>8.66</v>
       </c>
-      <c r="N29" s="96" t="n">
+      <c r="O29" s="96" t="n">
         <v>11.97</v>
       </c>
-      <c r="O29" s="96" t="n">
+      <c r="P29" s="96" t="n">
         <v>12.58</v>
       </c>
-      <c r="P29" s="96" t="n">
+      <c r="Q29" s="96" t="n">
         <v>12.66</v>
-      </c>
-      <c r="Q29" s="96" t="n">
-        <v>13.04</v>
       </c>
       <c r="R29" s="96" t="n">
         <v>13.04</v>
       </c>
       <c r="S29" s="96" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="T29" s="96" t="n">
         <v>13.03</v>
       </c>
-      <c r="T29" s="96" t="n">
+      <c r="U29" s="96" t="n">
         <v>13.74</v>
       </c>
-      <c r="U29" s="96" t="n">
+      <c r="V29" s="96" t="n">
         <v>12.54</v>
       </c>
-      <c r="V29" s="96" t="n">
+      <c r="W29" s="96" t="n">
         <v>12.83</v>
       </c>
-      <c r="W29" s="96" t="n">
+      <c r="X29" s="96" t="n">
         <v>13.07</v>
       </c>
-      <c r="X29" s="96" t="n">
+      <c r="Y29" s="96" t="n">
         <v>12.56</v>
       </c>
-      <c r="Y29" s="96" t="n">
+      <c r="Z29" s="96" t="n">
         <v>12.14</v>
       </c>
-      <c r="Z29" s="96" t="n">
+      <c r="AA29" s="96" t="n">
         <v>13.24</v>
       </c>
-      <c r="AA29" s="96" t="n">
+      <c r="AB29" s="96" t="n">
         <v>13.33</v>
       </c>
-      <c r="AB29" s="96" t="n">
+      <c r="AC29" s="96" t="n">
         <v>14.11</v>
       </c>
-      <c r="AC29" s="96" t="n">
+      <c r="AD29" s="96" t="n">
         <v>12.06</v>
       </c>
-      <c r="AD29" s="96" t="n">
+      <c r="AE29" s="96" t="n">
         <v>10.98</v>
-      </c>
-      <c r="AE29" s="96" t="n">
-        <v>10.91</v>
       </c>
     </row>
     <row r="30">
@@ -9579,94 +9560,94 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="C30" s="96" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="D30" s="96" t="n">
         <v>68.58</v>
       </c>
-      <c r="C30" s="96" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="D30" s="96" t="n">
+      <c r="E30" s="96" t="n">
         <v>62.23</v>
       </c>
-      <c r="E30" s="96" t="n">
+      <c r="F30" s="96" t="n">
         <v>54.82</v>
       </c>
-      <c r="F30" s="96" t="n">
+      <c r="G30" s="96" t="n">
         <v>44.15</v>
       </c>
-      <c r="G30" s="96" t="n">
+      <c r="H30" s="96" t="n">
         <v>50.71</v>
       </c>
-      <c r="H30" s="96" t="n">
+      <c r="I30" s="96" t="n">
         <v>2.58</v>
       </c>
-      <c r="I30" s="96" t="n">
+      <c r="J30" s="96" t="n">
         <v>4.12</v>
       </c>
-      <c r="J30" s="96" t="n">
+      <c r="K30" s="96" t="n">
         <v>8.18</v>
-      </c>
-      <c r="K30" s="96" t="n">
-        <v>12.5</v>
       </c>
       <c r="L30" s="96" t="n">
         <v>12.5</v>
       </c>
       <c r="M30" s="96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N30" s="96" t="n">
         <v>11.88</v>
       </c>
-      <c r="N30" s="96" t="n">
+      <c r="O30" s="96" t="n">
         <v>35.03</v>
       </c>
-      <c r="O30" s="96" t="n">
+      <c r="P30" s="96" t="n">
         <v>61.8</v>
       </c>
-      <c r="P30" s="96" t="n">
+      <c r="Q30" s="96" t="n">
         <v>54.14</v>
-      </c>
-      <c r="Q30" s="96" t="n">
-        <v>89.84999999999999</v>
       </c>
       <c r="R30" s="96" t="n">
         <v>89.84999999999999</v>
       </c>
       <c r="S30" s="96" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="T30" s="96" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="T30" s="96" t="n">
+      <c r="U30" s="96" t="n">
         <v>93.16</v>
       </c>
-      <c r="U30" s="96" t="n">
+      <c r="V30" s="96" t="n">
         <v>85.12</v>
       </c>
-      <c r="V30" s="96" t="n">
+      <c r="W30" s="96" t="n">
         <v>79.20999999999999</v>
       </c>
-      <c r="W30" s="96" t="n">
+      <c r="X30" s="96" t="n">
         <v>95.42</v>
       </c>
-      <c r="X30" s="96" t="n">
+      <c r="Y30" s="96" t="n">
         <v>94.2</v>
       </c>
-      <c r="Y30" s="96" t="n">
+      <c r="Z30" s="96" t="n">
         <v>89.09</v>
       </c>
-      <c r="Z30" s="96" t="n">
+      <c r="AA30" s="96" t="n">
         <v>84.28</v>
       </c>
-      <c r="AA30" s="96" t="n">
+      <c r="AB30" s="96" t="n">
         <v>83.37</v>
       </c>
-      <c r="AB30" s="96" t="n">
+      <c r="AC30" s="96" t="n">
         <v>78.88</v>
       </c>
-      <c r="AC30" s="96" t="n">
+      <c r="AD30" s="96" t="n">
         <v>61</v>
       </c>
-      <c r="AD30" s="96" t="n">
+      <c r="AE30" s="96" t="n">
         <v>34.52</v>
-      </c>
-      <c r="AE30" s="96" t="n">
-        <v>25.36</v>
       </c>
     </row>
     <row r="31">
@@ -9676,94 +9657,94 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="C31" s="96" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="D31" s="96" t="n">
         <v>54.32</v>
       </c>
-      <c r="C31" s="96" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="D31" s="96" t="n">
+      <c r="E31" s="96" t="n">
         <v>50.28</v>
       </c>
-      <c r="E31" s="96" t="n">
+      <c r="F31" s="96" t="n">
         <v>45.59</v>
       </c>
-      <c r="F31" s="96" t="n">
+      <c r="G31" s="96" t="n">
         <v>38.85</v>
       </c>
-      <c r="G31" s="96" t="n">
+      <c r="H31" s="96" t="n">
         <v>42.3</v>
       </c>
-      <c r="H31" s="96" t="n">
+      <c r="I31" s="96" t="n">
         <v>10.72</v>
       </c>
-      <c r="I31" s="96" t="n">
+      <c r="J31" s="96" t="n">
         <v>14.31</v>
       </c>
-      <c r="J31" s="96" t="n">
+      <c r="K31" s="96" t="n">
         <v>21.52</v>
-      </c>
-      <c r="K31" s="96" t="n">
-        <v>27.31</v>
       </c>
       <c r="L31" s="96" t="n">
         <v>27.31</v>
       </c>
       <c r="M31" s="96" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="N31" s="96" t="n">
         <v>27</v>
       </c>
-      <c r="N31" s="96" t="n">
+      <c r="O31" s="96" t="n">
         <v>52.3</v>
       </c>
-      <c r="O31" s="96" t="n">
+      <c r="P31" s="96" t="n">
         <v>69.72</v>
       </c>
-      <c r="P31" s="96" t="n">
+      <c r="Q31" s="96" t="n">
         <v>66.81999999999999</v>
-      </c>
-      <c r="Q31" s="96" t="n">
-        <v>86.52</v>
       </c>
       <c r="R31" s="96" t="n">
         <v>86.52</v>
       </c>
       <c r="S31" s="96" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="T31" s="96" t="n">
         <v>83.94</v>
       </c>
-      <c r="T31" s="96" t="n">
+      <c r="U31" s="96" t="n">
         <v>87.81</v>
       </c>
-      <c r="U31" s="96" t="n">
+      <c r="V31" s="96" t="n">
         <v>81.68000000000001</v>
       </c>
-      <c r="V31" s="96" t="n">
+      <c r="W31" s="96" t="n">
         <v>78.56</v>
       </c>
-      <c r="W31" s="96" t="n">
+      <c r="X31" s="96" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="X31" s="96" t="n">
+      <c r="Y31" s="96" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="Y31" s="96" t="n">
+      <c r="Z31" s="96" t="n">
         <v>77.98999999999999</v>
       </c>
-      <c r="Z31" s="96" t="n">
+      <c r="AA31" s="96" t="n">
         <v>73.66</v>
       </c>
-      <c r="AA31" s="96" t="n">
+      <c r="AB31" s="96" t="n">
         <v>72.87</v>
       </c>
-      <c r="AB31" s="96" t="n">
+      <c r="AC31" s="96" t="n">
         <v>68.7</v>
       </c>
-      <c r="AC31" s="96" t="n">
+      <c r="AD31" s="96" t="n">
         <v>54.42</v>
       </c>
-      <c r="AD31" s="96" t="n">
+      <c r="AE31" s="96" t="n">
         <v>38.29</v>
-      </c>
-      <c r="AE31" s="96" t="n">
-        <v>33.16</v>
       </c>
     </row>
     <row r="32">
@@ -9777,144 +9758,144 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C32" s="95" t="inlineStr">
+      <c r="C32" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D32" s="95" t="inlineStr">
+      <c r="E32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E32" s="93" t="inlineStr">
+      <c r="F32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F32" s="93" t="inlineStr">
+      <c r="G32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G32" s="93" t="inlineStr">
+      <c r="H32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H32" s="93" t="inlineStr">
+      <c r="I32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I32" s="93" t="inlineStr">
+      <c r="J32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J32" s="95" t="inlineStr">
+      <c r="K32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K32" s="93" t="inlineStr">
+      <c r="L32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L32" s="93" t="inlineStr">
+      <c r="M32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M32" s="93" t="inlineStr">
+      <c r="N32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N32" s="93" t="inlineStr">
+      <c r="O32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O32" s="93" t="inlineStr">
+      <c r="P32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P32" s="93" t="inlineStr">
+      <c r="Q32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q32" s="93" t="inlineStr">
+      <c r="R32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R32" s="93" t="inlineStr">
+      <c r="S32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="93" t="inlineStr">
+      <c r="T32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T32" s="95" t="inlineStr">
+      <c r="U32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U32" s="95" t="inlineStr">
+      <c r="V32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V32" s="93" t="inlineStr">
+      <c r="W32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W32" s="93" t="inlineStr">
+      <c r="X32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X32" s="95" t="inlineStr">
+      <c r="Y32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y32" s="95" t="inlineStr">
+      <c r="Z32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z32" s="95" t="inlineStr">
+      <c r="AA32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA32" s="95" t="inlineStr">
+      <c r="AB32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB32" s="95" t="inlineStr">
+      <c r="AC32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC32" s="95" t="inlineStr">
+      <c r="AD32" s="95" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AD32" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AE32" s="94" t="inlineStr">
@@ -9930,94 +9911,94 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C33" s="96" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="D33" s="96" t="n">
         <v>5.58</v>
       </c>
-      <c r="C33" s="96" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="D33" s="96" t="n">
+      <c r="E33" s="96" t="n">
         <v>7.3</v>
       </c>
-      <c r="E33" s="96" t="n">
+      <c r="F33" s="96" t="n">
         <v>4.8</v>
       </c>
-      <c r="F33" s="96" t="n">
+      <c r="G33" s="96" t="n">
         <v>3.41</v>
       </c>
-      <c r="G33" s="96" t="n">
+      <c r="H33" s="96" t="n">
         <v>4.39</v>
       </c>
-      <c r="H33" s="96" t="n">
+      <c r="I33" s="96" t="n">
         <v>5</v>
       </c>
-      <c r="I33" s="96" t="n">
+      <c r="J33" s="96" t="n">
         <v>4.4</v>
       </c>
-      <c r="J33" s="96" t="n">
+      <c r="K33" s="96" t="n">
         <v>4.58</v>
-      </c>
-      <c r="K33" s="96" t="n">
-        <v>5.15</v>
       </c>
       <c r="L33" s="96" t="n">
         <v>5.15</v>
       </c>
       <c r="M33" s="96" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N33" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="N33" s="96" t="n">
+      <c r="O33" s="96" t="n">
         <v>4.78</v>
       </c>
-      <c r="O33" s="96" t="n">
+      <c r="P33" s="96" t="n">
         <v>5.36</v>
       </c>
-      <c r="P33" s="96" t="n">
+      <c r="Q33" s="96" t="n">
         <v>4.99</v>
-      </c>
-      <c r="Q33" s="96" t="n">
-        <v>4.02</v>
       </c>
       <c r="R33" s="96" t="n">
         <v>4.02</v>
       </c>
       <c r="S33" s="96" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="T33" s="96" t="n">
         <v>7.17</v>
       </c>
-      <c r="T33" s="96" t="n">
+      <c r="U33" s="96" t="n">
         <v>7.11</v>
       </c>
-      <c r="U33" s="96" t="n">
+      <c r="V33" s="96" t="n">
         <v>4.66</v>
       </c>
-      <c r="V33" s="96" t="n">
+      <c r="W33" s="96" t="n">
         <v>3.03</v>
       </c>
-      <c r="W33" s="96" t="n">
+      <c r="X33" s="96" t="n">
         <v>3.04</v>
       </c>
-      <c r="X33" s="96" t="n">
+      <c r="Y33" s="96" t="n">
         <v>4.41</v>
       </c>
-      <c r="Y33" s="96" t="n">
+      <c r="Z33" s="96" t="n">
         <v>2.26</v>
       </c>
-      <c r="Z33" s="96" t="n">
+      <c r="AA33" s="96" t="n">
         <v>2.14</v>
       </c>
-      <c r="AA33" s="96" t="n">
+      <c r="AB33" s="96" t="n">
         <v>3.52</v>
       </c>
-      <c r="AB33" s="96" t="n">
+      <c r="AC33" s="96" t="n">
         <v>2.54</v>
       </c>
-      <c r="AC33" s="96" t="n">
+      <c r="AD33" s="96" t="n">
         <v>1.49</v>
       </c>
-      <c r="AD33" s="96" t="n">
+      <c r="AE33" s="96" t="n">
         <v>0.05</v>
-      </c>
-      <c r="AE33" s="96" t="n">
-        <v>0.18</v>
       </c>
     </row>
     <row r="34">
@@ -10027,94 +10008,94 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="C34" s="96" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D34" s="96" t="n">
         <v>16.55</v>
       </c>
-      <c r="C34" s="96" t="n">
-        <v>16.55</v>
-      </c>
-      <c r="D34" s="96" t="n">
+      <c r="E34" s="96" t="n">
         <v>18.26</v>
       </c>
-      <c r="E34" s="96" t="n">
+      <c r="F34" s="96" t="n">
         <v>16.8</v>
       </c>
-      <c r="F34" s="96" t="n">
+      <c r="G34" s="96" t="n">
         <v>16.83</v>
       </c>
-      <c r="G34" s="96" t="n">
+      <c r="H34" s="96" t="n">
         <v>16.7</v>
       </c>
-      <c r="H34" s="96" t="n">
+      <c r="I34" s="96" t="n">
         <v>18.31</v>
       </c>
-      <c r="I34" s="96" t="n">
+      <c r="J34" s="96" t="n">
         <v>18.91</v>
       </c>
-      <c r="J34" s="96" t="n">
+      <c r="K34" s="96" t="n">
         <v>19.98</v>
-      </c>
-      <c r="K34" s="96" t="n">
-        <v>18.29</v>
       </c>
       <c r="L34" s="96" t="n">
         <v>18.29</v>
       </c>
       <c r="M34" s="96" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="N34" s="96" t="n">
         <v>17.64</v>
       </c>
-      <c r="N34" s="96" t="n">
+      <c r="O34" s="96" t="n">
         <v>17.84</v>
       </c>
-      <c r="O34" s="96" t="n">
+      <c r="P34" s="96" t="n">
         <v>17.86</v>
       </c>
-      <c r="P34" s="96" t="n">
+      <c r="Q34" s="96" t="n">
         <v>17.93</v>
-      </c>
-      <c r="Q34" s="96" t="n">
-        <v>17.09</v>
       </c>
       <c r="R34" s="96" t="n">
         <v>17.09</v>
       </c>
       <c r="S34" s="96" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="T34" s="96" t="n">
         <v>17.05</v>
       </c>
-      <c r="T34" s="96" t="n">
+      <c r="U34" s="96" t="n">
         <v>17.9</v>
       </c>
-      <c r="U34" s="96" t="n">
+      <c r="V34" s="96" t="n">
         <v>15.59</v>
       </c>
-      <c r="V34" s="96" t="n">
+      <c r="W34" s="96" t="n">
         <v>16.02</v>
       </c>
-      <c r="W34" s="96" t="n">
+      <c r="X34" s="96" t="n">
         <v>15.78</v>
       </c>
-      <c r="X34" s="96" t="n">
+      <c r="Y34" s="96" t="n">
         <v>15.9</v>
       </c>
-      <c r="Y34" s="96" t="n">
+      <c r="Z34" s="96" t="n">
         <v>15.67</v>
       </c>
-      <c r="Z34" s="96" t="n">
+      <c r="AA34" s="96" t="n">
         <v>18.63</v>
       </c>
-      <c r="AA34" s="96" t="n">
+      <c r="AB34" s="96" t="n">
         <v>18.49</v>
       </c>
-      <c r="AB34" s="96" t="n">
+      <c r="AC34" s="96" t="n">
         <v>19.49</v>
       </c>
-      <c r="AC34" s="96" t="n">
+      <c r="AD34" s="96" t="n">
         <v>16.05</v>
       </c>
-      <c r="AD34" s="96" t="n">
+      <c r="AE34" s="96" t="n">
         <v>14.41</v>
-      </c>
-      <c r="AE34" s="96" t="n">
-        <v>15.82</v>
       </c>
     </row>
     <row r="35">
@@ -10124,191 +10105,191 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="C35" s="96" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="D35" s="96" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="C35" s="96" t="n">
-        <v>89.26000000000001</v>
-      </c>
-      <c r="D35" s="96" t="n">
+      <c r="E35" s="96" t="n">
         <v>96.08</v>
       </c>
-      <c r="E35" s="96" t="n">
+      <c r="F35" s="96" t="n">
         <v>72.87</v>
       </c>
-      <c r="F35" s="96" t="n">
+      <c r="G35" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="G35" s="96" t="n">
+      <c r="H35" s="96" t="n">
         <v>16.98</v>
       </c>
-      <c r="H35" s="96" t="n">
+      <c r="I35" s="96" t="n">
         <v>17.23</v>
       </c>
-      <c r="I35" s="96" t="n">
+      <c r="J35" s="96" t="n">
         <v>47.49</v>
       </c>
-      <c r="J35" s="96" t="n">
+      <c r="K35" s="96" t="n">
         <v>90.51000000000001</v>
-      </c>
-      <c r="K35" s="96" t="n">
-        <v>82.68000000000001</v>
       </c>
       <c r="L35" s="96" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="M35" s="96" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="N35" s="96" t="n">
         <v>25.11</v>
       </c>
-      <c r="N35" s="96" t="n">
+      <c r="O35" s="96" t="n">
         <v>61.16</v>
       </c>
-      <c r="O35" s="96" t="n">
+      <c r="P35" s="96" t="n">
         <v>92.75</v>
       </c>
-      <c r="P35" s="96" t="n">
+      <c r="Q35" s="96" t="n">
         <v>89.43000000000001</v>
-      </c>
-      <c r="Q35" s="96" t="n">
-        <v>68.98</v>
       </c>
       <c r="R35" s="96" t="n">
         <v>68.98</v>
       </c>
       <c r="S35" s="96" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="T35" s="96" t="n">
         <v>77.48</v>
       </c>
-      <c r="T35" s="96" t="n">
+      <c r="U35" s="96" t="n">
         <v>99.33</v>
       </c>
-      <c r="U35" s="96" t="n">
+      <c r="V35" s="96" t="n">
         <v>97.44</v>
       </c>
-      <c r="V35" s="96" t="n">
+      <c r="W35" s="96" t="n">
         <v>89.53</v>
       </c>
-      <c r="W35" s="96" t="n">
+      <c r="X35" s="96" t="n">
         <v>74.15000000000001</v>
       </c>
-      <c r="X35" s="96" t="n">
+      <c r="Y35" s="96" t="n">
         <v>80.91</v>
       </c>
-      <c r="Y35" s="96" t="n">
+      <c r="Z35" s="96" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="Z35" s="96" t="n">
+      <c r="AA35" s="96" t="n">
         <v>87.19</v>
       </c>
-      <c r="AA35" s="96" t="n">
+      <c r="AB35" s="96" t="n">
         <v>93.73</v>
       </c>
-      <c r="AB35" s="96" t="n">
+      <c r="AC35" s="96" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="AC35" s="96" t="n">
+      <c r="AD35" s="96" t="n">
         <v>70.39</v>
       </c>
-      <c r="AD35" s="96" t="n">
+      <c r="AE35" s="96" t="n">
         <v>20.92</v>
       </c>
-      <c r="AE35" s="96" t="n">
-        <v>25.69</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="96" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="C36" s="96" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="D36" s="96" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="C36" s="96" t="n">
-        <v>89.26000000000001</v>
-      </c>
-      <c r="D36" s="96" t="n">
+      <c r="E36" s="96" t="n">
         <v>96.08</v>
       </c>
-      <c r="E36" s="96" t="n">
+      <c r="F36" s="96" t="n">
         <v>72.87</v>
       </c>
-      <c r="F36" s="96" t="n">
+      <c r="G36" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="G36" s="96" t="n">
+      <c r="H36" s="96" t="n">
         <v>16.98</v>
       </c>
-      <c r="H36" s="96" t="n">
+      <c r="I36" s="96" t="n">
         <v>17.23</v>
       </c>
-      <c r="I36" s="96" t="n">
+      <c r="J36" s="96" t="n">
         <v>47.49</v>
       </c>
-      <c r="J36" s="96" t="n">
+      <c r="K36" s="96" t="n">
         <v>90.51000000000001</v>
-      </c>
-      <c r="K36" s="96" t="n">
-        <v>82.68000000000001</v>
       </c>
       <c r="L36" s="96" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="M36" s="96" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="N36" s="96" t="n">
         <v>25.11</v>
       </c>
-      <c r="N36" s="96" t="n">
+      <c r="O36" s="96" t="n">
         <v>61.16</v>
       </c>
-      <c r="O36" s="96" t="n">
+      <c r="P36" s="96" t="n">
         <v>92.75</v>
       </c>
-      <c r="P36" s="96" t="n">
+      <c r="Q36" s="96" t="n">
         <v>89.43000000000001</v>
-      </c>
-      <c r="Q36" s="96" t="n">
-        <v>68.98</v>
       </c>
       <c r="R36" s="96" t="n">
         <v>68.98</v>
       </c>
       <c r="S36" s="96" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="T36" s="96" t="n">
         <v>77.48</v>
       </c>
-      <c r="T36" s="96" t="n">
+      <c r="U36" s="96" t="n">
         <v>99.33</v>
       </c>
-      <c r="U36" s="96" t="n">
+      <c r="V36" s="96" t="n">
         <v>97.44</v>
       </c>
-      <c r="V36" s="96" t="n">
+      <c r="W36" s="96" t="n">
         <v>89.53</v>
       </c>
-      <c r="W36" s="96" t="n">
+      <c r="X36" s="96" t="n">
         <v>74.15000000000001</v>
       </c>
-      <c r="X36" s="96" t="n">
+      <c r="Y36" s="96" t="n">
         <v>80.91</v>
       </c>
-      <c r="Y36" s="96" t="n">
+      <c r="Z36" s="96" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="Z36" s="96" t="n">
+      <c r="AA36" s="96" t="n">
         <v>87.19</v>
       </c>
-      <c r="AA36" s="96" t="n">
+      <c r="AB36" s="96" t="n">
         <v>93.73</v>
       </c>
-      <c r="AB36" s="96" t="n">
+      <c r="AC36" s="96" t="n">
         <v>88.93000000000001</v>
       </c>
-      <c r="AC36" s="96" t="n">
+      <c r="AD36" s="96" t="n">
         <v>70.39</v>
       </c>
-      <c r="AD36" s="96" t="n">
+      <c r="AE36" s="96" t="n">
         <v>20.92</v>
-      </c>
-      <c r="AE36" s="96" t="n">
-        <v>25.69</v>
       </c>
     </row>
     <row r="37">
@@ -10317,154 +10298,154 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B37" s="93" t="inlineStr">
+      <c r="B37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="H37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C37" s="95" t="inlineStr">
+      <c r="L37" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D37" s="94" t="inlineStr">
+      <c r="O37" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E37" s="95" t="inlineStr">
+      <c r="X37" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z37" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="G37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="I37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J37" s="93" t="inlineStr">
+      <c r="AB37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K37" s="93" t="inlineStr">
+      <c r="AC37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N37" s="93" t="inlineStr">
+      <c r="AD37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W37" s="93" t="inlineStr">
+      <c r="AE37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="X37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y37" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA37" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB37" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC37" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD37" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -10475,82 +10456,82 @@
         </is>
       </c>
       <c r="B38" s="96" t="n">
-        <v>-0.41</v>
+        <v>0.66</v>
       </c>
       <c r="C38" s="96" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="D38" s="96" t="n">
         <v>-2.48</v>
       </c>
-      <c r="D38" s="96" t="n">
+      <c r="E38" s="96" t="n">
         <v>-2.8</v>
       </c>
-      <c r="E38" s="96" t="n">
+      <c r="F38" s="96" t="n">
         <v>-3.13</v>
       </c>
-      <c r="F38" s="96" t="n">
+      <c r="G38" s="96" t="n">
         <v>-2.93</v>
       </c>
-      <c r="G38" s="96" t="n">
+      <c r="H38" s="96" t="n">
         <v>-4.04</v>
       </c>
-      <c r="H38" s="96" t="n">
+      <c r="I38" s="96" t="n">
         <v>-4.65</v>
       </c>
-      <c r="I38" s="96" t="n">
+      <c r="J38" s="96" t="n">
         <v>-1.56</v>
       </c>
-      <c r="J38" s="96" t="n">
+      <c r="K38" s="96" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K38" s="96" t="n">
+      <c r="L38" s="96" t="n">
         <v>-0.87</v>
       </c>
-      <c r="L38" s="96" t="n">
+      <c r="M38" s="96" t="n">
         <v>-1.5</v>
       </c>
-      <c r="M38" s="96" t="n">
+      <c r="N38" s="96" t="n">
         <v>0.01</v>
       </c>
-      <c r="N38" s="96" t="n">
+      <c r="O38" s="96" t="n">
         <v>0.93</v>
       </c>
-      <c r="O38" s="96" t="n">
+      <c r="P38" s="96" t="n">
         <v>1.52</v>
       </c>
-      <c r="P38" s="96" t="n">
+      <c r="Q38" s="96" t="n">
         <v>1.56</v>
-      </c>
-      <c r="Q38" s="96" t="n">
-        <v>0.78</v>
       </c>
       <c r="R38" s="96" t="n">
         <v>0.78</v>
       </c>
       <c r="S38" s="96" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T38" s="96" t="n">
         <v>2</v>
       </c>
-      <c r="T38" s="96" t="n">
+      <c r="U38" s="96" t="n">
         <v>1.81</v>
       </c>
-      <c r="U38" s="96" t="n">
+      <c r="V38" s="96" t="n">
         <v>1.03</v>
       </c>
-      <c r="V38" s="96" t="n">
+      <c r="W38" s="96" t="n">
         <v>3.47</v>
       </c>
-      <c r="W38" s="96" t="n">
+      <c r="X38" s="96" t="n">
         <v>3.71</v>
       </c>
-      <c r="X38" s="96" t="n">
+      <c r="Y38" s="96" t="n">
         <v>5.41</v>
       </c>
-      <c r="Y38" s="96" t="n">
+      <c r="Z38" s="96" t="n">
         <v>5.65</v>
       </c>
-      <c r="Z38" s="96" t="n">
+      <c r="AA38" s="96" t="n">
         <v>6.82</v>
-      </c>
-      <c r="AA38" s="96" t="n">
-        <v>5.75</v>
       </c>
       <c r="AB38" s="96" t="n">
         <v>5.75</v>
@@ -10559,10 +10540,10 @@
         <v>5.75</v>
       </c>
       <c r="AD38" s="96" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE38" s="96" t="n">
         <v>6.28</v>
-      </c>
-      <c r="AE38" s="96" t="n">
-        <v>5.84</v>
       </c>
     </row>
     <row r="39">
@@ -10572,82 +10553,82 @@
         </is>
       </c>
       <c r="B39" s="96" t="n">
-        <v>19.66</v>
+        <v>19.1</v>
       </c>
       <c r="C39" s="96" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="D39" s="96" t="n">
         <v>17.79</v>
       </c>
-      <c r="D39" s="96" t="n">
+      <c r="E39" s="96" t="n">
         <v>15.08</v>
       </c>
-      <c r="E39" s="96" t="n">
+      <c r="F39" s="96" t="n">
         <v>18.49</v>
       </c>
-      <c r="F39" s="96" t="n">
+      <c r="G39" s="96" t="n">
         <v>17.13</v>
       </c>
-      <c r="G39" s="96" t="n">
+      <c r="H39" s="96" t="n">
         <v>15.12</v>
       </c>
-      <c r="H39" s="96" t="n">
+      <c r="I39" s="96" t="n">
         <v>13.64</v>
       </c>
-      <c r="I39" s="96" t="n">
+      <c r="J39" s="96" t="n">
         <v>15.71</v>
-      </c>
-      <c r="J39" s="96" t="n">
-        <v>16.3</v>
       </c>
       <c r="K39" s="96" t="n">
         <v>16.3</v>
       </c>
       <c r="L39" s="96" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M39" s="96" t="n">
         <v>14.93</v>
       </c>
-      <c r="M39" s="96" t="n">
+      <c r="N39" s="96" t="n">
         <v>16.89</v>
       </c>
-      <c r="N39" s="96" t="n">
+      <c r="O39" s="96" t="n">
         <v>15.78</v>
       </c>
-      <c r="O39" s="96" t="n">
+      <c r="P39" s="96" t="n">
         <v>16.65</v>
       </c>
-      <c r="P39" s="96" t="n">
+      <c r="Q39" s="96" t="n">
         <v>16.33</v>
-      </c>
-      <c r="Q39" s="96" t="n">
-        <v>16.05</v>
       </c>
       <c r="R39" s="96" t="n">
         <v>16.05</v>
       </c>
       <c r="S39" s="96" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="T39" s="96" t="n">
         <v>16.11</v>
       </c>
-      <c r="T39" s="96" t="n">
+      <c r="U39" s="96" t="n">
         <v>17.4</v>
       </c>
-      <c r="U39" s="96" t="n">
+      <c r="V39" s="96" t="n">
         <v>17.71</v>
       </c>
-      <c r="V39" s="96" t="n">
+      <c r="W39" s="96" t="n">
         <v>17.23</v>
       </c>
-      <c r="W39" s="96" t="n">
+      <c r="X39" s="96" t="n">
         <v>17.1</v>
       </c>
-      <c r="X39" s="96" t="n">
+      <c r="Y39" s="96" t="n">
         <v>18.37</v>
       </c>
-      <c r="Y39" s="96" t="n">
+      <c r="Z39" s="96" t="n">
         <v>18.38</v>
       </c>
-      <c r="Z39" s="96" t="n">
+      <c r="AA39" s="96" t="n">
         <v>18.73</v>
-      </c>
-      <c r="AA39" s="96" t="n">
-        <v>19.68</v>
       </c>
       <c r="AB39" s="96" t="n">
         <v>19.68</v>
@@ -10656,10 +10637,10 @@
         <v>19.68</v>
       </c>
       <c r="AD39" s="96" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AE39" s="96" t="n">
         <v>21.11</v>
-      </c>
-      <c r="AE39" s="96" t="n">
-        <v>24.46</v>
       </c>
     </row>
     <row r="40">
@@ -10669,82 +10650,82 @@
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>50.13</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="C40" s="96" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="D40" s="96" t="n">
         <v>51.98</v>
       </c>
-      <c r="D40" s="96" t="n">
+      <c r="E40" s="96" t="n">
         <v>43.77</v>
       </c>
-      <c r="E40" s="96" t="n">
+      <c r="F40" s="96" t="n">
         <v>56.3</v>
       </c>
-      <c r="F40" s="96" t="n">
+      <c r="G40" s="96" t="n">
         <v>59.66</v>
       </c>
-      <c r="G40" s="96" t="n">
+      <c r="H40" s="96" t="n">
         <v>46.7</v>
       </c>
-      <c r="H40" s="96" t="n">
+      <c r="I40" s="96" t="n">
         <v>28.32</v>
       </c>
-      <c r="I40" s="96" t="n">
+      <c r="J40" s="96" t="n">
         <v>41.63</v>
       </c>
-      <c r="J40" s="96" t="n">
+      <c r="K40" s="96" t="n">
         <v>53.58</v>
       </c>
-      <c r="K40" s="96" t="n">
+      <c r="L40" s="96" t="n">
         <v>55.49</v>
       </c>
-      <c r="L40" s="96" t="n">
+      <c r="M40" s="96" t="n">
         <v>46.89</v>
       </c>
-      <c r="M40" s="96" t="n">
+      <c r="N40" s="96" t="n">
         <v>64.97</v>
       </c>
-      <c r="N40" s="96" t="n">
+      <c r="O40" s="96" t="n">
         <v>47.87</v>
       </c>
-      <c r="O40" s="96" t="n">
+      <c r="P40" s="96" t="n">
         <v>65.12</v>
       </c>
-      <c r="P40" s="96" t="n">
+      <c r="Q40" s="96" t="n">
         <v>72.95999999999999</v>
-      </c>
-      <c r="Q40" s="96" t="n">
-        <v>65.27</v>
       </c>
       <c r="R40" s="96" t="n">
         <v>65.27</v>
       </c>
       <c r="S40" s="96" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="T40" s="96" t="n">
         <v>73.09</v>
       </c>
-      <c r="T40" s="96" t="n">
+      <c r="U40" s="96" t="n">
         <v>56.22</v>
       </c>
-      <c r="U40" s="96" t="n">
+      <c r="V40" s="96" t="n">
         <v>54.96</v>
       </c>
-      <c r="V40" s="96" t="n">
+      <c r="W40" s="96" t="n">
         <v>47.85</v>
       </c>
-      <c r="W40" s="96" t="n">
+      <c r="X40" s="96" t="n">
         <v>49.61</v>
       </c>
-      <c r="X40" s="96" t="n">
+      <c r="Y40" s="96" t="n">
         <v>44.51</v>
       </c>
-      <c r="Y40" s="96" t="n">
+      <c r="Z40" s="96" t="n">
         <v>47.71</v>
       </c>
-      <c r="Z40" s="96" t="n">
+      <c r="AA40" s="96" t="n">
         <v>66.59999999999999</v>
-      </c>
-      <c r="AA40" s="96" t="n">
-        <v>52.29</v>
       </c>
       <c r="AB40" s="96" t="n">
         <v>52.29</v>
@@ -10753,10 +10734,10 @@
         <v>52.29</v>
       </c>
       <c r="AD40" s="96" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AE40" s="96" t="n">
         <v>53.45</v>
-      </c>
-      <c r="AE40" s="96" t="n">
-        <v>56.96</v>
       </c>
     </row>
     <row r="41">
@@ -10766,82 +10747,82 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>50.4</v>
+        <v>58.09</v>
       </c>
       <c r="C41" s="96" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="D41" s="96" t="n">
         <v>51.31</v>
       </c>
-      <c r="D41" s="96" t="n">
+      <c r="E41" s="96" t="n">
         <v>47.14</v>
       </c>
-      <c r="E41" s="96" t="n">
+      <c r="F41" s="96" t="n">
         <v>53.8</v>
       </c>
-      <c r="F41" s="96" t="n">
+      <c r="G41" s="96" t="n">
         <v>55.52</v>
       </c>
-      <c r="G41" s="96" t="n">
+      <c r="H41" s="96" t="n">
         <v>48.02</v>
       </c>
-      <c r="H41" s="96" t="n">
+      <c r="I41" s="96" t="n">
         <v>38.89</v>
       </c>
-      <c r="I41" s="96" t="n">
+      <c r="J41" s="96" t="n">
         <v>47.48</v>
       </c>
-      <c r="J41" s="96" t="n">
+      <c r="K41" s="96" t="n">
         <v>53.74</v>
       </c>
-      <c r="K41" s="96" t="n">
+      <c r="L41" s="96" t="n">
         <v>54.7</v>
       </c>
-      <c r="L41" s="96" t="n">
+      <c r="M41" s="96" t="n">
         <v>50.21</v>
       </c>
-      <c r="M41" s="96" t="n">
+      <c r="N41" s="96" t="n">
         <v>59.68</v>
       </c>
-      <c r="N41" s="96" t="n">
+      <c r="O41" s="96" t="n">
         <v>50.93</v>
       </c>
-      <c r="O41" s="96" t="n">
+      <c r="P41" s="96" t="n">
         <v>58.6</v>
       </c>
-      <c r="P41" s="96" t="n">
+      <c r="Q41" s="96" t="n">
         <v>61.68</v>
-      </c>
-      <c r="Q41" s="96" t="n">
-        <v>57.08</v>
       </c>
       <c r="R41" s="96" t="n">
         <v>57.08</v>
       </c>
       <c r="S41" s="96" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="T41" s="96" t="n">
         <v>60.1</v>
       </c>
-      <c r="T41" s="96" t="n">
+      <c r="U41" s="96" t="n">
         <v>50.78</v>
       </c>
-      <c r="U41" s="96" t="n">
+      <c r="V41" s="96" t="n">
         <v>50.21</v>
       </c>
-      <c r="V41" s="96" t="n">
+      <c r="W41" s="96" t="n">
         <v>46.93</v>
       </c>
-      <c r="W41" s="96" t="n">
+      <c r="X41" s="96" t="n">
         <v>47.72</v>
       </c>
-      <c r="X41" s="96" t="n">
+      <c r="Y41" s="96" t="n">
         <v>45.18</v>
       </c>
-      <c r="Y41" s="96" t="n">
+      <c r="Z41" s="96" t="n">
         <v>46.85</v>
       </c>
-      <c r="Z41" s="96" t="n">
+      <c r="AA41" s="96" t="n">
         <v>55.94</v>
-      </c>
-      <c r="AA41" s="96" t="n">
-        <v>47.34</v>
       </c>
       <c r="AB41" s="96" t="n">
         <v>47.34</v>
@@ -10850,10 +10831,10 @@
         <v>47.34</v>
       </c>
       <c r="AD41" s="96" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="AE41" s="96" t="n">
         <v>47.87</v>
-      </c>
-      <c r="AE41" s="96" t="n">
-        <v>49.57</v>
       </c>
     </row>
     <row r="42">
@@ -10867,143 +10848,145 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="C42" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D42" s="95" t="inlineStr">
+      <c r="E42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E42" s="95" t="inlineStr">
+      <c r="F42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="95" t="inlineStr">
+      <c r="G42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="94" t="inlineStr">
+      <c r="H42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="I42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="J42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J42" s="95" t="inlineStr">
+      <c r="K42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="93" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="93" t="inlineStr">
+      <c r="M42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N42" s="93" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="93" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="95" t="inlineStr">
+      <c r="Q42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="95" t="inlineStr">
+      <c r="R42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="95" t="inlineStr">
+      <c r="S42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="95" t="inlineStr">
+      <c r="T42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="95" t="inlineStr">
+      <c r="U42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U42" s="93" t="inlineStr">
+      <c r="V42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="93" t="inlineStr">
+      <c r="W42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="93" t="inlineStr">
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="95" t="inlineStr">
+      <c r="Y42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y42" s="95" t="inlineStr">
+      <c r="Z42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z42" s="95" t="inlineStr">
+      <c r="AA42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA42" s="95" t="inlineStr">
+      <c r="AB42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB42" s="95" t="inlineStr">
+      <c r="AC42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC42" s="95" t="inlineStr">
+      <c r="AD42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
-      </c>
-      <c r="AD42" s="93" t="n">
-        <v/>
       </c>
       <c r="AE42" s="93" t="n">
         <v/>
@@ -11016,91 +10999,91 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C43" s="96" t="n">
         <v>4.22</v>
       </c>
-      <c r="C43" s="96" t="n">
+      <c r="D43" s="96" t="n">
         <v>2.9</v>
       </c>
-      <c r="D43" s="96" t="n">
+      <c r="E43" s="96" t="n">
         <v>1.25</v>
       </c>
-      <c r="E43" s="96" t="n">
+      <c r="F43" s="96" t="n">
         <v>1.65</v>
       </c>
-      <c r="F43" s="96" t="n">
+      <c r="G43" s="96" t="n">
         <v>0.79</v>
       </c>
-      <c r="G43" s="96" t="n">
+      <c r="H43" s="96" t="n">
         <v>0.02</v>
       </c>
-      <c r="H43" s="96" t="n">
+      <c r="I43" s="96" t="n">
         <v>0.64</v>
       </c>
-      <c r="I43" s="96" t="n">
+      <c r="J43" s="96" t="n">
         <v>1.59</v>
       </c>
-      <c r="J43" s="96" t="n">
+      <c r="K43" s="96" t="n">
         <v>2.17</v>
       </c>
-      <c r="K43" s="96" t="n">
+      <c r="L43" s="96" t="n">
         <v>2.44</v>
       </c>
-      <c r="L43" s="96" t="n">
+      <c r="M43" s="96" t="n">
         <v>3.08</v>
       </c>
-      <c r="M43" s="96" t="n">
+      <c r="N43" s="96" t="n">
         <v>5.7</v>
       </c>
-      <c r="N43" s="96" t="n">
+      <c r="O43" s="96" t="n">
         <v>3.23</v>
       </c>
-      <c r="O43" s="96" t="n">
+      <c r="P43" s="96" t="n">
         <v>3.83</v>
       </c>
-      <c r="P43" s="96" t="n">
+      <c r="Q43" s="96" t="n">
         <v>3.86</v>
-      </c>
-      <c r="Q43" s="96" t="n">
-        <v>3.93</v>
       </c>
       <c r="R43" s="96" t="n">
         <v>3.93</v>
       </c>
       <c r="S43" s="96" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="T43" s="96" t="n">
         <v>4.88</v>
       </c>
-      <c r="T43" s="96" t="n">
+      <c r="U43" s="96" t="n">
         <v>4.32</v>
       </c>
-      <c r="U43" s="96" t="n">
+      <c r="V43" s="96" t="n">
         <v>3.73</v>
       </c>
-      <c r="V43" s="96" t="n">
+      <c r="W43" s="96" t="n">
         <v>4.35</v>
       </c>
-      <c r="W43" s="96" t="n">
+      <c r="X43" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="X43" s="96" t="n">
+      <c r="Y43" s="96" t="n">
         <v>6.49</v>
       </c>
-      <c r="Y43" s="96" t="n">
+      <c r="Z43" s="96" t="n">
         <v>6.6</v>
       </c>
-      <c r="Z43" s="96" t="n">
+      <c r="AA43" s="96" t="n">
         <v>7.24</v>
       </c>
-      <c r="AA43" s="96" t="n">
+      <c r="AB43" s="96" t="n">
         <v>5.25</v>
       </c>
-      <c r="AB43" s="96" t="n">
+      <c r="AC43" s="96" t="n">
         <v>3.86</v>
       </c>
-      <c r="AC43" s="96" t="n">
+      <c r="AD43" s="96" t="n">
         <v>3.46</v>
-      </c>
-      <c r="AD43" s="96" t="n">
-        <v/>
       </c>
       <c r="AE43" s="96" t="n">
         <v/>
@@ -11113,91 +11096,91 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="C44" s="96" t="n">
         <v>14.51</v>
       </c>
-      <c r="C44" s="96" t="n">
+      <c r="D44" s="96" t="n">
         <v>14.45</v>
       </c>
-      <c r="D44" s="96" t="n">
+      <c r="E44" s="96" t="n">
         <v>14.02</v>
       </c>
-      <c r="E44" s="96" t="n">
+      <c r="F44" s="96" t="n">
         <v>15.01</v>
       </c>
-      <c r="F44" s="96" t="n">
+      <c r="G44" s="96" t="n">
         <v>14.24</v>
       </c>
-      <c r="G44" s="96" t="n">
+      <c r="H44" s="96" t="n">
         <v>14.48</v>
       </c>
-      <c r="H44" s="96" t="n">
+      <c r="I44" s="96" t="n">
         <v>15.74</v>
       </c>
-      <c r="I44" s="96" t="n">
+      <c r="J44" s="96" t="n">
         <v>15.4</v>
       </c>
-      <c r="J44" s="96" t="n">
+      <c r="K44" s="96" t="n">
         <v>17.01</v>
       </c>
-      <c r="K44" s="96" t="n">
+      <c r="L44" s="96" t="n">
         <v>16.51</v>
       </c>
-      <c r="L44" s="96" t="n">
+      <c r="M44" s="96" t="n">
         <v>15.18</v>
       </c>
-      <c r="M44" s="96" t="n">
+      <c r="N44" s="96" t="n">
         <v>17.69</v>
       </c>
-      <c r="N44" s="96" t="n">
+      <c r="O44" s="96" t="n">
         <v>13.74</v>
       </c>
-      <c r="O44" s="96" t="n">
+      <c r="P44" s="96" t="n">
         <v>15.01</v>
       </c>
-      <c r="P44" s="96" t="n">
+      <c r="Q44" s="96" t="n">
         <v>15.76</v>
-      </c>
-      <c r="Q44" s="96" t="n">
-        <v>15.61</v>
       </c>
       <c r="R44" s="96" t="n">
         <v>15.61</v>
       </c>
       <c r="S44" s="96" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="T44" s="96" t="n">
         <v>12.73</v>
       </c>
-      <c r="T44" s="96" t="n">
+      <c r="U44" s="96" t="n">
         <v>11.75</v>
       </c>
-      <c r="U44" s="96" t="n">
+      <c r="V44" s="96" t="n">
         <v>12.03</v>
       </c>
-      <c r="V44" s="96" t="n">
+      <c r="W44" s="96" t="n">
         <v>12.74</v>
       </c>
-      <c r="W44" s="96" t="n">
+      <c r="X44" s="96" t="n">
         <v>12.98</v>
       </c>
-      <c r="X44" s="96" t="n">
+      <c r="Y44" s="96" t="n">
         <v>12.1</v>
       </c>
-      <c r="Y44" s="96" t="n">
+      <c r="Z44" s="96" t="n">
         <v>12.31</v>
       </c>
-      <c r="Z44" s="96" t="n">
+      <c r="AA44" s="96" t="n">
         <v>15.58</v>
       </c>
-      <c r="AA44" s="96" t="n">
+      <c r="AB44" s="96" t="n">
         <v>13.94</v>
       </c>
-      <c r="AB44" s="96" t="n">
+      <c r="AC44" s="96" t="n">
         <v>13.4</v>
       </c>
-      <c r="AC44" s="96" t="n">
+      <c r="AD44" s="96" t="n">
         <v>13.1</v>
-      </c>
-      <c r="AD44" s="96" t="n">
-        <v/>
       </c>
       <c r="AE44" s="96" t="n">
         <v/>
@@ -11210,91 +11193,91 @@
         </is>
       </c>
       <c r="B45" s="96" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="C45" s="96" t="n">
         <v>79.09</v>
       </c>
-      <c r="C45" s="96" t="n">
+      <c r="D45" s="96" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="D45" s="96" t="n">
+      <c r="E45" s="96" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="E45" s="96" t="n">
+      <c r="F45" s="96" t="n">
         <v>72.56999999999999</v>
       </c>
-      <c r="F45" s="96" t="n">
+      <c r="G45" s="96" t="n">
         <v>68.26000000000001</v>
       </c>
-      <c r="G45" s="96" t="n">
+      <c r="H45" s="96" t="n">
         <v>30.48</v>
       </c>
-      <c r="H45" s="96" t="n">
+      <c r="I45" s="96" t="n">
         <v>38.08</v>
       </c>
-      <c r="I45" s="96" t="n">
+      <c r="J45" s="96" t="n">
         <v>49.36</v>
       </c>
-      <c r="J45" s="96" t="n">
+      <c r="K45" s="96" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="K45" s="96" t="n">
+      <c r="L45" s="96" t="n">
         <v>47.48</v>
       </c>
-      <c r="L45" s="96" t="n">
+      <c r="M45" s="96" t="n">
         <v>35.25</v>
       </c>
-      <c r="M45" s="96" t="n">
+      <c r="N45" s="96" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="N45" s="96" t="n">
+      <c r="O45" s="96" t="n">
         <v>42.72</v>
       </c>
-      <c r="O45" s="96" t="n">
+      <c r="P45" s="96" t="n">
         <v>91.28</v>
       </c>
-      <c r="P45" s="96" t="n">
+      <c r="Q45" s="96" t="n">
         <v>94.36</v>
-      </c>
-      <c r="Q45" s="96" t="n">
-        <v>92.69</v>
       </c>
       <c r="R45" s="96" t="n">
         <v>92.69</v>
       </c>
       <c r="S45" s="96" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="T45" s="96" t="n">
         <v>90.95999999999999</v>
       </c>
-      <c r="T45" s="96" t="n">
+      <c r="U45" s="96" t="n">
         <v>81.06</v>
       </c>
-      <c r="U45" s="96" t="n">
+      <c r="V45" s="96" t="n">
         <v>56.52</v>
       </c>
-      <c r="V45" s="96" t="n">
+      <c r="W45" s="96" t="n">
         <v>42.72</v>
       </c>
-      <c r="W45" s="96" t="n">
+      <c r="X45" s="96" t="n">
         <v>61.79</v>
       </c>
-      <c r="X45" s="96" t="n">
+      <c r="Y45" s="96" t="n">
         <v>83.42</v>
       </c>
-      <c r="Y45" s="96" t="n">
+      <c r="Z45" s="96" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="Z45" s="96" t="n">
+      <c r="AA45" s="96" t="n">
         <v>92.92</v>
       </c>
-      <c r="AA45" s="96" t="n">
+      <c r="AB45" s="96" t="n">
         <v>90.84999999999999</v>
       </c>
-      <c r="AB45" s="96" t="n">
+      <c r="AC45" s="96" t="n">
         <v>78.79000000000001</v>
       </c>
-      <c r="AC45" s="96" t="n">
+      <c r="AD45" s="96" t="n">
         <v>73.5</v>
-      </c>
-      <c r="AD45" s="96" t="n">
-        <v/>
       </c>
       <c r="AE45" s="96" t="n">
         <v/>
@@ -11307,91 +11290,91 @@
         </is>
       </c>
       <c r="B46" s="96" t="n">
+        <v>72.91</v>
+      </c>
+      <c r="C46" s="96" t="n">
         <v>69.2</v>
       </c>
-      <c r="C46" s="96" t="n">
+      <c r="D46" s="96" t="n">
         <v>64.08</v>
       </c>
-      <c r="D46" s="96" t="n">
+      <c r="E46" s="96" t="n">
         <v>65.8</v>
       </c>
-      <c r="E46" s="96" t="n">
+      <c r="F46" s="96" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="F46" s="96" t="n">
+      <c r="G46" s="96" t="n">
         <v>62.04</v>
       </c>
-      <c r="G46" s="96" t="n">
+      <c r="H46" s="96" t="n">
         <v>41.33</v>
       </c>
-      <c r="H46" s="96" t="n">
+      <c r="I46" s="96" t="n">
         <v>46.43</v>
       </c>
-      <c r="I46" s="96" t="n">
+      <c r="J46" s="96" t="n">
         <v>53.71</v>
       </c>
-      <c r="J46" s="96" t="n">
+      <c r="K46" s="96" t="n">
         <v>65.55</v>
       </c>
-      <c r="K46" s="96" t="n">
+      <c r="L46" s="96" t="n">
         <v>52.65</v>
       </c>
-      <c r="L46" s="96" t="n">
+      <c r="M46" s="96" t="n">
         <v>46.03</v>
       </c>
-      <c r="M46" s="96" t="n">
+      <c r="N46" s="96" t="n">
         <v>73.20999999999999</v>
       </c>
-      <c r="N46" s="96" t="n">
+      <c r="O46" s="96" t="n">
         <v>58.84</v>
       </c>
-      <c r="O46" s="96" t="n">
+      <c r="P46" s="96" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="P46" s="96" t="n">
+      <c r="Q46" s="96" t="n">
         <v>86.75</v>
-      </c>
-      <c r="Q46" s="96" t="n">
-        <v>84.8</v>
       </c>
       <c r="R46" s="96" t="n">
         <v>84.8</v>
       </c>
       <c r="S46" s="96" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="T46" s="96" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="T46" s="96" t="n">
+      <c r="U46" s="96" t="n">
         <v>73.92</v>
       </c>
-      <c r="U46" s="96" t="n">
+      <c r="V46" s="96" t="n">
         <v>61.58</v>
       </c>
-      <c r="V46" s="96" t="n">
+      <c r="W46" s="96" t="n">
         <v>57.04</v>
       </c>
-      <c r="W46" s="96" t="n">
+      <c r="X46" s="96" t="n">
         <v>66.16</v>
       </c>
-      <c r="X46" s="96" t="n">
+      <c r="Y46" s="96" t="n">
         <v>74.45999999999999</v>
       </c>
-      <c r="Y46" s="96" t="n">
+      <c r="Z46" s="96" t="n">
         <v>78.08</v>
       </c>
-      <c r="Z46" s="96" t="n">
+      <c r="AA46" s="96" t="n">
         <v>77.18000000000001</v>
       </c>
-      <c r="AA46" s="96" t="n">
+      <c r="AB46" s="96" t="n">
         <v>73.91</v>
       </c>
-      <c r="AB46" s="96" t="n">
+      <c r="AC46" s="96" t="n">
         <v>60.8</v>
       </c>
-      <c r="AC46" s="96" t="n">
+      <c r="AD46" s="96" t="n">
         <v>56.86</v>
-      </c>
-      <c r="AD46" s="96" t="n">
-        <v/>
       </c>
       <c r="AE46" s="96" t="n">
         <v/>
@@ -11418,140 +11401,138 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E47" s="94" t="inlineStr">
+      <c r="E47" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F47" s="95" t="inlineStr">
+      <c r="G47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G47" s="94" t="inlineStr">
+      <c r="H47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H47" s="94" t="inlineStr">
+      <c r="I47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I47" s="93" t="inlineStr">
+      <c r="J47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J47" s="93" t="inlineStr">
+      <c r="K47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K47" s="95" t="inlineStr">
+      <c r="L47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L47" s="95" t="inlineStr">
+      <c r="M47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M47" s="95" t="inlineStr">
+      <c r="N47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="95" t="inlineStr">
+      <c r="O47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="95" t="inlineStr">
+      <c r="P47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P47" s="95" t="inlineStr">
+      <c r="Q47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q47" s="95" t="inlineStr">
+      <c r="R47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R47" s="95" t="inlineStr">
+      <c r="S47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S47" s="95" t="inlineStr">
+      <c r="T47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T47" s="93" t="inlineStr">
+      <c r="U47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U47" s="93" t="inlineStr">
+      <c r="V47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V47" s="94" t="inlineStr">
+      <c r="W47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W47" s="94" t="inlineStr">
+      <c r="X47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X47" s="94" t="inlineStr">
+      <c r="Y47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y47" s="94" t="inlineStr">
+      <c r="Z47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z47" s="94" t="inlineStr">
+      <c r="AA47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA47" s="94" t="inlineStr">
+      <c r="AB47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB47" s="94" t="inlineStr">
+      <c r="AC47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC47" s="95" t="inlineStr">
+      <c r="AD47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD47" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE47" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
+      <c r="AE47" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -11561,94 +11542,94 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C48" s="96" t="n">
         <v>3.47</v>
       </c>
-      <c r="C48" s="96" t="n">
+      <c r="D48" s="96" t="n">
         <v>1.33</v>
       </c>
-      <c r="D48" s="96" t="n">
+      <c r="E48" s="96" t="n">
         <v>0.96</v>
       </c>
-      <c r="E48" s="96" t="n">
+      <c r="F48" s="96" t="n">
         <v>-2.43</v>
       </c>
-      <c r="F48" s="96" t="n">
+      <c r="G48" s="96" t="n">
         <v>3.61</v>
       </c>
-      <c r="G48" s="96" t="n">
+      <c r="H48" s="96" t="n">
         <v>0.29</v>
       </c>
-      <c r="H48" s="96" t="n">
+      <c r="I48" s="96" t="n">
         <v>1.91</v>
       </c>
-      <c r="I48" s="96" t="n">
+      <c r="J48" s="96" t="n">
         <v>3.04</v>
       </c>
-      <c r="J48" s="96" t="n">
+      <c r="K48" s="96" t="n">
         <v>2.84</v>
       </c>
-      <c r="K48" s="96" t="n">
+      <c r="L48" s="96" t="n">
         <v>3.57</v>
       </c>
-      <c r="L48" s="96" t="n">
+      <c r="M48" s="96" t="n">
         <v>3.1</v>
       </c>
-      <c r="M48" s="96" t="n">
+      <c r="N48" s="96" t="n">
         <v>3.09</v>
       </c>
-      <c r="N48" s="96" t="n">
+      <c r="O48" s="96" t="n">
         <v>2.2</v>
       </c>
-      <c r="O48" s="96" t="n">
+      <c r="P48" s="96" t="n">
         <v>1.23</v>
-      </c>
-      <c r="P48" s="96" t="n">
-        <v>1.78</v>
       </c>
       <c r="Q48" s="96" t="n">
         <v>1.78</v>
       </c>
       <c r="R48" s="96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S48" s="96" t="n">
         <v>2.06</v>
       </c>
-      <c r="S48" s="96" t="n">
+      <c r="T48" s="96" t="n">
         <v>2.24</v>
       </c>
-      <c r="T48" s="96" t="n">
+      <c r="U48" s="96" t="n">
         <v>1.62</v>
       </c>
-      <c r="U48" s="96" t="n">
+      <c r="V48" s="96" t="n">
         <v>2.17</v>
       </c>
-      <c r="V48" s="96" t="n">
+      <c r="W48" s="96" t="n">
         <v>2.4</v>
       </c>
-      <c r="W48" s="96" t="n">
+      <c r="X48" s="96" t="n">
         <v>1.49</v>
       </c>
-      <c r="X48" s="96" t="n">
+      <c r="Y48" s="96" t="n">
         <v>1.37</v>
       </c>
-      <c r="Y48" s="96" t="n">
+      <c r="Z48" s="96" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z48" s="96" t="n">
+      <c r="AA48" s="96" t="n">
         <v>1.84</v>
       </c>
-      <c r="AA48" s="96" t="n">
+      <c r="AB48" s="96" t="n">
         <v>3.02</v>
       </c>
-      <c r="AB48" s="96" t="n">
+      <c r="AC48" s="96" t="n">
         <v>2.49</v>
       </c>
-      <c r="AC48" s="96" t="n">
+      <c r="AD48" s="96" t="n">
         <v>4.14</v>
       </c>
-      <c r="AD48" s="96" t="n">
-        <v>3.81</v>
-      </c>
       <c r="AE48" s="96" t="n">
-        <v>3.81</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -11658,94 +11639,94 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="C49" s="96" t="n">
         <v>10.22</v>
       </c>
-      <c r="C49" s="96" t="n">
+      <c r="D49" s="96" t="n">
         <v>7.94</v>
       </c>
-      <c r="D49" s="96" t="n">
+      <c r="E49" s="96" t="n">
         <v>6.37</v>
       </c>
-      <c r="E49" s="96" t="n">
+      <c r="F49" s="96" t="n">
         <v>3.23</v>
       </c>
-      <c r="F49" s="96" t="n">
+      <c r="G49" s="96" t="n">
         <v>9.99</v>
       </c>
-      <c r="G49" s="96" t="n">
+      <c r="H49" s="96" t="n">
         <v>6.18</v>
       </c>
-      <c r="H49" s="96" t="n">
+      <c r="I49" s="96" t="n">
         <v>6.62</v>
       </c>
-      <c r="I49" s="96" t="n">
+      <c r="J49" s="96" t="n">
         <v>8.19</v>
       </c>
-      <c r="J49" s="96" t="n">
+      <c r="K49" s="96" t="n">
         <v>11.39</v>
       </c>
-      <c r="K49" s="96" t="n">
+      <c r="L49" s="96" t="n">
         <v>12.54</v>
       </c>
-      <c r="L49" s="96" t="n">
+      <c r="M49" s="96" t="n">
         <v>12.72</v>
       </c>
-      <c r="M49" s="96" t="n">
+      <c r="N49" s="96" t="n">
         <v>13.97</v>
       </c>
-      <c r="N49" s="96" t="n">
+      <c r="O49" s="96" t="n">
         <v>12.51</v>
       </c>
-      <c r="O49" s="96" t="n">
+      <c r="P49" s="96" t="n">
         <v>12.02</v>
-      </c>
-      <c r="P49" s="96" t="n">
-        <v>12.09</v>
       </c>
       <c r="Q49" s="96" t="n">
         <v>12.09</v>
       </c>
       <c r="R49" s="96" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="S49" s="96" t="n">
         <v>12.11</v>
       </c>
-      <c r="S49" s="96" t="n">
+      <c r="T49" s="96" t="n">
         <v>12.2</v>
       </c>
-      <c r="T49" s="96" t="n">
+      <c r="U49" s="96" t="n">
         <v>10.93</v>
       </c>
-      <c r="U49" s="96" t="n">
+      <c r="V49" s="96" t="n">
         <v>10.79</v>
       </c>
-      <c r="V49" s="96" t="n">
+      <c r="W49" s="96" t="n">
         <v>10.81</v>
       </c>
-      <c r="W49" s="96" t="n">
+      <c r="X49" s="96" t="n">
         <v>11.91</v>
       </c>
-      <c r="X49" s="96" t="n">
+      <c r="Y49" s="96" t="n">
         <v>10.95</v>
       </c>
-      <c r="Y49" s="96" t="n">
+      <c r="Z49" s="96" t="n">
         <v>13.19</v>
       </c>
-      <c r="Z49" s="96" t="n">
+      <c r="AA49" s="96" t="n">
         <v>13.39</v>
       </c>
-      <c r="AA49" s="96" t="n">
+      <c r="AB49" s="96" t="n">
         <v>13.73</v>
       </c>
-      <c r="AB49" s="96" t="n">
+      <c r="AC49" s="96" t="n">
         <v>13.76</v>
       </c>
-      <c r="AC49" s="96" t="n">
+      <c r="AD49" s="96" t="n">
         <v>14.86</v>
       </c>
-      <c r="AD49" s="96" t="n">
-        <v>15.72</v>
-      </c>
       <c r="AE49" s="96" t="n">
-        <v>15.72</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -11755,94 +11736,94 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="C50" s="96" t="n">
         <v>62.63</v>
       </c>
-      <c r="C50" s="96" t="n">
+      <c r="D50" s="96" t="n">
         <v>54.57</v>
       </c>
-      <c r="D50" s="96" t="n">
+      <c r="E50" s="96" t="n">
         <v>50.68</v>
       </c>
-      <c r="E50" s="96" t="n">
+      <c r="F50" s="96" t="n">
         <v>34.71</v>
       </c>
-      <c r="F50" s="96" t="n">
+      <c r="G50" s="96" t="n">
         <v>73.68000000000001</v>
       </c>
-      <c r="G50" s="96" t="n">
+      <c r="H50" s="96" t="n">
         <v>41.54</v>
       </c>
-      <c r="H50" s="96" t="n">
+      <c r="I50" s="96" t="n">
         <v>39.63</v>
       </c>
-      <c r="I50" s="96" t="n">
+      <c r="J50" s="96" t="n">
         <v>51.34</v>
       </c>
-      <c r="J50" s="96" t="n">
+      <c r="K50" s="96" t="n">
         <v>70.72</v>
       </c>
-      <c r="K50" s="96" t="n">
+      <c r="L50" s="96" t="n">
         <v>79.16</v>
       </c>
-      <c r="L50" s="96" t="n">
+      <c r="M50" s="96" t="n">
         <v>79.89</v>
       </c>
-      <c r="M50" s="96" t="n">
+      <c r="N50" s="96" t="n">
         <v>80.14</v>
       </c>
-      <c r="N50" s="96" t="n">
+      <c r="O50" s="96" t="n">
         <v>66.11</v>
       </c>
-      <c r="O50" s="96" t="n">
+      <c r="P50" s="96" t="n">
         <v>60.8</v>
-      </c>
-      <c r="P50" s="96" t="n">
-        <v>62.45</v>
       </c>
       <c r="Q50" s="96" t="n">
         <v>62.45</v>
       </c>
       <c r="R50" s="96" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="S50" s="96" t="n">
         <v>60.92</v>
       </c>
-      <c r="S50" s="96" t="n">
+      <c r="T50" s="96" t="n">
         <v>56.59</v>
       </c>
-      <c r="T50" s="96" t="n">
+      <c r="U50" s="96" t="n">
         <v>41.82</v>
       </c>
-      <c r="U50" s="96" t="n">
+      <c r="V50" s="96" t="n">
         <v>44.06</v>
       </c>
-      <c r="V50" s="96" t="n">
+      <c r="W50" s="96" t="n">
         <v>35.86</v>
       </c>
-      <c r="W50" s="96" t="n">
+      <c r="X50" s="96" t="n">
         <v>33</v>
       </c>
-      <c r="X50" s="96" t="n">
+      <c r="Y50" s="96" t="n">
         <v>26.45</v>
       </c>
-      <c r="Y50" s="96" t="n">
+      <c r="Z50" s="96" t="n">
         <v>40.2</v>
       </c>
-      <c r="Z50" s="96" t="n">
+      <c r="AA50" s="96" t="n">
         <v>40.98</v>
       </c>
-      <c r="AA50" s="96" t="n">
+      <c r="AB50" s="96" t="n">
         <v>47.69</v>
       </c>
-      <c r="AB50" s="96" t="n">
+      <c r="AC50" s="96" t="n">
         <v>47.35</v>
       </c>
-      <c r="AC50" s="96" t="n">
+      <c r="AD50" s="96" t="n">
         <v>61.59</v>
       </c>
-      <c r="AD50" s="96" t="n">
-        <v>59.77</v>
-      </c>
       <c r="AE50" s="96" t="n">
-        <v>59.77</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -11852,94 +11833,94 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="C51" s="96" t="n">
         <v>59.02</v>
       </c>
-      <c r="C51" s="96" t="n">
+      <c r="D51" s="96" t="n">
         <v>53.85</v>
       </c>
-      <c r="D51" s="96" t="n">
+      <c r="E51" s="96" t="n">
         <v>51.37</v>
       </c>
-      <c r="E51" s="96" t="n">
+      <c r="F51" s="96" t="n">
         <v>41.57</v>
       </c>
-      <c r="F51" s="96" t="n">
+      <c r="G51" s="96" t="n">
         <v>65.12</v>
       </c>
-      <c r="G51" s="96" t="n">
+      <c r="H51" s="96" t="n">
         <v>49.84</v>
       </c>
-      <c r="H51" s="96" t="n">
+      <c r="I51" s="96" t="n">
         <v>49.21</v>
       </c>
-      <c r="I51" s="96" t="n">
+      <c r="J51" s="96" t="n">
         <v>54.48</v>
       </c>
-      <c r="J51" s="96" t="n">
+      <c r="K51" s="96" t="n">
         <v>61.14</v>
       </c>
-      <c r="K51" s="96" t="n">
+      <c r="L51" s="96" t="n">
         <v>63.56</v>
       </c>
-      <c r="L51" s="96" t="n">
+      <c r="M51" s="96" t="n">
         <v>63.77</v>
       </c>
-      <c r="M51" s="96" t="n">
+      <c r="N51" s="96" t="n">
         <v>63.85</v>
       </c>
-      <c r="N51" s="96" t="n">
+      <c r="O51" s="96" t="n">
         <v>55.93</v>
       </c>
-      <c r="O51" s="96" t="n">
+      <c r="P51" s="96" t="n">
         <v>53.8</v>
-      </c>
-      <c r="P51" s="96" t="n">
-        <v>54.28</v>
       </c>
       <c r="Q51" s="96" t="n">
         <v>54.28</v>
       </c>
       <c r="R51" s="96" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="S51" s="96" t="n">
         <v>53.62</v>
       </c>
-      <c r="S51" s="96" t="n">
+      <c r="T51" s="96" t="n">
         <v>51.73</v>
       </c>
-      <c r="T51" s="96" t="n">
+      <c r="U51" s="96" t="n">
         <v>46.24</v>
       </c>
-      <c r="U51" s="96" t="n">
+      <c r="V51" s="96" t="n">
         <v>47.12</v>
       </c>
-      <c r="V51" s="96" t="n">
+      <c r="W51" s="96" t="n">
         <v>44.34</v>
       </c>
-      <c r="W51" s="96" t="n">
+      <c r="X51" s="96" t="n">
         <v>43.39</v>
       </c>
-      <c r="X51" s="96" t="n">
+      <c r="Y51" s="96" t="n">
         <v>41.19</v>
       </c>
-      <c r="Y51" s="96" t="n">
+      <c r="Z51" s="96" t="n">
         <v>48.43</v>
       </c>
-      <c r="Z51" s="96" t="n">
+      <c r="AA51" s="96" t="n">
         <v>48.77</v>
       </c>
-      <c r="AA51" s="96" t="n">
+      <c r="AB51" s="96" t="n">
         <v>51.7</v>
       </c>
-      <c r="AB51" s="96" t="n">
+      <c r="AC51" s="96" t="n">
         <v>51.58</v>
       </c>
-      <c r="AC51" s="96" t="n">
+      <c r="AD51" s="96" t="n">
         <v>57.42</v>
       </c>
-      <c r="AD51" s="96" t="n">
-        <v>56.61</v>
-      </c>
       <c r="AE51" s="96" t="n">
-        <v>56.61</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -11948,155 +11929,153 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="93" t="inlineStr">
+      <c r="B52" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C52" s="95" t="inlineStr">
+      <c r="D52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D52" s="93" t="inlineStr">
+      <c r="E52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E52" s="94" t="inlineStr">
+      <c r="F52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F52" s="93" t="inlineStr">
+      <c r="G52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G52" s="93" t="inlineStr">
+      <c r="H52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="94" t="inlineStr">
+      <c r="I52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I52" s="94" t="inlineStr">
+      <c r="J52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J52" s="94" t="inlineStr">
+      <c r="K52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K52" s="95" t="inlineStr">
+      <c r="L52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L52" s="94" t="inlineStr">
+      <c r="M52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M52" s="94" t="inlineStr">
+      <c r="N52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N52" s="94" t="inlineStr">
+      <c r="O52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O52" s="94" t="inlineStr">
+      <c r="P52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P52" s="93" t="inlineStr">
+      <c r="Q52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q52" s="93" t="inlineStr">
+      <c r="R52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R52" s="93" t="inlineStr">
+      <c r="S52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S52" s="93" t="inlineStr">
+      <c r="T52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T52" s="95" t="inlineStr">
+      <c r="U52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U52" s="95" t="inlineStr">
+      <c r="V52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V52" s="95" t="inlineStr">
+      <c r="W52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W52" s="95" t="inlineStr">
+      <c r="X52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X52" s="95" t="inlineStr">
+      <c r="Y52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y52" s="95" t="inlineStr">
+      <c r="Z52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z52" s="95" t="inlineStr">
+      <c r="AA52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA52" s="93" t="inlineStr">
+      <c r="AB52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB52" s="94" t="inlineStr">
+      <c r="AC52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC52" s="94" t="inlineStr">
+      <c r="AD52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD52" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE52" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE52" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -12106,94 +12085,94 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="C53" s="96" t="n">
         <v>-1.06</v>
       </c>
-      <c r="C53" s="96" t="n">
+      <c r="D53" s="96" t="n">
         <v>0.25</v>
       </c>
-      <c r="D53" s="96" t="n">
+      <c r="E53" s="96" t="n">
         <v>-0.27</v>
       </c>
-      <c r="E53" s="96" t="n">
+      <c r="F53" s="96" t="n">
         <v>-0.98</v>
       </c>
-      <c r="F53" s="96" t="n">
+      <c r="G53" s="96" t="n">
         <v>0.54</v>
       </c>
-      <c r="G53" s="96" t="n">
+      <c r="H53" s="96" t="n">
         <v>0.76</v>
       </c>
-      <c r="H53" s="96" t="n">
+      <c r="I53" s="96" t="n">
         <v>0.28</v>
       </c>
-      <c r="I53" s="96" t="n">
+      <c r="J53" s="96" t="n">
         <v>0.01</v>
       </c>
-      <c r="J53" s="96" t="n">
+      <c r="K53" s="96" t="n">
         <v>1.64</v>
       </c>
-      <c r="K53" s="96" t="n">
+      <c r="L53" s="96" t="n">
         <v>2.24</v>
       </c>
-      <c r="L53" s="96" t="n">
+      <c r="M53" s="96" t="n">
         <v>1.84</v>
       </c>
-      <c r="M53" s="96" t="n">
+      <c r="N53" s="96" t="n">
         <v>2.18</v>
       </c>
-      <c r="N53" s="96" t="n">
+      <c r="O53" s="96" t="n">
         <v>1.57</v>
       </c>
-      <c r="O53" s="96" t="n">
+      <c r="P53" s="96" t="n">
         <v>2.91</v>
       </c>
-      <c r="P53" s="96" t="n">
+      <c r="Q53" s="96" t="n">
         <v>4.91</v>
-      </c>
-      <c r="Q53" s="96" t="n">
-        <v>4.78</v>
       </c>
       <c r="R53" s="96" t="n">
         <v>4.78</v>
       </c>
       <c r="S53" s="96" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="T53" s="96" t="n">
         <v>5.41</v>
       </c>
-      <c r="T53" s="96" t="n">
+      <c r="U53" s="96" t="n">
         <v>6.07</v>
       </c>
-      <c r="U53" s="96" t="n">
+      <c r="V53" s="96" t="n">
         <v>6.23</v>
       </c>
-      <c r="V53" s="96" t="n">
+      <c r="W53" s="96" t="n">
         <v>6.93</v>
       </c>
-      <c r="W53" s="96" t="n">
+      <c r="X53" s="96" t="n">
         <v>7.79</v>
       </c>
-      <c r="X53" s="96" t="n">
+      <c r="Y53" s="96" t="n">
         <v>6.47</v>
       </c>
-      <c r="Y53" s="96" t="n">
+      <c r="Z53" s="96" t="n">
         <v>6.33</v>
       </c>
-      <c r="Z53" s="96" t="n">
+      <c r="AA53" s="96" t="n">
         <v>5.35</v>
       </c>
-      <c r="AA53" s="96" t="n">
+      <c r="AB53" s="96" t="n">
         <v>5.06</v>
       </c>
-      <c r="AB53" s="96" t="n">
+      <c r="AC53" s="96" t="n">
         <v>4.17</v>
       </c>
-      <c r="AC53" s="96" t="n">
+      <c r="AD53" s="96" t="n">
         <v>4.28</v>
       </c>
-      <c r="AD53" s="96" t="n">
-        <v>5.17</v>
-      </c>
       <c r="AE53" s="96" t="n">
-        <v>5.17</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -12203,191 +12182,191 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C54" s="96" t="n">
         <v>5.62</v>
       </c>
-      <c r="C54" s="96" t="n">
+      <c r="D54" s="96" t="n">
         <v>6.76</v>
       </c>
-      <c r="D54" s="96" t="n">
+      <c r="E54" s="96" t="n">
         <v>6.14</v>
       </c>
-      <c r="E54" s="96" t="n">
+      <c r="F54" s="96" t="n">
         <v>5.12</v>
       </c>
-      <c r="F54" s="96" t="n">
+      <c r="G54" s="96" t="n">
         <v>6.26</v>
       </c>
-      <c r="G54" s="96" t="n">
+      <c r="H54" s="96" t="n">
         <v>7.6</v>
       </c>
-      <c r="H54" s="96" t="n">
+      <c r="I54" s="96" t="n">
         <v>7.3</v>
       </c>
-      <c r="I54" s="96" t="n">
+      <c r="J54" s="96" t="n">
         <v>7.42</v>
       </c>
-      <c r="J54" s="96" t="n">
+      <c r="K54" s="96" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="K54" s="96" t="n">
+      <c r="L54" s="96" t="n">
         <v>10.7</v>
       </c>
-      <c r="L54" s="96" t="n">
+      <c r="M54" s="96" t="n">
         <v>10.73</v>
       </c>
-      <c r="M54" s="96" t="n">
+      <c r="N54" s="96" t="n">
         <v>11.49</v>
       </c>
-      <c r="N54" s="96" t="n">
+      <c r="O54" s="96" t="n">
         <v>11.61</v>
       </c>
-      <c r="O54" s="96" t="n">
+      <c r="P54" s="96" t="n">
         <v>12.06</v>
       </c>
-      <c r="P54" s="96" t="n">
+      <c r="Q54" s="96" t="n">
         <v>12.38</v>
-      </c>
-      <c r="Q54" s="96" t="n">
-        <v>12.22</v>
       </c>
       <c r="R54" s="96" t="n">
         <v>12.22</v>
       </c>
       <c r="S54" s="96" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="T54" s="96" t="n">
         <v>12.78</v>
       </c>
-      <c r="T54" s="96" t="n">
+      <c r="U54" s="96" t="n">
         <v>13.98</v>
       </c>
-      <c r="U54" s="96" t="n">
+      <c r="V54" s="96" t="n">
         <v>13.51</v>
       </c>
-      <c r="V54" s="96" t="n">
+      <c r="W54" s="96" t="n">
         <v>13.48</v>
       </c>
-      <c r="W54" s="96" t="n">
+      <c r="X54" s="96" t="n">
         <v>14.66</v>
       </c>
-      <c r="X54" s="96" t="n">
+      <c r="Y54" s="96" t="n">
         <v>13.57</v>
       </c>
-      <c r="Y54" s="96" t="n">
+      <c r="Z54" s="96" t="n">
         <v>13.16</v>
       </c>
-      <c r="Z54" s="96" t="n">
+      <c r="AA54" s="96" t="n">
         <v>13.95</v>
       </c>
-      <c r="AA54" s="96" t="n">
+      <c r="AB54" s="96" t="n">
         <v>13.51</v>
       </c>
-      <c r="AB54" s="96" t="n">
+      <c r="AC54" s="96" t="n">
         <v>11.86</v>
       </c>
-      <c r="AC54" s="96" t="n">
+      <c r="AD54" s="96" t="n">
         <v>12.52</v>
       </c>
-      <c r="AD54" s="96" t="n">
-        <v>14.3</v>
-      </c>
       <c r="AE54" s="96" t="n">
-        <v>14.3</v>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="78" t="inlineStr">
+      <c r="A55" s="98" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="96" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="C55" s="96" t="n">
         <v>47.54</v>
       </c>
-      <c r="C55" s="96" t="n">
+      <c r="D55" s="96" t="n">
         <v>67.86</v>
       </c>
-      <c r="D55" s="96" t="n">
+      <c r="E55" s="96" t="n">
         <v>57.18</v>
       </c>
-      <c r="E55" s="96" t="n">
+      <c r="F55" s="96" t="n">
         <v>21.68</v>
       </c>
-      <c r="F55" s="96" t="n">
+      <c r="G55" s="96" t="n">
         <v>42</v>
       </c>
-      <c r="G55" s="96" t="n">
+      <c r="H55" s="96" t="n">
         <v>38.72</v>
       </c>
-      <c r="H55" s="96" t="n">
+      <c r="I55" s="96" t="n">
         <v>31.52</v>
       </c>
-      <c r="I55" s="96" t="n">
+      <c r="J55" s="96" t="n">
         <v>10.24</v>
       </c>
-      <c r="J55" s="96" t="n">
+      <c r="K55" s="96" t="n">
         <v>24.68</v>
       </c>
-      <c r="K55" s="96" t="n">
+      <c r="L55" s="96" t="n">
         <v>57.67</v>
       </c>
-      <c r="L55" s="96" t="n">
+      <c r="M55" s="96" t="n">
         <v>23.36</v>
       </c>
-      <c r="M55" s="96" t="n">
+      <c r="N55" s="96" t="n">
         <v>26.13</v>
       </c>
-      <c r="N55" s="96" t="n">
+      <c r="O55" s="96" t="n">
         <v>17.02</v>
       </c>
-      <c r="O55" s="96" t="n">
+      <c r="P55" s="96" t="n">
         <v>28.23</v>
       </c>
-      <c r="P55" s="96" t="n">
+      <c r="Q55" s="96" t="n">
         <v>54.76</v>
-      </c>
-      <c r="Q55" s="96" t="n">
-        <v>32.74</v>
       </c>
       <c r="R55" s="96" t="n">
         <v>32.74</v>
       </c>
       <c r="S55" s="96" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="T55" s="96" t="n">
         <v>43.04</v>
       </c>
-      <c r="T55" s="96" t="n">
+      <c r="U55" s="96" t="n">
         <v>88.56999999999999</v>
       </c>
-      <c r="U55" s="96" t="n">
+      <c r="V55" s="96" t="n">
         <v>85.81</v>
       </c>
-      <c r="V55" s="96" t="n">
+      <c r="W55" s="96" t="n">
         <v>82.54000000000001</v>
       </c>
-      <c r="W55" s="96" t="n">
+      <c r="X55" s="96" t="n">
         <v>90.87</v>
       </c>
-      <c r="X55" s="96" t="n">
+      <c r="Y55" s="96" t="n">
         <v>88.38</v>
       </c>
-      <c r="Y55" s="96" t="n">
+      <c r="Z55" s="96" t="n">
         <v>82.76000000000001</v>
       </c>
-      <c r="Z55" s="96" t="n">
+      <c r="AA55" s="96" t="n">
         <v>74.68000000000001</v>
       </c>
-      <c r="AA55" s="96" t="n">
+      <c r="AB55" s="96" t="n">
         <v>54.51</v>
       </c>
-      <c r="AB55" s="96" t="n">
+      <c r="AC55" s="96" t="n">
         <v>38.32</v>
       </c>
-      <c r="AC55" s="96" t="n">
+      <c r="AD55" s="96" t="n">
         <v>16.58</v>
       </c>
-      <c r="AD55" s="96" t="n">
-        <v>26.94</v>
-      </c>
       <c r="AE55" s="96" t="n">
-        <v>26.94</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -12397,94 +12376,94 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="C56" s="96" t="n">
         <v>45.76</v>
       </c>
-      <c r="C56" s="96" t="n">
+      <c r="D56" s="96" t="n">
         <v>55.59</v>
       </c>
-      <c r="D56" s="96" t="n">
+      <c r="E56" s="96" t="n">
         <v>47.72</v>
       </c>
-      <c r="E56" s="96" t="n">
+      <c r="F56" s="96" t="n">
         <v>26.35</v>
       </c>
-      <c r="F56" s="96" t="n">
+      <c r="G56" s="96" t="n">
         <v>36.92</v>
       </c>
-      <c r="G56" s="96" t="n">
+      <c r="H56" s="96" t="n">
         <v>35.14</v>
       </c>
-      <c r="H56" s="96" t="n">
+      <c r="I56" s="96" t="n">
         <v>30.77</v>
       </c>
-      <c r="I56" s="96" t="n">
+      <c r="J56" s="96" t="n">
         <v>17.28</v>
       </c>
-      <c r="J56" s="96" t="n">
+      <c r="K56" s="96" t="n">
         <v>30.86</v>
       </c>
-      <c r="K56" s="96" t="n">
+      <c r="L56" s="96" t="n">
         <v>49.99</v>
       </c>
-      <c r="L56" s="96" t="n">
+      <c r="M56" s="96" t="n">
         <v>33.4</v>
       </c>
-      <c r="M56" s="96" t="n">
+      <c r="N56" s="96" t="n">
         <v>35.24</v>
       </c>
-      <c r="N56" s="96" t="n">
+      <c r="O56" s="96" t="n">
         <v>31.03</v>
       </c>
-      <c r="O56" s="96" t="n">
+      <c r="P56" s="96" t="n">
         <v>41.42</v>
       </c>
-      <c r="P56" s="96" t="n">
+      <c r="Q56" s="96" t="n">
         <v>58.82</v>
-      </c>
-      <c r="Q56" s="96" t="n">
-        <v>50.06</v>
       </c>
       <c r="R56" s="96" t="n">
         <v>50.06</v>
       </c>
       <c r="S56" s="96" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="T56" s="96" t="n">
         <v>57.25</v>
       </c>
-      <c r="T56" s="96" t="n">
+      <c r="U56" s="96" t="n">
         <v>79.72</v>
       </c>
-      <c r="U56" s="96" t="n">
+      <c r="V56" s="96" t="n">
         <v>77.8</v>
       </c>
-      <c r="V56" s="96" t="n">
+      <c r="W56" s="96" t="n">
         <v>75.65000000000001</v>
       </c>
-      <c r="W56" s="96" t="n">
+      <c r="X56" s="96" t="n">
         <v>79.31999999999999</v>
       </c>
-      <c r="X56" s="96" t="n">
+      <c r="Y56" s="96" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="Y56" s="96" t="n">
+      <c r="Z56" s="96" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="Z56" s="96" t="n">
+      <c r="AA56" s="96" t="n">
         <v>63.01</v>
       </c>
-      <c r="AA56" s="96" t="n">
+      <c r="AB56" s="96" t="n">
         <v>48.31</v>
       </c>
-      <c r="AB56" s="96" t="n">
+      <c r="AC56" s="96" t="n">
         <v>38.67</v>
       </c>
-      <c r="AC56" s="96" t="n">
+      <c r="AD56" s="96" t="n">
         <v>26.64</v>
       </c>
-      <c r="AD56" s="96" t="n">
-        <v>35.85</v>
-      </c>
       <c r="AE56" s="96" t="n">
-        <v>35.85</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -12493,155 +12472,153 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="93" t="inlineStr">
+      <c r="B57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C57" s="95" t="inlineStr">
+      <c r="D57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D57" s="95" t="inlineStr">
+      <c r="E57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E57" s="94" t="inlineStr">
+      <c r="F57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F57" s="95" t="inlineStr">
+      <c r="G57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G57" s="94" t="inlineStr">
+      <c r="H57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H57" s="94" t="inlineStr">
+      <c r="I57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I57" s="94" t="inlineStr">
+      <c r="J57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J57" s="93" t="inlineStr">
+      <c r="K57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K57" s="93" t="inlineStr">
+      <c r="L57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L57" s="93" t="inlineStr">
+      <c r="M57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M57" s="93" t="inlineStr">
+      <c r="N57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N57" s="93" t="inlineStr">
+      <c r="O57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O57" s="93" t="inlineStr">
+      <c r="P57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P57" s="93" t="inlineStr">
+      <c r="Q57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q57" s="93" t="inlineStr">
+      <c r="R57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R57" s="93" t="inlineStr">
+      <c r="S57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S57" s="93" t="inlineStr">
+      <c r="T57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T57" s="95" t="inlineStr">
+      <c r="U57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U57" s="93" t="inlineStr">
+      <c r="V57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V57" s="95" t="inlineStr">
+      <c r="W57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W57" s="95" t="inlineStr">
+      <c r="X57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X57" s="95" t="inlineStr">
+      <c r="Y57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y57" s="95" t="inlineStr">
+      <c r="Z57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z57" s="95" t="inlineStr">
+      <c r="AA57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA57" s="95" t="inlineStr">
+      <c r="AB57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB57" s="95" t="inlineStr">
+      <c r="AC57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC57" s="94" t="inlineStr">
+      <c r="AD57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD57" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AE57" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
+      <c r="AE57" s="93" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -12651,94 +12628,94 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>3.29</v>
+        <v>2.93</v>
       </c>
       <c r="C58" s="96" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D58" s="96" t="n">
         <v>5.11</v>
       </c>
-      <c r="D58" s="96" t="n">
+      <c r="E58" s="96" t="n">
         <v>4.27</v>
       </c>
-      <c r="E58" s="96" t="n">
+      <c r="F58" s="96" t="n">
         <v>3.15</v>
       </c>
-      <c r="F58" s="96" t="n">
+      <c r="G58" s="96" t="n">
         <v>5.03</v>
       </c>
-      <c r="G58" s="96" t="n">
+      <c r="H58" s="96" t="n">
         <v>4.52</v>
       </c>
-      <c r="H58" s="96" t="n">
+      <c r="I58" s="96" t="n">
         <v>4.41</v>
       </c>
-      <c r="I58" s="96" t="n">
+      <c r="J58" s="96" t="n">
         <v>4.16</v>
       </c>
-      <c r="J58" s="96" t="n">
+      <c r="K58" s="96" t="n">
         <v>5.65</v>
       </c>
-      <c r="K58" s="96" t="n">
+      <c r="L58" s="96" t="n">
         <v>6.67</v>
       </c>
-      <c r="L58" s="96" t="n">
+      <c r="M58" s="96" t="n">
         <v>6.48</v>
       </c>
-      <c r="M58" s="96" t="n">
+      <c r="N58" s="96" t="n">
         <v>7.28</v>
       </c>
-      <c r="N58" s="96" t="n">
+      <c r="O58" s="96" t="n">
         <v>7.24</v>
       </c>
-      <c r="O58" s="96" t="n">
+      <c r="P58" s="96" t="n">
         <v>7.81</v>
       </c>
-      <c r="P58" s="96" t="n">
+      <c r="Q58" s="96" t="n">
         <v>9.640000000000001</v>
-      </c>
-      <c r="Q58" s="96" t="n">
-        <v>9.58</v>
       </c>
       <c r="R58" s="96" t="n">
         <v>9.58</v>
       </c>
       <c r="S58" s="96" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="T58" s="96" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="T58" s="96" t="n">
+      <c r="U58" s="96" t="n">
         <v>10.23</v>
       </c>
-      <c r="U58" s="96" t="n">
+      <c r="V58" s="96" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V58" s="96" t="n">
+      <c r="W58" s="96" t="n">
         <v>10.6</v>
       </c>
-      <c r="W58" s="96" t="n">
+      <c r="X58" s="96" t="n">
         <v>11.21</v>
       </c>
-      <c r="X58" s="96" t="n">
+      <c r="Y58" s="96" t="n">
         <v>9.68</v>
       </c>
-      <c r="Y58" s="96" t="n">
+      <c r="Z58" s="96" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="Z58" s="96" t="n">
+      <c r="AA58" s="96" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="AA58" s="96" t="n">
+      <c r="AB58" s="96" t="n">
         <v>7.41</v>
       </c>
-      <c r="AB58" s="96" t="n">
+      <c r="AC58" s="96" t="n">
         <v>5.64</v>
       </c>
-      <c r="AC58" s="96" t="n">
+      <c r="AD58" s="96" t="n">
         <v>5.87</v>
       </c>
-      <c r="AD58" s="96" t="n">
-        <v>5.99</v>
-      </c>
       <c r="AE58" s="96" t="n">
-        <v>5.99</v>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -12748,94 +12725,94 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.76</v>
+        <v>10.37</v>
       </c>
       <c r="C59" s="96" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="D59" s="96" t="n">
         <v>11.25</v>
       </c>
-      <c r="D59" s="96" t="n">
+      <c r="E59" s="96" t="n">
         <v>10.63</v>
       </c>
-      <c r="E59" s="96" t="n">
+      <c r="F59" s="96" t="n">
         <v>9.59</v>
       </c>
-      <c r="F59" s="96" t="n">
+      <c r="G59" s="96" t="n">
         <v>11.03</v>
       </c>
-      <c r="G59" s="96" t="n">
+      <c r="H59" s="96" t="n">
         <v>11.24</v>
       </c>
-      <c r="H59" s="96" t="n">
+      <c r="I59" s="96" t="n">
         <v>11.05</v>
       </c>
-      <c r="I59" s="96" t="n">
+      <c r="J59" s="96" t="n">
         <v>11.74</v>
       </c>
-      <c r="J59" s="96" t="n">
+      <c r="K59" s="96" t="n">
         <v>13.86</v>
       </c>
-      <c r="K59" s="96" t="n">
+      <c r="L59" s="96" t="n">
         <v>14.5</v>
       </c>
-      <c r="L59" s="96" t="n">
+      <c r="M59" s="96" t="n">
         <v>15.28</v>
       </c>
-      <c r="M59" s="96" t="n">
+      <c r="N59" s="96" t="n">
         <v>15.62</v>
       </c>
-      <c r="N59" s="96" t="n">
+      <c r="O59" s="96" t="n">
         <v>16.8</v>
       </c>
-      <c r="O59" s="96" t="n">
+      <c r="P59" s="96" t="n">
         <v>17.29</v>
       </c>
-      <c r="P59" s="96" t="n">
+      <c r="Q59" s="96" t="n">
         <v>17.09</v>
-      </c>
-      <c r="Q59" s="96" t="n">
-        <v>16.94</v>
       </c>
       <c r="R59" s="96" t="n">
         <v>16.94</v>
       </c>
       <c r="S59" s="96" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="T59" s="96" t="n">
         <v>17.43</v>
       </c>
-      <c r="T59" s="96" t="n">
+      <c r="U59" s="96" t="n">
         <v>18.67</v>
       </c>
-      <c r="U59" s="96" t="n">
+      <c r="V59" s="96" t="n">
         <v>17.7</v>
       </c>
-      <c r="V59" s="96" t="n">
+      <c r="W59" s="96" t="n">
         <v>17.73</v>
       </c>
-      <c r="W59" s="96" t="n">
+      <c r="X59" s="96" t="n">
         <v>18.92</v>
       </c>
-      <c r="X59" s="96" t="n">
+      <c r="Y59" s="96" t="n">
         <v>18.66</v>
       </c>
-      <c r="Y59" s="96" t="n">
+      <c r="Z59" s="96" t="n">
         <v>18.47</v>
       </c>
-      <c r="Z59" s="96" t="n">
+      <c r="AA59" s="96" t="n">
         <v>20.1</v>
       </c>
-      <c r="AA59" s="96" t="n">
+      <c r="AB59" s="96" t="n">
         <v>19.3</v>
       </c>
-      <c r="AB59" s="96" t="n">
+      <c r="AC59" s="96" t="n">
         <v>17.2</v>
       </c>
-      <c r="AC59" s="96" t="n">
+      <c r="AD59" s="96" t="n">
         <v>17.51</v>
       </c>
-      <c r="AD59" s="96" t="n">
-        <v>18.34</v>
-      </c>
       <c r="AE59" s="96" t="n">
-        <v>18.34</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -12845,94 +12822,94 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>47.52</v>
+        <v>39.26</v>
       </c>
       <c r="C60" s="96" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="D60" s="96" t="n">
         <v>61.52</v>
       </c>
-      <c r="D60" s="96" t="n">
+      <c r="E60" s="96" t="n">
         <v>53.4</v>
       </c>
-      <c r="E60" s="96" t="n">
+      <c r="F60" s="96" t="n">
         <v>28.17</v>
       </c>
-      <c r="F60" s="96" t="n">
+      <c r="G60" s="96" t="n">
         <v>54.46</v>
       </c>
-      <c r="G60" s="96" t="n">
+      <c r="H60" s="96" t="n">
         <v>26.44</v>
       </c>
-      <c r="H60" s="96" t="n">
+      <c r="I60" s="96" t="n">
         <v>26.09</v>
       </c>
-      <c r="I60" s="96" t="n">
+      <c r="J60" s="96" t="n">
         <v>20.17</v>
       </c>
-      <c r="J60" s="96" t="n">
+      <c r="K60" s="96" t="n">
         <v>42.28</v>
       </c>
-      <c r="K60" s="96" t="n">
+      <c r="L60" s="96" t="n">
         <v>69.20999999999999</v>
       </c>
-      <c r="L60" s="96" t="n">
+      <c r="M60" s="96" t="n">
         <v>48.57</v>
       </c>
-      <c r="M60" s="96" t="n">
+      <c r="N60" s="96" t="n">
         <v>47.91</v>
       </c>
-      <c r="N60" s="96" t="n">
+      <c r="O60" s="96" t="n">
         <v>45.04</v>
       </c>
-      <c r="O60" s="96" t="n">
+      <c r="P60" s="96" t="n">
         <v>54.46</v>
       </c>
-      <c r="P60" s="96" t="n">
+      <c r="Q60" s="96" t="n">
         <v>63.48</v>
-      </c>
-      <c r="Q60" s="96" t="n">
-        <v>54.91</v>
       </c>
       <c r="R60" s="96" t="n">
         <v>54.91</v>
       </c>
       <c r="S60" s="96" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="T60" s="96" t="n">
         <v>60.6</v>
       </c>
-      <c r="T60" s="96" t="n">
+      <c r="U60" s="96" t="n">
         <v>85.93000000000001</v>
       </c>
-      <c r="U60" s="96" t="n">
+      <c r="V60" s="96" t="n">
         <v>77.76000000000001</v>
       </c>
-      <c r="V60" s="96" t="n">
+      <c r="W60" s="96" t="n">
         <v>83.92</v>
       </c>
-      <c r="W60" s="96" t="n">
+      <c r="X60" s="96" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="X60" s="96" t="n">
+      <c r="Y60" s="96" t="n">
         <v>88.44</v>
       </c>
-      <c r="Y60" s="96" t="n">
+      <c r="Z60" s="96" t="n">
         <v>83.18000000000001</v>
       </c>
-      <c r="Z60" s="96" t="n">
+      <c r="AA60" s="96" t="n">
         <v>80.8</v>
       </c>
-      <c r="AA60" s="96" t="n">
+      <c r="AB60" s="96" t="n">
         <v>68.27</v>
       </c>
-      <c r="AB60" s="96" t="n">
+      <c r="AC60" s="96" t="n">
         <v>51.26</v>
       </c>
-      <c r="AC60" s="96" t="n">
+      <c r="AD60" s="96" t="n">
         <v>37.9</v>
       </c>
-      <c r="AD60" s="96" t="n">
-        <v>40.99</v>
-      </c>
       <c r="AE60" s="96" t="n">
-        <v>40.99</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -12942,107 +12919,107 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>47.74</v>
+        <v>42.14</v>
       </c>
       <c r="C61" s="96" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="D61" s="96" t="n">
         <v>56.82</v>
       </c>
-      <c r="D61" s="96" t="n">
+      <c r="E61" s="96" t="n">
         <v>50.65</v>
       </c>
-      <c r="E61" s="96" t="n">
+      <c r="F61" s="96" t="n">
         <v>32.93</v>
       </c>
-      <c r="F61" s="96" t="n">
+      <c r="G61" s="96" t="n">
         <v>51.12</v>
       </c>
-      <c r="G61" s="96" t="n">
+      <c r="H61" s="96" t="n">
         <v>34.78</v>
       </c>
-      <c r="H61" s="96" t="n">
+      <c r="I61" s="96" t="n">
         <v>34.59</v>
       </c>
-      <c r="I61" s="96" t="n">
+      <c r="J61" s="96" t="n">
         <v>31.17</v>
       </c>
-      <c r="J61" s="96" t="n">
+      <c r="K61" s="96" t="n">
         <v>50.2</v>
       </c>
-      <c r="K61" s="96" t="n">
+      <c r="L61" s="96" t="n">
         <v>66.11</v>
       </c>
-      <c r="L61" s="96" t="n">
+      <c r="M61" s="96" t="n">
         <v>56.44</v>
       </c>
-      <c r="M61" s="96" t="n">
+      <c r="N61" s="96" t="n">
         <v>56.18</v>
       </c>
-      <c r="N61" s="96" t="n">
+      <c r="O61" s="96" t="n">
         <v>54.96</v>
       </c>
-      <c r="O61" s="96" t="n">
+      <c r="P61" s="96" t="n">
         <v>60.91</v>
       </c>
-      <c r="P61" s="96" t="n">
+      <c r="Q61" s="96" t="n">
         <v>66.34</v>
-      </c>
-      <c r="Q61" s="96" t="n">
-        <v>62.02</v>
       </c>
       <c r="R61" s="96" t="n">
         <v>62.02</v>
       </c>
       <c r="S61" s="96" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="T61" s="96" t="n">
         <v>65.76000000000001</v>
       </c>
-      <c r="T61" s="96" t="n">
+      <c r="U61" s="96" t="n">
         <v>81.28</v>
       </c>
-      <c r="U61" s="96" t="n">
+      <c r="V61" s="96" t="n">
         <v>75.68000000000001</v>
       </c>
-      <c r="V61" s="96" t="n">
+      <c r="W61" s="96" t="n">
         <v>79</v>
       </c>
-      <c r="W61" s="96" t="n">
+      <c r="X61" s="96" t="n">
         <v>82.58</v>
       </c>
-      <c r="X61" s="96" t="n">
+      <c r="Y61" s="96" t="n">
         <v>80.51000000000001</v>
       </c>
-      <c r="Y61" s="96" t="n">
+      <c r="Z61" s="96" t="n">
         <v>75.11</v>
       </c>
-      <c r="Z61" s="96" t="n">
+      <c r="AA61" s="96" t="n">
         <v>72.83</v>
       </c>
-      <c r="AA61" s="96" t="n">
+      <c r="AB61" s="96" t="n">
         <v>62.05</v>
       </c>
-      <c r="AB61" s="96" t="n">
+      <c r="AC61" s="96" t="n">
         <v>50.35</v>
       </c>
-      <c r="AC61" s="96" t="n">
+      <c r="AD61" s="96" t="n">
         <v>42.44</v>
       </c>
-      <c r="AD61" s="96" t="n">
-        <v>44.61</v>
-      </c>
       <c r="AE61" s="96" t="n">
-        <v>44.61</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：fr40:RSI3:21.01&lt;=28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:93.04&gt;=91;us500:RSI2:93.04&gt;=85;ixic:RSI2:89.26&gt;=85</t>
+          <t>今日卖报：us500:RSI2:86.23&gt;=85</t>
         </is>
       </c>
     </row>
@@ -16698,13 +16675,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="99" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="99">
+      <c r="J2" s="100">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16735,13 +16712,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="100">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16772,13 +16749,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16809,13 +16786,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16846,13 +16823,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="100" t="n">
+      <c r="H6" s="101" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16883,13 +16860,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16920,13 +16897,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="100" t="n">
+      <c r="H8" s="101" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16957,13 +16934,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="100" t="n">
+      <c r="H9" s="101" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16994,13 +16971,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17031,13 +17008,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="102" t="n">
+      <c r="H11" s="103" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="104">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17068,13 +17045,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="100" t="n">
+      <c r="H12" s="101" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="102">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17105,13 +17082,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="102" t="n">
+      <c r="H13" s="103" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="104">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17142,13 +17119,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="100" t="n">
+      <c r="H14" s="101" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="102">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17179,13 +17156,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="102" t="n">
+      <c r="H15" s="103" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="104">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17216,13 +17193,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="100" t="n">
+      <c r="H16" s="101" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="102">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17253,13 +17230,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="102" t="n">
+      <c r="H17" s="103" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="104">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17290,13 +17267,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="100" t="n">
+      <c r="H18" s="101" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="102">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17327,13 +17304,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="102" t="n">
+      <c r="H19" s="103" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="104">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17364,13 +17341,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="100" t="n">
+      <c r="H20" s="101" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="102">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17401,13 +17378,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="102" t="n">
+      <c r="H21" s="103" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="103">
+      <c r="J21" s="104">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17436,13 +17413,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="104" t="n">
+      <c r="H22" s="105" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="102">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17471,13 +17448,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="105" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="102">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17506,13 +17483,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="n">
+      <c r="H24" s="101" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="102">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17541,13 +17518,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="100" t="n">
+      <c r="H25" s="101" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="102">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17576,13 +17553,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="100" t="n">
+      <c r="H26" s="101" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="102">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17611,13 +17588,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="100" t="n">
+      <c r="H27" s="101" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="102">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17646,13 +17623,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="104" t="n">
+      <c r="H28" s="105" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="102">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17681,13 +17658,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="105" t="n">
+      <c r="H29" s="106" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="104">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17716,13 +17693,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="104" t="n">
+      <c r="H30" s="105" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="102">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17751,13 +17728,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="105" t="n">
+      <c r="H31" s="106" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="103">
+      <c r="J31" s="104">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17786,13 +17763,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="104" t="n">
+      <c r="H32" s="105" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="102">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17821,13 +17798,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="105" t="n">
+      <c r="H33" s="106" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="104">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17856,13 +17833,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="105" t="n">
+      <c r="H34" s="106" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="104">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17891,13 +17868,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="105" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="102">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17926,13 +17903,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="105" t="n">
+      <c r="H36" s="106" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="103">
+      <c r="J36" s="104">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17961,13 +17938,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="105" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="102">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -17996,13 +17973,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="104" t="n">
+      <c r="H38" s="105" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="102">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18031,13 +18008,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="105" t="n">
+      <c r="H39" s="106" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="103">
+      <c r="J39" s="104">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -1058,8 +1058,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2154,19 +2154,19 @@
         <v>1.05</v>
       </c>
       <c r="C7" s="80" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="D7" s="80" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E7" s="80" t="n">
         <v>1.02</v>
       </c>
       <c r="F7" s="80" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G7" s="80" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H7" s="80" t="n">
         <v>1.05</v>
@@ -2175,13 +2175,13 @@
         <v>1.06</v>
       </c>
       <c r="J7" s="80" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K7" s="80" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="L7" s="80" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M7" s="80" t="n">
         <v>1.12</v>
@@ -2199,7 +2199,7 @@
         <v>1.42</v>
       </c>
       <c r="R7" s="80" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S7" s="80" t="n">
         <v>1.23</v>
@@ -2345,85 +2345,85 @@
         </is>
       </c>
       <c r="B9" s="84" t="n">
-        <v>0.4636</v>
+        <v>0.468</v>
       </c>
       <c r="C9" s="84" t="n">
-        <v>0.4881</v>
+        <v>0.489</v>
       </c>
       <c r="D9" s="84" t="n">
-        <v>0.4826</v>
+        <v>0.4831</v>
       </c>
       <c r="E9" s="84" t="n">
-        <v>0.4942</v>
+        <v>0.4935</v>
       </c>
       <c r="F9" s="84" t="n">
-        <v>0.5317</v>
+        <v>0.5314</v>
       </c>
       <c r="G9" s="84" t="n">
-        <v>0.5032</v>
+        <v>0.5031</v>
       </c>
       <c r="H9" s="84" t="n">
-        <v>0.512</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="I9" s="84" t="n">
-        <v>0.5165</v>
+        <v>0.5158</v>
       </c>
       <c r="J9" s="84" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5389</v>
       </c>
       <c r="K9" s="84" t="n">
-        <v>0.5339</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="L9" s="84" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="M9" s="84" t="n">
-        <v>0.521</v>
+        <v>0.5204</v>
       </c>
       <c r="N9" s="84" t="n">
-        <v>0.5569</v>
+        <v>0.5564</v>
       </c>
       <c r="O9" s="84" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6167</v>
       </c>
       <c r="P9" s="84" t="n">
-        <v>0.6155</v>
+        <v>0.6148</v>
       </c>
       <c r="Q9" s="84" t="n">
-        <v>0.6382</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="R9" s="84" t="n">
-        <v>0.6189</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="S9" s="84" t="n">
-        <v>0.577</v>
+        <v>0.5764</v>
       </c>
       <c r="T9" s="84" t="n">
-        <v>0.4479</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="U9" s="84" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6073</v>
       </c>
       <c r="V9" s="84" t="n">
-        <v>0.605</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="W9" s="84" t="n">
-        <v>0.6282</v>
+        <v>0.628</v>
       </c>
       <c r="X9" s="84" t="n">
         <v>0.6389</v>
       </c>
       <c r="Y9" s="84" t="n">
-        <v>0.6018</v>
+        <v>0.6017</v>
       </c>
       <c r="Z9" s="84" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6405</v>
       </c>
       <c r="AA9" s="84" t="n">
-        <v>0.6363</v>
+        <v>0.6364</v>
       </c>
       <c r="AB9" s="84" t="n">
-        <v>0.5873</v>
+        <v>0.5874</v>
       </c>
       <c r="AC9" s="84" t="n">
         <v>0.6054</v>
@@ -2432,7 +2432,7 @@
         <v>0.574</v>
       </c>
       <c r="AE9" s="84" t="n">
-        <v>0.5302</v>
+        <v>0.5298</v>
       </c>
     </row>
     <row r="10">
@@ -2539,94 +2539,94 @@
         </is>
       </c>
       <c r="B11" s="86" t="n">
-        <v>-0.029</v>
+        <v>-0.03139999999999998</v>
       </c>
       <c r="C11" s="86" t="n">
-        <v>-0.03059999999999996</v>
+        <v>-0.03159999999999999</v>
       </c>
       <c r="D11" s="86" t="n">
-        <v>-0.03139999999999998</v>
+        <v>-0.03180000000000002</v>
       </c>
       <c r="E11" s="86" t="n">
-        <v>-0.03239999999999998</v>
+        <v>-0.03280000000000002</v>
       </c>
       <c r="F11" s="86" t="n">
-        <v>-0.03540000000000001</v>
+        <v>-0.0358</v>
       </c>
       <c r="G11" s="86" t="n">
-        <v>-0.03569999999999998</v>
+        <v>-0.0363</v>
       </c>
       <c r="H11" s="86" t="n">
-        <v>-0.03720000000000001</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="I11" s="86" t="n">
-        <v>-0.03759999999999997</v>
+        <v>-0.03800000000000003</v>
       </c>
       <c r="J11" s="86" t="n">
-        <v>-0.03810000000000002</v>
+        <v>-0.0383</v>
       </c>
       <c r="K11" s="86" t="n">
-        <v>-0.03859999999999997</v>
+        <v>-0.0386</v>
       </c>
       <c r="L11" s="86" t="n">
-        <v>-0.03880000000000003</v>
+        <v>-0.03920000000000001</v>
       </c>
       <c r="M11" s="86" t="n">
-        <v>-0.0423</v>
+        <v>-0.0428</v>
       </c>
       <c r="N11" s="86" t="n">
-        <v>-0.04560000000000003</v>
+        <v>-0.04610000000000003</v>
       </c>
       <c r="O11" s="86" t="n">
-        <v>-0.04759999999999998</v>
+        <v>-0.04820000000000002</v>
       </c>
       <c r="P11" s="86" t="n">
-        <v>-0.04750000000000001</v>
+        <v>-0.04790000000000003</v>
       </c>
       <c r="Q11" s="86" t="n">
-        <v>-0.05100000000000002</v>
+        <v>-0.0512</v>
       </c>
       <c r="R11" s="86" t="n">
-        <v>-0.05729999999999996</v>
+        <v>-0.05759999999999998</v>
       </c>
       <c r="S11" s="86" t="n">
-        <v>-0.05900000000000002</v>
+        <v>-0.05930000000000002</v>
       </c>
       <c r="T11" s="86" t="n">
-        <v>-0.0446</v>
+        <v>-0.05880000000000002</v>
       </c>
       <c r="U11" s="86" t="n">
-        <v>-0.05589999999999998</v>
+        <v>-0.0562</v>
       </c>
       <c r="V11" s="86" t="n">
-        <v>-0.05439999999999998</v>
+        <v>-0.05679999999999999</v>
       </c>
       <c r="W11" s="86" t="n">
-        <v>-0.0544</v>
+        <v>-0.05460000000000001</v>
       </c>
       <c r="X11" s="86" t="n">
-        <v>-0.05600000000000002</v>
+        <v>-0.05609999999999998</v>
       </c>
       <c r="Y11" s="86" t="n">
-        <v>-0.05729999999999996</v>
+        <v>-0.0575</v>
       </c>
       <c r="Z11" s="86" t="n">
-        <v>-0.06390000000000001</v>
+        <v>-0.06410000000000002</v>
       </c>
       <c r="AA11" s="86" t="n">
-        <v>-0.06620000000000001</v>
+        <v>-0.06640000000000001</v>
       </c>
       <c r="AB11" s="86" t="n">
-        <v>-0.0683</v>
+        <v>-0.06840000000000002</v>
       </c>
       <c r="AC11" s="86" t="n">
-        <v>-0.06960000000000002</v>
+        <v>-0.06969999999999998</v>
       </c>
       <c r="AD11" s="86" t="n">
-        <v>-0.0665</v>
+        <v>-0.06649999999999998</v>
       </c>
       <c r="AE11" s="86" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.06799999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -3027,10 +3027,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="87" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="87" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E16" s="87" t="n">
         <v>43</v>
@@ -3039,7 +3039,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="87" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="87" t="n">
         <v>2</v>
@@ -3121,28 +3121,28 @@
         </is>
       </c>
       <c r="B17" s="87" t="n">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C17" s="87" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" s="87" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" s="87" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G17" s="87" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H17" s="87" t="n">
         <v>12</v>
       </c>
       <c r="I17" s="87" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J17" s="87" t="n">
         <v>17</v>
@@ -3151,7 +3151,7 @@
         <v>19</v>
       </c>
       <c r="L17" s="87" t="n">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="M17" s="87" t="n">
         <v>10</v>
@@ -3160,19 +3160,19 @@
         <v>5</v>
       </c>
       <c r="O17" s="87" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P17" s="87" t="n">
         <v>7</v>
       </c>
       <c r="Q17" s="87" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R17" s="87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S17" s="87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" s="87" t="n">
         <v>3</v>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="87" t="n">
         <v>3</v>
@@ -3218,67 +3218,67 @@
         </is>
       </c>
       <c r="B18" s="87" t="n">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="C18" s="87" t="n">
         <v>554</v>
       </c>
       <c r="D18" s="87" t="n">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="E18" s="87" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F18" s="87" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="G18" s="87" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H18" s="87" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I18" s="87" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J18" s="87" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K18" s="87" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="L18" s="87" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M18" s="87" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="N18" s="87" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O18" s="87" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P18" s="87" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q18" s="87" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R18" s="87" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S18" s="87" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="T18" s="87" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="U18" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="V18" s="87" t="n">
         <v>15</v>
-      </c>
-      <c r="V18" s="87" t="n">
-        <v>12</v>
       </c>
       <c r="W18" s="87" t="n">
         <v>8</v>
@@ -3296,7 +3296,7 @@
         <v>12</v>
       </c>
       <c r="AB18" s="87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC18" s="87" t="n">
         <v>20</v>
@@ -3305,7 +3305,7 @@
         <v>33</v>
       </c>
       <c r="AE18" s="87" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B22" s="87" t="n">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C22" s="87" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D22" s="87" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E22" s="87" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F22" s="87" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G22" s="87" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H22" s="87" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I22" s="87" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J22" s="87" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K22" s="87" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="L22" s="87" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="M22" s="87" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="N22" s="87" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O22" s="87" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P22" s="87" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Q22" s="87" t="n">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="R22" s="87" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="S22" s="87" t="n">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="T22" s="87" t="n">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="U22" s="87" t="n">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="V22" s="87" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="W22" s="87" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="X22" s="87" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Y22" s="87" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Z22" s="87" t="n">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="AA22" s="87" t="n">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="AB22" s="87" t="n">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="AC22" s="87" t="n">
         <v>507</v>
@@ -3693,7 +3693,7 @@
         <v>239</v>
       </c>
       <c r="AE22" s="87" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.03</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.39</v>
@@ -6505,150 +6505,150 @@
       </c>
       <c r="B2" s="93" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C2" s="94" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C2" s="93" t="inlineStr">
+      <c r="D2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D2" s="94" t="inlineStr">
+      <c r="G2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E2" s="94" t="inlineStr">
+      <c r="I2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="G2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="H2" s="94" t="inlineStr">
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="P2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q2" s="94" t="inlineStr">
+      <c r="S2" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T2" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U2" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="94" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S2" s="95" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Y2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Z2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AA2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T2" s="95" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="AC2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U2" s="95" t="inlineStr">
+      <c r="AD2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="W2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="X2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Y2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Z2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AA2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD2" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AE2" s="94" t="n">
+      <c r="AE2" s="93" t="n">
         <v/>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="B3" s="96" t="n">
-        <v>-1.32</v>
+        <v>-0.51</v>
       </c>
       <c r="C3" s="96" t="n">
         <v>-1.32</v>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" s="96" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="C4" s="96" t="n">
         <v>2.08</v>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="B5" s="96" t="n">
-        <v>31.36</v>
+        <v>36.14</v>
       </c>
       <c r="C5" s="96" t="n">
         <v>31.36</v>
@@ -6944,13 +6944,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="97" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>sh:RSI2</t>
         </is>
       </c>
       <c r="B6" s="96" t="n">
-        <v>6.26</v>
+        <v>45.89</v>
       </c>
       <c r="C6" s="96" t="n">
         <v>6.26</v>
@@ -7056,17 +7056,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D7" s="93" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E7" s="93" t="inlineStr">
+      <c r="E7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F7" s="93" t="inlineStr">
+      <c r="F7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7086,87 +7086,87 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J7" s="94" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K7" s="94" t="inlineStr">
+      <c r="K7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L7" s="94" t="inlineStr">
+      <c r="L7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M7" s="93" t="inlineStr">
+      <c r="M7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N7" s="94" t="inlineStr">
+      <c r="N7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O7" s="93" t="inlineStr">
+      <c r="O7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P7" s="93" t="inlineStr">
+      <c r="P7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q7" s="94" t="inlineStr">
+      <c r="Q7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R7" s="93" t="inlineStr">
+      <c r="R7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S7" s="93" t="inlineStr">
+      <c r="S7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T7" s="93" t="inlineStr">
+      <c r="T7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U7" s="93" t="inlineStr">
+      <c r="U7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V7" s="93" t="inlineStr">
+      <c r="V7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W7" s="93" t="inlineStr">
+      <c r="W7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X7" s="93" t="inlineStr">
+      <c r="X7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y7" s="94" t="inlineStr">
+      <c r="Y7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z7" s="94" t="inlineStr">
+      <c r="Z7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7176,12 +7176,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AB7" s="94" t="inlineStr">
+      <c r="AB7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC7" s="94" t="inlineStr">
+      <c r="AC7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7191,7 +7191,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AE7" s="94" t="n">
+      <c r="AE7" s="93" t="n">
         <v/>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="B8" s="96" t="n">
-        <v>-7.65</v>
+        <v>-7.57</v>
       </c>
       <c r="C8" s="96" t="n">
         <v>-7.65</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="B9" s="96" t="n">
-        <v>-10.81</v>
+        <v>-12.94</v>
       </c>
       <c r="C9" s="96" t="n">
         <v>-10.81</v>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B10" s="96" t="n">
-        <v>56.03</v>
+        <v>56.04</v>
       </c>
       <c r="C10" s="96" t="n">
         <v>56.03</v>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="B11" s="96" t="n">
-        <v>64.08</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="C11" s="96" t="n">
         <v>64.08</v>
@@ -7589,27 +7589,27 @@
           <t>cy:EIDE</t>
         </is>
       </c>
-      <c r="B12" s="93" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D12" s="93" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E12" s="93" t="inlineStr">
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F12" s="94" t="inlineStr">
+      <c r="F12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7624,42 +7624,42 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I12" s="94" t="inlineStr">
+      <c r="I12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J12" s="93" t="inlineStr">
+      <c r="J12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K12" s="94" t="inlineStr">
+      <c r="K12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L12" s="93" t="inlineStr">
+      <c r="L12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="93" t="inlineStr">
+      <c r="M12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="93" t="inlineStr">
+      <c r="N12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O12" s="93" t="inlineStr">
+      <c r="O12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P12" s="93" t="inlineStr">
+      <c r="P12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7669,7 +7669,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="R12" s="94" t="inlineStr">
+      <c r="R12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7679,37 +7679,37 @@
           <t>red</t>
         </is>
       </c>
-      <c r="T12" s="94" t="inlineStr">
+      <c r="T12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U12" s="94" t="inlineStr">
+      <c r="U12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V12" s="93" t="inlineStr">
+      <c r="V12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W12" s="93" t="inlineStr">
+      <c r="W12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X12" s="94" t="inlineStr">
+      <c r="X12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y12" s="94" t="inlineStr">
+      <c r="Y12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z12" s="94" t="inlineStr">
+      <c r="Z12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7719,7 +7719,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AB12" s="94" t="inlineStr">
+      <c r="AB12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7734,7 +7734,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AE12" s="94" t="n">
+      <c r="AE12" s="93" t="n">
         <v/>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B13" s="96" t="n">
-        <v>-5.45</v>
+        <v>-6.47</v>
       </c>
       <c r="C13" s="96" t="n">
         <v>-5.45</v>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="B14" s="96" t="n">
-        <v>-4.79</v>
+        <v>-5.79</v>
       </c>
       <c r="C14" s="96" t="n">
         <v>-4.79</v>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="B15" s="96" t="n">
-        <v>38.37</v>
+        <v>37.26</v>
       </c>
       <c r="C15" s="96" t="n">
         <v>38.37</v>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="B16" s="96" t="n">
-        <v>37.28</v>
+        <v>36.06</v>
       </c>
       <c r="C16" s="96" t="n">
         <v>37.28</v>
@@ -8132,102 +8132,102 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C17" s="93" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D17" s="94" t="inlineStr">
+      <c r="D17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E17" s="94" t="inlineStr">
+      <c r="E17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F17" s="94" t="inlineStr">
+      <c r="F17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G17" s="94" t="inlineStr">
+      <c r="G17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H17" s="94" t="inlineStr">
+      <c r="H17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I17" s="94" t="inlineStr">
+      <c r="I17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J17" s="93" t="inlineStr">
+      <c r="J17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K17" s="93" t="inlineStr">
+      <c r="K17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L17" s="93" t="inlineStr">
+      <c r="L17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M17" s="93" t="inlineStr">
+      <c r="M17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N17" s="93" t="inlineStr">
+      <c r="N17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O17" s="93" t="inlineStr">
+      <c r="O17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P17" s="93" t="inlineStr">
+      <c r="P17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q17" s="94" t="inlineStr">
+      <c r="Q17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R17" s="94" t="inlineStr">
+      <c r="R17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S17" s="94" t="inlineStr">
+      <c r="S17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T17" s="94" t="inlineStr">
+      <c r="T17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U17" s="94" t="inlineStr">
+      <c r="U17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8237,12 +8237,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="W17" s="94" t="inlineStr">
+      <c r="W17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X17" s="94" t="inlineStr">
+      <c r="X17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8257,17 +8257,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AA17" s="94" t="inlineStr">
+      <c r="AA17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB17" s="94" t="inlineStr">
+      <c r="AB17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC17" s="94" t="inlineStr">
+      <c r="AC17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B18" s="96" t="n">
-        <v>9.58</v>
+        <v>5.14</v>
       </c>
       <c r="C18" s="96" t="n">
         <v>9.58</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="B19" s="96" t="n">
-        <v>12.19</v>
+        <v>9.76</v>
       </c>
       <c r="C19" s="96" t="n">
         <v>12.19</v>
@@ -8478,13 +8478,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="97" t="inlineStr">
         <is>
           <t>hk50:RSI6</t>
         </is>
       </c>
       <c r="B20" s="96" t="n">
-        <v>31.92</v>
+        <v>25.06</v>
       </c>
       <c r="C20" s="96" t="n">
         <v>31.92</v>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="B21" s="96" t="n">
-        <v>49.52</v>
+        <v>46.59</v>
       </c>
       <c r="C21" s="96" t="n">
         <v>49.52</v>
@@ -8712,72 +8712,72 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="94" t="inlineStr">
+      <c r="I22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J22" s="94" t="inlineStr">
+      <c r="J22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K22" s="93" t="inlineStr">
+      <c r="K22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L22" s="93" t="inlineStr">
+      <c r="L22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M22" s="94" t="inlineStr">
+      <c r="M22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N22" s="94" t="inlineStr">
+      <c r="N22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O22" s="94" t="inlineStr">
+      <c r="O22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P22" s="94" t="inlineStr">
+      <c r="P22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q22" s="94" t="inlineStr">
+      <c r="Q22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="94" t="inlineStr">
+      <c r="R22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="94" t="inlineStr">
+      <c r="S22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="94" t="inlineStr">
+      <c r="T22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="94" t="inlineStr">
+      <c r="U22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V22" s="94" t="inlineStr">
+      <c r="V22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8792,7 +8792,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Y22" s="94" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9222,12 +9222,12 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
+      <c r="C27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9237,7 +9237,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E27" s="94" t="inlineStr">
+      <c r="E27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9247,82 +9247,82 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G27" s="94" t="inlineStr">
+      <c r="G27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H27" s="94" t="inlineStr">
+      <c r="H27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I27" s="94" t="inlineStr">
+      <c r="I27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J27" s="94" t="inlineStr">
+      <c r="J27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K27" s="93" t="inlineStr">
+      <c r="K27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L27" s="93" t="inlineStr">
+      <c r="L27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M27" s="93" t="inlineStr">
+      <c r="M27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N27" s="93" t="inlineStr">
+      <c r="N27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O27" s="93" t="inlineStr">
+      <c r="O27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P27" s="93" t="inlineStr">
+      <c r="P27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q27" s="94" t="inlineStr">
+      <c r="Q27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R27" s="94" t="inlineStr">
+      <c r="R27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S27" s="94" t="inlineStr">
+      <c r="S27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="94" t="inlineStr">
+      <c r="T27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U27" s="94" t="inlineStr">
+      <c r="U27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V27" s="94" t="inlineStr">
+      <c r="V27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9332,12 +9332,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="X27" s="94" t="inlineStr">
+      <c r="X27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y27" s="94" t="inlineStr">
+      <c r="Y27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9782,7 +9782,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E32" s="94" t="inlineStr">
+      <c r="E32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9797,27 +9797,27 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H32" s="94" t="inlineStr">
+      <c r="H32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I32" s="94" t="inlineStr">
+      <c r="I32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J32" s="94" t="inlineStr">
+      <c r="J32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K32" s="94" t="inlineStr">
+      <c r="K32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L32" s="94" t="inlineStr">
+      <c r="L32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9827,47 +9827,47 @@
           <t>red</t>
         </is>
       </c>
-      <c r="N32" s="94" t="inlineStr">
+      <c r="N32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O32" s="94" t="inlineStr">
+      <c r="O32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P32" s="94" t="inlineStr">
+      <c r="P32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q32" s="94" t="inlineStr">
+      <c r="Q32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R32" s="94" t="inlineStr">
+      <c r="R32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="94" t="inlineStr">
+      <c r="S32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T32" s="94" t="inlineStr">
+      <c r="T32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U32" s="94" t="inlineStr">
+      <c r="U32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V32" s="94" t="inlineStr">
+      <c r="V32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9882,12 +9882,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Y32" s="94" t="inlineStr">
+      <c r="Y32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z32" s="94" t="inlineStr">
+      <c r="Z32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10312,7 +10312,7 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B37" s="94" t="inlineStr">
+      <c r="B37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10337,7 +10337,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G37" s="93" t="inlineStr">
+      <c r="G37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10352,32 +10352,32 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J37" s="93" t="inlineStr">
+      <c r="J37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K37" s="93" t="inlineStr">
+      <c r="K37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L37" s="93" t="inlineStr">
+      <c r="L37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M37" s="94" t="inlineStr">
+      <c r="M37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N37" s="94" t="inlineStr">
+      <c r="N37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O37" s="93" t="inlineStr">
+      <c r="O37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10387,7 +10387,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q37" s="94" t="inlineStr">
+      <c r="Q37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10427,22 +10427,22 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Y37" s="93" t="inlineStr">
+      <c r="Y37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z37" s="94" t="inlineStr">
+      <c r="Z37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA37" s="93" t="inlineStr">
+      <c r="AA37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB37" s="93" t="inlineStr">
+      <c r="AB37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10452,10 +10452,10 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AD37" s="94" t="n">
+      <c r="AD37" s="93" t="n">
         <v/>
       </c>
-      <c r="AE37" s="94" t="n">
+      <c r="AE37" s="93" t="n">
         <v/>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="B38" s="96" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="C38" s="96" t="n">
         <v>1.13</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="B39" s="96" t="n">
-        <v>18.17</v>
+        <v>18.13</v>
       </c>
       <c r="C39" s="96" t="n">
         <v>19.15</v>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>54.06</v>
+        <v>53.35</v>
       </c>
       <c r="C40" s="96" t="n">
         <v>67.40000000000001</v>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>53.72</v>
+        <v>53.37</v>
       </c>
       <c r="C41" s="96" t="n">
         <v>59.57</v>
@@ -10853,12 +10853,12 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C42" s="94" t="inlineStr">
+      <c r="C42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10873,7 +10873,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F42" s="94" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10893,17 +10893,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="J42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="94" t="inlineStr">
+      <c r="K42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L42" s="94" t="inlineStr">
+      <c r="L42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10913,27 +10913,27 @@
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="94" t="inlineStr">
+      <c r="N42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O42" s="94" t="inlineStr">
+      <c r="O42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="94" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q42" s="94" t="inlineStr">
+      <c r="Q42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R42" s="94" t="inlineStr">
+      <c r="R42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10963,17 +10963,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="94" t="inlineStr">
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="94" t="inlineStr">
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="94" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="C43" s="96" t="n">
         <v>1.09</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
-        <v>13.9</v>
+        <v>15.27</v>
       </c>
       <c r="C44" s="96" t="n">
         <v>13.9</v>
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="B45" s="96" t="n">
-        <v>46.62</v>
+        <v>46.17</v>
       </c>
       <c r="C45" s="96" t="n">
         <v>46.62</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="B46" s="96" t="n">
-        <v>55.87</v>
+        <v>55.63</v>
       </c>
       <c r="C46" s="96" t="n">
         <v>55.87</v>
@@ -11428,7 +11428,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H47" s="93" t="inlineStr">
+      <c r="H47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -11438,22 +11438,22 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J47" s="93" t="inlineStr">
+      <c r="J47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K47" s="93" t="inlineStr">
+      <c r="K47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L47" s="94" t="inlineStr">
+      <c r="L47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M47" s="94" t="inlineStr">
+      <c r="M47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11503,47 +11503,47 @@
           <t>red</t>
         </is>
       </c>
-      <c r="W47" s="94" t="inlineStr">
+      <c r="W47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X47" s="94" t="inlineStr">
+      <c r="X47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y47" s="93" t="inlineStr">
+      <c r="Y47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z47" s="93" t="inlineStr">
+      <c r="Z47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA47" s="93" t="inlineStr">
+      <c r="AA47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB47" s="93" t="inlineStr">
+      <c r="AB47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC47" s="93" t="inlineStr">
+      <c r="AC47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD47" s="93" t="inlineStr">
+      <c r="AD47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AE47" s="93" t="inlineStr">
+      <c r="AE47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>3.79</v>
+        <v>5.34</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>3.79</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>6.96</v>
+        <v>7.48</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>6.96</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>60.75</v>
+        <v>61.99</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>60.75</v>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>58</v>
+        <v>58.66</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>58</v>
@@ -11943,22 +11943,22 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="93" t="inlineStr">
+      <c r="B52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C52" s="93" t="inlineStr">
+      <c r="C52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D52" s="93" t="inlineStr">
+      <c r="D52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E52" s="94" t="inlineStr">
+      <c r="E52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11968,37 +11968,37 @@
           <t>red</t>
         </is>
       </c>
-      <c r="G52" s="94" t="inlineStr">
+      <c r="G52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="93" t="inlineStr">
+      <c r="H52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I52" s="94" t="inlineStr">
+      <c r="I52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J52" s="94" t="inlineStr">
+      <c r="J52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K52" s="93" t="inlineStr">
+      <c r="K52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L52" s="93" t="inlineStr">
+      <c r="L52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M52" s="93" t="inlineStr">
+      <c r="M52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -12008,42 +12008,42 @@
           <t>red</t>
         </is>
       </c>
-      <c r="O52" s="93" t="inlineStr">
+      <c r="O52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P52" s="93" t="inlineStr">
+      <c r="P52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q52" s="93" t="inlineStr">
+      <c r="Q52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R52" s="93" t="inlineStr">
+      <c r="R52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S52" s="94" t="inlineStr">
+      <c r="S52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T52" s="94" t="inlineStr">
+      <c r="T52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U52" s="94" t="inlineStr">
+      <c r="U52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V52" s="94" t="inlineStr">
+      <c r="V52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12083,12 +12083,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AD52" s="94" t="inlineStr">
+      <c r="AD52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE52" s="93" t="inlineStr">
+      <c r="AE52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -12488,22 +12488,22 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="93" t="inlineStr">
+      <c r="B57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C57" s="93" t="inlineStr">
+      <c r="C57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D57" s="93" t="inlineStr">
+      <c r="D57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E57" s="94" t="inlineStr">
+      <c r="E57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12518,7 +12518,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H57" s="93" t="inlineStr">
+      <c r="H57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -12528,67 +12528,67 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J57" s="93" t="inlineStr">
+      <c r="J57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K57" s="93" t="inlineStr">
+      <c r="K57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L57" s="93" t="inlineStr">
+      <c r="L57" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M57" s="94" t="inlineStr">
+      <c r="M57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N57" s="94" t="inlineStr">
+      <c r="N57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O57" s="94" t="inlineStr">
+      <c r="O57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P57" s="94" t="inlineStr">
+      <c r="P57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q57" s="94" t="inlineStr">
+      <c r="Q57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R57" s="94" t="inlineStr">
+      <c r="R57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S57" s="94" t="inlineStr">
+      <c r="S57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T57" s="94" t="inlineStr">
+      <c r="T57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U57" s="94" t="inlineStr">
+      <c r="U57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V57" s="94" t="inlineStr">
+      <c r="V57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12598,7 +12598,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="X57" s="94" t="inlineStr">
+      <c r="X57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -13030,7 +13030,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI2:6.26&lt;=7;fr40:RSI3:11.58&lt;=28;fr40:RSI5:19.24&lt;=20</t>
+          <t>今日买报：hk50:RSI6:25.06&lt;=30;fr40:RSI3:11.58&lt;=28;fr40:RSI5:19.24&lt;=20</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -480,12 +480,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000ff00"/>
+        <fgColor rgb="000000ff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000ff"/>
+        <fgColor rgb="0000ff00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1058,12 +1058,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1450,152 +1450,152 @@
       </c>
       <c r="B1" s="79" t="inlineStr">
         <is>
+          <t>240612</t>
+        </is>
+      </c>
+      <c r="C1" s="79" t="inlineStr">
+        <is>
           <t>240611</t>
         </is>
       </c>
-      <c r="C1" s="79" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>240607</t>
         </is>
       </c>
-      <c r="D1" s="79" t="inlineStr">
+      <c r="E1" s="79" t="inlineStr">
         <is>
           <t>240606</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="F1" s="79" t="inlineStr">
         <is>
           <t>240605</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>240604</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>240603</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>240531</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="J1" s="79" t="inlineStr">
         <is>
           <t>240530</t>
         </is>
       </c>
-      <c r="J1" s="79" t="inlineStr">
+      <c r="K1" s="79" t="inlineStr">
         <is>
           <t>240529</t>
         </is>
       </c>
-      <c r="K1" s="79" t="inlineStr">
+      <c r="L1" s="79" t="inlineStr">
         <is>
           <t>240528</t>
         </is>
       </c>
-      <c r="L1" s="79" t="inlineStr">
+      <c r="M1" s="79" t="inlineStr">
         <is>
           <t>240527</t>
         </is>
       </c>
-      <c r="M1" s="79" t="inlineStr">
+      <c r="N1" s="79" t="inlineStr">
         <is>
           <t>240524</t>
         </is>
       </c>
-      <c r="N1" s="79" t="inlineStr">
+      <c r="O1" s="79" t="inlineStr">
         <is>
           <t>240523</t>
         </is>
       </c>
-      <c r="O1" s="79" t="inlineStr">
+      <c r="P1" s="79" t="inlineStr">
         <is>
           <t>240522</t>
         </is>
       </c>
-      <c r="P1" s="79" t="inlineStr">
+      <c r="Q1" s="79" t="inlineStr">
         <is>
           <t>240521</t>
         </is>
       </c>
-      <c r="Q1" s="79" t="inlineStr">
+      <c r="R1" s="79" t="inlineStr">
         <is>
           <t>240520</t>
         </is>
       </c>
-      <c r="R1" s="79" t="inlineStr">
+      <c r="S1" s="79" t="inlineStr">
         <is>
           <t>240517</t>
         </is>
       </c>
-      <c r="S1" s="79" t="inlineStr">
+      <c r="T1" s="79" t="inlineStr">
         <is>
           <t>240516</t>
         </is>
       </c>
-      <c r="T1" s="79" t="inlineStr">
+      <c r="U1" s="79" t="inlineStr">
         <is>
           <t>240515</t>
         </is>
       </c>
-      <c r="U1" s="79" t="inlineStr">
+      <c r="V1" s="79" t="inlineStr">
         <is>
           <t>240514</t>
         </is>
       </c>
-      <c r="V1" s="79" t="inlineStr">
+      <c r="W1" s="79" t="inlineStr">
         <is>
           <t>240513</t>
         </is>
       </c>
-      <c r="W1" s="79" t="inlineStr">
+      <c r="X1" s="79" t="inlineStr">
         <is>
           <t>240510</t>
         </is>
       </c>
-      <c r="X1" s="79" t="inlineStr">
+      <c r="Y1" s="79" t="inlineStr">
         <is>
           <t>240509</t>
         </is>
       </c>
-      <c r="Y1" s="79" t="inlineStr">
+      <c r="Z1" s="79" t="inlineStr">
         <is>
           <t>240508</t>
         </is>
       </c>
-      <c r="Z1" s="79" t="inlineStr">
+      <c r="AA1" s="79" t="inlineStr">
         <is>
           <t>240507</t>
         </is>
       </c>
-      <c r="AA1" s="79" t="inlineStr">
+      <c r="AB1" s="79" t="inlineStr">
         <is>
           <t>240506</t>
         </is>
       </c>
-      <c r="AB1" s="79" t="inlineStr">
+      <c r="AC1" s="79" t="inlineStr">
         <is>
           <t>240430</t>
         </is>
       </c>
-      <c r="AC1" s="79" t="inlineStr">
+      <c r="AD1" s="79" t="inlineStr">
         <is>
           <t>240429</t>
         </is>
       </c>
-      <c r="AD1" s="79" t="inlineStr">
+      <c r="AE1" s="79" t="inlineStr">
         <is>
           <t>240426</t>
-        </is>
-      </c>
-      <c r="AE1" s="79" t="inlineStr">
-        <is>
-          <t>240425</t>
         </is>
       </c>
     </row>
@@ -1606,94 +1606,94 @@
         </is>
       </c>
       <c r="B2" s="80" t="n">
+        <v>3037.47</v>
+      </c>
+      <c r="C2" s="80" t="n">
         <v>3028.05</v>
       </c>
-      <c r="C2" s="80" t="n">
+      <c r="D2" s="80" t="n">
         <v>3051.28</v>
       </c>
-      <c r="D2" s="80" t="n">
+      <c r="E2" s="80" t="n">
         <v>3048.79</v>
       </c>
-      <c r="E2" s="80" t="n">
+      <c r="F2" s="80" t="n">
         <v>3065.4</v>
       </c>
-      <c r="F2" s="80" t="n">
+      <c r="G2" s="80" t="n">
         <v>3091.2</v>
       </c>
-      <c r="G2" s="80" t="n">
+      <c r="H2" s="80" t="n">
         <v>3078.49</v>
       </c>
-      <c r="H2" s="80" t="n">
+      <c r="I2" s="80" t="n">
         <v>3086.81</v>
       </c>
-      <c r="I2" s="80" t="n">
+      <c r="J2" s="80" t="n">
         <v>3091.68</v>
       </c>
-      <c r="J2" s="80" t="n">
+      <c r="K2" s="80" t="n">
         <v>3111.02</v>
       </c>
-      <c r="K2" s="80" t="n">
+      <c r="L2" s="80" t="n">
         <v>3109.57</v>
       </c>
-      <c r="L2" s="80" t="n">
+      <c r="M2" s="80" t="n">
         <v>3124.04</v>
       </c>
-      <c r="M2" s="80" t="n">
+      <c r="N2" s="80" t="n">
         <v>3088.87</v>
       </c>
-      <c r="N2" s="80" t="n">
+      <c r="O2" s="80" t="n">
         <v>3116.39</v>
       </c>
-      <c r="O2" s="80" t="n">
+      <c r="P2" s="80" t="n">
         <v>3158.54</v>
       </c>
-      <c r="P2" s="80" t="n">
+      <c r="Q2" s="80" t="n">
         <v>3157.97</v>
       </c>
-      <c r="Q2" s="80" t="n">
+      <c r="R2" s="80" t="n">
         <v>3171.15</v>
       </c>
-      <c r="R2" s="80" t="n">
+      <c r="S2" s="80" t="n">
         <v>3154.03</v>
       </c>
-      <c r="S2" s="80" t="n">
+      <c r="T2" s="80" t="n">
         <v>3122.4</v>
       </c>
-      <c r="T2" s="80" t="n">
+      <c r="U2" s="80" t="n">
         <v>3119.9</v>
       </c>
-      <c r="U2" s="80" t="n">
+      <c r="V2" s="80" t="n">
         <v>3145.77</v>
       </c>
-      <c r="V2" s="80" t="n">
+      <c r="W2" s="80" t="n">
         <v>3148.02</v>
       </c>
-      <c r="W2" s="80" t="n">
+      <c r="X2" s="80" t="n">
         <v>3154.55</v>
       </c>
-      <c r="X2" s="80" t="n">
+      <c r="Y2" s="80" t="n">
         <v>3154.32</v>
       </c>
-      <c r="Y2" s="80" t="n">
+      <c r="Z2" s="80" t="n">
         <v>3128.48</v>
       </c>
-      <c r="Z2" s="80" t="n">
+      <c r="AA2" s="80" t="n">
         <v>3147.74</v>
       </c>
-      <c r="AA2" s="80" t="n">
+      <c r="AB2" s="80" t="n">
         <v>3140.72</v>
       </c>
-      <c r="AB2" s="80" t="n">
+      <c r="AC2" s="80" t="n">
         <v>3104.82</v>
       </c>
-      <c r="AC2" s="80" t="n">
+      <c r="AD2" s="80" t="n">
         <v>3113.04</v>
       </c>
-      <c r="AD2" s="80" t="n">
+      <c r="AE2" s="80" t="n">
         <v>3088.64</v>
-      </c>
-      <c r="AE2" s="80" t="n">
-        <v>3052.9</v>
       </c>
     </row>
     <row r="3">
@@ -1704,127 +1704,127 @@
       </c>
       <c r="B3" s="81" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C3" s="82" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C3" s="82" t="inlineStr">
+      <c r="D3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D3" s="81" t="inlineStr">
+      <c r="E3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E3" s="81" t="inlineStr">
+      <c r="F3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F3" s="82" t="inlineStr">
+      <c r="G3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G3" s="81" t="inlineStr">
+      <c r="H3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H3" s="81" t="inlineStr">
+      <c r="I3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I3" s="81" t="inlineStr">
+      <c r="J3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J3" s="81" t="inlineStr">
+      <c r="K3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K3" s="81" t="inlineStr">
+      <c r="L3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L3" s="81" t="inlineStr">
+      <c r="M3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M3" s="81" t="inlineStr">
+      <c r="N3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N3" s="81" t="inlineStr">
+      <c r="O3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O3" s="82" t="inlineStr">
+      <c r="P3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P3" s="82" t="inlineStr">
+      <c r="Q3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q3" s="83" t="inlineStr">
+      <c r="R3" s="83" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R3" s="83" t="inlineStr">
+      <c r="S3" s="83" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S3" s="82" t="inlineStr">
+      <c r="T3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T3" s="82" t="inlineStr">
+      <c r="U3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U3" s="82" t="inlineStr">
+      <c r="V3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V3" s="82" t="inlineStr">
+      <c r="W3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W3" s="82" t="inlineStr">
+      <c r="X3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X3" s="83" t="inlineStr">
+      <c r="Y3" s="83" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y3" s="82" t="inlineStr">
+      <c r="Z3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="Z3" s="83" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AA3" s="83" t="inlineStr">
@@ -1860,94 +1860,94 @@
         </is>
       </c>
       <c r="B4" s="80" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C4" s="80" t="n">
         <v>-0.76</v>
       </c>
-      <c r="C4" s="80" t="n">
+      <c r="D4" s="80" t="n">
         <v>0.08</v>
       </c>
-      <c r="D4" s="80" t="n">
+      <c r="E4" s="80" t="n">
         <v>-0.54</v>
       </c>
-      <c r="E4" s="80" t="n">
+      <c r="F4" s="80" t="n">
         <v>-0.83</v>
       </c>
-      <c r="F4" s="80" t="n">
+      <c r="G4" s="80" t="n">
         <v>0.41</v>
       </c>
-      <c r="G4" s="80" t="n">
+      <c r="H4" s="80" t="n">
         <v>-0.27</v>
       </c>
-      <c r="H4" s="80" t="n">
+      <c r="I4" s="80" t="n">
         <v>-0.16</v>
       </c>
-      <c r="I4" s="80" t="n">
+      <c r="J4" s="80" t="n">
         <v>-0.62</v>
       </c>
-      <c r="J4" s="80" t="n">
+      <c r="K4" s="80" t="n">
         <v>0.05</v>
       </c>
-      <c r="K4" s="80" t="n">
+      <c r="L4" s="80" t="n">
         <v>-0.46</v>
       </c>
-      <c r="L4" s="80" t="n">
+      <c r="M4" s="80" t="n">
         <v>1.14</v>
       </c>
-      <c r="M4" s="80" t="n">
+      <c r="N4" s="80" t="n">
         <v>-0.88</v>
       </c>
-      <c r="N4" s="80" t="n">
+      <c r="O4" s="80" t="n">
         <v>-1.33</v>
       </c>
-      <c r="O4" s="80" t="n">
+      <c r="P4" s="80" t="n">
         <v>0.02</v>
       </c>
-      <c r="P4" s="80" t="n">
+      <c r="Q4" s="80" t="n">
         <v>-0.42</v>
       </c>
-      <c r="Q4" s="80" t="n">
+      <c r="R4" s="80" t="n">
         <v>0.54</v>
       </c>
-      <c r="R4" s="80" t="n">
+      <c r="S4" s="80" t="n">
         <v>1.01</v>
       </c>
-      <c r="S4" s="80" t="n">
+      <c r="T4" s="80" t="n">
         <v>0.08</v>
       </c>
-      <c r="T4" s="80" t="n">
+      <c r="U4" s="80" t="n">
         <v>-0.82</v>
       </c>
-      <c r="U4" s="80" t="n">
+      <c r="V4" s="80" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="V4" s="80" t="n">
+      <c r="W4" s="80" t="n">
         <v>-0.21</v>
       </c>
-      <c r="W4" s="80" t="n">
+      <c r="X4" s="80" t="n">
         <v>0.01</v>
       </c>
-      <c r="X4" s="80" t="n">
+      <c r="Y4" s="80" t="n">
         <v>0.83</v>
       </c>
-      <c r="Y4" s="80" t="n">
+      <c r="Z4" s="80" t="n">
         <v>-0.61</v>
       </c>
-      <c r="Z4" s="80" t="n">
+      <c r="AA4" s="80" t="n">
         <v>0.22</v>
       </c>
-      <c r="AA4" s="80" t="n">
+      <c r="AB4" s="80" t="n">
         <v>1.16</v>
       </c>
-      <c r="AB4" s="80" t="n">
+      <c r="AC4" s="80" t="n">
         <v>-0.26</v>
       </c>
-      <c r="AC4" s="80" t="n">
+      <c r="AD4" s="80" t="n">
         <v>0.79</v>
       </c>
-      <c r="AD4" s="80" t="n">
+      <c r="AE4" s="80" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AE4" s="80" t="n">
-        <v>0.27</v>
       </c>
     </row>
     <row r="5">
@@ -1957,94 +1957,94 @@
         </is>
       </c>
       <c r="B5" s="80" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C5" s="80" t="n">
         <v>-1.32</v>
       </c>
-      <c r="C5" s="80" t="n">
+      <c r="D5" s="80" t="n">
         <v>0.17</v>
       </c>
-      <c r="D5" s="80" t="n">
+      <c r="E5" s="80" t="n">
         <v>0.71</v>
       </c>
-      <c r="E5" s="80" t="n">
+      <c r="F5" s="80" t="n">
         <v>0.84</v>
       </c>
-      <c r="F5" s="80" t="n">
+      <c r="G5" s="80" t="n">
         <v>1.42</v>
       </c>
-      <c r="G5" s="80" t="n">
+      <c r="H5" s="80" t="n">
         <v>1.29</v>
       </c>
-      <c r="H5" s="80" t="n">
+      <c r="I5" s="80" t="n">
         <v>1.98</v>
       </c>
-      <c r="I5" s="80" t="n">
+      <c r="J5" s="80" t="n">
         <v>2.54</v>
       </c>
-      <c r="J5" s="80" t="n">
+      <c r="K5" s="80" t="n">
         <v>5.18</v>
       </c>
-      <c r="K5" s="80" t="n">
+      <c r="L5" s="80" t="n">
         <v>3.12</v>
       </c>
-      <c r="L5" s="80" t="n">
+      <c r="M5" s="80" t="n">
         <v>4.94</v>
       </c>
-      <c r="M5" s="80" t="n">
+      <c r="N5" s="80" t="n">
         <v>2.8</v>
       </c>
-      <c r="N5" s="80" t="n">
+      <c r="O5" s="80" t="n">
         <v>4.28</v>
       </c>
-      <c r="O5" s="80" t="n">
+      <c r="P5" s="80" t="n">
         <v>7.03</v>
       </c>
-      <c r="P5" s="80" t="n">
+      <c r="Q5" s="80" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="Q5" s="80" t="n">
+      <c r="R5" s="80" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="R5" s="80" t="n">
+      <c r="S5" s="80" t="n">
         <v>10.05</v>
       </c>
-      <c r="S5" s="80" t="n">
+      <c r="T5" s="80" t="n">
         <v>10.34</v>
       </c>
-      <c r="T5" s="80" t="n">
+      <c r="U5" s="80" t="n">
         <v>11.84</v>
       </c>
-      <c r="U5" s="80" t="n">
+      <c r="V5" s="80" t="n">
         <v>16.42</v>
       </c>
-      <c r="V5" s="80" t="n">
+      <c r="W5" s="80" t="n">
         <v>15.31</v>
       </c>
-      <c r="W5" s="80" t="n">
+      <c r="X5" s="80" t="n">
         <v>13.85</v>
       </c>
-      <c r="X5" s="80" t="n">
+      <c r="Y5" s="80" t="n">
         <v>13.12</v>
       </c>
-      <c r="Y5" s="80" t="n">
+      <c r="Z5" s="80" t="n">
         <v>10.53</v>
       </c>
-      <c r="Z5" s="80" t="n">
+      <c r="AA5" s="80" t="n">
         <v>9.17</v>
       </c>
-      <c r="AA5" s="80" t="n">
+      <c r="AB5" s="80" t="n">
         <v>7.92</v>
       </c>
-      <c r="AB5" s="80" t="n">
+      <c r="AC5" s="80" t="n">
         <v>6.84</v>
       </c>
-      <c r="AC5" s="80" t="n">
+      <c r="AD5" s="80" t="n">
         <v>10.36</v>
       </c>
-      <c r="AD5" s="80" t="n">
+      <c r="AE5" s="80" t="n">
         <v>11.46</v>
-      </c>
-      <c r="AE5" s="80" t="n">
-        <v>10.76</v>
       </c>
     </row>
     <row r="6">
@@ -2054,94 +2054,94 @@
         </is>
       </c>
       <c r="B6" s="80" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C6" s="80" t="n">
         <v>2.08</v>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="D6" s="80" t="n">
         <v>2.77</v>
       </c>
-      <c r="D6" s="80" t="n">
+      <c r="E6" s="80" t="n">
         <v>2.57</v>
       </c>
-      <c r="E6" s="80" t="n">
+      <c r="F6" s="80" t="n">
         <v>1.41</v>
       </c>
-      <c r="F6" s="80" t="n">
+      <c r="G6" s="80" t="n">
         <v>1.96</v>
       </c>
-      <c r="G6" s="80" t="n">
+      <c r="H6" s="80" t="n">
         <v>1.61</v>
       </c>
-      <c r="H6" s="80" t="n">
+      <c r="I6" s="80" t="n">
         <v>2.16</v>
       </c>
-      <c r="I6" s="80" t="n">
+      <c r="J6" s="80" t="n">
         <v>1.75</v>
       </c>
-      <c r="J6" s="80" t="n">
+      <c r="K6" s="80" t="n">
         <v>2.62</v>
       </c>
-      <c r="K6" s="80" t="n">
+      <c r="L6" s="80" t="n">
         <v>2.26</v>
       </c>
-      <c r="L6" s="80" t="n">
+      <c r="M6" s="80" t="n">
         <v>2.03</v>
       </c>
-      <c r="M6" s="80" t="n">
+      <c r="N6" s="80" t="n">
         <v>1.49</v>
       </c>
-      <c r="N6" s="80" t="n">
+      <c r="O6" s="80" t="n">
         <v>1.58</v>
       </c>
-      <c r="O6" s="80" t="n">
+      <c r="P6" s="80" t="n">
         <v>2.94</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="Q6" s="80" t="n">
         <v>3.39</v>
       </c>
-      <c r="Q6" s="80" t="n">
+      <c r="R6" s="80" t="n">
         <v>3.94</v>
       </c>
-      <c r="R6" s="80" t="n">
+      <c r="S6" s="80" t="n">
         <v>2.64</v>
       </c>
-      <c r="S6" s="80" t="n">
+      <c r="T6" s="80" t="n">
         <v>2.17</v>
       </c>
-      <c r="T6" s="80" t="n">
+      <c r="U6" s="80" t="n">
         <v>2.41</v>
       </c>
-      <c r="U6" s="80" t="n">
+      <c r="V6" s="80" t="n">
         <v>3.51</v>
       </c>
-      <c r="V6" s="80" t="n">
+      <c r="W6" s="80" t="n">
         <v>3.1</v>
       </c>
-      <c r="W6" s="80" t="n">
+      <c r="X6" s="80" t="n">
         <v>3.35</v>
       </c>
-      <c r="X6" s="80" t="n">
+      <c r="Y6" s="80" t="n">
         <v>3.17</v>
       </c>
-      <c r="Y6" s="80" t="n">
+      <c r="Z6" s="80" t="n">
         <v>2.29</v>
       </c>
-      <c r="Z6" s="80" t="n">
+      <c r="AA6" s="80" t="n">
         <v>3.86</v>
       </c>
-      <c r="AA6" s="80" t="n">
+      <c r="AB6" s="80" t="n">
         <v>4.36</v>
       </c>
-      <c r="AB6" s="80" t="n">
+      <c r="AC6" s="80" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC6" s="80" t="n">
+      <c r="AD6" s="80" t="n">
         <v>3.12</v>
       </c>
-      <c r="AD6" s="80" t="n">
+      <c r="AE6" s="80" t="n">
         <v>2.22</v>
-      </c>
-      <c r="AE6" s="80" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="7">
@@ -2151,94 +2151,94 @@
         </is>
       </c>
       <c r="B7" s="80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C7" s="80" t="n">
         <v>1.05</v>
       </c>
-      <c r="C7" s="80" t="n">
+      <c r="D7" s="80" t="n">
         <v>1.06</v>
       </c>
-      <c r="D7" s="80" t="n">
+      <c r="E7" s="80" t="n">
         <v>1.26</v>
       </c>
-      <c r="E7" s="80" t="n">
+      <c r="F7" s="80" t="n">
         <v>1.02</v>
       </c>
-      <c r="F7" s="80" t="n">
+      <c r="G7" s="80" t="n">
         <v>1.09</v>
       </c>
-      <c r="G7" s="80" t="n">
+      <c r="H7" s="80" t="n">
         <v>1.22</v>
       </c>
-      <c r="H7" s="80" t="n">
+      <c r="I7" s="80" t="n">
         <v>1.05</v>
       </c>
-      <c r="I7" s="80" t="n">
+      <c r="J7" s="80" t="n">
         <v>1.06</v>
       </c>
-      <c r="J7" s="80" t="n">
+      <c r="K7" s="80" t="n">
         <v>1.03</v>
       </c>
-      <c r="K7" s="80" t="n">
+      <c r="L7" s="80" t="n">
         <v>1.08</v>
-      </c>
-      <c r="L7" s="80" t="n">
-        <v>1.12</v>
       </c>
       <c r="M7" s="80" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" s="80" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O7" s="80" t="n">
         <v>1.23</v>
       </c>
-      <c r="O7" s="80" t="n">
+      <c r="P7" s="80" t="n">
         <v>1.19</v>
       </c>
-      <c r="P7" s="80" t="n">
+      <c r="Q7" s="80" t="n">
         <v>1.15</v>
       </c>
-      <c r="Q7" s="80" t="n">
+      <c r="R7" s="80" t="n">
         <v>1.42</v>
       </c>
-      <c r="R7" s="80" t="n">
+      <c r="S7" s="80" t="n">
         <v>1.27</v>
       </c>
-      <c r="S7" s="80" t="n">
+      <c r="T7" s="80" t="n">
         <v>1.23</v>
       </c>
-      <c r="T7" s="80" t="n">
+      <c r="U7" s="80" t="n">
         <v>1.11</v>
       </c>
-      <c r="U7" s="80" t="n">
+      <c r="V7" s="80" t="n">
         <v>1.19</v>
-      </c>
-      <c r="V7" s="80" t="n">
-        <v>1.31</v>
       </c>
       <c r="W7" s="80" t="n">
         <v>1.31</v>
       </c>
       <c r="X7" s="80" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Y7" s="80" t="n">
         <v>1.29</v>
       </c>
-      <c r="Y7" s="80" t="n">
+      <c r="Z7" s="80" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z7" s="80" t="n">
+      <c r="AA7" s="80" t="n">
         <v>1.39</v>
       </c>
-      <c r="AA7" s="80" t="n">
+      <c r="AB7" s="80" t="n">
         <v>1.59</v>
       </c>
-      <c r="AB7" s="80" t="n">
+      <c r="AC7" s="80" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC7" s="80" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AD7" s="80" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE7" s="80" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE7" s="80" t="n">
-        <v>1.16</v>
       </c>
     </row>
     <row r="8">
@@ -2248,94 +2248,94 @@
         </is>
       </c>
       <c r="B8" s="80" t="n">
+        <v>6919.21</v>
+      </c>
+      <c r="C8" s="80" t="n">
         <v>7029.28</v>
       </c>
-      <c r="C8" s="80" t="n">
+      <c r="D8" s="80" t="n">
         <v>7168.32</v>
       </c>
-      <c r="D8" s="80" t="n">
+      <c r="E8" s="80" t="n">
         <v>8459.32</v>
       </c>
-      <c r="E8" s="80" t="n">
+      <c r="F8" s="80" t="n">
         <v>6885.79</v>
       </c>
-      <c r="F8" s="80" t="n">
+      <c r="G8" s="80" t="n">
         <v>7457.13</v>
       </c>
-      <c r="G8" s="80" t="n">
+      <c r="H8" s="80" t="n">
         <v>8306.99</v>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="I8" s="80" t="n">
         <v>7149.59</v>
       </c>
-      <c r="I8" s="80" t="n">
+      <c r="J8" s="80" t="n">
         <v>7232.88</v>
       </c>
-      <c r="J8" s="80" t="n">
+      <c r="K8" s="80" t="n">
         <v>7083.91</v>
       </c>
-      <c r="K8" s="80" t="n">
+      <c r="L8" s="80" t="n">
         <v>7417.25</v>
       </c>
-      <c r="L8" s="80" t="n">
+      <c r="M8" s="80" t="n">
         <v>7748.07</v>
       </c>
-      <c r="M8" s="80" t="n">
+      <c r="N8" s="80" t="n">
         <v>7639.24</v>
       </c>
-      <c r="N8" s="80" t="n">
+      <c r="O8" s="80" t="n">
         <v>8477.030000000001</v>
       </c>
-      <c r="O8" s="80" t="n">
+      <c r="P8" s="80" t="n">
         <v>8312.84</v>
       </c>
-      <c r="P8" s="80" t="n">
+      <c r="Q8" s="80" t="n">
         <v>7992.46</v>
       </c>
-      <c r="Q8" s="80" t="n">
+      <c r="R8" s="80" t="n">
         <v>9954.440000000001</v>
       </c>
-      <c r="R8" s="80" t="n">
+      <c r="S8" s="80" t="n">
         <v>8873.639999999999</v>
       </c>
-      <c r="S8" s="80" t="n">
+      <c r="T8" s="80" t="n">
         <v>8477.879999999999</v>
       </c>
-      <c r="T8" s="80" t="n">
+      <c r="U8" s="80" t="n">
         <v>7610.71</v>
       </c>
-      <c r="U8" s="80" t="n">
+      <c r="V8" s="80" t="n">
         <v>8245.620000000001</v>
       </c>
-      <c r="V8" s="80" t="n">
+      <c r="W8" s="80" t="n">
         <v>9097.200000000001</v>
       </c>
-      <c r="W8" s="80" t="n">
+      <c r="X8" s="80" t="n">
         <v>9125.33</v>
       </c>
-      <c r="X8" s="80" t="n">
+      <c r="Y8" s="80" t="n">
         <v>9011.16</v>
       </c>
-      <c r="Y8" s="80" t="n">
+      <c r="Z8" s="80" t="n">
         <v>8643.83</v>
       </c>
-      <c r="Z8" s="80" t="n">
+      <c r="AA8" s="80" t="n">
         <v>9686.940000000001</v>
       </c>
-      <c r="AA8" s="80" t="n">
+      <c r="AB8" s="80" t="n">
         <v>11024.59</v>
       </c>
-      <c r="AB8" s="80" t="n">
+      <c r="AC8" s="80" t="n">
         <v>10306.49</v>
       </c>
-      <c r="AC8" s="80" t="n">
+      <c r="AD8" s="80" t="n">
         <v>12111.31</v>
       </c>
-      <c r="AD8" s="80" t="n">
+      <c r="AE8" s="80" t="n">
         <v>10863.78</v>
-      </c>
-      <c r="AE8" s="80" t="n">
-        <v>7742.96</v>
       </c>
     </row>
     <row r="9">
@@ -2345,94 +2345,94 @@
         </is>
       </c>
       <c r="B9" s="84" t="n">
-        <v>0.468</v>
+        <v>0.4886</v>
       </c>
       <c r="C9" s="84" t="n">
-        <v>0.489</v>
+        <v>0.4682</v>
       </c>
       <c r="D9" s="84" t="n">
-        <v>0.4831</v>
+        <v>0.4893</v>
       </c>
       <c r="E9" s="84" t="n">
-        <v>0.4935</v>
+        <v>0.4833</v>
       </c>
       <c r="F9" s="84" t="n">
+        <v>0.4934</v>
+      </c>
+      <c r="G9" s="84" t="n">
         <v>0.5314</v>
       </c>
-      <c r="G9" s="84" t="n">
-        <v>0.5031</v>
-      </c>
       <c r="H9" s="84" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="I9" s="84" t="n">
-        <v>0.5158</v>
+        <v>0.5115</v>
       </c>
       <c r="J9" s="84" t="n">
-        <v>0.5389</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="K9" s="84" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5387</v>
       </c>
       <c r="L9" s="84" t="n">
-        <v>0.5625</v>
+        <v>0.5327</v>
       </c>
       <c r="M9" s="84" t="n">
-        <v>0.5204</v>
+        <v>0.5623</v>
       </c>
       <c r="N9" s="84" t="n">
-        <v>0.5564</v>
+        <v>0.5203</v>
       </c>
       <c r="O9" s="84" t="n">
-        <v>0.6167</v>
+        <v>0.5562</v>
       </c>
       <c r="P9" s="84" t="n">
-        <v>0.6148</v>
+        <v>0.6165</v>
       </c>
       <c r="Q9" s="84" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="R9" s="84" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6374</v>
       </c>
       <c r="S9" s="84" t="n">
-        <v>0.5764</v>
+        <v>0.6182</v>
       </c>
       <c r="T9" s="84" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5762</v>
       </c>
       <c r="U9" s="84" t="n">
-        <v>0.6073</v>
+        <v>0.574</v>
       </c>
       <c r="V9" s="84" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="W9" s="84" t="n">
-        <v>0.628</v>
+        <v>0.6093</v>
       </c>
       <c r="X9" s="84" t="n">
-        <v>0.6389</v>
+        <v>0.6279</v>
       </c>
       <c r="Y9" s="84" t="n">
-        <v>0.6017</v>
+        <v>0.6387</v>
       </c>
       <c r="Z9" s="84" t="n">
-        <v>0.6405</v>
+        <v>0.6016</v>
       </c>
       <c r="AA9" s="84" t="n">
-        <v>0.6364</v>
+        <v>0.6403</v>
       </c>
       <c r="AB9" s="84" t="n">
-        <v>0.5874</v>
+        <v>0.6362</v>
       </c>
       <c r="AC9" s="84" t="n">
-        <v>0.6054</v>
+        <v>0.5873</v>
       </c>
       <c r="AD9" s="84" t="n">
-        <v>0.574</v>
+        <v>0.6052</v>
       </c>
       <c r="AE9" s="84" t="n">
-        <v>0.5298</v>
+        <v>0.5739</v>
       </c>
     </row>
     <row r="10">
@@ -2442,94 +2442,94 @@
         </is>
       </c>
       <c r="B10" s="84" t="n">
+        <v>0.651015</v>
+      </c>
+      <c r="C10" s="84" t="n">
         <v>0.597652</v>
       </c>
-      <c r="C10" s="84" t="n">
+      <c r="D10" s="84" t="n">
         <v>0.71348</v>
       </c>
-      <c r="D10" s="84" t="n">
+      <c r="E10" s="84" t="n">
         <v>0.702858</v>
       </c>
-      <c r="E10" s="84" t="n">
+      <c r="F10" s="84" t="n">
         <v>0.778069</v>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="G10" s="84" t="n">
         <v>0.855721</v>
       </c>
-      <c r="G10" s="84" t="n">
+      <c r="H10" s="84" t="n">
         <v>0.829256</v>
       </c>
-      <c r="H10" s="84" t="n">
+      <c r="I10" s="84" t="n">
         <v>0.845056</v>
       </c>
-      <c r="I10" s="84" t="n">
+      <c r="J10" s="84" t="n">
         <v>0.85697</v>
       </c>
-      <c r="J10" s="84" t="n">
+      <c r="K10" s="84" t="n">
         <v>0.893103</v>
       </c>
-      <c r="K10" s="84" t="n">
+      <c r="L10" s="84" t="n">
         <v>0.891944</v>
       </c>
-      <c r="L10" s="84" t="n">
+      <c r="M10" s="84" t="n">
         <v>0.92065</v>
       </c>
-      <c r="M10" s="84" t="n">
+      <c r="N10" s="84" t="n">
         <v>0.8739130000000001</v>
       </c>
-      <c r="N10" s="84" t="n">
+      <c r="O10" s="84" t="n">
         <v>0.90562</v>
       </c>
-      <c r="O10" s="84" t="n">
+      <c r="P10" s="84" t="n">
         <v>0.9932029999999999</v>
       </c>
-      <c r="P10" s="84" t="n">
+      <c r="Q10" s="84" t="n">
         <v>0.993279</v>
       </c>
-      <c r="Q10" s="84" t="n">
+      <c r="R10" s="84" t="n">
         <v>0.999889</v>
       </c>
-      <c r="R10" s="84" t="n">
+      <c r="S10" s="84" t="n">
         <v>0.99874</v>
       </c>
-      <c r="S10" s="84" t="n">
+      <c r="T10" s="84" t="n">
         <v>0.944308</v>
       </c>
-      <c r="T10" s="84" t="n">
+      <c r="U10" s="84" t="n">
         <v>0.945653</v>
       </c>
-      <c r="U10" s="84" t="n">
+      <c r="V10" s="84" t="n">
         <v>0.992076</v>
       </c>
-      <c r="V10" s="84" t="n">
+      <c r="W10" s="84" t="n">
         <v>0.995193</v>
       </c>
-      <c r="W10" s="84" t="n">
+      <c r="X10" s="84" t="n">
         <v>0.999117</v>
       </c>
-      <c r="X10" s="84" t="n">
+      <c r="Y10" s="84" t="n">
         <v>0.999896</v>
       </c>
-      <c r="Y10" s="84" t="n">
+      <c r="Z10" s="84" t="n">
         <v>0.985627</v>
       </c>
-      <c r="Z10" s="84" t="n">
+      <c r="AA10" s="84" t="n">
         <v>0.999887</v>
       </c>
-      <c r="AA10" s="84" t="n">
+      <c r="AB10" s="84" t="n">
         <v>0.999935</v>
       </c>
-      <c r="AB10" s="84" t="n">
+      <c r="AC10" s="84" t="n">
         <v>0.989797</v>
       </c>
-      <c r="AC10" s="84" t="n">
+      <c r="AD10" s="84" t="n">
         <v>0.999458</v>
       </c>
-      <c r="AD10" s="84" t="n">
+      <c r="AE10" s="84" t="n">
         <v>0.99831</v>
-      </c>
-      <c r="AE10" s="84" t="n">
-        <v>0.891613</v>
       </c>
     </row>
     <row r="11" ht="19" customFormat="1" customHeight="1" s="30">
@@ -2539,94 +2539,94 @@
         </is>
       </c>
       <c r="B11" s="86" t="n">
+        <v>-0.03939999999999999</v>
+      </c>
+      <c r="C11" s="86" t="n">
+        <v>-0.03119999999999998</v>
+      </c>
+      <c r="D11" s="86" t="n">
         <v>-0.03139999999999998</v>
       </c>
-      <c r="C11" s="86" t="n">
-        <v>-0.03159999999999999</v>
-      </c>
-      <c r="D11" s="86" t="n">
-        <v>-0.03180000000000002</v>
-      </c>
       <c r="E11" s="86" t="n">
-        <v>-0.03280000000000002</v>
+        <v>-0.03149999999999997</v>
       </c>
       <c r="F11" s="86" t="n">
-        <v>-0.0358</v>
+        <v>-0.03239999999999998</v>
       </c>
       <c r="G11" s="86" t="n">
-        <v>-0.0363</v>
+        <v>-0.03560000000000002</v>
       </c>
       <c r="H11" s="86" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.03600000000000003</v>
       </c>
       <c r="I11" s="86" t="n">
-        <v>-0.03800000000000003</v>
+        <v>-0.0373</v>
       </c>
       <c r="J11" s="86" t="n">
+        <v>-0.03779999999999997</v>
+      </c>
+      <c r="K11" s="86" t="n">
+        <v>-0.03810000000000002</v>
+      </c>
+      <c r="L11" s="86" t="n">
         <v>-0.0383</v>
       </c>
-      <c r="K11" s="86" t="n">
-        <v>-0.0386</v>
-      </c>
-      <c r="L11" s="86" t="n">
-        <v>-0.03920000000000001</v>
-      </c>
       <c r="M11" s="86" t="n">
-        <v>-0.0428</v>
+        <v>-0.03889999999999999</v>
       </c>
       <c r="N11" s="86" t="n">
-        <v>-0.04610000000000003</v>
+        <v>-0.04250000000000001</v>
       </c>
       <c r="O11" s="86" t="n">
-        <v>-0.04820000000000002</v>
+        <v>-0.04569999999999999</v>
       </c>
       <c r="P11" s="86" t="n">
-        <v>-0.04790000000000003</v>
+        <v>-0.04779999999999998</v>
       </c>
       <c r="Q11" s="86" t="n">
-        <v>-0.0512</v>
+        <v>-0.04739999999999997</v>
       </c>
       <c r="R11" s="86" t="n">
-        <v>-0.05759999999999998</v>
+        <v>-0.05080000000000001</v>
       </c>
       <c r="S11" s="86" t="n">
-        <v>-0.05930000000000002</v>
+        <v>-0.05710000000000001</v>
       </c>
       <c r="T11" s="86" t="n">
-        <v>-0.05880000000000002</v>
+        <v>-0.05879999999999999</v>
       </c>
       <c r="U11" s="86" t="n">
-        <v>-0.0562</v>
+        <v>-0.05839999999999998</v>
       </c>
       <c r="V11" s="86" t="n">
-        <v>-0.05679999999999999</v>
+        <v>-0.05579999999999999</v>
       </c>
       <c r="W11" s="86" t="n">
-        <v>-0.05460000000000001</v>
+        <v>-0.05640000000000001</v>
       </c>
       <c r="X11" s="86" t="n">
-        <v>-0.05609999999999998</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="Y11" s="86" t="n">
-        <v>-0.0575</v>
+        <v>-0.0557</v>
       </c>
       <c r="Z11" s="86" t="n">
-        <v>-0.06410000000000002</v>
+        <v>-0.05710000000000001</v>
       </c>
       <c r="AA11" s="86" t="n">
-        <v>-0.06640000000000001</v>
+        <v>-0.06369999999999998</v>
       </c>
       <c r="AB11" s="86" t="n">
-        <v>-0.06840000000000002</v>
+        <v>-0.06610000000000002</v>
       </c>
       <c r="AC11" s="86" t="n">
-        <v>-0.06969999999999998</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="AD11" s="86" t="n">
-        <v>-0.06649999999999998</v>
+        <v>-0.06940000000000002</v>
       </c>
       <c r="AE11" s="86" t="n">
-        <v>-0.06799999999999998</v>
+        <v>-0.06619999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -2636,94 +2636,94 @@
         </is>
       </c>
       <c r="B12" s="80" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="C12" s="80" t="n">
         <v>21.25</v>
       </c>
-      <c r="C12" s="80" t="n">
+      <c r="D12" s="80" t="n">
         <v>16.12</v>
       </c>
-      <c r="D12" s="80" t="n">
+      <c r="E12" s="80" t="n">
         <v>12.18</v>
       </c>
-      <c r="E12" s="80" t="n">
+      <c r="F12" s="80" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="F12" s="80" t="n">
+      <c r="G12" s="80" t="n">
         <v>5.83</v>
       </c>
-      <c r="G12" s="80" t="n">
+      <c r="H12" s="80" t="n">
         <v>4.59</v>
       </c>
-      <c r="H12" s="80" t="n">
+      <c r="I12" s="80" t="n">
         <v>3.05</v>
       </c>
-      <c r="I12" s="80" t="n">
+      <c r="J12" s="80" t="n">
         <v>1.6</v>
       </c>
-      <c r="J12" s="80" t="n">
+      <c r="K12" s="80" t="n">
         <v>0.16</v>
       </c>
-      <c r="K12" s="80" t="n">
+      <c r="L12" s="80" t="n">
         <v>-0.83</v>
       </c>
-      <c r="L12" s="80" t="n">
+      <c r="M12" s="80" t="n">
         <v>-1.95</v>
       </c>
-      <c r="M12" s="80" t="n">
+      <c r="N12" s="80" t="n">
         <v>-2.74</v>
       </c>
-      <c r="N12" s="80" t="n">
+      <c r="O12" s="80" t="n">
         <v>-4.61</v>
       </c>
-      <c r="O12" s="80" t="n">
+      <c r="P12" s="80" t="n">
         <v>-5.83</v>
       </c>
-      <c r="P12" s="80" t="n">
+      <c r="Q12" s="80" t="n">
         <v>-5.92</v>
       </c>
-      <c r="Q12" s="80" t="n">
+      <c r="R12" s="80" t="n">
         <v>-6</v>
       </c>
-      <c r="R12" s="80" t="n">
+      <c r="S12" s="80" t="n">
         <v>-5.67</v>
       </c>
-      <c r="S12" s="80" t="n">
+      <c r="T12" s="80" t="n">
         <v>-5.46</v>
       </c>
-      <c r="T12" s="80" t="n">
+      <c r="U12" s="80" t="n">
         <v>-6.13</v>
       </c>
-      <c r="U12" s="80" t="n">
+      <c r="V12" s="80" t="n">
         <v>-6.92</v>
       </c>
-      <c r="V12" s="80" t="n">
+      <c r="W12" s="80" t="n">
         <v>-6.98</v>
       </c>
-      <c r="W12" s="80" t="n">
+      <c r="X12" s="80" t="n">
         <v>-6.94</v>
       </c>
-      <c r="X12" s="80" t="n">
+      <c r="Y12" s="80" t="n">
         <v>-6.66</v>
       </c>
-      <c r="Y12" s="80" t="n">
+      <c r="Z12" s="80" t="n">
         <v>-6.18</v>
       </c>
-      <c r="Z12" s="80" t="n">
+      <c r="AA12" s="80" t="n">
         <v>-6.19</v>
       </c>
-      <c r="AA12" s="80" t="n">
+      <c r="AB12" s="80" t="n">
         <v>-5.57</v>
       </c>
-      <c r="AB12" s="80" t="n">
+      <c r="AC12" s="80" t="n">
         <v>-4.79</v>
       </c>
-      <c r="AC12" s="80" t="n">
+      <c r="AD12" s="80" t="n">
         <v>-4.44</v>
       </c>
-      <c r="AD12" s="80" t="n">
+      <c r="AE12" s="80" t="n">
         <v>-3.63</v>
-      </c>
-      <c r="AE12" s="80" t="n">
-        <v>-2.95</v>
       </c>
     </row>
     <row r="13">
@@ -2733,94 +2733,94 @@
         </is>
       </c>
       <c r="B13" s="87" t="n">
+        <v>-33.35</v>
+      </c>
+      <c r="C13" s="87" t="n">
         <v>-74.97</v>
       </c>
-      <c r="C13" s="87" t="n">
+      <c r="D13" s="87" t="n">
         <v>-7.05</v>
       </c>
-      <c r="D13" s="87" t="n">
+      <c r="E13" s="87" t="n">
         <v>67.73</v>
       </c>
-      <c r="E13" s="87" t="n">
+      <c r="F13" s="87" t="n">
         <v>-56.8</v>
       </c>
-      <c r="F13" s="87" t="n">
+      <c r="G13" s="87" t="n">
         <v>33.78</v>
       </c>
-      <c r="G13" s="87" t="n">
+      <c r="H13" s="87" t="n">
         <v>15.39</v>
       </c>
-      <c r="H13" s="87" t="n">
+      <c r="I13" s="87" t="n">
         <v>-77.98</v>
       </c>
-      <c r="I13" s="87" t="n">
+      <c r="J13" s="87" t="n">
         <v>10.45</v>
       </c>
-      <c r="J13" s="87" t="n">
+      <c r="K13" s="87" t="n">
         <v>33.99</v>
       </c>
-      <c r="K13" s="87" t="n">
+      <c r="L13" s="87" t="n">
         <v>-50.55</v>
       </c>
-      <c r="L13" s="87" t="n">
+      <c r="M13" s="87" t="n">
         <v>27.48</v>
       </c>
-      <c r="M13" s="87" t="n">
+      <c r="N13" s="87" t="n">
         <v>-40.39</v>
       </c>
-      <c r="N13" s="87" t="n">
+      <c r="O13" s="87" t="n">
         <v>-32.66</v>
       </c>
-      <c r="O13" s="87" t="n">
+      <c r="P13" s="87" t="n">
         <v>47.76</v>
       </c>
-      <c r="P13" s="87" t="n">
+      <c r="Q13" s="87" t="n">
         <v>-19.67</v>
       </c>
-      <c r="Q13" s="87" t="n">
+      <c r="R13" s="87" t="n">
         <v>53.33</v>
       </c>
-      <c r="R13" s="87" t="n">
+      <c r="S13" s="87" t="n">
         <v>139.56</v>
       </c>
-      <c r="S13" s="87" t="n">
+      <c r="T13" s="87" t="n">
         <v>60.67</v>
       </c>
-      <c r="T13" s="87" t="n">
+      <c r="U13" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="87" t="n">
+      <c r="V13" s="87" t="n">
         <v>-66.7</v>
       </c>
-      <c r="V13" s="87" t="n">
+      <c r="W13" s="87" t="n">
         <v>-45.91</v>
       </c>
-      <c r="W13" s="87" t="n">
+      <c r="X13" s="87" t="n">
         <v>-63.04</v>
       </c>
-      <c r="X13" s="87" t="n">
+      <c r="Y13" s="87" t="n">
         <v>80.14</v>
       </c>
-      <c r="Y13" s="87" t="n">
+      <c r="Z13" s="87" t="n">
         <v>-40.44</v>
       </c>
-      <c r="Z13" s="87" t="n">
+      <c r="AA13" s="87" t="n">
         <v>-21.4</v>
       </c>
-      <c r="AA13" s="87" t="n">
+      <c r="AB13" s="87" t="n">
         <v>93.16</v>
       </c>
-      <c r="AB13" s="87" t="n">
+      <c r="AC13" s="87" t="n">
         <v>-86.17</v>
       </c>
-      <c r="AC13" s="87" t="n">
+      <c r="AD13" s="87" t="n">
         <v>108.92</v>
       </c>
-      <c r="AD13" s="87" t="n">
+      <c r="AE13" s="87" t="n">
         <v>224.49</v>
-      </c>
-      <c r="AE13" s="87" t="n">
-        <v>3.49</v>
       </c>
     </row>
     <row r="14">
@@ -2830,64 +2830,64 @@
         </is>
       </c>
       <c r="B14" s="88" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C14" s="87" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" s="87" t="n">
         <v>23</v>
       </c>
-      <c r="D14" s="87" t="n">
-        <v>5</v>
-      </c>
       <c r="E14" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="87" t="n">
+      <c r="G14" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="87" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="87" t="n">
+      <c r="J14" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="87" t="n">
+      <c r="M14" s="87" t="n">
+        <v>95</v>
+      </c>
+      <c r="N14" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="87" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" s="87" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="87" t="n">
-        <v>86</v>
-      </c>
-      <c r="M14" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="87" t="n">
-        <v>0</v>
       </c>
       <c r="P14" s="87" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="R14" s="87" t="n">
-        <v>2</v>
-      </c>
       <c r="S14" s="87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" s="87" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="87" t="n">
         <v>0</v>
@@ -2908,16 +2908,16 @@
         <v>0</v>
       </c>
       <c r="AB14" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="AC14" s="87" t="n">
+      <c r="AD14" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" s="87" t="n">
+      <c r="AE14" s="87" t="n">
         <v>4</v>
-      </c>
-      <c r="AE14" s="87" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2927,25 +2927,25 @@
         </is>
       </c>
       <c r="B15" s="88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="87" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" s="87" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E15" s="87" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F15" s="87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" s="87" t="n">
         <v>5</v>
       </c>
       <c r="H15" s="87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" s="87" t="n">
         <v>0</v>
@@ -3024,28 +3024,28 @@
         </is>
       </c>
       <c r="B16" s="87" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="87" t="n">
+        <v>85</v>
+      </c>
+      <c r="F16" s="87" t="n">
+        <v>43</v>
+      </c>
+      <c r="G16" s="87" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="87" t="n">
         <v>2</v>
-      </c>
-      <c r="C16" s="87" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="87" t="n">
-        <v>85</v>
-      </c>
-      <c r="E16" s="87" t="n">
-        <v>43</v>
-      </c>
-      <c r="F16" s="87" t="n">
-        <v>11</v>
-      </c>
-      <c r="G16" s="87" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="87" t="n">
-        <v>0</v>
       </c>
       <c r="J16" s="87" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="AE16" s="87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3121,73 +3121,73 @@
         </is>
       </c>
       <c r="B17" s="87" t="n">
-        <v>314</v>
+        <v>14</v>
       </c>
       <c r="C17" s="87" t="n">
+        <v>315</v>
+      </c>
+      <c r="D17" s="87" t="n">
         <v>101</v>
       </c>
-      <c r="D17" s="87" t="n">
+      <c r="E17" s="87" t="n">
         <v>96</v>
       </c>
-      <c r="E17" s="87" t="n">
+      <c r="F17" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="F17" s="87" t="n">
+      <c r="G17" s="87" t="n">
         <v>151</v>
       </c>
-      <c r="G17" s="87" t="n">
+      <c r="H17" s="87" t="n">
         <v>46</v>
       </c>
-      <c r="H17" s="87" t="n">
+      <c r="I17" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="87" t="n">
+      <c r="J17" s="87" t="n">
         <v>32</v>
       </c>
-      <c r="J17" s="87" t="n">
+      <c r="K17" s="87" t="n">
         <v>17</v>
       </c>
-      <c r="K17" s="87" t="n">
+      <c r="L17" s="87" t="n">
         <v>19</v>
       </c>
-      <c r="L17" s="87" t="n">
-        <v>461</v>
-      </c>
       <c r="M17" s="87" t="n">
+        <v>462</v>
+      </c>
+      <c r="N17" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="N17" s="87" t="n">
+      <c r="O17" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="O17" s="87" t="n">
+      <c r="P17" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="P17" s="87" t="n">
+      <c r="Q17" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" s="87" t="n">
+      <c r="R17" s="87" t="n">
         <v>40</v>
       </c>
-      <c r="R17" s="87" t="n">
-        <v>12</v>
-      </c>
       <c r="S17" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="T17" s="87" t="n">
+      <c r="U17" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="U17" s="87" t="n">
+      <c r="V17" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="87" t="n">
+      <c r="W17" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="W17" s="87" t="n">
+      <c r="X17" s="87" t="n">
         <v>1</v>
-      </c>
-      <c r="X17" s="87" t="n">
-        <v>0</v>
       </c>
       <c r="Y17" s="87" t="n">
         <v>0</v>
@@ -3196,19 +3196,19 @@
         <v>0</v>
       </c>
       <c r="AA17" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" s="87" t="n">
+      <c r="AC17" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="AC17" s="87" t="n">
+      <c r="AD17" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="AD17" s="87" t="n">
+      <c r="AE17" s="87" t="n">
         <v>33</v>
-      </c>
-      <c r="AE17" s="87" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -3218,94 +3218,94 @@
         </is>
       </c>
       <c r="B18" s="87" t="n">
-        <v>706</v>
+        <v>162</v>
       </c>
       <c r="C18" s="87" t="n">
+        <v>707</v>
+      </c>
+      <c r="D18" s="87" t="n">
         <v>554</v>
       </c>
-      <c r="D18" s="87" t="n">
-        <v>665</v>
-      </c>
       <c r="E18" s="87" t="n">
+        <v>666</v>
+      </c>
+      <c r="F18" s="87" t="n">
         <v>209</v>
       </c>
-      <c r="F18" s="87" t="n">
-        <v>324</v>
-      </c>
       <c r="G18" s="87" t="n">
+        <v>325</v>
+      </c>
+      <c r="H18" s="87" t="n">
         <v>363</v>
       </c>
-      <c r="H18" s="87" t="n">
+      <c r="I18" s="87" t="n">
         <v>88</v>
       </c>
-      <c r="I18" s="87" t="n">
+      <c r="J18" s="87" t="n">
         <v>209</v>
       </c>
-      <c r="J18" s="87" t="n">
-        <v>169</v>
-      </c>
       <c r="K18" s="87" t="n">
+        <v>170</v>
+      </c>
+      <c r="L18" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="L18" s="87" t="n">
+      <c r="M18" s="87" t="n">
         <v>319</v>
       </c>
-      <c r="M18" s="87" t="n">
+      <c r="N18" s="87" t="n">
         <v>194</v>
       </c>
-      <c r="N18" s="87" t="n">
+      <c r="O18" s="87" t="n">
         <v>111</v>
       </c>
-      <c r="O18" s="87" t="n">
+      <c r="P18" s="87" t="n">
         <v>34</v>
       </c>
-      <c r="P18" s="87" t="n">
+      <c r="Q18" s="87" t="n">
         <v>53</v>
       </c>
-      <c r="Q18" s="87" t="n">
+      <c r="R18" s="87" t="n">
         <v>28</v>
       </c>
-      <c r="R18" s="87" t="n">
+      <c r="S18" s="87" t="n">
         <v>62</v>
       </c>
-      <c r="S18" s="87" t="n">
+      <c r="T18" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="T18" s="87" t="n">
+      <c r="U18" s="87" t="n">
         <v>31</v>
       </c>
-      <c r="U18" s="87" t="n">
+      <c r="V18" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="V18" s="87" t="n">
+      <c r="W18" s="87" t="n">
         <v>15</v>
       </c>
-      <c r="W18" s="87" t="n">
+      <c r="X18" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="X18" s="87" t="n">
+      <c r="Y18" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="Y18" s="87" t="n">
+      <c r="Z18" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="Z18" s="87" t="n">
+      <c r="AA18" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="AA18" s="87" t="n">
+      <c r="AB18" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="AB18" s="87" t="n">
+      <c r="AC18" s="87" t="n">
         <v>19</v>
       </c>
-      <c r="AC18" s="87" t="n">
+      <c r="AD18" s="87" t="n">
         <v>20</v>
       </c>
-      <c r="AD18" s="87" t="n">
+      <c r="AE18" s="87" t="n">
         <v>33</v>
-      </c>
-      <c r="AE18" s="87" t="n">
-        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -3315,94 +3315,94 @@
         </is>
       </c>
       <c r="B19" s="87" t="n">
+        <v>152</v>
+      </c>
+      <c r="C19" s="87" t="n">
         <v>207</v>
       </c>
-      <c r="C19" s="87" t="n">
+      <c r="D19" s="87" t="n">
         <v>286</v>
       </c>
-      <c r="D19" s="87" t="n">
+      <c r="E19" s="87" t="n">
         <v>1883</v>
       </c>
-      <c r="E19" s="87" t="n">
+      <c r="F19" s="87" t="n">
         <v>1032</v>
       </c>
-      <c r="F19" s="87" t="n">
+      <c r="G19" s="87" t="n">
         <v>658</v>
       </c>
-      <c r="G19" s="87" t="n">
+      <c r="H19" s="87" t="n">
         <v>641</v>
       </c>
-      <c r="H19" s="87" t="n">
+      <c r="I19" s="87" t="n">
         <v>191</v>
       </c>
-      <c r="I19" s="87" t="n">
+      <c r="J19" s="87" t="n">
         <v>335</v>
       </c>
-      <c r="J19" s="87" t="n">
+      <c r="K19" s="87" t="n">
         <v>312</v>
       </c>
-      <c r="K19" s="87" t="n">
+      <c r="L19" s="87" t="n">
         <v>409</v>
       </c>
-      <c r="L19" s="87" t="n">
+      <c r="M19" s="87" t="n">
         <v>215</v>
       </c>
-      <c r="M19" s="87" t="n">
+      <c r="N19" s="87" t="n">
         <v>370</v>
       </c>
-      <c r="N19" s="87" t="n">
+      <c r="O19" s="87" t="n">
         <v>272</v>
       </c>
-      <c r="O19" s="87" t="n">
+      <c r="P19" s="87" t="n">
         <v>78</v>
       </c>
-      <c r="P19" s="87" t="n">
+      <c r="Q19" s="87" t="n">
         <v>153</v>
       </c>
-      <c r="Q19" s="87" t="n">
+      <c r="R19" s="87" t="n">
         <v>74</v>
       </c>
-      <c r="R19" s="87" t="n">
+      <c r="S19" s="87" t="n">
         <v>51</v>
       </c>
-      <c r="S19" s="87" t="n">
+      <c r="T19" s="87" t="n">
         <v>114</v>
       </c>
-      <c r="T19" s="87" t="n">
+      <c r="U19" s="87" t="n">
         <v>111</v>
       </c>
-      <c r="U19" s="87" t="n">
+      <c r="V19" s="87" t="n">
         <v>74</v>
       </c>
-      <c r="V19" s="87" t="n">
+      <c r="W19" s="87" t="n">
         <v>95</v>
       </c>
-      <c r="W19" s="87" t="n">
+      <c r="X19" s="87" t="n">
         <v>66</v>
       </c>
-      <c r="X19" s="87" t="n">
+      <c r="Y19" s="87" t="n">
         <v>52</v>
       </c>
-      <c r="Y19" s="87" t="n">
+      <c r="Z19" s="87" t="n">
         <v>50</v>
       </c>
-      <c r="Z19" s="87" t="n">
+      <c r="AA19" s="87" t="n">
         <v>33</v>
       </c>
-      <c r="AA19" s="87" t="n">
+      <c r="AB19" s="87" t="n">
         <v>24</v>
       </c>
-      <c r="AB19" s="87" t="n">
+      <c r="AC19" s="87" t="n">
         <v>30</v>
       </c>
-      <c r="AC19" s="87" t="n">
+      <c r="AD19" s="87" t="n">
         <v>24</v>
       </c>
-      <c r="AD19" s="87" t="n">
+      <c r="AE19" s="87" t="n">
         <v>40</v>
-      </c>
-      <c r="AE19" s="87" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -3415,91 +3415,91 @@
         <v>44</v>
       </c>
       <c r="C20" s="87" t="n">
+        <v>44</v>
+      </c>
+      <c r="D20" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="D20" s="87" t="n">
+      <c r="E20" s="87" t="n">
         <v>145</v>
       </c>
-      <c r="E20" s="87" t="n">
+      <c r="F20" s="87" t="n">
         <v>89</v>
       </c>
-      <c r="F20" s="87" t="n">
+      <c r="G20" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="G20" s="87" t="n">
+      <c r="H20" s="87" t="n">
         <v>97</v>
       </c>
-      <c r="H20" s="87" t="n">
+      <c r="I20" s="87" t="n">
         <v>35</v>
       </c>
-      <c r="I20" s="87" t="n">
+      <c r="J20" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="J20" s="87" t="n">
+      <c r="K20" s="87" t="n">
         <v>55</v>
       </c>
-      <c r="K20" s="87" t="n">
+      <c r="L20" s="87" t="n">
         <v>71</v>
       </c>
-      <c r="L20" s="87" t="n">
+      <c r="M20" s="87" t="n">
         <v>35</v>
       </c>
-      <c r="M20" s="87" t="n">
+      <c r="N20" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="N20" s="87" t="n">
+      <c r="O20" s="87" t="n">
         <v>60</v>
       </c>
-      <c r="O20" s="87" t="n">
+      <c r="P20" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="P20" s="87" t="n">
+      <c r="Q20" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="Q20" s="87" t="n">
+      <c r="R20" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="R20" s="87" t="n">
+      <c r="S20" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="S20" s="87" t="n">
+      <c r="T20" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="T20" s="87" t="n">
+      <c r="U20" s="87" t="n">
         <v>29</v>
       </c>
-      <c r="U20" s="87" t="n">
+      <c r="V20" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="87" t="n">
+      <c r="W20" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="W20" s="87" t="n">
+      <c r="X20" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="X20" s="87" t="n">
+      <c r="Y20" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" s="87" t="n">
+      <c r="Z20" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="Z20" s="87" t="n">
+      <c r="AA20" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="AA20" s="87" t="n">
+      <c r="AB20" s="87" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" s="87" t="n">
+      <c r="AC20" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="AC20" s="87" t="n">
+      <c r="AD20" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="AD20" s="87" t="n">
+      <c r="AE20" s="87" t="n">
         <v>4</v>
-      </c>
-      <c r="AE20" s="87" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -3509,94 +3509,94 @@
         </is>
       </c>
       <c r="B21" s="87" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C21" s="87" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D21" s="87" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E21" s="87" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F21" s="87" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G21" s="87" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" s="87" t="n">
         <v>26</v>
       </c>
-      <c r="H21" s="87" t="n">
-        <v>22</v>
-      </c>
       <c r="I21" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="J21" s="87" t="n">
+        <v>31</v>
+      </c>
+      <c r="K21" s="87" t="n">
         <v>28</v>
       </c>
-      <c r="J21" s="87" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" s="87" t="n">
+      <c r="L21" s="87" t="n">
         <v>46</v>
       </c>
-      <c r="L21" s="87" t="n">
-        <v>30</v>
-      </c>
       <c r="M21" s="87" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N21" s="87" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O21" s="87" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="P21" s="87" t="n">
         <v>73</v>
       </c>
       <c r="Q21" s="87" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="R21" s="87" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="S21" s="87" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="T21" s="87" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U21" s="87" t="n">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="V21" s="87" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="W21" s="87" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="Y21" s="87" t="n">
+        <v>125</v>
+      </c>
+      <c r="Z21" s="87" t="n">
         <v>93</v>
       </c>
-      <c r="Z21" s="87" t="n">
-        <v>164</v>
-      </c>
       <c r="AA21" s="87" t="n">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="AB21" s="87" t="n">
+        <v>227</v>
+      </c>
+      <c r="AC21" s="87" t="n">
         <v>142</v>
       </c>
-      <c r="AC21" s="87" t="n">
-        <v>112</v>
-      </c>
       <c r="AD21" s="87" t="n">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="AE21" s="87" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -3606,94 +3606,94 @@
         </is>
       </c>
       <c r="B22" s="87" t="n">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="C22" s="87" t="n">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="D22" s="87" t="n">
-        <v>330</v>
+        <v>162</v>
       </c>
       <c r="E22" s="87" t="n">
+        <v>331</v>
+      </c>
+      <c r="F22" s="87" t="n">
         <v>288</v>
       </c>
-      <c r="F22" s="87" t="n">
+      <c r="G22" s="87" t="n">
         <v>187</v>
       </c>
-      <c r="G22" s="87" t="n">
+      <c r="H22" s="87" t="n">
         <v>199</v>
       </c>
-      <c r="H22" s="87" t="n">
+      <c r="I22" s="87" t="n">
         <v>122</v>
       </c>
-      <c r="I22" s="87" t="n">
-        <v>223</v>
-      </c>
       <c r="J22" s="87" t="n">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="K22" s="87" t="n">
-        <v>388</v>
+        <v>140</v>
       </c>
       <c r="L22" s="87" t="n">
-        <v>255</v>
+        <v>389</v>
       </c>
       <c r="M22" s="87" t="n">
+        <v>256</v>
+      </c>
+      <c r="N22" s="87" t="n">
         <v>149</v>
       </c>
-      <c r="N22" s="87" t="n">
-        <v>155</v>
-      </c>
       <c r="O22" s="87" t="n">
-        <v>411</v>
+        <v>156</v>
       </c>
       <c r="P22" s="87" t="n">
+        <v>412</v>
+      </c>
+      <c r="Q22" s="87" t="n">
         <v>315</v>
       </c>
-      <c r="Q22" s="87" t="n">
-        <v>673</v>
-      </c>
       <c r="R22" s="87" t="n">
+        <v>674</v>
+      </c>
+      <c r="S22" s="87" t="n">
         <v>465</v>
       </c>
-      <c r="S22" s="87" t="n">
-        <v>396</v>
-      </c>
       <c r="T22" s="87" t="n">
+        <v>397</v>
+      </c>
+      <c r="U22" s="87" t="n">
         <v>274</v>
       </c>
-      <c r="U22" s="87" t="n">
-        <v>520</v>
-      </c>
       <c r="V22" s="87" t="n">
-        <v>670</v>
+        <v>521</v>
       </c>
       <c r="W22" s="87" t="n">
-        <v>531</v>
+        <v>671</v>
       </c>
       <c r="X22" s="87" t="n">
-        <v>364</v>
+        <v>532</v>
       </c>
       <c r="Y22" s="87" t="n">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="Z22" s="87" t="n">
-        <v>656</v>
+        <v>256</v>
       </c>
       <c r="AA22" s="87" t="n">
-        <v>1064</v>
+        <v>657</v>
       </c>
       <c r="AB22" s="87" t="n">
+        <v>1065</v>
+      </c>
+      <c r="AC22" s="87" t="n">
         <v>472</v>
       </c>
-      <c r="AC22" s="87" t="n">
-        <v>507</v>
-      </c>
       <c r="AD22" s="87" t="n">
+        <v>508</v>
+      </c>
+      <c r="AE22" s="87" t="n">
         <v>239</v>
-      </c>
-      <c r="AE22" s="87" t="n">
-        <v>196</v>
       </c>
     </row>
     <row r="23">
@@ -3703,94 +3703,94 @@
         </is>
       </c>
       <c r="B23" s="87" t="n">
+        <v>82</v>
+      </c>
+      <c r="C23" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="C23" s="87" t="n">
+      <c r="D23" s="87" t="n">
         <v>65</v>
       </c>
-      <c r="D23" s="87" t="n">
+      <c r="E23" s="87" t="n">
         <v>58</v>
       </c>
-      <c r="E23" s="87" t="n">
+      <c r="F23" s="87" t="n">
         <v>61</v>
       </c>
-      <c r="F23" s="87" t="n">
+      <c r="G23" s="87" t="n">
         <v>103</v>
       </c>
-      <c r="G23" s="87" t="n">
+      <c r="H23" s="87" t="n">
         <v>81</v>
       </c>
-      <c r="H23" s="87" t="n">
+      <c r="I23" s="87" t="n">
         <v>91</v>
       </c>
-      <c r="I23" s="87" t="n">
+      <c r="J23" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="J23" s="87" t="n">
+      <c r="K23" s="87" t="n">
         <v>118</v>
       </c>
-      <c r="K23" s="87" t="n">
+      <c r="L23" s="87" t="n">
         <v>126</v>
       </c>
-      <c r="L23" s="87" t="n">
+      <c r="M23" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="M23" s="87" t="n">
+      <c r="N23" s="87" t="n">
         <v>86</v>
       </c>
-      <c r="N23" s="87" t="n">
+      <c r="O23" s="87" t="n">
         <v>75</v>
       </c>
-      <c r="O23" s="87" t="n">
+      <c r="P23" s="87" t="n">
         <v>201</v>
       </c>
-      <c r="P23" s="87" t="n">
+      <c r="Q23" s="87" t="n">
         <v>202</v>
       </c>
-      <c r="Q23" s="87" t="n">
+      <c r="R23" s="87" t="n">
         <v>328</v>
       </c>
-      <c r="R23" s="87" t="n">
+      <c r="S23" s="87" t="n">
         <v>332</v>
       </c>
-      <c r="S23" s="87" t="n">
+      <c r="T23" s="87" t="n">
         <v>196</v>
       </c>
-      <c r="T23" s="87" t="n">
+      <c r="U23" s="87" t="n">
         <v>172</v>
       </c>
-      <c r="U23" s="87" t="n">
+      <c r="V23" s="87" t="n">
         <v>356</v>
       </c>
-      <c r="V23" s="87" t="n">
+      <c r="W23" s="87" t="n">
         <v>396</v>
       </c>
-      <c r="W23" s="87" t="n">
+      <c r="X23" s="87" t="n">
         <v>374</v>
       </c>
-      <c r="X23" s="87" t="n">
+      <c r="Y23" s="87" t="n">
         <v>468</v>
       </c>
-      <c r="Y23" s="87" t="n">
+      <c r="Z23" s="87" t="n">
         <v>253</v>
       </c>
-      <c r="Z23" s="87" t="n">
+      <c r="AA23" s="87" t="n">
         <v>538</v>
       </c>
-      <c r="AA23" s="87" t="n">
+      <c r="AB23" s="87" t="n">
         <v>661</v>
       </c>
-      <c r="AB23" s="87" t="n">
+      <c r="AC23" s="87" t="n">
         <v>306</v>
       </c>
-      <c r="AC23" s="87" t="n">
+      <c r="AD23" s="87" t="n">
         <v>347</v>
       </c>
-      <c r="AD23" s="87" t="n">
+      <c r="AE23" s="87" t="n">
         <v>181</v>
-      </c>
-      <c r="AE23" s="87" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -3800,94 +3800,94 @@
         </is>
       </c>
       <c r="B24" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="87" t="n">
+      <c r="D24" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="87" t="n">
+      <c r="E24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="E24" s="87" t="n">
+      <c r="F24" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="87" t="n">
+      <c r="G24" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="G24" s="87" t="n">
+      <c r="H24" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="87" t="n">
+      <c r="I24" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="87" t="n">
+      <c r="J24" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="87" t="n">
+      <c r="K24" s="87" t="n">
         <v>15</v>
       </c>
-      <c r="K24" s="87" t="n">
+      <c r="L24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="L24" s="87" t="n">
+      <c r="M24" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="M24" s="87" t="n">
+      <c r="N24" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="N24" s="87" t="n">
+      <c r="O24" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="O24" s="87" t="n">
+      <c r="P24" s="87" t="n">
         <v>20</v>
       </c>
-      <c r="P24" s="87" t="n">
+      <c r="Q24" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="Q24" s="87" t="n">
+      <c r="R24" s="87" t="n">
         <v>33</v>
       </c>
-      <c r="R24" s="87" t="n">
+      <c r="S24" s="87" t="n">
         <v>44</v>
       </c>
-      <c r="S24" s="87" t="n">
+      <c r="T24" s="87" t="n">
         <v>22</v>
       </c>
-      <c r="T24" s="87" t="n">
+      <c r="U24" s="87" t="n">
         <v>17</v>
       </c>
-      <c r="U24" s="87" t="n">
+      <c r="V24" s="87" t="n">
         <v>40</v>
       </c>
-      <c r="V24" s="87" t="n">
+      <c r="W24" s="87" t="n">
         <v>68</v>
       </c>
-      <c r="W24" s="87" t="n">
+      <c r="X24" s="87" t="n">
         <v>65</v>
       </c>
-      <c r="X24" s="87" t="n">
+      <c r="Y24" s="87" t="n">
         <v>71</v>
       </c>
-      <c r="Y24" s="87" t="n">
+      <c r="Z24" s="87" t="n">
         <v>19</v>
       </c>
-      <c r="Z24" s="87" t="n">
+      <c r="AA24" s="87" t="n">
         <v>60</v>
       </c>
-      <c r="AA24" s="87" t="n">
+      <c r="AB24" s="87" t="n">
         <v>89</v>
       </c>
-      <c r="AB24" s="87" t="n">
+      <c r="AC24" s="87" t="n">
         <v>51</v>
       </c>
-      <c r="AC24" s="87" t="n">
+      <c r="AD24" s="87" t="n">
         <v>64</v>
       </c>
-      <c r="AD24" s="87" t="n">
+      <c r="AE24" s="87" t="n">
         <v>37</v>
-      </c>
-      <c r="AE24" s="87" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="B25" s="89" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="C25" s="89" t="n">
         <v>7.27</v>
-      </c>
-      <c r="C25" s="89" t="n">
-        <v>7.26</v>
       </c>
       <c r="D25" s="89" t="n">
         <v>7.26</v>
@@ -3909,22 +3909,22 @@
         <v>7.26</v>
       </c>
       <c r="F25" s="89" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="G25" s="89" t="n">
         <v>7.25</v>
       </c>
       <c r="H25" s="89" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I25" s="89" t="n">
         <v>7.26</v>
       </c>
-      <c r="I25" s="89" t="n">
+      <c r="J25" s="89" t="n">
         <v>7.25</v>
       </c>
-      <c r="J25" s="89" t="n">
+      <c r="K25" s="89" t="n">
         <v>7.27</v>
-      </c>
-      <c r="K25" s="89" t="n">
-        <v>7.26</v>
       </c>
       <c r="L25" s="89" t="n">
         <v>7.26</v>
@@ -3936,7 +3936,7 @@
         <v>7.26</v>
       </c>
       <c r="O25" s="89" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="P25" s="89" t="n">
         <v>7.25</v>
@@ -3945,46 +3945,46 @@
         <v>7.25</v>
       </c>
       <c r="R25" s="89" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S25" s="89" t="n">
         <v>7.23</v>
       </c>
-      <c r="S25" s="89" t="n">
+      <c r="T25" s="89" t="n">
         <v>7.22</v>
       </c>
-      <c r="T25" s="89" t="n">
+      <c r="U25" s="89" t="n">
         <v>7.21</v>
-      </c>
-      <c r="U25" s="89" t="n">
-        <v>7.24</v>
       </c>
       <c r="V25" s="89" t="n">
         <v>7.24</v>
       </c>
       <c r="W25" s="89" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="X25" s="89" t="n">
         <v>7.23</v>
       </c>
-      <c r="X25" s="89" t="n">
+      <c r="Y25" s="89" t="n">
         <v>7.22</v>
-      </c>
-      <c r="Y25" s="89" t="n">
-        <v>7.23</v>
       </c>
       <c r="Z25" s="89" t="n">
         <v>7.23</v>
       </c>
       <c r="AA25" s="89" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AB25" s="89" t="n">
         <v>7.22</v>
       </c>
-      <c r="AB25" s="89" t="n">
+      <c r="AC25" s="89" t="n">
         <v>7.25</v>
       </c>
-      <c r="AC25" s="89" t="n">
+      <c r="AD25" s="89" t="n">
         <v>7.24</v>
       </c>
-      <c r="AD25" s="89" t="n">
+      <c r="AE25" s="89" t="n">
         <v>7.27</v>
-      </c>
-      <c r="AE25" s="89" t="n">
-        <v>7.26</v>
       </c>
     </row>
     <row r="26">
@@ -3994,94 +3994,94 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="C26" s="90" t="n">
         <v>0.14</v>
       </c>
-      <c r="C26" s="90" t="n">
+      <c r="D26" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="D26" s="89" t="n">
+      <c r="E26" s="89" t="n">
         <v>0.05</v>
       </c>
-      <c r="E26" s="89" t="n">
+      <c r="F26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="F26" s="89" t="n">
+      <c r="G26" s="89" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G26" s="89" t="n">
+      <c r="H26" s="89" t="n">
         <v>-0.16</v>
       </c>
-      <c r="H26" s="89" t="n">
+      <c r="I26" s="89" t="n">
         <v>0.15</v>
       </c>
-      <c r="I26" s="89" t="n">
+      <c r="J26" s="89" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J26" s="89" t="n">
+      <c r="K26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="K26" s="89" t="n">
+      <c r="L26" s="89" t="n">
         <v>0.08</v>
       </c>
-      <c r="L26" s="89" t="n">
+      <c r="M26" s="89" t="n">
         <v>-0.04</v>
       </c>
-      <c r="M26" s="89" t="n">
+      <c r="N26" s="89" t="n">
         <v>0.05</v>
-      </c>
-      <c r="N26" s="89" t="n">
-        <v>0.06</v>
       </c>
       <c r="O26" s="89" t="n">
         <v>0.06</v>
       </c>
       <c r="P26" s="89" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q26" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q26" s="89" t="n">
+      <c r="R26" s="89" t="n">
         <v>0.19</v>
       </c>
-      <c r="R26" s="89" t="n">
+      <c r="S26" s="89" t="n">
         <v>0.12</v>
       </c>
-      <c r="S26" s="89" t="n">
+      <c r="T26" s="89" t="n">
         <v>0.18</v>
       </c>
-      <c r="T26" s="89" t="n">
+      <c r="U26" s="89" t="n">
         <v>-0.44</v>
       </c>
-      <c r="U26" s="89" t="n">
+      <c r="V26" s="89" t="n">
         <v>0.04</v>
       </c>
-      <c r="V26" s="89" t="n">
+      <c r="W26" s="89" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="W26" s="89" t="n">
+      <c r="X26" s="89" t="n">
         <v>0.18</v>
       </c>
-      <c r="X26" s="89" t="n">
+      <c r="Y26" s="89" t="n">
         <v>-0.1</v>
       </c>
-      <c r="Y26" s="89" t="n">
+      <c r="Z26" s="89" t="n">
         <v>0.02</v>
       </c>
-      <c r="Z26" s="89" t="n">
+      <c r="AA26" s="89" t="n">
         <v>0.13</v>
       </c>
-      <c r="AA26" s="89" t="n">
+      <c r="AB26" s="89" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AB26" s="89" t="n">
+      <c r="AC26" s="89" t="n">
         <v>0.14</v>
       </c>
-      <c r="AC26" s="89" t="n">
+      <c r="AD26" s="89" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AD26" s="89" t="n">
+      <c r="AE26" s="89" t="n">
         <v>0.16</v>
-      </c>
-      <c r="AE26" s="89" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="27">
@@ -4091,94 +4091,94 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C27" s="90" t="n">
         <v>0.46</v>
       </c>
-      <c r="C27" s="90" t="n">
+      <c r="D27" s="89" t="n">
         <v>0.39</v>
       </c>
-      <c r="D27" s="89" t="n">
+      <c r="E27" s="89" t="n">
         <v>0.55</v>
       </c>
-      <c r="E27" s="89" t="n">
+      <c r="F27" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="F27" s="89" t="n">
+      <c r="G27" s="89" t="n">
         <v>0.32</v>
       </c>
-      <c r="G27" s="89" t="n">
+      <c r="H27" s="89" t="n">
         <v>0.45</v>
       </c>
-      <c r="H27" s="89" t="n">
+      <c r="I27" s="89" t="n">
         <v>0.11</v>
       </c>
-      <c r="I27" s="89" t="n">
+      <c r="J27" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="J27" s="89" t="n">
+      <c r="K27" s="89" t="n">
         <v>0.06</v>
       </c>
-      <c r="K27" s="89" t="n">
+      <c r="L27" s="89" t="n">
         <v>0.12</v>
       </c>
-      <c r="L27" s="89" t="n">
+      <c r="M27" s="89" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M27" s="89" t="n">
+      <c r="N27" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="N27" s="89" t="n">
+      <c r="O27" s="89" t="n">
         <v>0.09</v>
       </c>
-      <c r="O27" s="89" t="n">
+      <c r="P27" s="89" t="n">
         <v>0.04</v>
       </c>
-      <c r="P27" s="89" t="n">
+      <c r="Q27" s="89" t="n">
         <v>-0.04</v>
       </c>
-      <c r="Q27" s="89" t="n">
+      <c r="R27" s="89" t="n">
         <v>0.02</v>
       </c>
-      <c r="R27" s="89" t="n">
+      <c r="S27" s="89" t="n">
         <v>-0.43</v>
       </c>
-      <c r="S27" s="89" t="n">
+      <c r="T27" s="89" t="n">
         <v>-0.52</v>
       </c>
-      <c r="T27" s="89" t="n">
+      <c r="U27" s="89" t="n">
         <v>-0.77</v>
       </c>
-      <c r="U27" s="89" t="n">
+      <c r="V27" s="89" t="n">
         <v>-0.16</v>
       </c>
-      <c r="V27" s="89" t="n">
+      <c r="W27" s="89" t="n">
         <v>-0.32</v>
       </c>
-      <c r="W27" s="89" t="n">
+      <c r="X27" s="89" t="n">
         <v>-0.06</v>
       </c>
-      <c r="X27" s="89" t="n">
+      <c r="Y27" s="89" t="n">
         <v>-0.29</v>
       </c>
-      <c r="Y27" s="89" t="n">
+      <c r="Z27" s="89" t="n">
         <v>-0.28</v>
       </c>
-      <c r="Z27" s="89" t="n">
+      <c r="AA27" s="89" t="n">
         <v>-0.38</v>
       </c>
-      <c r="AA27" s="89" t="n">
+      <c r="AB27" s="89" t="n">
         <v>-0.57</v>
       </c>
-      <c r="AB27" s="89" t="n">
+      <c r="AC27" s="89" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AC27" s="89" t="n">
+      <c r="AD27" s="89" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD27" s="89" t="n">
+      <c r="AE27" s="89" t="n">
         <v>0.2</v>
-      </c>
-      <c r="AE27" s="89" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="28">
@@ -4188,94 +4188,94 @@
         </is>
       </c>
       <c r="B28" s="87" t="n">
+        <v>2629</v>
+      </c>
+      <c r="C28" s="87" t="n">
         <v>2628</v>
       </c>
-      <c r="C28" s="87" t="n">
+      <c r="D28" s="87" t="n">
         <v>2624</v>
       </c>
-      <c r="D28" s="87" t="n">
+      <c r="E28" s="87" t="n">
         <v>2634</v>
       </c>
-      <c r="E28" s="87" t="n">
+      <c r="F28" s="87" t="n">
         <v>2656</v>
       </c>
-      <c r="F28" s="87" t="n">
+      <c r="G28" s="87" t="n">
         <v>2679</v>
       </c>
-      <c r="G28" s="87" t="n">
+      <c r="H28" s="87" t="n">
         <v>2654</v>
       </c>
-      <c r="H28" s="87" t="n">
+      <c r="I28" s="87" t="n">
         <v>2676</v>
       </c>
-      <c r="I28" s="87" t="n">
+      <c r="J28" s="87" t="n">
         <v>2677</v>
       </c>
-      <c r="J28" s="87" t="n">
+      <c r="K28" s="87" t="n">
         <v>2680</v>
       </c>
-      <c r="K28" s="87" t="n">
+      <c r="L28" s="87" t="n">
         <v>2678</v>
       </c>
-      <c r="L28" s="87" t="n">
+      <c r="M28" s="87" t="n">
         <v>2700</v>
       </c>
-      <c r="M28" s="87" t="n">
+      <c r="N28" s="87" t="n">
         <v>2677</v>
       </c>
-      <c r="N28" s="87" t="n">
+      <c r="O28" s="87" t="n">
         <v>2709</v>
       </c>
-      <c r="O28" s="87" t="n">
+      <c r="P28" s="87" t="n">
         <v>2753</v>
       </c>
-      <c r="P28" s="87" t="n">
+      <c r="Q28" s="87" t="n">
         <v>2755</v>
       </c>
-      <c r="Q28" s="87" t="n">
+      <c r="R28" s="87" t="n">
         <v>2773</v>
       </c>
-      <c r="R28" s="87" t="n">
+      <c r="S28" s="87" t="n">
         <v>2768</v>
       </c>
-      <c r="S28" s="87" t="n">
+      <c r="T28" s="87" t="n">
         <v>2722</v>
       </c>
-      <c r="T28" s="87" t="n">
+      <c r="U28" s="87" t="n">
         <v>2725</v>
       </c>
-      <c r="U28" s="87" t="n">
+      <c r="V28" s="87" t="n">
         <v>2748</v>
       </c>
-      <c r="V28" s="87" t="n">
+      <c r="W28" s="87" t="n">
         <v>2747</v>
       </c>
-      <c r="W28" s="87" t="n">
+      <c r="X28" s="87" t="n">
         <v>2763</v>
       </c>
-      <c r="X28" s="87" t="n">
+      <c r="Y28" s="87" t="n">
         <v>2775</v>
       </c>
-      <c r="Y28" s="87" t="n">
+      <c r="Z28" s="87" t="n">
         <v>2734</v>
       </c>
-      <c r="Z28" s="87" t="n">
+      <c r="AA28" s="87" t="n">
         <v>2769</v>
       </c>
-      <c r="AA28" s="87" t="n">
+      <c r="AB28" s="87" t="n">
         <v>2768</v>
       </c>
-      <c r="AB28" s="87" t="n">
+      <c r="AC28" s="87" t="n">
         <v>2727</v>
       </c>
-      <c r="AC28" s="87" t="n">
+      <c r="AD28" s="87" t="n">
         <v>2751</v>
       </c>
-      <c r="AD28" s="87" t="n">
+      <c r="AE28" s="87" t="n">
         <v>2694</v>
-      </c>
-      <c r="AE28" s="87" t="n">
-        <v>2636</v>
       </c>
     </row>
     <row r="29">
@@ -4285,94 +4285,94 @@
         </is>
       </c>
       <c r="B29" s="87" t="n">
+        <v>13676.26</v>
+      </c>
+      <c r="C29" s="87" t="n">
         <v>14085.55</v>
       </c>
-      <c r="C29" s="87" t="n">
+      <c r="D29" s="87" t="n">
         <v>13874.95</v>
       </c>
-      <c r="D29" s="87" t="n">
+      <c r="E29" s="87" t="n">
         <v>14300.01</v>
       </c>
-      <c r="E29" s="87" t="n">
+      <c r="F29" s="87" t="n">
         <v>13513.73</v>
       </c>
-      <c r="F29" s="87" t="n">
+      <c r="G29" s="87" t="n">
         <v>13855.46</v>
       </c>
-      <c r="G29" s="87" t="n">
+      <c r="H29" s="87" t="n">
         <v>13994.74</v>
       </c>
-      <c r="H29" s="87" t="n">
+      <c r="I29" s="87" t="n">
         <v>13436.37</v>
       </c>
-      <c r="I29" s="87" t="n">
+      <c r="J29" s="87" t="n">
         <v>13431.28</v>
       </c>
-      <c r="J29" s="87" t="n">
+      <c r="K29" s="87" t="n">
         <v>13315.67</v>
       </c>
-      <c r="K29" s="87" t="n">
+      <c r="L29" s="87" t="n">
         <v>12995.34</v>
       </c>
-      <c r="L29" s="87" t="n">
+      <c r="M29" s="87" t="n">
         <v>13417.35</v>
       </c>
-      <c r="M29" s="87" t="n">
+      <c r="N29" s="87" t="n">
         <v>13400.53</v>
       </c>
-      <c r="N29" s="87" t="n">
+      <c r="O29" s="87" t="n">
         <v>13682.26</v>
       </c>
-      <c r="O29" s="87" t="n">
+      <c r="P29" s="87" t="n">
         <v>13684.07</v>
       </c>
-      <c r="P29" s="87" t="n">
+      <c r="Q29" s="87" t="n">
         <v>13695.7</v>
       </c>
-      <c r="Q29" s="87" t="n">
+      <c r="R29" s="87" t="n">
         <v>14009.49</v>
       </c>
-      <c r="R29" s="87" t="n">
+      <c r="S29" s="87" t="n">
         <v>14200.74</v>
       </c>
-      <c r="S29" s="87" t="n">
+      <c r="T29" s="87" t="n">
         <v>14644.3</v>
       </c>
-      <c r="T29" s="87" t="n">
+      <c r="U29" s="87" t="n">
         <v>14427.61</v>
       </c>
-      <c r="U29" s="87" t="n">
+      <c r="V29" s="87" t="n">
         <v>14647.14</v>
       </c>
-      <c r="V29" s="87" t="n">
+      <c r="W29" s="87" t="n">
         <v>14749.88</v>
       </c>
-      <c r="W29" s="87" t="n">
+      <c r="X29" s="87" t="n">
         <v>15074.4</v>
       </c>
-      <c r="X29" s="87" t="n">
+      <c r="Y29" s="87" t="n">
         <v>14733.75</v>
       </c>
-      <c r="Y29" s="87" t="n">
+      <c r="Z29" s="87" t="n">
         <v>14475.39</v>
       </c>
-      <c r="Z29" s="87" t="n">
+      <c r="AA29" s="87" t="n">
         <v>14536.8</v>
       </c>
-      <c r="AA29" s="87" t="n">
+      <c r="AB29" s="87" t="n">
         <v>15107.71</v>
       </c>
-      <c r="AB29" s="87" t="n">
+      <c r="AC29" s="87" t="n">
         <v>14596.76</v>
       </c>
-      <c r="AC29" s="87" t="n">
+      <c r="AD29" s="87" t="n">
         <v>15204.54</v>
       </c>
-      <c r="AD29" s="87" t="n">
+      <c r="AE29" s="87" t="n">
         <v>14431.4</v>
-      </c>
-      <c r="AE29" s="87" t="n">
-        <v>13864.97</v>
       </c>
     </row>
     <row r="30">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="B30" s="91" t="n">
+        <v>47.19</v>
+      </c>
+      <c r="C30" s="91" t="n">
         <v>47.2</v>
       </c>
-      <c r="C30" s="91" t="n">
+      <c r="D30" s="91" t="n">
         <v>47.23</v>
-      </c>
-      <c r="D30" s="91" t="n">
-        <v>47.31</v>
       </c>
       <c r="E30" s="91" t="n">
         <v>47.31</v>
@@ -4397,79 +4397,79 @@
         <v>47.31</v>
       </c>
       <c r="G30" s="91" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="H30" s="91" t="n">
         <v>47.32</v>
       </c>
-      <c r="H30" s="91" t="n">
+      <c r="I30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="I30" s="91" t="n">
+      <c r="J30" s="91" t="n">
         <v>47.16</v>
       </c>
-      <c r="J30" s="91" t="n">
+      <c r="K30" s="91" t="n">
         <v>47.24</v>
       </c>
-      <c r="K30" s="91" t="n">
+      <c r="L30" s="91" t="n">
         <v>47.3</v>
       </c>
-      <c r="L30" s="91" t="n">
+      <c r="M30" s="91" t="n">
         <v>47.27</v>
       </c>
-      <c r="M30" s="91" t="n">
+      <c r="N30" s="91" t="n">
         <v>47.19</v>
       </c>
-      <c r="N30" s="91" t="n">
+      <c r="O30" s="91" t="n">
         <v>47.25</v>
       </c>
-      <c r="O30" s="91" t="n">
+      <c r="P30" s="91" t="n">
         <v>47.08</v>
       </c>
-      <c r="P30" s="91" t="n">
+      <c r="Q30" s="91" t="n">
         <v>46.99</v>
       </c>
-      <c r="Q30" s="91" t="n">
+      <c r="R30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="R30" s="91" t="n">
+      <c r="S30" s="91" t="n">
         <v>46.92</v>
       </c>
-      <c r="S30" s="91" t="n">
+      <c r="T30" s="91" t="n">
         <v>47.16</v>
       </c>
-      <c r="T30" s="91" t="n">
+      <c r="U30" s="91" t="n">
         <v>47.13</v>
-      </c>
-      <c r="U30" s="91" t="n">
-        <v>47.06</v>
       </c>
       <c r="V30" s="91" t="n">
         <v>47.06</v>
       </c>
       <c r="W30" s="91" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="X30" s="91" t="n">
         <v>47.07</v>
       </c>
-      <c r="X30" s="91" t="n">
+      <c r="Y30" s="91" t="n">
         <v>46.87</v>
       </c>
-      <c r="Y30" s="91" t="n">
+      <c r="Z30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="Z30" s="91" t="n">
+      <c r="AA30" s="91" t="n">
         <v>46.87</v>
       </c>
-      <c r="AA30" s="91" t="n">
+      <c r="AB30" s="91" t="n">
         <v>46.85</v>
       </c>
-      <c r="AB30" s="91" t="n">
+      <c r="AC30" s="91" t="n">
         <v>46.7</v>
       </c>
-      <c r="AC30" s="91" t="n">
+      <c r="AD30" s="91" t="n">
         <v>46.81</v>
       </c>
-      <c r="AD30" s="91" t="n">
+      <c r="AE30" s="91" t="n">
         <v>46.88</v>
-      </c>
-      <c r="AE30" s="91" t="n">
-        <v>46.92</v>
       </c>
     </row>
     <row r="31">
@@ -4479,94 +4479,94 @@
         </is>
       </c>
       <c r="B31" s="87" t="n">
+        <v>-768.4</v>
+      </c>
+      <c r="C31" s="87" t="n">
         <v>-787.86</v>
       </c>
-      <c r="C31" s="87" t="n">
+      <c r="D31" s="87" t="n">
         <v>-768.96</v>
       </c>
-      <c r="D31" s="87" t="n">
+      <c r="E31" s="87" t="n">
         <v>-770.47</v>
       </c>
-      <c r="E31" s="87" t="n">
+      <c r="F31" s="87" t="n">
         <v>-726.3099999999999</v>
       </c>
-      <c r="F31" s="87" t="n">
+      <c r="G31" s="87" t="n">
         <v>-746.26</v>
       </c>
-      <c r="G31" s="87" t="n">
+      <c r="H31" s="87" t="n">
         <v>-749.58</v>
       </c>
-      <c r="H31" s="87" t="n">
+      <c r="I31" s="87" t="n">
         <v>-803.5</v>
       </c>
-      <c r="I31" s="87" t="n">
+      <c r="J31" s="87" t="n">
         <v>-762.4400000000001</v>
       </c>
-      <c r="J31" s="87" t="n">
+      <c r="K31" s="87" t="n">
         <v>-735.5599999999999</v>
       </c>
-      <c r="K31" s="87" t="n">
+      <c r="L31" s="87" t="n">
         <v>-702.0599999999999</v>
       </c>
-      <c r="L31" s="87" t="n">
+      <c r="M31" s="87" t="n">
         <v>-732.28</v>
       </c>
-      <c r="M31" s="87" t="n">
+      <c r="N31" s="87" t="n">
         <v>-753.28</v>
       </c>
-      <c r="N31" s="87" t="n">
+      <c r="O31" s="87" t="n">
         <v>-753.6799999999999</v>
       </c>
-      <c r="O31" s="87" t="n">
+      <c r="P31" s="87" t="n">
         <v>-799.49</v>
       </c>
-      <c r="P31" s="87" t="n">
+      <c r="Q31" s="87" t="n">
         <v>-824.87</v>
       </c>
-      <c r="Q31" s="87" t="n">
+      <c r="R31" s="87" t="n">
         <v>-838.41</v>
       </c>
-      <c r="R31" s="87" t="n">
+      <c r="S31" s="87" t="n">
         <v>-875.21</v>
       </c>
-      <c r="S31" s="87" t="n">
+      <c r="T31" s="87" t="n">
         <v>-833.22</v>
       </c>
-      <c r="T31" s="87" t="n">
+      <c r="U31" s="87" t="n">
         <v>-828.75</v>
       </c>
-      <c r="U31" s="87" t="n">
+      <c r="V31" s="87" t="n">
         <v>-861.96</v>
       </c>
-      <c r="V31" s="87" t="n">
+      <c r="W31" s="87" t="n">
         <v>-866.79</v>
       </c>
-      <c r="W31" s="87" t="n">
+      <c r="X31" s="87" t="n">
         <v>-882.79</v>
       </c>
-      <c r="X31" s="87" t="n">
+      <c r="Y31" s="87" t="n">
         <v>-923.21</v>
       </c>
-      <c r="Y31" s="87" t="n">
+      <c r="Z31" s="87" t="n">
         <v>-866.72</v>
       </c>
-      <c r="Z31" s="87" t="n">
+      <c r="AA31" s="87" t="n">
         <v>-911.4299999999999</v>
       </c>
-      <c r="AA31" s="87" t="n">
+      <c r="AB31" s="87" t="n">
         <v>-952.03</v>
       </c>
-      <c r="AB31" s="87" t="n">
+      <c r="AC31" s="87" t="n">
         <v>-963.05</v>
       </c>
-      <c r="AC31" s="87" t="n">
+      <c r="AD31" s="87" t="n">
         <v>-969.67</v>
       </c>
-      <c r="AD31" s="87" t="n">
+      <c r="AE31" s="87" t="n">
         <v>-901.0599999999999</v>
-      </c>
-      <c r="AE31" s="87" t="n">
-        <v>-853.6</v>
       </c>
     </row>
     <row r="32">
@@ -4576,94 +4576,94 @@
         </is>
       </c>
       <c r="B32" s="87" t="n">
+        <v>-24887</v>
+      </c>
+      <c r="C32" s="87" t="n">
         <v>-28237</v>
       </c>
-      <c r="C32" s="87" t="n">
+      <c r="D32" s="87" t="n">
         <v>-27204</v>
       </c>
-      <c r="D32" s="87" t="n">
+      <c r="E32" s="87" t="n">
         <v>-29347</v>
       </c>
-      <c r="E32" s="87" t="n">
+      <c r="F32" s="87" t="n">
         <v>-21316</v>
       </c>
-      <c r="F32" s="87" t="n">
+      <c r="G32" s="87" t="n">
         <v>-27707</v>
       </c>
-      <c r="G32" s="87" t="n">
+      <c r="H32" s="87" t="n">
         <v>-25723</v>
       </c>
-      <c r="H32" s="87" t="n">
+      <c r="I32" s="87" t="n">
         <v>-30642</v>
       </c>
-      <c r="I32" s="87" t="n">
+      <c r="J32" s="87" t="n">
         <v>-25064</v>
       </c>
-      <c r="J32" s="87" t="n">
+      <c r="K32" s="87" t="n">
         <v>-14410</v>
       </c>
-      <c r="K32" s="87" t="n">
+      <c r="L32" s="87" t="n">
         <v>-17749</v>
       </c>
-      <c r="L32" s="87" t="n">
+      <c r="M32" s="87" t="n">
         <v>-22631</v>
       </c>
-      <c r="M32" s="87" t="n">
+      <c r="N32" s="87" t="n">
         <v>-24009</v>
       </c>
-      <c r="N32" s="87" t="n">
+      <c r="O32" s="87" t="n">
         <v>-21715</v>
       </c>
-      <c r="O32" s="87" t="n">
+      <c r="P32" s="87" t="n">
         <v>-19175</v>
       </c>
-      <c r="P32" s="87" t="n">
+      <c r="Q32" s="87" t="n">
         <v>-17642</v>
       </c>
-      <c r="Q32" s="87" t="n">
+      <c r="R32" s="87" t="n">
         <v>-22961</v>
       </c>
-      <c r="R32" s="87" t="n">
+      <c r="S32" s="87" t="n">
         <v>-30279</v>
       </c>
-      <c r="S32" s="87" t="n">
+      <c r="T32" s="87" t="n">
         <v>-35761</v>
       </c>
-      <c r="T32" s="87" t="n">
+      <c r="U32" s="87" t="n">
         <v>-31934</v>
       </c>
-      <c r="U32" s="87" t="n">
+      <c r="V32" s="87" t="n">
         <v>-24510</v>
       </c>
-      <c r="V32" s="87" t="n">
+      <c r="W32" s="87" t="n">
         <v>-24106</v>
       </c>
-      <c r="W32" s="87" t="n">
+      <c r="X32" s="87" t="n">
         <v>-26697</v>
       </c>
-      <c r="X32" s="87" t="n">
+      <c r="Y32" s="87" t="n">
         <v>-22344</v>
       </c>
-      <c r="Y32" s="87" t="n">
+      <c r="Z32" s="87" t="n">
         <v>-29091</v>
       </c>
-      <c r="Z32" s="87" t="n">
+      <c r="AA32" s="87" t="n">
         <v>-30170</v>
       </c>
-      <c r="AA32" s="87" t="n">
+      <c r="AB32" s="87" t="n">
         <v>-32290</v>
       </c>
-      <c r="AB32" s="87" t="n">
+      <c r="AC32" s="87" t="n">
         <v>-35096</v>
       </c>
-      <c r="AC32" s="87" t="n">
+      <c r="AD32" s="87" t="n">
         <v>-36781</v>
       </c>
-      <c r="AD32" s="87" t="n">
+      <c r="AE32" s="87" t="n">
         <v>-42288</v>
-      </c>
-      <c r="AE32" s="87" t="n">
-        <v>-34311</v>
       </c>
     </row>
     <row r="33">
@@ -4673,94 +4673,94 @@
         </is>
       </c>
       <c r="B33" s="87" t="n">
+        <v>7344</v>
+      </c>
+      <c r="C33" s="87" t="n">
         <v>8297</v>
       </c>
-      <c r="C33" s="87" t="n">
+      <c r="D33" s="87" t="n">
         <v>8757</v>
       </c>
-      <c r="D33" s="87" t="n">
+      <c r="E33" s="87" t="n">
         <v>6268</v>
       </c>
-      <c r="E33" s="87" t="n">
+      <c r="F33" s="87" t="n">
         <v>7513</v>
       </c>
-      <c r="F33" s="87" t="n">
+      <c r="G33" s="87" t="n">
         <v>7055</v>
       </c>
-      <c r="G33" s="87" t="n">
+      <c r="H33" s="87" t="n">
         <v>4167</v>
       </c>
-      <c r="H33" s="87" t="n">
+      <c r="I33" s="87" t="n">
         <v>825</v>
       </c>
-      <c r="I33" s="87" t="n">
+      <c r="J33" s="87" t="n">
         <v>1656</v>
       </c>
-      <c r="J33" s="87" t="n">
+      <c r="K33" s="87" t="n">
         <v>4911</v>
       </c>
-      <c r="K33" s="87" t="n">
+      <c r="L33" s="87" t="n">
         <v>10067</v>
       </c>
-      <c r="L33" s="87" t="n">
+      <c r="M33" s="87" t="n">
         <v>7777</v>
       </c>
-      <c r="M33" s="87" t="n">
+      <c r="N33" s="87" t="n">
         <v>5332</v>
       </c>
-      <c r="N33" s="87" t="n">
+      <c r="O33" s="87" t="n">
         <v>7800</v>
       </c>
-      <c r="O33" s="87" t="n">
+      <c r="P33" s="87" t="n">
         <v>5405</v>
       </c>
-      <c r="P33" s="87" t="n">
+      <c r="Q33" s="87" t="n">
         <v>6378</v>
       </c>
-      <c r="Q33" s="87" t="n">
+      <c r="R33" s="87" t="n">
         <v>3153</v>
       </c>
-      <c r="R33" s="87" t="n">
+      <c r="S33" s="87" t="n">
         <v>729</v>
       </c>
-      <c r="S33" s="87" t="n">
+      <c r="T33" s="87" t="n">
         <v>2667</v>
       </c>
-      <c r="T33" s="87" t="n">
+      <c r="U33" s="87" t="n">
         <v>13776</v>
       </c>
-      <c r="U33" s="87" t="n">
+      <c r="V33" s="87" t="n">
         <v>15956</v>
       </c>
-      <c r="V33" s="87" t="n">
+      <c r="W33" s="87" t="n">
         <v>14793</v>
       </c>
-      <c r="W33" s="87" t="n">
+      <c r="X33" s="87" t="n">
         <v>16486</v>
       </c>
-      <c r="X33" s="87" t="n">
+      <c r="Y33" s="87" t="n">
         <v>15530</v>
       </c>
-      <c r="Y33" s="87" t="n">
+      <c r="Z33" s="87" t="n">
         <v>13877</v>
       </c>
-      <c r="Z33" s="87" t="n">
+      <c r="AA33" s="87" t="n">
         <v>14927</v>
       </c>
-      <c r="AA33" s="87" t="n">
+      <c r="AB33" s="87" t="n">
         <v>12549</v>
       </c>
-      <c r="AB33" s="87" t="n">
+      <c r="AC33" s="87" t="n">
         <v>14817</v>
       </c>
-      <c r="AC33" s="87" t="n">
+      <c r="AD33" s="87" t="n">
         <v>12591</v>
       </c>
-      <c r="AD33" s="87" t="n">
+      <c r="AE33" s="87" t="n">
         <v>10872</v>
-      </c>
-      <c r="AE33" s="87" t="n">
-        <v>11764</v>
       </c>
     </row>
     <row r="34">
@@ -4770,94 +4770,94 @@
         </is>
       </c>
       <c r="B34" s="87" t="n">
+        <v>-32469</v>
+      </c>
+      <c r="C34" s="87" t="n">
         <v>-33076</v>
       </c>
-      <c r="C34" s="87" t="n">
+      <c r="D34" s="87" t="n">
         <v>-30361</v>
       </c>
-      <c r="D34" s="87" t="n">
+      <c r="E34" s="87" t="n">
         <v>-28635</v>
       </c>
-      <c r="E34" s="87" t="n">
+      <c r="F34" s="87" t="n">
         <v>-26241</v>
       </c>
-      <c r="F34" s="87" t="n">
+      <c r="G34" s="87" t="n">
         <v>-26360</v>
       </c>
-      <c r="G34" s="87" t="n">
+      <c r="H34" s="87" t="n">
         <v>-29373</v>
       </c>
-      <c r="H34" s="87" t="n">
+      <c r="I34" s="87" t="n">
         <v>-31844</v>
       </c>
-      <c r="I34" s="87" t="n">
+      <c r="J34" s="87" t="n">
         <v>-30383</v>
       </c>
-      <c r="J34" s="87" t="n">
+      <c r="K34" s="87" t="n">
         <v>-21910</v>
       </c>
-      <c r="K34" s="87" t="n">
+      <c r="L34" s="87" t="n">
         <v>-21975</v>
       </c>
-      <c r="L34" s="87" t="n">
+      <c r="M34" s="87" t="n">
         <v>-21240</v>
       </c>
-      <c r="M34" s="87" t="n">
+      <c r="N34" s="87" t="n">
         <v>-21904</v>
       </c>
-      <c r="N34" s="87" t="n">
+      <c r="O34" s="87" t="n">
         <v>-22144</v>
       </c>
-      <c r="O34" s="87" t="n">
+      <c r="P34" s="87" t="n">
         <v>-21833</v>
       </c>
-      <c r="P34" s="87" t="n">
+      <c r="Q34" s="87" t="n">
         <v>-23667</v>
       </c>
-      <c r="Q34" s="87" t="n">
+      <c r="R34" s="87" t="n">
         <v>-23027</v>
       </c>
-      <c r="R34" s="87" t="n">
+      <c r="S34" s="87" t="n">
         <v>-22034</v>
       </c>
-      <c r="S34" s="87" t="n">
+      <c r="T34" s="87" t="n">
         <v>-33664</v>
       </c>
-      <c r="T34" s="87" t="n">
+      <c r="U34" s="87" t="n">
         <v>-32281</v>
       </c>
-      <c r="U34" s="87" t="n">
+      <c r="V34" s="87" t="n">
         <v>-29115</v>
       </c>
-      <c r="V34" s="87" t="n">
+      <c r="W34" s="87" t="n">
         <v>-30994</v>
       </c>
-      <c r="W34" s="87" t="n">
+      <c r="X34" s="87" t="n">
         <v>-29305</v>
       </c>
-      <c r="X34" s="87" t="n">
+      <c r="Y34" s="87" t="n">
         <v>-29083</v>
       </c>
-      <c r="Y34" s="87" t="n">
+      <c r="Z34" s="87" t="n">
         <v>-28904</v>
       </c>
-      <c r="Z34" s="87" t="n">
+      <c r="AA34" s="87" t="n">
         <v>-28818</v>
       </c>
-      <c r="AA34" s="87" t="n">
+      <c r="AB34" s="87" t="n">
         <v>-30430</v>
       </c>
-      <c r="AB34" s="87" t="n">
+      <c r="AC34" s="87" t="n">
         <v>-31858</v>
       </c>
-      <c r="AC34" s="87" t="n">
+      <c r="AD34" s="87" t="n">
         <v>-31214</v>
       </c>
-      <c r="AD34" s="87" t="n">
+      <c r="AE34" s="87" t="n">
         <v>-33083</v>
-      </c>
-      <c r="AE34" s="87" t="n">
-        <v>-32655</v>
       </c>
     </row>
     <row r="35">
@@ -4867,94 +4867,94 @@
         </is>
       </c>
       <c r="B35" s="87" t="n">
+        <v>-3829</v>
+      </c>
+      <c r="C35" s="87" t="n">
         <v>-4389</v>
       </c>
-      <c r="C35" s="87" t="n">
+      <c r="D35" s="87" t="n">
         <v>-3228</v>
       </c>
-      <c r="D35" s="87" t="n">
+      <c r="E35" s="87" t="n">
         <v>-3925</v>
       </c>
-      <c r="E35" s="87" t="n">
+      <c r="F35" s="87" t="n">
         <v>-4189</v>
       </c>
-      <c r="F35" s="87" t="n">
+      <c r="G35" s="87" t="n">
         <v>-3693</v>
       </c>
-      <c r="G35" s="87" t="n">
+      <c r="H35" s="87" t="n">
         <v>-5291</v>
       </c>
-      <c r="H35" s="87" t="n">
+      <c r="I35" s="87" t="n">
         <v>-7949</v>
       </c>
-      <c r="I35" s="87" t="n">
+      <c r="J35" s="87" t="n">
         <v>-7149</v>
       </c>
-      <c r="J35" s="87" t="n">
+      <c r="K35" s="87" t="n">
         <v>-5836</v>
       </c>
-      <c r="K35" s="87" t="n">
+      <c r="L35" s="87" t="n">
         <v>-5763</v>
       </c>
-      <c r="L35" s="87" t="n">
+      <c r="M35" s="87" t="n">
         <v>-6288</v>
       </c>
-      <c r="M35" s="87" t="n">
+      <c r="N35" s="87" t="n">
         <v>-7760</v>
       </c>
-      <c r="N35" s="87" t="n">
+      <c r="O35" s="87" t="n">
         <v>-6647</v>
       </c>
-      <c r="O35" s="87" t="n">
+      <c r="P35" s="87" t="n">
         <v>-5501</v>
       </c>
-      <c r="P35" s="87" t="n">
+      <c r="Q35" s="87" t="n">
         <v>-6893</v>
       </c>
-      <c r="Q35" s="87" t="n">
+      <c r="R35" s="87" t="n">
         <v>-6178</v>
       </c>
-      <c r="R35" s="87" t="n">
+      <c r="S35" s="87" t="n">
         <v>-7857</v>
       </c>
-      <c r="S35" s="87" t="n">
+      <c r="T35" s="87" t="n">
         <v>-7778</v>
       </c>
-      <c r="T35" s="87" t="n">
+      <c r="U35" s="87" t="n">
         <v>3316</v>
       </c>
-      <c r="U35" s="87" t="n">
+      <c r="V35" s="87" t="n">
         <v>3068</v>
       </c>
-      <c r="V35" s="87" t="n">
+      <c r="W35" s="87" t="n">
         <v>424</v>
       </c>
-      <c r="W35" s="87" t="n">
+      <c r="X35" s="87" t="n">
         <v>2142</v>
       </c>
-      <c r="X35" s="87" t="n">
+      <c r="Y35" s="87" t="n">
         <v>1655</v>
       </c>
-      <c r="Y35" s="87" t="n">
+      <c r="Z35" s="87" t="n">
         <v>1746</v>
       </c>
-      <c r="Z35" s="87" t="n">
+      <c r="AA35" s="87" t="n">
         <v>2380</v>
       </c>
-      <c r="AA35" s="87" t="n">
+      <c r="AB35" s="87" t="n">
         <v>1447</v>
       </c>
-      <c r="AB35" s="87" t="n">
+      <c r="AC35" s="87" t="n">
         <v>1452</v>
       </c>
-      <c r="AC35" s="87" t="n">
+      <c r="AD35" s="87" t="n">
         <v>538</v>
       </c>
-      <c r="AD35" s="87" t="n">
+      <c r="AE35" s="87" t="n">
         <v>-486</v>
-      </c>
-      <c r="AE35" s="87" t="n">
-        <v>-1507</v>
       </c>
     </row>
     <row r="36">
@@ -4964,94 +4964,94 @@
         </is>
       </c>
       <c r="B36" s="87" t="n">
+        <v>53101</v>
+      </c>
+      <c r="C36" s="87" t="n">
         <v>58839</v>
       </c>
-      <c r="C36" s="87" t="n">
+      <c r="D36" s="87" t="n">
         <v>65212</v>
       </c>
-      <c r="D36" s="87" t="n">
+      <c r="E36" s="87" t="n">
         <v>62949</v>
       </c>
-      <c r="E36" s="87" t="n">
+      <c r="F36" s="87" t="n">
         <v>66197</v>
       </c>
-      <c r="F36" s="87" t="n">
+      <c r="G36" s="87" t="n">
         <v>68838</v>
       </c>
-      <c r="G36" s="87" t="n">
+      <c r="H36" s="87" t="n">
         <v>66373</v>
       </c>
-      <c r="H36" s="87" t="n">
+      <c r="I36" s="87" t="n">
         <v>76163</v>
       </c>
-      <c r="I36" s="87" t="n">
+      <c r="J36" s="87" t="n">
         <v>70604</v>
       </c>
-      <c r="J36" s="87" t="n">
+      <c r="K36" s="87" t="n">
         <v>76315</v>
       </c>
-      <c r="K36" s="87" t="n">
+      <c r="L36" s="87" t="n">
         <v>72620</v>
       </c>
-      <c r="L36" s="87" t="n">
+      <c r="M36" s="87" t="n">
         <v>77671</v>
       </c>
-      <c r="M36" s="87" t="n">
+      <c r="N36" s="87" t="n">
         <v>82025</v>
       </c>
-      <c r="N36" s="87" t="n">
+      <c r="O36" s="87" t="n">
         <v>84772</v>
       </c>
-      <c r="O36" s="87" t="n">
+      <c r="P36" s="87" t="n">
         <v>86448</v>
       </c>
-      <c r="P36" s="87" t="n">
+      <c r="Q36" s="87" t="n">
         <v>89869</v>
       </c>
-      <c r="Q36" s="87" t="n">
+      <c r="R36" s="87" t="n">
         <v>90418</v>
       </c>
-      <c r="R36" s="87" t="n">
+      <c r="S36" s="87" t="n">
         <v>93250</v>
       </c>
-      <c r="S36" s="87" t="n">
+      <c r="T36" s="87" t="n">
         <v>89993</v>
       </c>
-      <c r="T36" s="87" t="n">
+      <c r="U36" s="87" t="n">
         <v>14143</v>
       </c>
-      <c r="U36" s="87" t="n">
+      <c r="V36" s="87" t="n">
         <v>15877</v>
       </c>
-      <c r="V36" s="87" t="n">
+      <c r="W36" s="87" t="n">
         <v>19039</v>
       </c>
-      <c r="W36" s="87" t="n">
+      <c r="X36" s="87" t="n">
         <v>19288</v>
       </c>
-      <c r="X36" s="87" t="n">
+      <c r="Y36" s="87" t="n">
         <v>25312</v>
       </c>
-      <c r="Y36" s="87" t="n">
+      <c r="Z36" s="87" t="n">
         <v>21970</v>
       </c>
-      <c r="Z36" s="87" t="n">
+      <c r="AA36" s="87" t="n">
         <v>26157</v>
       </c>
-      <c r="AA36" s="87" t="n">
+      <c r="AB36" s="87" t="n">
         <v>25451</v>
       </c>
-      <c r="AB36" s="87" t="n">
+      <c r="AC36" s="87" t="n">
         <v>33082</v>
       </c>
-      <c r="AC36" s="87" t="n">
+      <c r="AD36" s="87" t="n">
         <v>35645</v>
       </c>
-      <c r="AD36" s="87" t="n">
+      <c r="AE36" s="87" t="n">
         <v>35204</v>
-      </c>
-      <c r="AE36" s="87" t="n">
-        <v>36088</v>
       </c>
     </row>
     <row r="37">
@@ -5061,94 +5061,94 @@
         </is>
       </c>
       <c r="B37" s="87" t="n">
+        <v>125498</v>
+      </c>
+      <c r="C37" s="87" t="n">
         <v>126825</v>
       </c>
-      <c r="C37" s="87" t="n">
+      <c r="D37" s="87" t="n">
         <v>122035</v>
       </c>
-      <c r="D37" s="87" t="n">
+      <c r="E37" s="87" t="n">
         <v>125656</v>
       </c>
-      <c r="E37" s="87" t="n">
+      <c r="F37" s="87" t="n">
         <v>118142</v>
       </c>
-      <c r="F37" s="87" t="n">
+      <c r="G37" s="87" t="n">
         <v>118235</v>
       </c>
-      <c r="G37" s="87" t="n">
+      <c r="H37" s="87" t="n">
         <v>110786</v>
       </c>
-      <c r="H37" s="87" t="n">
+      <c r="I37" s="87" t="n">
         <v>122924</v>
       </c>
-      <c r="I37" s="87" t="n">
+      <c r="J37" s="87" t="n">
         <v>117927</v>
       </c>
-      <c r="J37" s="87" t="n">
+      <c r="K37" s="87" t="n">
         <v>116647</v>
       </c>
-      <c r="K37" s="87" t="n">
+      <c r="L37" s="87" t="n">
         <v>115300</v>
       </c>
-      <c r="L37" s="87" t="n">
+      <c r="M37" s="87" t="n">
         <v>115552</v>
       </c>
-      <c r="M37" s="87" t="n">
+      <c r="N37" s="87" t="n">
         <v>119400</v>
       </c>
-      <c r="N37" s="87" t="n">
+      <c r="O37" s="87" t="n">
         <v>121852</v>
       </c>
-      <c r="O37" s="87" t="n">
+      <c r="P37" s="87" t="n">
         <v>129562</v>
       </c>
-      <c r="P37" s="87" t="n">
+      <c r="Q37" s="87" t="n">
         <v>125109</v>
       </c>
-      <c r="Q37" s="87" t="n">
+      <c r="R37" s="87" t="n">
         <v>135159</v>
       </c>
-      <c r="R37" s="87" t="n">
+      <c r="S37" s="87" t="n">
         <v>143826</v>
       </c>
-      <c r="S37" s="87" t="n">
+      <c r="T37" s="87" t="n">
         <v>128738</v>
       </c>
-      <c r="T37" s="87" t="n">
+      <c r="U37" s="87" t="n">
         <v>130829</v>
       </c>
-      <c r="U37" s="87" t="n">
+      <c r="V37" s="87" t="n">
         <v>131214</v>
       </c>
-      <c r="V37" s="87" t="n">
+      <c r="W37" s="87" t="n">
         <v>123073</v>
       </c>
-      <c r="W37" s="87" t="n">
+      <c r="X37" s="87" t="n">
         <v>131961</v>
       </c>
-      <c r="X37" s="87" t="n">
+      <c r="Y37" s="87" t="n">
         <v>148330</v>
       </c>
-      <c r="Y37" s="87" t="n">
+      <c r="Z37" s="87" t="n">
         <v>137202</v>
       </c>
-      <c r="Z37" s="87" t="n">
+      <c r="AA37" s="87" t="n">
         <v>147647</v>
       </c>
-      <c r="AA37" s="87" t="n">
+      <c r="AB37" s="87" t="n">
         <v>148116</v>
       </c>
-      <c r="AB37" s="87" t="n">
+      <c r="AC37" s="87" t="n">
         <v>152500</v>
       </c>
-      <c r="AC37" s="87" t="n">
+      <c r="AD37" s="87" t="n">
         <v>148530</v>
       </c>
-      <c r="AD37" s="87" t="n">
+      <c r="AE37" s="87" t="n">
         <v>138042</v>
-      </c>
-      <c r="AE37" s="87" t="n">
-        <v>136114</v>
       </c>
     </row>
     <row r="38">
@@ -5158,94 +5158,94 @@
         </is>
       </c>
       <c r="B38" s="87" t="n">
+        <v>58169</v>
+      </c>
+      <c r="C38" s="87" t="n">
         <v>59356</v>
       </c>
-      <c r="C38" s="87" t="n">
+      <c r="D38" s="87" t="n">
         <v>55425</v>
       </c>
-      <c r="D38" s="87" t="n">
+      <c r="E38" s="87" t="n">
         <v>54843</v>
       </c>
-      <c r="E38" s="87" t="n">
+      <c r="F38" s="87" t="n">
         <v>52920</v>
       </c>
-      <c r="F38" s="87" t="n">
+      <c r="G38" s="87" t="n">
         <v>53807</v>
       </c>
-      <c r="G38" s="87" t="n">
+      <c r="H38" s="87" t="n">
         <v>53539</v>
       </c>
-      <c r="H38" s="87" t="n">
+      <c r="I38" s="87" t="n">
         <v>53866</v>
       </c>
-      <c r="I38" s="87" t="n">
+      <c r="J38" s="87" t="n">
         <v>53868</v>
       </c>
-      <c r="J38" s="87" t="n">
+      <c r="K38" s="87" t="n">
         <v>52372</v>
       </c>
-      <c r="K38" s="87" t="n">
+      <c r="L38" s="87" t="n">
         <v>51020</v>
       </c>
-      <c r="L38" s="87" t="n">
+      <c r="M38" s="87" t="n">
         <v>53738</v>
       </c>
-      <c r="M38" s="87" t="n">
+      <c r="N38" s="87" t="n">
         <v>56388</v>
       </c>
-      <c r="N38" s="87" t="n">
+      <c r="O38" s="87" t="n">
         <v>54848</v>
       </c>
-      <c r="O38" s="87" t="n">
+      <c r="P38" s="87" t="n">
         <v>58393</v>
       </c>
-      <c r="P38" s="87" t="n">
+      <c r="Q38" s="87" t="n">
         <v>56777</v>
       </c>
-      <c r="Q38" s="87" t="n">
+      <c r="R38" s="87" t="n">
         <v>57602</v>
       </c>
-      <c r="R38" s="87" t="n">
+      <c r="S38" s="87" t="n">
         <v>60702</v>
       </c>
-      <c r="S38" s="87" t="n">
+      <c r="T38" s="87" t="n">
         <v>58706</v>
       </c>
-      <c r="T38" s="87" t="n">
+      <c r="U38" s="87" t="n">
         <v>59655</v>
       </c>
-      <c r="U38" s="87" t="n">
+      <c r="V38" s="87" t="n">
         <v>60384</v>
       </c>
-      <c r="V38" s="87" t="n">
+      <c r="W38" s="87" t="n">
         <v>58117</v>
       </c>
-      <c r="W38" s="87" t="n">
+      <c r="X38" s="87" t="n">
         <v>64802</v>
       </c>
-      <c r="X38" s="87" t="n">
+      <c r="Y38" s="87" t="n">
         <v>70025</v>
       </c>
-      <c r="Y38" s="87" t="n">
+      <c r="Z38" s="87" t="n">
         <v>70149</v>
       </c>
-      <c r="Z38" s="87" t="n">
+      <c r="AA38" s="87" t="n">
         <v>70393</v>
       </c>
-      <c r="AA38" s="87" t="n">
+      <c r="AB38" s="87" t="n">
         <v>71521</v>
       </c>
-      <c r="AB38" s="87" t="n">
+      <c r="AC38" s="87" t="n">
         <v>74181</v>
       </c>
-      <c r="AC38" s="87" t="n">
+      <c r="AD38" s="87" t="n">
         <v>73178</v>
       </c>
-      <c r="AD38" s="87" t="n">
+      <c r="AE38" s="87" t="n">
         <v>67887</v>
-      </c>
-      <c r="AE38" s="87" t="n">
-        <v>67773</v>
       </c>
     </row>
     <row r="39">
@@ -5255,94 +5255,94 @@
         </is>
       </c>
       <c r="B39" s="87" t="n">
+        <v>21844</v>
+      </c>
+      <c r="C39" s="87" t="n">
         <v>23440</v>
       </c>
-      <c r="C39" s="87" t="n">
+      <c r="D39" s="87" t="n">
         <v>26714</v>
       </c>
-      <c r="D39" s="87" t="n">
+      <c r="E39" s="87" t="n">
         <v>23548</v>
       </c>
-      <c r="E39" s="87" t="n">
+      <c r="F39" s="87" t="n">
         <v>23276</v>
       </c>
-      <c r="F39" s="87" t="n">
+      <c r="G39" s="87" t="n">
         <v>23891</v>
       </c>
-      <c r="G39" s="87" t="n">
+      <c r="H39" s="87" t="n">
         <v>25503</v>
       </c>
-      <c r="H39" s="87" t="n">
+      <c r="I39" s="87" t="n">
         <v>27367</v>
       </c>
-      <c r="I39" s="87" t="n">
+      <c r="J39" s="87" t="n">
         <v>26882</v>
       </c>
-      <c r="J39" s="87" t="n">
+      <c r="K39" s="87" t="n">
         <v>26314</v>
       </c>
-      <c r="K39" s="87" t="n">
+      <c r="L39" s="87" t="n">
         <v>26343</v>
       </c>
-      <c r="L39" s="87" t="n">
+      <c r="M39" s="87" t="n">
         <v>27611</v>
       </c>
-      <c r="M39" s="87" t="n">
+      <c r="N39" s="87" t="n">
         <v>30360</v>
       </c>
-      <c r="N39" s="87" t="n">
+      <c r="O39" s="87" t="n">
         <v>30957</v>
       </c>
-      <c r="O39" s="87" t="n">
+      <c r="P39" s="87" t="n">
         <v>30447</v>
       </c>
-      <c r="P39" s="87" t="n">
+      <c r="Q39" s="87" t="n">
         <v>32090</v>
       </c>
-      <c r="Q39" s="87" t="n">
+      <c r="R39" s="87" t="n">
         <v>31857</v>
       </c>
-      <c r="R39" s="87" t="n">
+      <c r="S39" s="87" t="n">
         <v>33458</v>
       </c>
-      <c r="S39" s="87" t="n">
+      <c r="T39" s="87" t="n">
         <v>38662</v>
       </c>
-      <c r="T39" s="87" t="n">
+      <c r="U39" s="87" t="n">
         <v>3733</v>
       </c>
-      <c r="U39" s="87" t="n">
+      <c r="V39" s="87" t="n">
         <v>4401</v>
       </c>
-      <c r="V39" s="87" t="n">
+      <c r="W39" s="87" t="n">
         <v>5993</v>
       </c>
-      <c r="W39" s="87" t="n">
+      <c r="X39" s="87" t="n">
         <v>6643</v>
       </c>
-      <c r="X39" s="87" t="n">
+      <c r="Y39" s="87" t="n">
         <v>7791</v>
       </c>
-      <c r="Y39" s="87" t="n">
+      <c r="Z39" s="87" t="n">
         <v>9442</v>
       </c>
-      <c r="Z39" s="87" t="n">
+      <c r="AA39" s="87" t="n">
         <v>9640</v>
       </c>
-      <c r="AA39" s="87" t="n">
+      <c r="AB39" s="87" t="n">
         <v>9312</v>
       </c>
-      <c r="AB39" s="87" t="n">
+      <c r="AC39" s="87" t="n">
         <v>11474</v>
       </c>
-      <c r="AC39" s="87" t="n">
+      <c r="AD39" s="87" t="n">
         <v>12696</v>
       </c>
-      <c r="AD39" s="87" t="n">
+      <c r="AE39" s="87" t="n">
         <v>13167</v>
-      </c>
-      <c r="AE39" s="87" t="n">
-        <v>13361</v>
       </c>
     </row>
     <row r="41">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="B3" s="96" t="n">
-        <v>-0.51</v>
+        <v>-0.6</v>
       </c>
       <c r="C3" s="96" t="n">
         <v>-1.32</v>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" s="96" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="C4" s="96" t="n">
         <v>2.08</v>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="B5" s="96" t="n">
-        <v>36.14</v>
+        <v>35.12</v>
       </c>
       <c r="C5" s="96" t="n">
         <v>31.36</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="B6" s="96" t="n">
-        <v>45.89</v>
+        <v>40.18</v>
       </c>
       <c r="C6" s="96" t="n">
         <v>6.26</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="B8" s="96" t="n">
-        <v>-7.57</v>
+        <v>-7.68</v>
       </c>
       <c r="C8" s="96" t="n">
         <v>-7.65</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="B9" s="96" t="n">
-        <v>-12.94</v>
+        <v>-13.05</v>
       </c>
       <c r="C9" s="96" t="n">
         <v>-10.81</v>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B10" s="96" t="n">
-        <v>56.04</v>
+        <v>55.3</v>
       </c>
       <c r="C10" s="96" t="n">
         <v>56.03</v>
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="B11" s="96" t="n">
-        <v>64.09999999999999</v>
+        <v>62.33</v>
       </c>
       <c r="C11" s="96" t="n">
         <v>64.08</v>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B13" s="96" t="n">
-        <v>-6.47</v>
+        <v>-6.64</v>
       </c>
       <c r="C13" s="96" t="n">
         <v>-5.45</v>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="B14" s="96" t="n">
-        <v>-5.79</v>
+        <v>-5.96</v>
       </c>
       <c r="C14" s="96" t="n">
         <v>-4.79</v>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="B15" s="96" t="n">
-        <v>37.26</v>
+        <v>36.51</v>
       </c>
       <c r="C15" s="96" t="n">
         <v>38.37</v>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="B16" s="96" t="n">
-        <v>36.06</v>
+        <v>35.23</v>
       </c>
       <c r="C16" s="96" t="n">
         <v>37.28</v>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B18" s="96" t="n">
-        <v>5.14</v>
+        <v>4.94</v>
       </c>
       <c r="C18" s="96" t="n">
         <v>9.58</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="B19" s="96" t="n">
-        <v>9.76</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C19" s="96" t="n">
         <v>12.19</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="B20" s="96" t="n">
-        <v>25.06</v>
+        <v>24.17</v>
       </c>
       <c r="C20" s="96" t="n">
         <v>31.92</v>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="B21" s="96" t="n">
-        <v>46.59</v>
+        <v>46.12</v>
       </c>
       <c r="C21" s="96" t="n">
         <v>49.52</v>
@@ -10853,9 +10853,9 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C42" s="93" t="inlineStr">
@@ -11011,7 +11011,7 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
-        <v>1.59</v>
+        <v>2.84</v>
       </c>
       <c r="C43" s="96" t="n">
         <v>1.09</v>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
-        <v>15.27</v>
+        <v>16.69</v>
       </c>
       <c r="C44" s="96" t="n">
         <v>13.9</v>
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="B45" s="96" t="n">
-        <v>46.17</v>
+        <v>80.23</v>
       </c>
       <c r="C45" s="96" t="n">
         <v>46.62</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="B46" s="96" t="n">
-        <v>55.63</v>
+        <v>74.59</v>
       </c>
       <c r="C46" s="96" t="n">
         <v>55.87</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>3.79</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>7.48</v>
+        <v>7.42</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>6.96</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>61.99</v>
+        <v>61.72</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>60.75</v>
@@ -11847,7 +11847,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>58.66</v>
+        <v>58.51</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>58</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-4.56</v>
+        <v>-4.06</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-4.56</v>
@@ -12198,7 +12198,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>2.91</v>
+        <v>3.41</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>2.91</v>
@@ -12289,13 +12289,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="97" t="inlineStr">
+      <c r="A55" s="78" t="inlineStr">
         <is>
           <t>fr40:RSI3</t>
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>11.58</v>
+        <v>30.97</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>11.58</v>
@@ -12386,13 +12386,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="97" t="inlineStr">
+      <c r="A56" s="78" t="inlineStr">
         <is>
           <t>fr40:RSI5</t>
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>19.24</v>
+        <v>30.73</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>19.24</v>
@@ -12488,9 +12488,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B57" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C57" s="94" t="inlineStr">
@@ -12646,10 +12646,10 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="C58" s="96" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="D58" s="96" t="n">
         <v>2.97</v>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.34</v>
+        <v>10.43</v>
       </c>
       <c r="C59" s="96" t="n">
-        <v>10.34</v>
+        <v>10.33</v>
       </c>
       <c r="D59" s="96" t="n">
         <v>10.41</v>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>27.96</v>
+        <v>48.11</v>
       </c>
       <c r="C60" s="96" t="n">
-        <v>27.96</v>
+        <v>27.8</v>
       </c>
       <c r="D60" s="96" t="n">
         <v>39.93</v>
@@ -12937,10 +12937,10 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>33.87</v>
+        <v>46.64</v>
       </c>
       <c r="C61" s="96" t="n">
-        <v>33.87</v>
+        <v>33.73</v>
       </c>
       <c r="D61" s="96" t="n">
         <v>42.63</v>
@@ -13030,7 +13030,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RSI6:25.06&lt;=30;fr40:RSI3:11.58&lt;=28;fr40:RSI5:19.24&lt;=20</t>
+          <t>今日买报：hk50:RSI6:24.17&lt;=30</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>-0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.14</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.46</v>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>5.05</v>
+        <v>5.27</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>5.05</v>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>13.39</v>
+        <v>13.69</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>13.39</v>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>93.41</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>93.41</v>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>93.41</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>93.41</v>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>0.08</v>
+        <v>-0.2</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>0.08</v>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.86</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>41.04</v>
+        <v>35.59</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>41.04</v>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>44.63</v>
+        <v>42.08</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>44.63</v>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.58</v>
+        <v>9.35</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.58</v>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>16.36</v>
+        <v>17.36</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>16.36</v>
@@ -10113,13 +10113,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="78" t="inlineStr">
+      <c r="A35" s="98" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>94.09999999999999</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>94.09999999999999</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>94.09999999999999</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>94.09999999999999</v>
@@ -11943,9 +11943,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B52" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C52" s="94" t="inlineStr">
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-4.06</v>
+        <v>-3.67</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-4.56</v>
@@ -12198,7 +12198,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>2.91</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>30.97</v>
+        <v>40.45</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>11.58</v>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>30.73</v>
+        <v>37.21</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>19.24</v>
@@ -12488,9 +12488,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C57" s="94" t="inlineStr">
@@ -12646,7 +12646,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>3.09</v>
+        <v>3.95</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>2.38</v>
@@ -12743,7 +12743,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.43</v>
+        <v>11.35</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>10.33</v>
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>48.11</v>
+        <v>61.79</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>27.8</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>46.64</v>
+        <v>57.25</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>33.73</v>
@@ -13037,7 +13037,7 @@
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:93.41&gt;=91;us500:RSI2:93.41&gt;=85;ixic:RSI2:94.1&gt;=85</t>
+          <t>今日卖报：us500:RSI2:98.46&gt;=91;us500:RSI2:98.46&gt;=85;ixic:RSI2:98.29&gt;=95;ixic:RSI2:98.29&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.13</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.3</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>5.27</v>
+        <v>4.93</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>5.27</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>13.69</v>
+        <v>15.65</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>13.69</v>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>98.45999999999999</v>
+        <v>98.92</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>98.45999999999999</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>98.45999999999999</v>
+        <v>98.92</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>98.45999999999999</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.2</v>
+        <v>-1.19</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.2</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.07</v>
+        <v>4.22</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.07</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>35.59</v>
+        <v>26</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>35.59</v>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>42.08</v>
+        <v>37.19</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>42.08</v>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>9.35</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>17.36</v>
+        <v>19.55</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>17.36</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>98.29000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>98.29000000000001</v>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>98.29000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>98.29000000000001</v>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-4.61</v>
+        <v>-5.4</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-3.67</v>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>3.83</v>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>25.33</v>
+        <v>20.06</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>40.45</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>27.79</v>
+        <v>23.59</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>37.21</v>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>2.81</v>
+        <v>1.85</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>3.87</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.19</v>
+        <v>9.15</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>11.27</v>
@@ -12848,7 +12848,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>41.9</v>
+        <v>32.75</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>60.89</v>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>43.27</v>
+        <v>35.76</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>56.49</v>
@@ -13038,14 +13038,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：fr40:RSI3:25.33&lt;=28</t>
+          <t>今日买报：fr40:RSI3:20.06&lt;=28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：kc:RSI5:67.36&gt;=65;us500:RSI2:98.46&gt;=91;us500:RSI2:98.46&gt;=85;ixic:RSI2:98.29&gt;=95;ixic:RSI2:98.29&gt;=85</t>
+          <t>今日卖报：kc:RSI5:67.36&gt;=65;us500:RSI2:98.92&gt;=91;us500:RSI2:98.92&gt;=85;ixic:RSI2:98.7&gt;=95;ixic:RSI2:98.7&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.65</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>3.96</v>
+        <v>4.42</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>3.96</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.43</v>
+        <v>15.11</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.43</v>
@@ -9029,13 +9029,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>89.88</v>
+        <v>97.78</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>89.88</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>89.88</v>
+        <v>97.78</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>89.88</v>
@@ -9228,9 +9228,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B27" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C27" s="94" t="inlineStr">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-2.34</v>
+        <v>-2.52</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-2.34</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.17</v>
+        <v>3.72</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.17</v>
@@ -9574,13 +9574,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="98" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>19.12</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>19.12</v>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>32.92</v>
+        <v>54.28</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>32.92</v>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.06</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.06</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>18.21</v>
+        <v>19.1</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>18.21</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>98.89</v>
+        <v>99.67</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>98.89</v>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>98.89</v>
+        <v>99.67</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>98.89</v>
@@ -12111,7 +12111,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-7.93</v>
+        <v>-7.23</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-8.51</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>-0.72</v>
+        <v>0.04</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>-0.9</v>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>13.52</v>
+        <v>28</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>10.09</v>
@@ -12396,13 +12396,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="98" t="inlineStr">
+      <c r="A56" s="78" t="inlineStr">
         <is>
           <t>fr40:RSI5</t>
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>16.84</v>
+        <v>26.27</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>14.76</v>
@@ -12656,7 +12656,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>0.08</v>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>7.94</v>
+        <v>8.19</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>7.88</v>
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>26.21</v>
+        <v>30.48</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>22.73</v>
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>29.54</v>
+        <v>32.51</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>27.2</v>
@@ -13040,14 +13040,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：us30:RSI3:19.12&lt;=25;vn:RSI3:23.75&lt;=25;fr40:RSI3:13.52&lt;=28;fr40:RSI5:16.84&lt;=20</t>
+          <t>今日买报：vn:RSI3:23.75&lt;=25;fr40:RSI3:28.0&lt;=28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:89.88&gt;=85;ixic:RSI2:98.89&gt;=95;ixic:RSI2:98.89&gt;=85</t>
+          <t>今日卖报：us500:RSI2:97.78&gt;=91;us500:RSI2:97.78&gt;=85;ixic:RSI2:99.67&gt;=95;ixic:RSI2:99.67&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.01</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.51</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.42</v>
+        <v>4.83</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.42</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>15.11</v>
+        <v>14.92</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>15.11</v>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>97.78</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>97.78</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>97.78</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>97.78</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-2.52</v>
+        <v>-1.62</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-2.52</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.72</v>
+        <v>3.43</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.72</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>64.73999999999999</v>
+        <v>71.89</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>64.73999999999999</v>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>54.28</v>
+        <v>59.17</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>54.28</v>
@@ -9773,9 +9773,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="95" t="inlineStr">
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.869999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.869999999999999</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>19.1</v>
+        <v>18.49</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>19.1</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>99.67</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>99.67</v>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>99.67</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>99.67</v>
@@ -12111,7 +12111,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.94</v>
+        <v>-6.74</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-7.23</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>0.04</v>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>38.88</v>
+        <v>42.41</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>28</v>
@@ -12402,7 +12402,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>33.01</v>
+        <v>35.4</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>26.27</v>
@@ -12656,7 +12656,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-0.46</v>
+        <v>-0.31</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>0.29</v>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>8.08</v>
+        <v>8.25</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>8.15</v>
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>33.29</v>
+        <v>36.54</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>29.94</v>
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>34.28</v>
+        <v>36.44</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>32.12</v>
@@ -13047,7 +13047,7 @@
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:97.78&gt;=91;us500:RSI2:97.78&gt;=85;ixic:RSI2:99.67&gt;=95;ixic:RSI2:99.67&gt;=85</t>
+          <t>今日卖报：us500:RSI2:98.54&gt;=91;us500:RSI2:98.54&gt;=85;ixic:RSI2:99.68&gt;=95;ixic:RSI2:99.68&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.04</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.36</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.98</v>
+        <v>-7.14</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-6.74</v>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>0.75</v>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>34.2</v>
+        <v>32.44</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>42.41</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>31.5</v>
+        <v>30.56</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>35.4</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-0.65</v>
+        <v>-0.76</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-0.26</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>8.289999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>8.300000000000001</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>34</v>
+        <v>32.72</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>37.44</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>34.9</v>
+        <v>34.05</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>37.04</v>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2344,13 +2345,13 @@
         </is>
       </c>
       <c r="B9" s="84" t="n">
-        <v>0.4251</v>
+        <v>0.4574</v>
       </c>
       <c r="C9" s="84" t="n">
         <v>0.4805</v>
       </c>
       <c r="D9" s="84" t="n">
-        <v>0.4949</v>
+        <v>0.495</v>
       </c>
       <c r="E9" s="84" t="n">
         <v>0.477</v>
@@ -2362,10 +2363,10 @@
         <v>0.4768</v>
       </c>
       <c r="H9" s="84" t="n">
-        <v>0.4878</v>
+        <v>0.4879</v>
       </c>
       <c r="I9" s="84" t="n">
-        <v>0.4686</v>
+        <v>0.4687</v>
       </c>
       <c r="J9" s="84" t="n">
         <v>0.4906</v>
@@ -2380,7 +2381,7 @@
         <v>0.5323</v>
       </c>
       <c r="N9" s="84" t="n">
-        <v>0.504</v>
+        <v>0.5041</v>
       </c>
       <c r="O9" s="84" t="n">
         <v>0.5125999999999999</v>
@@ -2389,19 +2390,19 @@
         <v>0.5167</v>
       </c>
       <c r="Q9" s="84" t="n">
-        <v>0.5392</v>
+        <v>0.5393</v>
       </c>
       <c r="R9" s="84" t="n">
         <v>0.5333</v>
       </c>
       <c r="S9" s="84" t="n">
-        <v>0.5625</v>
+        <v>0.5626</v>
       </c>
       <c r="T9" s="84" t="n">
         <v>0.5208</v>
       </c>
       <c r="U9" s="84" t="n">
-        <v>0.5564</v>
+        <v>0.5565</v>
       </c>
       <c r="V9" s="84" t="n">
         <v>0.6166</v>
@@ -2410,7 +2411,7 @@
         <v>0.615</v>
       </c>
       <c r="X9" s="84" t="n">
-        <v>0.6378</v>
+        <v>0.6379</v>
       </c>
       <c r="Y9" s="84" t="n">
         <v>0.6185</v>
@@ -2419,7 +2420,7 @@
         <v>0.5766</v>
       </c>
       <c r="AA9" s="84" t="n">
-        <v>0.5743</v>
+        <v>0.5744</v>
       </c>
       <c r="AB9" s="84" t="n">
         <v>0.6079</v>
@@ -2431,7 +2432,7 @@
         <v>0.6281</v>
       </c>
       <c r="AE9" s="84" t="n">
-        <v>0.6394</v>
+        <v>0.6395</v>
       </c>
     </row>
     <row r="10">
@@ -2538,7 +2539,7 @@
         </is>
       </c>
       <c r="B11" s="86" t="n">
-        <v>-0.01450000000000001</v>
+        <v>-0.02569999999999997</v>
       </c>
       <c r="C11" s="86" t="n">
         <v>-0.02679999999999996</v>
@@ -2550,10 +2551,10 @@
         <v>-0.0287</v>
       </c>
       <c r="F11" s="86" t="n">
-        <v>-0.02819999999999998</v>
+        <v>-0.02809999999999999</v>
       </c>
       <c r="G11" s="86" t="n">
-        <v>-0.03420000000000001</v>
+        <v>-0.03410000000000002</v>
       </c>
       <c r="H11" s="86" t="n">
         <v>-0.0348</v>
@@ -2562,7 +2563,7 @@
         <v>-0.0275</v>
       </c>
       <c r="J11" s="86" t="n">
-        <v>-0.02760000000000001</v>
+        <v>-0.02750000000000002</v>
       </c>
       <c r="K11" s="86" t="n">
         <v>-0.02750000000000002</v>
@@ -2571,10 +2572,10 @@
         <v>-0.02820000000000003</v>
       </c>
       <c r="M11" s="86" t="n">
-        <v>-0.0315</v>
+        <v>-0.03140000000000001</v>
       </c>
       <c r="N11" s="86" t="n">
-        <v>-0.032</v>
+        <v>-0.03190000000000001</v>
       </c>
       <c r="O11" s="86" t="n">
         <v>-0.03310000000000002</v>
@@ -2595,7 +2596,7 @@
         <v>-0.03809999999999999</v>
       </c>
       <c r="U11" s="86" t="n">
-        <v>-0.04119999999999999</v>
+        <v>-0.0411</v>
       </c>
       <c r="V11" s="86" t="n">
         <v>-0.0431</v>
@@ -2619,7 +2620,7 @@
         <v>-0.04940000000000003</v>
       </c>
       <c r="AC11" s="86" t="n">
-        <v>-0.04990000000000003</v>
+        <v>-0.04980000000000001</v>
       </c>
       <c r="AD11" s="86" t="n">
         <v>-0.04789999999999997</v>
@@ -3023,7 +3024,7 @@
         </is>
       </c>
       <c r="B16" s="87" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C16" s="87" t="n">
         <v>40</v>
@@ -3120,7 +3121,7 @@
         </is>
       </c>
       <c r="B17" s="87" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="87" t="n">
         <v>12</v>
@@ -3217,7 +3218,7 @@
         </is>
       </c>
       <c r="B18" s="87" t="n">
-        <v>634</v>
+        <v>701</v>
       </c>
       <c r="C18" s="87" t="n">
         <v>263</v>
@@ -3271,7 +3272,7 @@
         <v>320</v>
       </c>
       <c r="T18" s="87" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U18" s="87" t="n">
         <v>112</v>
@@ -3280,7 +3281,7 @@
         <v>34</v>
       </c>
       <c r="W18" s="87" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X18" s="87" t="n">
         <v>28</v>
@@ -3605,7 +3606,7 @@
         </is>
       </c>
       <c r="B22" s="87" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="C22" s="87" t="n">
         <v>155</v>
@@ -3632,7 +3633,7 @@
         <v>162</v>
       </c>
       <c r="K22" s="87" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L22" s="87" t="n">
         <v>288</v>
@@ -3671,7 +3672,7 @@
         <v>315</v>
       </c>
       <c r="X22" s="87" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Y22" s="87" t="n">
         <v>467</v>
@@ -3993,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.1</v>
@@ -4090,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.43</v>
@@ -8682,9 +8683,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="95" t="inlineStr">
@@ -8840,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.83</v>
@@ -8937,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.92</v>
+        <v>14.46</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.92</v>
@@ -9028,13 +9029,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>98.54000000000001</v>
+        <v>58.48</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>98.54000000000001</v>
@@ -9125,13 +9126,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="97" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>98.54000000000001</v>
+        <v>58.48</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>98.54000000000001</v>
@@ -9385,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-1.62</v>
+        <v>-0.46</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-1.62</v>
@@ -9482,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.43</v>
+        <v>3.93</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.43</v>
@@ -9573,13 +9574,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="inlineStr">
+      <c r="A30" s="97" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>71.89</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>71.89</v>
@@ -9676,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>59.17</v>
+        <v>76.06</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>59.17</v>
@@ -9930,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.720000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.720000000000001</v>
@@ -10027,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>18.49</v>
+        <v>17.37</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>18.49</v>
@@ -10118,13 +10119,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="inlineStr">
+      <c r="A35" s="98" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>99.68000000000001</v>
+        <v>30.72</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>99.68000000000001</v>
@@ -10215,13 +10216,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="inlineStr">
+      <c r="A36" s="98" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>99.68000000000001</v>
+        <v>30.72</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>99.68000000000001</v>
@@ -12110,7 +12111,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.32</v>
+        <v>-5.89</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-7.14</v>
@@ -12207,7 +12208,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>0.47</v>
@@ -12304,7 +12305,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>51.66</v>
+        <v>58.01</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>32.44</v>
@@ -12401,7 +12402,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>41.78</v>
+        <v>46.38</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>30.56</v>
@@ -12655,7 +12656,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-0.76</v>
@@ -12752,7 +12753,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>8.41</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>8.18</v>
@@ -12849,7 +12850,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>45.74</v>
+        <v>53.51</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>32.74</v>
@@ -12946,7 +12947,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>42.08</v>
+        <v>47.58</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>34.07</v>
@@ -13039,14 +13040,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：</t>
+          <t>今日买报：ixic:RSI2:30.72&lt;=36;ixic:RSI2:30.72&lt;=35</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us500:RSI2:98.54&gt;=91;us500:RSI2:98.54&gt;=85;ixic:RSI2:99.68&gt;=95;ixic:RSI2:99.68&gt;=85</t>
+          <t>今日卖报：us30:RSI3:89.21&gt;=85</t>
         </is>
       </c>
     </row>
@@ -16702,13 +16703,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="99" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="99">
+      <c r="J2" s="100">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16739,13 +16740,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="100">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16776,13 +16777,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16813,13 +16814,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16850,13 +16851,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="100" t="n">
+      <c r="H6" s="101" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16887,13 +16888,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16924,13 +16925,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="100" t="n">
+      <c r="H8" s="101" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16961,13 +16962,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="100" t="n">
+      <c r="H9" s="101" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16998,13 +16999,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17035,13 +17036,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="102" t="n">
+      <c r="H11" s="103" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="104">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17072,13 +17073,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="100" t="n">
+      <c r="H12" s="101" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="102">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17109,13 +17110,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="102" t="n">
+      <c r="H13" s="103" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="104">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17146,13 +17147,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="100" t="n">
+      <c r="H14" s="101" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="102">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17183,13 +17184,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="102" t="n">
+      <c r="H15" s="103" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="104">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17220,13 +17221,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="100" t="n">
+      <c r="H16" s="101" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="102">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17257,13 +17258,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="102" t="n">
+      <c r="H17" s="103" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="104">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17294,13 +17295,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="100" t="n">
+      <c r="H18" s="101" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="102">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17331,13 +17332,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="102" t="n">
+      <c r="H19" s="103" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="104">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17368,13 +17369,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="100" t="n">
+      <c r="H20" s="101" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="102">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17405,13 +17406,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="102" t="n">
+      <c r="H21" s="103" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="103">
+      <c r="J21" s="104">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17440,13 +17441,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="104" t="n">
+      <c r="H22" s="105" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="102">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17475,13 +17476,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="105" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="102">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17510,13 +17511,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="n">
+      <c r="H24" s="101" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="102">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17545,13 +17546,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="100" t="n">
+      <c r="H25" s="101" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="102">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17580,13 +17581,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="100" t="n">
+      <c r="H26" s="101" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="102">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17615,13 +17616,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="100" t="n">
+      <c r="H27" s="101" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="102">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17650,13 +17651,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="104" t="n">
+      <c r="H28" s="105" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="102">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17685,13 +17686,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="105" t="n">
+      <c r="H29" s="106" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="104">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17720,13 +17721,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="104" t="n">
+      <c r="H30" s="105" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="102">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17755,13 +17756,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="105" t="n">
+      <c r="H31" s="106" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="103">
+      <c r="J31" s="104">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17790,13 +17791,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="104" t="n">
+      <c r="H32" s="105" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="102">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17825,13 +17826,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="105" t="n">
+      <c r="H33" s="106" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="104">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17860,13 +17861,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="105" t="n">
+      <c r="H34" s="106" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="104">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17895,13 +17896,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="105" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="102">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17930,13 +17931,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="105" t="n">
+      <c r="H36" s="106" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="103">
+      <c r="J36" s="104">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17965,13 +17966,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="105" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="102">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18000,13 +18001,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="104" t="n">
+      <c r="H38" s="105" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="102">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18035,13 +18036,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="105" t="n">
+      <c r="H39" s="106" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="103">
+      <c r="J39" s="104">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.17</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.53</v>
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.89</v>
+        <v>5.02</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.89</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.46</v>
+        <v>14.24</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.46</v>
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>58.48</v>
+        <v>38.94</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>58.48</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>58.48</v>
+        <v>38.94</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>58.48</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.46</v>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.93</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>89.20999999999999</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>89.20999999999999</v>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>76.06</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>76.06</v>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.16</v>
+        <v>8.42</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.16</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>17.37</v>
+        <v>17.19</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>17.37</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>30.72</v>
+        <v>23.33</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>30.72</v>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>30.72</v>
+        <v>23.33</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>30.72</v>
@@ -13040,14 +13040,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RSI2:30.72&lt;=36;ixic:RSI2:30.72&lt;=35</t>
+          <t>今日买报：ixic:RSI2:23.33&lt;=36;ixic:RSI2:23.33&lt;=35</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us30:RSI3:89.21&gt;=85</t>
+          <t>今日卖报：us30:RSI3:89.71&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.03</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.44</v>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>5.02</v>
+        <v>3.8</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>5.02</v>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.24</v>
+        <v>14.22</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.24</v>
@@ -9027,13 +9027,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>38.94</v>
+        <v>16.87</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>38.94</v>
@@ -9124,13 +9124,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>38.94</v>
+        <v>16.87</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>38.94</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.34</v>
+        <v>-0.88</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.34</v>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.82</v>
+        <v>4.57</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.82</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>89.70999999999999</v>
+        <v>95.22</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>89.70999999999999</v>
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>76.68000000000001</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>76.68000000000001</v>
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.42</v>
+        <v>6.69</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.42</v>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>17.19</v>
+        <v>16.56</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>17.19</v>
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>23.33</v>
+        <v>6.02</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>23.33</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>23.33</v>
+        <v>6.02</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>23.33</v>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.23</v>
+        <v>-6.07</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-6.8</v>
@@ -12206,7 +12206,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>1.3</v>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>63.04</v>
+        <v>65.25</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>46.78</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>51.32</v>
+        <v>52.97</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>41.4</v>
@@ -12496,9 +12496,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C57" s="94" t="inlineStr">
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-1.25</v>
+        <v>-0.73</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-1.2</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.32</v>
+        <v>10.91</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>8.31</v>
@@ -12848,7 +12848,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>54.72</v>
+        <v>62.48</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>45.16</v>
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>49.25</v>
+        <v>55.09</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>43.01</v>
@@ -13038,14 +13038,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI11:23.83&lt;=27;sh:RSI2:2.21&lt;=7;ixic:RSI2:23.33&lt;=36;ixic:RSI2:23.33&lt;=35;vn:RSI3:8.86&lt;=25</t>
+          <t>今日买报：sh:RSI11:23.83&lt;=27;sh:RSI2:2.21&lt;=7;us500:RSI2:16.87&lt;=28;us500:RSI2:16.87&lt;=22;ixic:RSI2:6.02&lt;=36;ixic:RSI2:6.02&lt;=35;vn:RSI3:8.86&lt;=25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us30:RSI3:89.71&gt;=85</t>
+          <t>今日卖报：us30:RSI3:95.22&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,7 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3994,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.08</v>
@@ -4091,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.31</v>
@@ -8841,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>3.8</v>
@@ -8938,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>14.22</v>
+        <v>15.32</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>14.22</v>
@@ -9029,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>16.87</v>
+        <v>66.08</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>16.87</v>
@@ -9126,13 +9125,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="97" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>16.87</v>
+        <v>66.08</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>16.87</v>
@@ -9228,9 +9227,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C27" s="95" t="inlineStr">
@@ -9386,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-0.88</v>
+        <v>-1.75</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-0.88</v>
@@ -9483,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>4.57</v>
+        <v>3.7</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>4.57</v>
@@ -9574,13 +9573,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="98" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>95.22</v>
+        <v>49.59</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>95.22</v>
@@ -9677,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>84.93000000000001</v>
+        <v>56.36</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>84.93000000000001</v>
@@ -9931,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>6.69</v>
+        <v>8.17</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>6.69</v>
@@ -10028,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>16.56</v>
+        <v>19.99</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>16.56</v>
@@ -10119,13 +10118,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="inlineStr">
+      <c r="A35" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>6.02</v>
+        <v>65.22</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>6.02</v>
@@ -10216,13 +10215,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>6.02</v>
+        <v>65.22</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>6.02</v>
@@ -12111,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.9</v>
+        <v>-6.62</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-6.07</v>
@@ -12208,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>3.98</v>
@@ -12305,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>45.1</v>
+        <v>50.33</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>65.25</v>
@@ -12402,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>43.71</v>
+        <v>46.44</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>52.97</v>
@@ -12656,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-1.88</v>
+        <v>-1.78</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-0.82</v>
@@ -12753,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>9.19</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>10.81</v>
@@ -12850,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>42.66</v>
+        <v>43.95</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>61.3</v>
@@ -12947,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>42.93</v>
+        <v>43.81</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>54.16</v>
@@ -13040,14 +13039,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI11:21.95&lt;=27;sh:RSI2:1.4&lt;=7;kc:RSI5:16.13&lt;=21;us500:RSI2:16.87&lt;=28;us500:RSI2:16.87&lt;=22;ixic:RSI2:6.02&lt;=36;ixic:RSI2:6.02&lt;=35;vn:RSI3:17.75&lt;=25</t>
+          <t>今日买报：sh:RSI11:21.95&lt;=27;sh:RSI2:1.4&lt;=7;kc:RSI5:16.13&lt;=21;vn:RSI3:17.75&lt;=25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：us30:RSI3:95.22&gt;=85</t>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -16703,13 +16702,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="99" t="n">
+      <c r="H2" s="98" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="100">
+      <c r="J2" s="99">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16740,13 +16739,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="100">
+      <c r="J3" s="99">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16777,13 +16776,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16814,13 +16813,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16851,13 +16850,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="101" t="n">
+      <c r="H6" s="100" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16888,13 +16887,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16925,13 +16924,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="101" t="n">
+      <c r="H8" s="100" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16962,13 +16961,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="101" t="n">
+      <c r="H9" s="100" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16999,13 +16998,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="101">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17036,13 +17035,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="103" t="n">
+      <c r="H11" s="102" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="104">
+      <c r="J11" s="103">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17073,13 +17072,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="101" t="n">
+      <c r="H12" s="100" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="102">
+      <c r="J12" s="101">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17110,13 +17109,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="103" t="n">
+      <c r="H13" s="102" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="104">
+      <c r="J13" s="103">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17147,13 +17146,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="101" t="n">
+      <c r="H14" s="100" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="102">
+      <c r="J14" s="101">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17184,13 +17183,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="103" t="n">
+      <c r="H15" s="102" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="104">
+      <c r="J15" s="103">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17221,13 +17220,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="101" t="n">
+      <c r="H16" s="100" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="102">
+      <c r="J16" s="101">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17258,13 +17257,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="103" t="n">
+      <c r="H17" s="102" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="104">
+      <c r="J17" s="103">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17295,13 +17294,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="101" t="n">
+      <c r="H18" s="100" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="102">
+      <c r="J18" s="101">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17332,13 +17331,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="103" t="n">
+      <c r="H19" s="102" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="104">
+      <c r="J19" s="103">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17369,13 +17368,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="101" t="n">
+      <c r="H20" s="100" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="102">
+      <c r="J20" s="101">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17406,13 +17405,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="103" t="n">
+      <c r="H21" s="102" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="104">
+      <c r="J21" s="103">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17441,13 +17440,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="105" t="n">
+      <c r="H22" s="104" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="102">
+      <c r="J22" s="101">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17476,13 +17475,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="105" t="n">
+      <c r="H23" s="104" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="102">
+      <c r="J23" s="101">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17511,13 +17510,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="101" t="n">
+      <c r="H24" s="100" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="102">
+      <c r="J24" s="101">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17546,13 +17545,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="101" t="n">
+      <c r="H25" s="100" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="102">
+      <c r="J25" s="101">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17581,13 +17580,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="101" t="n">
+      <c r="H26" s="100" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="102">
+      <c r="J26" s="101">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17616,13 +17615,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="101" t="n">
+      <c r="H27" s="100" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="102">
+      <c r="J27" s="101">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17651,13 +17650,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="105" t="n">
+      <c r="H28" s="104" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="102">
+      <c r="J28" s="101">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17686,13 +17685,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="106" t="n">
+      <c r="H29" s="105" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="104">
+      <c r="J29" s="103">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17721,13 +17720,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="105" t="n">
+      <c r="H30" s="104" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="102">
+      <c r="J30" s="101">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17756,13 +17755,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="106" t="n">
+      <c r="H31" s="105" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="104">
+      <c r="J31" s="103">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17791,13 +17790,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="105" t="n">
+      <c r="H32" s="104" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="102">
+      <c r="J32" s="101">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17826,13 +17825,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="106" t="n">
+      <c r="H33" s="105" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="104">
+      <c r="J33" s="103">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17861,13 +17860,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="106" t="n">
+      <c r="H34" s="105" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="104">
+      <c r="J34" s="103">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17896,13 +17895,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="105" t="n">
+      <c r="H35" s="104" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="102">
+      <c r="J35" s="101">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17931,13 +17930,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="106" t="n">
+      <c r="H36" s="105" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="104">
+      <c r="J36" s="103">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17966,13 +17965,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="105" t="n">
+      <c r="H37" s="104" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="102">
+      <c r="J37" s="101">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18001,13 +18000,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="105" t="n">
+      <c r="H38" s="104" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="102">
+      <c r="J38" s="101">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18036,13 +18035,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="106" t="n">
+      <c r="H39" s="105" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="104">
+      <c r="J39" s="103">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1063,6 +1063,7 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3993,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.08</v>
@@ -4090,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.31</v>
@@ -6347,152 +6348,152 @@
       </c>
       <c r="B1" s="79" t="inlineStr">
         <is>
+          <t>240626</t>
+        </is>
+      </c>
+      <c r="C1" s="79" t="inlineStr">
+        <is>
           <t>240625</t>
         </is>
       </c>
-      <c r="C1" s="79" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>240624</t>
         </is>
       </c>
-      <c r="D1" s="79" t="inlineStr">
+      <c r="E1" s="79" t="inlineStr">
         <is>
           <t>240621</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="F1" s="79" t="inlineStr">
         <is>
           <t>240620</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>240619</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>240618</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>240617</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="J1" s="79" t="inlineStr">
         <is>
           <t>240614</t>
         </is>
       </c>
-      <c r="J1" s="79" t="inlineStr">
+      <c r="K1" s="79" t="inlineStr">
         <is>
           <t>240613</t>
         </is>
       </c>
-      <c r="K1" s="79" t="inlineStr">
+      <c r="L1" s="79" t="inlineStr">
         <is>
           <t>240612</t>
         </is>
       </c>
-      <c r="L1" s="79" t="inlineStr">
+      <c r="M1" s="79" t="inlineStr">
         <is>
           <t>240611</t>
         </is>
       </c>
-      <c r="M1" s="79" t="inlineStr">
+      <c r="N1" s="79" t="inlineStr">
         <is>
           <t>240610</t>
         </is>
       </c>
-      <c r="N1" s="79" t="inlineStr">
+      <c r="O1" s="79" t="inlineStr">
         <is>
           <t>240607</t>
         </is>
       </c>
-      <c r="O1" s="79" t="inlineStr">
+      <c r="P1" s="79" t="inlineStr">
         <is>
           <t>240606</t>
         </is>
       </c>
-      <c r="P1" s="79" t="inlineStr">
+      <c r="Q1" s="79" t="inlineStr">
         <is>
           <t>240605</t>
         </is>
       </c>
-      <c r="Q1" s="79" t="inlineStr">
+      <c r="R1" s="79" t="inlineStr">
         <is>
           <t>240604</t>
         </is>
       </c>
-      <c r="R1" s="79" t="inlineStr">
+      <c r="S1" s="79" t="inlineStr">
         <is>
           <t>240603</t>
         </is>
       </c>
-      <c r="S1" s="79" t="inlineStr">
+      <c r="T1" s="79" t="inlineStr">
         <is>
           <t>240531</t>
         </is>
       </c>
-      <c r="T1" s="79" t="inlineStr">
+      <c r="U1" s="79" t="inlineStr">
         <is>
           <t>240530</t>
         </is>
       </c>
-      <c r="U1" s="79" t="inlineStr">
+      <c r="V1" s="79" t="inlineStr">
         <is>
           <t>240529</t>
         </is>
       </c>
-      <c r="V1" s="79" t="inlineStr">
+      <c r="W1" s="79" t="inlineStr">
         <is>
           <t>240528</t>
         </is>
       </c>
-      <c r="W1" s="79" t="inlineStr">
+      <c r="X1" s="79" t="inlineStr">
         <is>
           <t>240527</t>
         </is>
       </c>
-      <c r="X1" s="79" t="inlineStr">
+      <c r="Y1" s="79" t="inlineStr">
         <is>
           <t>240524</t>
         </is>
       </c>
-      <c r="Y1" s="79" t="inlineStr">
+      <c r="Z1" s="79" t="inlineStr">
         <is>
           <t>240523</t>
         </is>
       </c>
-      <c r="Z1" s="79" t="inlineStr">
+      <c r="AA1" s="79" t="inlineStr">
         <is>
           <t>240522</t>
         </is>
       </c>
-      <c r="AA1" s="79" t="inlineStr">
+      <c r="AB1" s="79" t="inlineStr">
         <is>
           <t>240521</t>
         </is>
       </c>
-      <c r="AB1" s="79" t="inlineStr">
+      <c r="AC1" s="79" t="inlineStr">
         <is>
           <t>240520</t>
         </is>
       </c>
-      <c r="AC1" s="79" t="inlineStr">
+      <c r="AD1" s="79" t="inlineStr">
         <is>
           <t>240518</t>
         </is>
       </c>
-      <c r="AD1" s="79" t="inlineStr">
+      <c r="AE1" s="79" t="inlineStr">
         <is>
           <t>240517</t>
-        </is>
-      </c>
-      <c r="AE1" s="79" t="inlineStr">
-        <is>
-          <t>240516</t>
         </is>
       </c>
     </row>
@@ -6512,144 +6513,144 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D2" s="94" t="inlineStr">
+      <c r="D2" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E2" s="94" t="inlineStr">
+      <c r="F2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="94" t="inlineStr">
+      <c r="G2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="94" t="inlineStr">
+      <c r="H2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="94" t="inlineStr">
+      <c r="I2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="94" t="inlineStr">
+      <c r="J2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="94" t="inlineStr">
+      <c r="K2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="94" t="inlineStr">
+      <c r="L2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="93" t="inlineStr">
+      <c r="M2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M2" s="94" t="inlineStr">
+      <c r="N2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="94" t="inlineStr">
+      <c r="O2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="93" t="inlineStr">
+      <c r="P2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P2" s="93" t="inlineStr">
+      <c r="Q2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q2" s="94" t="inlineStr">
+      <c r="R2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="93" t="inlineStr">
+      <c r="S2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S2" s="93" t="inlineStr">
+      <c r="T2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T2" s="93" t="inlineStr">
+      <c r="U2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U2" s="93" t="inlineStr">
+      <c r="V2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V2" s="93" t="inlineStr">
+      <c r="W2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="X2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="Y2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Z2" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z2" s="94" t="inlineStr">
+      <c r="AA2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA2" s="94" t="inlineStr">
+      <c r="AB2" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB2" s="95" t="inlineStr">
+      <c r="AC2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC2" s="95" t="inlineStr">
+      <c r="AD2" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD2" s="95" t="inlineStr">
+      <c r="AE2" s="95" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="AE2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
     </row>
@@ -6660,94 +6661,94 @@
         </is>
       </c>
       <c r="B3" s="96" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C3" s="96" t="n">
         <v>-2.52</v>
       </c>
-      <c r="C3" s="96" t="n">
+      <c r="D3" s="96" t="n">
         <v>-2.79</v>
       </c>
-      <c r="D3" s="96" t="n">
+      <c r="E3" s="96" t="n">
         <v>-2.57</v>
       </c>
-      <c r="E3" s="96" t="n">
+      <c r="F3" s="96" t="n">
         <v>-2.41</v>
       </c>
-      <c r="F3" s="96" t="n">
+      <c r="G3" s="96" t="n">
         <v>-1.46</v>
       </c>
-      <c r="G3" s="96" t="n">
+      <c r="H3" s="96" t="n">
         <v>-1.77</v>
       </c>
-      <c r="H3" s="96" t="n">
+      <c r="I3" s="96" t="n">
         <v>-1.27</v>
       </c>
-      <c r="I3" s="96" t="n">
+      <c r="J3" s="96" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J3" s="96" t="n">
+      <c r="K3" s="96" t="n">
         <v>-0.49</v>
       </c>
-      <c r="K3" s="96" t="n">
+      <c r="L3" s="96" t="n">
         <v>-0.6</v>
       </c>
-      <c r="L3" s="96" t="n">
+      <c r="M3" s="96" t="n">
         <v>-1.32</v>
-      </c>
-      <c r="M3" s="96" t="n">
-        <v>0.17</v>
       </c>
       <c r="N3" s="96" t="n">
         <v>0.17</v>
       </c>
       <c r="O3" s="96" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P3" s="96" t="n">
         <v>0.71</v>
       </c>
-      <c r="P3" s="96" t="n">
+      <c r="Q3" s="96" t="n">
         <v>0.84</v>
       </c>
-      <c r="Q3" s="96" t="n">
+      <c r="R3" s="96" t="n">
         <v>1.42</v>
       </c>
-      <c r="R3" s="96" t="n">
+      <c r="S3" s="96" t="n">
         <v>1.29</v>
       </c>
-      <c r="S3" s="96" t="n">
+      <c r="T3" s="96" t="n">
         <v>1.98</v>
       </c>
-      <c r="T3" s="96" t="n">
+      <c r="U3" s="96" t="n">
         <v>2.54</v>
       </c>
-      <c r="U3" s="96" t="n">
+      <c r="V3" s="96" t="n">
         <v>5.18</v>
       </c>
-      <c r="V3" s="96" t="n">
+      <c r="W3" s="96" t="n">
         <v>3.12</v>
       </c>
-      <c r="W3" s="96" t="n">
+      <c r="X3" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="X3" s="96" t="n">
+      <c r="Y3" s="96" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y3" s="96" t="n">
+      <c r="Z3" s="96" t="n">
         <v>4.28</v>
       </c>
-      <c r="Z3" s="96" t="n">
+      <c r="AA3" s="96" t="n">
         <v>7.03</v>
       </c>
-      <c r="AA3" s="96" t="n">
+      <c r="AB3" s="96" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="AB3" s="96" t="n">
+      <c r="AC3" s="96" t="n">
         <v>8.949999999999999</v>
-      </c>
-      <c r="AC3" s="96" t="n">
-        <v>10.05</v>
       </c>
       <c r="AD3" s="96" t="n">
         <v>10.05</v>
       </c>
       <c r="AE3" s="96" t="n">
-        <v>10.34</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="4">
@@ -6757,94 +6758,94 @@
         </is>
       </c>
       <c r="B4" s="96" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C4" s="96" t="n">
         <v>1.07</v>
       </c>
-      <c r="C4" s="96" t="n">
+      <c r="D4" s="96" t="n">
         <v>2.1</v>
       </c>
-      <c r="D4" s="96" t="n">
+      <c r="E4" s="96" t="n">
         <v>2.24</v>
       </c>
-      <c r="E4" s="96" t="n">
+      <c r="F4" s="96" t="n">
         <v>2.55</v>
       </c>
-      <c r="F4" s="96" t="n">
+      <c r="G4" s="96" t="n">
         <v>2.57</v>
       </c>
-      <c r="G4" s="96" t="n">
+      <c r="H4" s="96" t="n">
         <v>2.41</v>
       </c>
-      <c r="H4" s="96" t="n">
+      <c r="I4" s="96" t="n">
         <v>1.59</v>
       </c>
-      <c r="I4" s="96" t="n">
+      <c r="J4" s="96" t="n">
         <v>0.97</v>
       </c>
-      <c r="J4" s="96" t="n">
+      <c r="K4" s="96" t="n">
         <v>1.25</v>
       </c>
-      <c r="K4" s="96" t="n">
+      <c r="L4" s="96" t="n">
         <v>2.29</v>
       </c>
-      <c r="L4" s="96" t="n">
+      <c r="M4" s="96" t="n">
         <v>2.08</v>
-      </c>
-      <c r="M4" s="96" t="n">
-        <v>2.77</v>
       </c>
       <c r="N4" s="96" t="n">
         <v>2.77</v>
       </c>
       <c r="O4" s="96" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P4" s="96" t="n">
         <v>2.57</v>
       </c>
-      <c r="P4" s="96" t="n">
+      <c r="Q4" s="96" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q4" s="96" t="n">
+      <c r="R4" s="96" t="n">
         <v>1.96</v>
       </c>
-      <c r="R4" s="96" t="n">
+      <c r="S4" s="96" t="n">
         <v>1.61</v>
       </c>
-      <c r="S4" s="96" t="n">
+      <c r="T4" s="96" t="n">
         <v>2.16</v>
       </c>
-      <c r="T4" s="96" t="n">
+      <c r="U4" s="96" t="n">
         <v>1.75</v>
       </c>
-      <c r="U4" s="96" t="n">
+      <c r="V4" s="96" t="n">
         <v>2.62</v>
       </c>
-      <c r="V4" s="96" t="n">
+      <c r="W4" s="96" t="n">
         <v>2.26</v>
       </c>
-      <c r="W4" s="96" t="n">
+      <c r="X4" s="96" t="n">
         <v>2.03</v>
       </c>
-      <c r="X4" s="96" t="n">
+      <c r="Y4" s="96" t="n">
         <v>1.49</v>
       </c>
-      <c r="Y4" s="96" t="n">
+      <c r="Z4" s="96" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z4" s="96" t="n">
+      <c r="AA4" s="96" t="n">
         <v>2.94</v>
       </c>
-      <c r="AA4" s="96" t="n">
+      <c r="AB4" s="96" t="n">
         <v>3.39</v>
       </c>
-      <c r="AB4" s="96" t="n">
+      <c r="AC4" s="96" t="n">
         <v>3.94</v>
-      </c>
-      <c r="AC4" s="96" t="n">
-        <v>2.64</v>
       </c>
       <c r="AD4" s="96" t="n">
         <v>2.64</v>
       </c>
       <c r="AE4" s="96" t="n">
-        <v>2.17</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="5">
@@ -6854,94 +6855,94 @@
         </is>
       </c>
       <c r="B5" s="96" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="C5" s="96" t="n">
         <v>21.95</v>
       </c>
-      <c r="C5" s="96" t="n">
+      <c r="D5" s="96" t="n">
         <v>23.83</v>
       </c>
-      <c r="D5" s="96" t="n">
+      <c r="E5" s="96" t="n">
         <v>30.1</v>
       </c>
-      <c r="E5" s="96" t="n">
+      <c r="F5" s="96" t="n">
         <v>31.68</v>
       </c>
-      <c r="F5" s="96" t="n">
+      <c r="G5" s="96" t="n">
         <v>34.53</v>
       </c>
-      <c r="G5" s="96" t="n">
+      <c r="H5" s="96" t="n">
         <v>37.49</v>
       </c>
-      <c r="H5" s="96" t="n">
+      <c r="I5" s="96" t="n">
         <v>31.17</v>
       </c>
-      <c r="I5" s="96" t="n">
+      <c r="J5" s="96" t="n">
         <v>34.91</v>
       </c>
-      <c r="J5" s="96" t="n">
+      <c r="K5" s="96" t="n">
         <v>33.3</v>
       </c>
-      <c r="K5" s="96" t="n">
+      <c r="L5" s="96" t="n">
         <v>35.12</v>
       </c>
-      <c r="L5" s="96" t="n">
+      <c r="M5" s="96" t="n">
         <v>31.36</v>
-      </c>
-      <c r="M5" s="96" t="n">
-        <v>36.04</v>
       </c>
       <c r="N5" s="96" t="n">
         <v>36.04</v>
       </c>
       <c r="O5" s="96" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="P5" s="96" t="n">
         <v>35.1</v>
       </c>
-      <c r="P5" s="96" t="n">
+      <c r="Q5" s="96" t="n">
         <v>38.55</v>
       </c>
-      <c r="Q5" s="96" t="n">
+      <c r="R5" s="96" t="n">
         <v>44.78</v>
       </c>
-      <c r="R5" s="96" t="n">
+      <c r="S5" s="96" t="n">
         <v>40.48</v>
       </c>
-      <c r="S5" s="96" t="n">
+      <c r="T5" s="96" t="n">
         <v>42.44</v>
       </c>
-      <c r="T5" s="96" t="n">
+      <c r="U5" s="96" t="n">
         <v>43.57</v>
       </c>
-      <c r="U5" s="96" t="n">
+      <c r="V5" s="96" t="n">
         <v>48.19</v>
       </c>
-      <c r="V5" s="96" t="n">
+      <c r="W5" s="96" t="n">
         <v>47.82</v>
       </c>
-      <c r="W5" s="96" t="n">
+      <c r="X5" s="96" t="n">
         <v>51.2</v>
       </c>
-      <c r="X5" s="96" t="n">
+      <c r="Y5" s="96" t="n">
         <v>42.16</v>
       </c>
-      <c r="Y5" s="96" t="n">
+      <c r="Z5" s="96" t="n">
         <v>48.56</v>
       </c>
-      <c r="Z5" s="96" t="n">
+      <c r="AA5" s="96" t="n">
         <v>61.58</v>
       </c>
-      <c r="AA5" s="96" t="n">
+      <c r="AB5" s="96" t="n">
         <v>61.45</v>
       </c>
-      <c r="AB5" s="96" t="n">
+      <c r="AC5" s="96" t="n">
         <v>66.04000000000001</v>
-      </c>
-      <c r="AC5" s="96" t="n">
-        <v>62.75</v>
       </c>
       <c r="AD5" s="96" t="n">
         <v>62.75</v>
       </c>
       <c r="AE5" s="96" t="n">
-        <v>55.52</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="6">
@@ -6951,94 +6952,94 @@
         </is>
       </c>
       <c r="B6" s="96" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C6" s="96" t="n">
         <v>1.4</v>
       </c>
-      <c r="C6" s="96" t="n">
+      <c r="D6" s="96" t="n">
         <v>2.21</v>
       </c>
-      <c r="D6" s="96" t="n">
+      <c r="E6" s="96" t="n">
         <v>9.99</v>
       </c>
-      <c r="E6" s="96" t="n">
+      <c r="F6" s="96" t="n">
         <v>15.75</v>
       </c>
-      <c r="F6" s="96" t="n">
+      <c r="G6" s="96" t="n">
         <v>31.41</v>
       </c>
-      <c r="G6" s="96" t="n">
+      <c r="H6" s="96" t="n">
         <v>60.49</v>
       </c>
-      <c r="H6" s="96" t="n">
+      <c r="I6" s="96" t="n">
         <v>13.18</v>
       </c>
-      <c r="I6" s="96" t="n">
+      <c r="J6" s="96" t="n">
         <v>43.64</v>
       </c>
-      <c r="J6" s="96" t="n">
+      <c r="K6" s="96" t="n">
         <v>24.25</v>
       </c>
-      <c r="K6" s="96" t="n">
+      <c r="L6" s="96" t="n">
         <v>40.18</v>
       </c>
-      <c r="L6" s="96" t="n">
+      <c r="M6" s="96" t="n">
         <v>6.26</v>
-      </c>
-      <c r="M6" s="96" t="n">
-        <v>20.81</v>
       </c>
       <c r="N6" s="96" t="n">
         <v>20.81</v>
       </c>
       <c r="O6" s="96" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="P6" s="96" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="P6" s="96" t="n">
+      <c r="Q6" s="96" t="n">
         <v>18.16</v>
       </c>
-      <c r="Q6" s="96" t="n">
+      <c r="R6" s="96" t="n">
         <v>60.74</v>
       </c>
-      <c r="R6" s="96" t="n">
+      <c r="S6" s="96" t="n">
         <v>7.07</v>
       </c>
-      <c r="S6" s="96" t="n">
+      <c r="T6" s="96" t="n">
         <v>12.8</v>
       </c>
-      <c r="T6" s="96" t="n">
+      <c r="U6" s="96" t="n">
         <v>16.77</v>
       </c>
-      <c r="U6" s="96" t="n">
+      <c r="V6" s="96" t="n">
         <v>43.73</v>
       </c>
-      <c r="V6" s="96" t="n">
+      <c r="W6" s="96" t="n">
         <v>40.12</v>
       </c>
-      <c r="W6" s="96" t="n">
+      <c r="X6" s="96" t="n">
         <v>58.99</v>
       </c>
-      <c r="X6" s="96" t="n">
+      <c r="Y6" s="96" t="n">
         <v>4.28</v>
       </c>
-      <c r="Y6" s="96" t="n">
+      <c r="Z6" s="96" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="Z6" s="96" t="n">
+      <c r="AA6" s="96" t="n">
         <v>54.6</v>
       </c>
-      <c r="AA6" s="96" t="n">
+      <c r="AB6" s="96" t="n">
         <v>52.98</v>
       </c>
-      <c r="AB6" s="96" t="n">
+      <c r="AC6" s="96" t="n">
         <v>90.23999999999999</v>
-      </c>
-      <c r="AC6" s="96" t="n">
-        <v>82.04000000000001</v>
       </c>
       <c r="AD6" s="96" t="n">
         <v>82.04000000000001</v>
       </c>
       <c r="AE6" s="96" t="n">
-        <v>19.58</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -7057,124 +7058,124 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D7" s="95" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E7" s="94" t="inlineStr">
+      <c r="F7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F7" s="93" t="inlineStr">
+      <c r="G7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G7" s="94" t="inlineStr">
+      <c r="H7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H7" s="95" t="inlineStr">
+      <c r="I7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I7" s="94" t="inlineStr">
+      <c r="J7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J7" s="95" t="inlineStr">
+      <c r="K7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K7" s="95" t="inlineStr">
+      <c r="L7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L7" s="95" t="inlineStr">
+      <c r="M7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M7" s="93" t="inlineStr">
+      <c r="N7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N7" s="93" t="inlineStr">
+      <c r="O7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O7" s="93" t="inlineStr">
+      <c r="P7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P7" s="95" t="inlineStr">
+      <c r="Q7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q7" s="95" t="inlineStr">
+      <c r="R7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R7" s="95" t="inlineStr">
+      <c r="S7" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S7" s="94" t="inlineStr">
+      <c r="T7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T7" s="94" t="inlineStr">
+      <c r="U7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U7" s="94" t="inlineStr">
+      <c r="V7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V7" s="93" t="inlineStr">
+      <c r="W7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W7" s="94" t="inlineStr">
+      <c r="X7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X7" s="93" t="inlineStr">
+      <c r="Y7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y7" s="93" t="inlineStr">
+      <c r="Z7" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z7" s="94" t="inlineStr">
+      <c r="AA7" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AA7" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="AB7" s="93" t="inlineStr">
@@ -7205,94 +7206,94 @@
         </is>
       </c>
       <c r="B8" s="96" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="C8" s="96" t="n">
         <v>-8.18</v>
       </c>
-      <c r="C8" s="96" t="n">
+      <c r="D8" s="96" t="n">
         <v>-6.93</v>
       </c>
-      <c r="D8" s="96" t="n">
+      <c r="E8" s="96" t="n">
         <v>-5.93</v>
       </c>
-      <c r="E8" s="96" t="n">
+      <c r="F8" s="96" t="n">
         <v>-7.23</v>
       </c>
-      <c r="F8" s="96" t="n">
+      <c r="G8" s="96" t="n">
         <v>-7.4</v>
       </c>
-      <c r="G8" s="96" t="n">
+      <c r="H8" s="96" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H8" s="96" t="n">
+      <c r="I8" s="96" t="n">
         <v>-6.38</v>
       </c>
-      <c r="I8" s="96" t="n">
+      <c r="J8" s="96" t="n">
         <v>-6.29</v>
       </c>
-      <c r="J8" s="96" t="n">
+      <c r="K8" s="96" t="n">
         <v>-6.87</v>
       </c>
-      <c r="K8" s="96" t="n">
+      <c r="L8" s="96" t="n">
         <v>-7.68</v>
       </c>
-      <c r="L8" s="96" t="n">
+      <c r="M8" s="96" t="n">
         <v>-7.65</v>
-      </c>
-      <c r="M8" s="96" t="n">
-        <v>-8.130000000000001</v>
       </c>
       <c r="N8" s="96" t="n">
         <v>-8.130000000000001</v>
       </c>
       <c r="O8" s="96" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="P8" s="96" t="n">
         <v>-6.42</v>
       </c>
-      <c r="P8" s="96" t="n">
+      <c r="Q8" s="96" t="n">
         <v>-7.37</v>
       </c>
-      <c r="Q8" s="96" t="n">
+      <c r="R8" s="96" t="n">
         <v>-7.84</v>
       </c>
-      <c r="R8" s="96" t="n">
+      <c r="S8" s="96" t="n">
         <v>-8.32</v>
       </c>
-      <c r="S8" s="96" t="n">
+      <c r="T8" s="96" t="n">
         <v>-8.859999999999999</v>
       </c>
-      <c r="T8" s="96" t="n">
+      <c r="U8" s="96" t="n">
         <v>-8.050000000000001</v>
       </c>
-      <c r="U8" s="96" t="n">
+      <c r="V8" s="96" t="n">
         <v>-4.83</v>
       </c>
-      <c r="V8" s="96" t="n">
+      <c r="W8" s="96" t="n">
         <v>-7.79</v>
       </c>
-      <c r="W8" s="96" t="n">
+      <c r="X8" s="96" t="n">
         <v>-3.88</v>
       </c>
-      <c r="X8" s="96" t="n">
+      <c r="Y8" s="96" t="n">
         <v>-4.88</v>
       </c>
-      <c r="Y8" s="96" t="n">
+      <c r="Z8" s="96" t="n">
         <v>-2.62</v>
       </c>
-      <c r="Z8" s="96" t="n">
+      <c r="AA8" s="96" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AA8" s="96" t="n">
+      <c r="AB8" s="96" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AB8" s="96" t="n">
+      <c r="AC8" s="96" t="n">
         <v>-1.28</v>
-      </c>
-      <c r="AC8" s="96" t="n">
-        <v>0.39</v>
       </c>
       <c r="AD8" s="96" t="n">
         <v>0.39</v>
       </c>
       <c r="AE8" s="96" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="9">
@@ -7302,94 +7303,94 @@
         </is>
       </c>
       <c r="B9" s="96" t="n">
+        <v>-15.16</v>
+      </c>
+      <c r="C9" s="96" t="n">
         <v>-15.34</v>
       </c>
-      <c r="C9" s="96" t="n">
+      <c r="D9" s="96" t="n">
         <v>-11.56</v>
       </c>
-      <c r="D9" s="96" t="n">
+      <c r="E9" s="96" t="n">
         <v>-10.34</v>
       </c>
-      <c r="E9" s="96" t="n">
+      <c r="F9" s="96" t="n">
         <v>-10.17</v>
       </c>
-      <c r="F9" s="96" t="n">
+      <c r="G9" s="96" t="n">
         <v>-11.31</v>
       </c>
-      <c r="G9" s="96" t="n">
+      <c r="H9" s="96" t="n">
         <v>-11.57</v>
       </c>
-      <c r="H9" s="96" t="n">
+      <c r="I9" s="96" t="n">
         <v>-12.09</v>
       </c>
-      <c r="I9" s="96" t="n">
+      <c r="J9" s="96" t="n">
         <v>-13.3</v>
       </c>
-      <c r="J9" s="96" t="n">
+      <c r="K9" s="96" t="n">
         <v>-13.61</v>
       </c>
-      <c r="K9" s="96" t="n">
+      <c r="L9" s="96" t="n">
         <v>-13.05</v>
       </c>
-      <c r="L9" s="96" t="n">
+      <c r="M9" s="96" t="n">
         <v>-10.81</v>
-      </c>
-      <c r="M9" s="96" t="n">
-        <v>-13.06</v>
       </c>
       <c r="N9" s="96" t="n">
         <v>-13.06</v>
       </c>
       <c r="O9" s="96" t="n">
+        <v>-13.06</v>
+      </c>
+      <c r="P9" s="96" t="n">
         <v>-12.13</v>
       </c>
-      <c r="P9" s="96" t="n">
+      <c r="Q9" s="96" t="n">
         <v>-12.75</v>
       </c>
-      <c r="Q9" s="96" t="n">
+      <c r="R9" s="96" t="n">
         <v>-13.13</v>
       </c>
-      <c r="R9" s="96" t="n">
+      <c r="S9" s="96" t="n">
         <v>-13.31</v>
       </c>
-      <c r="S9" s="96" t="n">
+      <c r="T9" s="96" t="n">
         <v>-13.78</v>
       </c>
-      <c r="T9" s="96" t="n">
+      <c r="U9" s="96" t="n">
         <v>-14.82</v>
       </c>
-      <c r="U9" s="96" t="n">
+      <c r="V9" s="96" t="n">
         <v>-15.4</v>
       </c>
-      <c r="V9" s="96" t="n">
+      <c r="W9" s="96" t="n">
         <v>-15.02</v>
       </c>
-      <c r="W9" s="96" t="n">
+      <c r="X9" s="96" t="n">
         <v>-15.85</v>
       </c>
-      <c r="X9" s="96" t="n">
+      <c r="Y9" s="96" t="n">
         <v>-16.49</v>
       </c>
-      <c r="Y9" s="96" t="n">
+      <c r="Z9" s="96" t="n">
         <v>-16.1</v>
       </c>
-      <c r="Z9" s="96" t="n">
+      <c r="AA9" s="96" t="n">
         <v>-15.42</v>
       </c>
-      <c r="AA9" s="96" t="n">
+      <c r="AB9" s="96" t="n">
         <v>-16.06</v>
       </c>
-      <c r="AB9" s="96" t="n">
+      <c r="AC9" s="96" t="n">
         <v>-15.06</v>
-      </c>
-      <c r="AC9" s="96" t="n">
-        <v>-16.38</v>
       </c>
       <c r="AD9" s="96" t="n">
         <v>-16.38</v>
       </c>
       <c r="AE9" s="96" t="n">
-        <v>-17.46</v>
+        <v>-16.38</v>
       </c>
     </row>
     <row r="10">
@@ -7399,94 +7400,94 @@
         </is>
       </c>
       <c r="B10" s="96" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="C10" s="96" t="n">
         <v>29.08</v>
       </c>
-      <c r="C10" s="96" t="n">
+      <c r="D10" s="96" t="n">
         <v>39.78</v>
       </c>
-      <c r="D10" s="96" t="n">
+      <c r="E10" s="96" t="n">
         <v>56.63</v>
       </c>
-      <c r="E10" s="96" t="n">
+      <c r="F10" s="96" t="n">
         <v>53.67</v>
       </c>
-      <c r="F10" s="96" t="n">
+      <c r="G10" s="96" t="n">
         <v>50.4</v>
       </c>
-      <c r="G10" s="96" t="n">
+      <c r="H10" s="96" t="n">
         <v>55.73</v>
       </c>
-      <c r="H10" s="96" t="n">
+      <c r="I10" s="96" t="n">
         <v>55.95</v>
       </c>
-      <c r="I10" s="96" t="n">
+      <c r="J10" s="96" t="n">
         <v>53.77</v>
       </c>
-      <c r="J10" s="96" t="n">
+      <c r="K10" s="96" t="n">
         <v>58.04</v>
       </c>
-      <c r="K10" s="96" t="n">
+      <c r="L10" s="96" t="n">
         <v>55.3</v>
       </c>
-      <c r="L10" s="96" t="n">
+      <c r="M10" s="96" t="n">
         <v>56.03</v>
-      </c>
-      <c r="M10" s="96" t="n">
-        <v>42.36</v>
       </c>
       <c r="N10" s="96" t="n">
         <v>42.36</v>
       </c>
       <c r="O10" s="96" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="P10" s="96" t="n">
         <v>46.19</v>
       </c>
-      <c r="P10" s="96" t="n">
+      <c r="Q10" s="96" t="n">
         <v>53.41</v>
       </c>
-      <c r="Q10" s="96" t="n">
+      <c r="R10" s="96" t="n">
         <v>54.81</v>
       </c>
-      <c r="R10" s="96" t="n">
+      <c r="S10" s="96" t="n">
         <v>52.56</v>
       </c>
-      <c r="S10" s="96" t="n">
+      <c r="T10" s="96" t="n">
         <v>47.27</v>
       </c>
-      <c r="T10" s="96" t="n">
+      <c r="U10" s="96" t="n">
         <v>46.88</v>
       </c>
-      <c r="U10" s="96" t="n">
+      <c r="V10" s="96" t="n">
         <v>40.6</v>
       </c>
-      <c r="V10" s="96" t="n">
+      <c r="W10" s="96" t="n">
         <v>40.87</v>
       </c>
-      <c r="W10" s="96" t="n">
+      <c r="X10" s="96" t="n">
         <v>42.74</v>
       </c>
-      <c r="X10" s="96" t="n">
+      <c r="Y10" s="96" t="n">
         <v>34.63</v>
       </c>
-      <c r="Y10" s="96" t="n">
+      <c r="Z10" s="96" t="n">
         <v>41.69</v>
       </c>
-      <c r="Z10" s="96" t="n">
+      <c r="AA10" s="96" t="n">
         <v>49.14</v>
       </c>
-      <c r="AA10" s="96" t="n">
+      <c r="AB10" s="96" t="n">
         <v>44.35</v>
       </c>
-      <c r="AB10" s="96" t="n">
+      <c r="AC10" s="96" t="n">
         <v>47.52</v>
-      </c>
-      <c r="AC10" s="96" t="n">
-        <v>48.04</v>
       </c>
       <c r="AD10" s="96" t="n">
         <v>48.04</v>
       </c>
       <c r="AE10" s="96" t="n">
-        <v>43.02</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="11">
@@ -7496,94 +7497,94 @@
         </is>
       </c>
       <c r="B11" s="96" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="C11" s="96" t="n">
         <v>16.13</v>
       </c>
-      <c r="C11" s="96" t="n">
+      <c r="D11" s="96" t="n">
         <v>28.34</v>
       </c>
-      <c r="D11" s="96" t="n">
+      <c r="E11" s="96" t="n">
         <v>62.26</v>
       </c>
-      <c r="E11" s="96" t="n">
+      <c r="F11" s="96" t="n">
         <v>55.06</v>
       </c>
-      <c r="F11" s="96" t="n">
+      <c r="G11" s="96" t="n">
         <v>46.24</v>
       </c>
-      <c r="G11" s="96" t="n">
+      <c r="H11" s="96" t="n">
         <v>60.55</v>
       </c>
-      <c r="H11" s="96" t="n">
+      <c r="I11" s="96" t="n">
         <v>61.16</v>
       </c>
-      <c r="I11" s="96" t="n">
+      <c r="J11" s="96" t="n">
         <v>56.39</v>
       </c>
-      <c r="J11" s="96" t="n">
+      <c r="K11" s="96" t="n">
         <v>67.36</v>
       </c>
-      <c r="K11" s="96" t="n">
+      <c r="L11" s="96" t="n">
         <v>62.33</v>
       </c>
-      <c r="L11" s="96" t="n">
+      <c r="M11" s="96" t="n">
         <v>64.08</v>
-      </c>
-      <c r="M11" s="96" t="n">
-        <v>34.88</v>
       </c>
       <c r="N11" s="96" t="n">
         <v>34.88</v>
       </c>
       <c r="O11" s="96" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="P11" s="96" t="n">
         <v>43.2</v>
       </c>
-      <c r="P11" s="96" t="n">
+      <c r="Q11" s="96" t="n">
         <v>63.28</v>
       </c>
-      <c r="Q11" s="96" t="n">
+      <c r="R11" s="96" t="n">
         <v>67.86</v>
       </c>
-      <c r="R11" s="96" t="n">
+      <c r="S11" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="S11" s="96" t="n">
+      <c r="T11" s="96" t="n">
         <v>52.4</v>
       </c>
-      <c r="T11" s="96" t="n">
+      <c r="U11" s="96" t="n">
         <v>51.52</v>
       </c>
-      <c r="U11" s="96" t="n">
+      <c r="V11" s="96" t="n">
         <v>36.71</v>
       </c>
-      <c r="V11" s="96" t="n">
+      <c r="W11" s="96" t="n">
         <v>37.28</v>
       </c>
-      <c r="W11" s="96" t="n">
+      <c r="X11" s="96" t="n">
         <v>40.97</v>
       </c>
-      <c r="X11" s="96" t="n">
+      <c r="Y11" s="96" t="n">
         <v>22.47</v>
       </c>
-      <c r="Y11" s="96" t="n">
+      <c r="Z11" s="96" t="n">
         <v>33.68</v>
       </c>
-      <c r="Z11" s="96" t="n">
+      <c r="AA11" s="96" t="n">
         <v>50.29</v>
       </c>
-      <c r="AA11" s="96" t="n">
+      <c r="AB11" s="96" t="n">
         <v>36.98</v>
       </c>
-      <c r="AB11" s="96" t="n">
+      <c r="AC11" s="96" t="n">
         <v>44.48</v>
-      </c>
-      <c r="AC11" s="96" t="n">
-        <v>45.72</v>
       </c>
       <c r="AD11" s="96" t="n">
         <v>45.72</v>
       </c>
       <c r="AE11" s="96" t="n">
-        <v>32.12</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="12">
@@ -7617,129 +7618,129 @@
           <t>green</t>
         </is>
       </c>
-      <c r="G12" s="95" t="inlineStr">
+      <c r="G12" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="H12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H12" s="95" t="inlineStr">
+      <c r="I12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I12" s="94" t="inlineStr">
+      <c r="J12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J12" s="93" t="inlineStr">
+      <c r="K12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K12" s="93" t="inlineStr">
+      <c r="L12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L12" s="93" t="inlineStr">
+      <c r="M12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="93" t="inlineStr">
+      <c r="N12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="93" t="inlineStr">
+      <c r="O12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O12" s="94" t="inlineStr">
+      <c r="P12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P12" s="95" t="inlineStr">
+      <c r="Q12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q12" s="95" t="inlineStr">
+      <c r="R12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R12" s="94" t="inlineStr">
+      <c r="S12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S12" s="93" t="inlineStr">
+      <c r="T12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T12" s="94" t="inlineStr">
+      <c r="U12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U12" s="93" t="inlineStr">
+      <c r="V12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V12" s="93" t="inlineStr">
+      <c r="W12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W12" s="93" t="inlineStr">
+      <c r="X12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X12" s="93" t="inlineStr">
+      <c r="Y12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y12" s="93" t="inlineStr">
+      <c r="Z12" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z12" s="95" t="inlineStr">
+      <c r="AA12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA12" s="94" t="inlineStr">
+      <c r="AB12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB12" s="95" t="inlineStr">
+      <c r="AC12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC12" s="94" t="inlineStr">
+      <c r="AD12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD12" s="94" t="inlineStr">
+      <c r="AE12" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -7750,94 +7751,94 @@
         </is>
       </c>
       <c r="B13" s="96" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="C13" s="96" t="n">
         <v>-7.28</v>
       </c>
-      <c r="C13" s="96" t="n">
+      <c r="D13" s="96" t="n">
         <v>-7.36</v>
       </c>
-      <c r="D13" s="96" t="n">
+      <c r="E13" s="96" t="n">
         <v>-7.44</v>
       </c>
-      <c r="E13" s="96" t="n">
+      <c r="F13" s="96" t="n">
         <v>-7.68</v>
       </c>
-      <c r="F13" s="96" t="n">
+      <c r="G13" s="96" t="n">
         <v>-6.21</v>
       </c>
-      <c r="G13" s="96" t="n">
+      <c r="H13" s="96" t="n">
         <v>-5.97</v>
       </c>
-      <c r="H13" s="96" t="n">
+      <c r="I13" s="96" t="n">
         <v>-4.13</v>
       </c>
-      <c r="I13" s="96" t="n">
+      <c r="J13" s="96" t="n">
         <v>-4.87</v>
       </c>
-      <c r="J13" s="96" t="n">
+      <c r="K13" s="96" t="n">
         <v>-6.19</v>
       </c>
-      <c r="K13" s="96" t="n">
+      <c r="L13" s="96" t="n">
         <v>-6.64</v>
       </c>
-      <c r="L13" s="96" t="n">
+      <c r="M13" s="96" t="n">
         <v>-5.45</v>
-      </c>
-      <c r="M13" s="96" t="n">
-        <v>-1.45</v>
       </c>
       <c r="N13" s="96" t="n">
         <v>-1.45</v>
       </c>
       <c r="O13" s="96" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="P13" s="96" t="n">
         <v>1.7</v>
       </c>
-      <c r="P13" s="96" t="n">
+      <c r="Q13" s="96" t="n">
         <v>0.05</v>
       </c>
-      <c r="Q13" s="96" t="n">
+      <c r="R13" s="96" t="n">
         <v>0.54</v>
       </c>
-      <c r="R13" s="96" t="n">
+      <c r="S13" s="96" t="n">
         <v>-0.84</v>
       </c>
-      <c r="S13" s="96" t="n">
+      <c r="T13" s="96" t="n">
         <v>-1.04</v>
       </c>
-      <c r="T13" s="96" t="n">
+      <c r="U13" s="96" t="n">
         <v>0.34</v>
       </c>
-      <c r="U13" s="96" t="n">
+      <c r="V13" s="96" t="n">
         <v>3.55</v>
       </c>
-      <c r="V13" s="96" t="n">
+      <c r="W13" s="96" t="n">
         <v>0.68</v>
       </c>
-      <c r="W13" s="96" t="n">
+      <c r="X13" s="96" t="n">
         <v>4.52</v>
       </c>
-      <c r="X13" s="96" t="n">
+      <c r="Y13" s="96" t="n">
         <v>3.43</v>
       </c>
-      <c r="Y13" s="96" t="n">
+      <c r="Z13" s="96" t="n">
         <v>5.36</v>
       </c>
-      <c r="Z13" s="96" t="n">
+      <c r="AA13" s="96" t="n">
         <v>7.16</v>
       </c>
-      <c r="AA13" s="96" t="n">
+      <c r="AB13" s="96" t="n">
         <v>6.6</v>
       </c>
-      <c r="AB13" s="96" t="n">
+      <c r="AC13" s="96" t="n">
         <v>7.42</v>
-      </c>
-      <c r="AC13" s="96" t="n">
-        <v>8</v>
       </c>
       <c r="AD13" s="96" t="n">
         <v>8</v>
       </c>
       <c r="AE13" s="96" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -7847,94 +7848,94 @@
         </is>
       </c>
       <c r="B14" s="96" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="C14" s="96" t="n">
         <v>-7.24</v>
       </c>
-      <c r="C14" s="96" t="n">
+      <c r="D14" s="96" t="n">
         <v>-3.96</v>
       </c>
-      <c r="D14" s="96" t="n">
+      <c r="E14" s="96" t="n">
         <v>-3.93</v>
       </c>
-      <c r="E14" s="96" t="n">
+      <c r="F14" s="96" t="n">
         <v>-3.15</v>
       </c>
-      <c r="F14" s="96" t="n">
+      <c r="G14" s="96" t="n">
         <v>-3.25</v>
       </c>
-      <c r="G14" s="96" t="n">
+      <c r="H14" s="96" t="n">
         <v>-2.64</v>
       </c>
-      <c r="H14" s="96" t="n">
+      <c r="I14" s="96" t="n">
         <v>-3.53</v>
       </c>
-      <c r="I14" s="96" t="n">
+      <c r="J14" s="96" t="n">
         <v>-5.91</v>
       </c>
-      <c r="J14" s="96" t="n">
+      <c r="K14" s="96" t="n">
         <v>-7.2</v>
       </c>
-      <c r="K14" s="96" t="n">
+      <c r="L14" s="96" t="n">
         <v>-5.96</v>
       </c>
-      <c r="L14" s="96" t="n">
+      <c r="M14" s="96" t="n">
         <v>-4.79</v>
-      </c>
-      <c r="M14" s="96" t="n">
-        <v>-5.36</v>
       </c>
       <c r="N14" s="96" t="n">
         <v>-5.36</v>
       </c>
       <c r="O14" s="96" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="P14" s="96" t="n">
         <v>-2.71</v>
       </c>
-      <c r="P14" s="96" t="n">
+      <c r="Q14" s="96" t="n">
         <v>-3.95</v>
       </c>
-      <c r="Q14" s="96" t="n">
+      <c r="R14" s="96" t="n">
         <v>-4.29</v>
       </c>
-      <c r="R14" s="96" t="n">
+      <c r="S14" s="96" t="n">
         <v>-5.36</v>
       </c>
-      <c r="S14" s="96" t="n">
+      <c r="T14" s="96" t="n">
         <v>-5.88</v>
       </c>
-      <c r="T14" s="96" t="n">
+      <c r="U14" s="96" t="n">
         <v>-6.46</v>
       </c>
-      <c r="U14" s="96" t="n">
+      <c r="V14" s="96" t="n">
         <v>-5.98</v>
       </c>
-      <c r="V14" s="96" t="n">
+      <c r="W14" s="96" t="n">
         <v>-6.8</v>
       </c>
-      <c r="W14" s="96" t="n">
+      <c r="X14" s="96" t="n">
         <v>-6.65</v>
       </c>
-      <c r="X14" s="96" t="n">
+      <c r="Y14" s="96" t="n">
         <v>-6.74</v>
       </c>
-      <c r="Y14" s="96" t="n">
+      <c r="Z14" s="96" t="n">
         <v>-6.66</v>
       </c>
-      <c r="Z14" s="96" t="n">
+      <c r="AA14" s="96" t="n">
         <v>-5.77</v>
       </c>
-      <c r="AA14" s="96" t="n">
+      <c r="AB14" s="96" t="n">
         <v>-6.29</v>
       </c>
-      <c r="AB14" s="96" t="n">
+      <c r="AC14" s="96" t="n">
         <v>-5.17</v>
-      </c>
-      <c r="AC14" s="96" t="n">
-        <v>-7.46</v>
       </c>
       <c r="AD14" s="96" t="n">
         <v>-7.46</v>
       </c>
       <c r="AE14" s="96" t="n">
-        <v>-8.01</v>
+        <v>-7.46</v>
       </c>
     </row>
     <row r="15">
@@ -7944,94 +7945,94 @@
         </is>
       </c>
       <c r="B15" s="96" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="C15" s="96" t="n">
         <v>23.23</v>
       </c>
-      <c r="C15" s="96" t="n">
+      <c r="D15" s="96" t="n">
         <v>28.38</v>
       </c>
-      <c r="D15" s="96" t="n">
+      <c r="E15" s="96" t="n">
         <v>33.55</v>
       </c>
-      <c r="E15" s="96" t="n">
+      <c r="F15" s="96" t="n">
         <v>35.17</v>
       </c>
-      <c r="F15" s="96" t="n">
+      <c r="G15" s="96" t="n">
         <v>42.06</v>
       </c>
-      <c r="G15" s="96" t="n">
+      <c r="H15" s="96" t="n">
         <v>49.86</v>
       </c>
-      <c r="H15" s="96" t="n">
+      <c r="I15" s="96" t="n">
         <v>47.9</v>
       </c>
-      <c r="I15" s="96" t="n">
+      <c r="J15" s="96" t="n">
         <v>42.03</v>
       </c>
-      <c r="J15" s="96" t="n">
+      <c r="K15" s="96" t="n">
         <v>36.1</v>
       </c>
-      <c r="K15" s="96" t="n">
+      <c r="L15" s="96" t="n">
         <v>36.51</v>
       </c>
-      <c r="L15" s="96" t="n">
+      <c r="M15" s="96" t="n">
         <v>38.37</v>
-      </c>
-      <c r="M15" s="96" t="n">
-        <v>36.04</v>
       </c>
       <c r="N15" s="96" t="n">
         <v>36.04</v>
       </c>
       <c r="O15" s="96" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="P15" s="96" t="n">
         <v>45.9</v>
       </c>
-      <c r="P15" s="96" t="n">
+      <c r="Q15" s="96" t="n">
         <v>49.99</v>
       </c>
-      <c r="Q15" s="96" t="n">
+      <c r="R15" s="96" t="n">
         <v>53.27</v>
       </c>
-      <c r="R15" s="96" t="n">
+      <c r="S15" s="96" t="n">
         <v>45.55</v>
       </c>
-      <c r="S15" s="96" t="n">
+      <c r="T15" s="96" t="n">
         <v>40.27</v>
       </c>
-      <c r="T15" s="96" t="n">
+      <c r="U15" s="96" t="n">
         <v>42.34</v>
       </c>
-      <c r="U15" s="96" t="n">
+      <c r="V15" s="96" t="n">
         <v>41.64</v>
       </c>
-      <c r="V15" s="96" t="n">
+      <c r="W15" s="96" t="n">
         <v>40.13</v>
       </c>
-      <c r="W15" s="96" t="n">
+      <c r="X15" s="96" t="n">
         <v>45.58</v>
       </c>
-      <c r="X15" s="96" t="n">
+      <c r="Y15" s="96" t="n">
         <v>42.02</v>
       </c>
-      <c r="Y15" s="96" t="n">
+      <c r="Z15" s="96" t="n">
         <v>49.97</v>
       </c>
-      <c r="Z15" s="96" t="n">
+      <c r="AA15" s="96" t="n">
         <v>57.52</v>
       </c>
-      <c r="AA15" s="96" t="n">
+      <c r="AB15" s="96" t="n">
         <v>53.49</v>
       </c>
-      <c r="AB15" s="96" t="n">
+      <c r="AC15" s="96" t="n">
         <v>57.82</v>
-      </c>
-      <c r="AC15" s="96" t="n">
-        <v>55.35</v>
       </c>
       <c r="AD15" s="96" t="n">
         <v>55.35</v>
       </c>
       <c r="AE15" s="96" t="n">
-        <v>50.41</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="16">
@@ -8041,94 +8042,94 @@
         </is>
       </c>
       <c r="B16" s="96" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="C16" s="96" t="n">
         <v>21.37</v>
       </c>
-      <c r="C16" s="96" t="n">
+      <c r="D16" s="96" t="n">
         <v>26.72</v>
       </c>
-      <c r="D16" s="96" t="n">
+      <c r="E16" s="96" t="n">
         <v>32.27</v>
       </c>
-      <c r="E16" s="96" t="n">
+      <c r="F16" s="96" t="n">
         <v>34.03</v>
       </c>
-      <c r="F16" s="96" t="n">
+      <c r="G16" s="96" t="n">
         <v>41.67</v>
       </c>
-      <c r="G16" s="96" t="n">
+      <c r="H16" s="96" t="n">
         <v>50.62</v>
       </c>
-      <c r="H16" s="96" t="n">
+      <c r="I16" s="96" t="n">
         <v>48.39</v>
       </c>
-      <c r="I16" s="96" t="n">
+      <c r="J16" s="96" t="n">
         <v>41.68</v>
       </c>
-      <c r="J16" s="96" t="n">
+      <c r="K16" s="96" t="n">
         <v>34.78</v>
       </c>
-      <c r="K16" s="96" t="n">
+      <c r="L16" s="96" t="n">
         <v>35.23</v>
       </c>
-      <c r="L16" s="96" t="n">
+      <c r="M16" s="96" t="n">
         <v>37.28</v>
-      </c>
-      <c r="M16" s="96" t="n">
-        <v>34.6</v>
       </c>
       <c r="N16" s="96" t="n">
         <v>34.6</v>
       </c>
       <c r="O16" s="96" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="P16" s="96" t="n">
         <v>45.5</v>
       </c>
-      <c r="P16" s="96" t="n">
+      <c r="Q16" s="96" t="n">
         <v>50.17</v>
       </c>
-      <c r="Q16" s="96" t="n">
+      <c r="R16" s="96" t="n">
         <v>53.94</v>
       </c>
-      <c r="R16" s="96" t="n">
+      <c r="S16" s="96" t="n">
         <v>45.12</v>
       </c>
-      <c r="S16" s="96" t="n">
+      <c r="T16" s="96" t="n">
         <v>38.95</v>
       </c>
-      <c r="T16" s="96" t="n">
+      <c r="U16" s="96" t="n">
         <v>41.26</v>
       </c>
-      <c r="U16" s="96" t="n">
+      <c r="V16" s="96" t="n">
         <v>40.45</v>
       </c>
-      <c r="V16" s="96" t="n">
+      <c r="W16" s="96" t="n">
         <v>38.7</v>
       </c>
-      <c r="W16" s="96" t="n">
+      <c r="X16" s="96" t="n">
         <v>44.68</v>
       </c>
-      <c r="X16" s="96" t="n">
+      <c r="Y16" s="96" t="n">
         <v>40.58</v>
       </c>
-      <c r="Y16" s="96" t="n">
+      <c r="Z16" s="96" t="n">
         <v>49.35</v>
       </c>
-      <c r="Z16" s="96" t="n">
+      <c r="AA16" s="96" t="n">
         <v>57.93</v>
       </c>
-      <c r="AA16" s="96" t="n">
+      <c r="AB16" s="96" t="n">
         <v>53.35</v>
       </c>
-      <c r="AB16" s="96" t="n">
+      <c r="AC16" s="96" t="n">
         <v>58.31</v>
-      </c>
-      <c r="AC16" s="96" t="n">
-        <v>55.51</v>
       </c>
       <c r="AD16" s="96" t="n">
         <v>55.51</v>
       </c>
       <c r="AE16" s="96" t="n">
-        <v>49.87</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="17">
@@ -8147,144 +8148,144 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="D17" s="93" t="inlineStr">
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="F17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F17" s="95" t="inlineStr">
+      <c r="G17" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G17" s="94" t="inlineStr">
+      <c r="H17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H17" s="94" t="inlineStr">
+      <c r="I17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I17" s="94" t="inlineStr">
+      <c r="J17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J17" s="94" t="inlineStr">
+      <c r="K17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K17" s="93" t="inlineStr">
+      <c r="L17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L17" s="93" t="inlineStr">
+      <c r="M17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M17" s="94" t="inlineStr">
+      <c r="N17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N17" s="94" t="inlineStr">
+      <c r="O17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="94" t="inlineStr">
+      <c r="P17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="94" t="inlineStr">
+      <c r="Q17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q17" s="94" t="inlineStr">
+      <c r="R17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R17" s="94" t="inlineStr">
+      <c r="S17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S17" s="93" t="inlineStr">
+      <c r="T17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T17" s="93" t="inlineStr">
+      <c r="U17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U17" s="93" t="inlineStr">
+      <c r="V17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V17" s="93" t="inlineStr">
+      <c r="W17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W17" s="93" t="inlineStr">
+      <c r="X17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X17" s="93" t="inlineStr">
+      <c r="Y17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y17" s="93" t="inlineStr">
+      <c r="Z17" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z17" s="94" t="inlineStr">
+      <c r="AA17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA17" s="94" t="inlineStr">
+      <c r="AB17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB17" s="94" t="inlineStr">
+      <c r="AC17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC17" s="94" t="inlineStr">
+      <c r="AD17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD17" s="94" t="inlineStr">
+      <c r="AE17" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AE17" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
     </row>
@@ -8295,94 +8296,94 @@
         </is>
       </c>
       <c r="B18" s="96" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="C18" s="96" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="C18" s="96" t="n">
+      <c r="D18" s="96" t="n">
         <v>9.26</v>
       </c>
-      <c r="D18" s="96" t="n">
+      <c r="E18" s="96" t="n">
         <v>6.91</v>
       </c>
-      <c r="E18" s="96" t="n">
+      <c r="F18" s="96" t="n">
         <v>10.83</v>
       </c>
-      <c r="F18" s="96" t="n">
+      <c r="G18" s="96" t="n">
         <v>11.5</v>
       </c>
-      <c r="G18" s="96" t="n">
+      <c r="H18" s="96" t="n">
         <v>7.04</v>
       </c>
-      <c r="H18" s="96" t="n">
+      <c r="I18" s="96" t="n">
         <v>7.27</v>
       </c>
-      <c r="I18" s="96" t="n">
+      <c r="J18" s="96" t="n">
         <v>5.78</v>
       </c>
-      <c r="J18" s="96" t="n">
+      <c r="K18" s="96" t="n">
         <v>6.03</v>
       </c>
-      <c r="K18" s="96" t="n">
+      <c r="L18" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="L18" s="96" t="n">
+      <c r="M18" s="96" t="n">
         <v>9.58</v>
-      </c>
-      <c r="M18" s="96" t="n">
-        <v>12.31</v>
       </c>
       <c r="N18" s="96" t="n">
         <v>12.31</v>
       </c>
       <c r="O18" s="96" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="P18" s="96" t="n">
         <v>13.85</v>
       </c>
-      <c r="P18" s="96" t="n">
+      <c r="Q18" s="96" t="n">
         <v>12.09</v>
       </c>
-      <c r="Q18" s="96" t="n">
+      <c r="R18" s="96" t="n">
         <v>14.12</v>
       </c>
-      <c r="R18" s="96" t="n">
+      <c r="S18" s="96" t="n">
         <v>10.89</v>
       </c>
-      <c r="S18" s="96" t="n">
+      <c r="T18" s="96" t="n">
         <v>8.98</v>
       </c>
-      <c r="T18" s="96" t="n">
+      <c r="U18" s="96" t="n">
         <v>10.41</v>
       </c>
-      <c r="U18" s="96" t="n">
+      <c r="V18" s="96" t="n">
         <v>11.73</v>
       </c>
-      <c r="V18" s="96" t="n">
+      <c r="W18" s="96" t="n">
         <v>12.09</v>
       </c>
-      <c r="W18" s="96" t="n">
+      <c r="X18" s="96" t="n">
         <v>13.18</v>
       </c>
-      <c r="X18" s="96" t="n">
+      <c r="Y18" s="96" t="n">
         <v>11.26</v>
       </c>
-      <c r="Y18" s="96" t="n">
+      <c r="Z18" s="96" t="n">
         <v>12.7</v>
       </c>
-      <c r="Z18" s="96" t="n">
+      <c r="AA18" s="96" t="n">
         <v>16.32</v>
       </c>
-      <c r="AA18" s="96" t="n">
+      <c r="AB18" s="96" t="n">
         <v>18.3</v>
       </c>
-      <c r="AB18" s="96" t="n">
+      <c r="AC18" s="96" t="n">
         <v>21.54</v>
-      </c>
-      <c r="AC18" s="96" t="n">
-        <v>19.67</v>
       </c>
       <c r="AD18" s="96" t="n">
         <v>19.67</v>
       </c>
       <c r="AE18" s="96" t="n">
-        <v>21.52</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="19">
@@ -8392,94 +8393,94 @@
         </is>
       </c>
       <c r="B19" s="96" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="C19" s="96" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="C19" s="96" t="n">
+      <c r="D19" s="96" t="n">
         <v>10.33</v>
       </c>
-      <c r="D19" s="96" t="n">
+      <c r="E19" s="96" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="E19" s="96" t="n">
+      <c r="F19" s="96" t="n">
         <v>10.36</v>
       </c>
-      <c r="F19" s="96" t="n">
+      <c r="G19" s="96" t="n">
         <v>11.67</v>
       </c>
-      <c r="G19" s="96" t="n">
+      <c r="H19" s="96" t="n">
         <v>7.74</v>
       </c>
-      <c r="H19" s="96" t="n">
+      <c r="I19" s="96" t="n">
         <v>6.81</v>
       </c>
-      <c r="I19" s="96" t="n">
+      <c r="J19" s="96" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="J19" s="96" t="n">
+      <c r="K19" s="96" t="n">
         <v>11.61</v>
       </c>
-      <c r="K19" s="96" t="n">
+      <c r="L19" s="96" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="L19" s="96" t="n">
+      <c r="M19" s="96" t="n">
         <v>12.19</v>
-      </c>
-      <c r="M19" s="96" t="n">
-        <v>12.44</v>
       </c>
       <c r="N19" s="96" t="n">
         <v>12.44</v>
       </c>
       <c r="O19" s="96" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="P19" s="96" t="n">
         <v>13.04</v>
       </c>
-      <c r="P19" s="96" t="n">
+      <c r="Q19" s="96" t="n">
         <v>11.92</v>
       </c>
-      <c r="Q19" s="96" t="n">
+      <c r="R19" s="96" t="n">
         <v>12.96</v>
       </c>
-      <c r="R19" s="96" t="n">
+      <c r="S19" s="96" t="n">
         <v>10.55</v>
       </c>
-      <c r="S19" s="96" t="n">
+      <c r="T19" s="96" t="n">
         <v>7.42</v>
       </c>
-      <c r="T19" s="96" t="n">
+      <c r="U19" s="96" t="n">
         <v>6.97</v>
       </c>
-      <c r="U19" s="96" t="n">
+      <c r="V19" s="96" t="n">
         <v>8.73</v>
       </c>
-      <c r="V19" s="96" t="n">
+      <c r="W19" s="96" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="W19" s="96" t="n">
+      <c r="X19" s="96" t="n">
         <v>7.43</v>
       </c>
-      <c r="X19" s="96" t="n">
+      <c r="Y19" s="96" t="n">
         <v>5.98</v>
       </c>
-      <c r="Y19" s="96" t="n">
+      <c r="Z19" s="96" t="n">
         <v>5.35</v>
       </c>
-      <c r="Z19" s="96" t="n">
+      <c r="AA19" s="96" t="n">
         <v>8.24</v>
       </c>
-      <c r="AA19" s="96" t="n">
+      <c r="AB19" s="96" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="AB19" s="96" t="n">
+      <c r="AC19" s="96" t="n">
         <v>10.45</v>
-      </c>
-      <c r="AC19" s="96" t="n">
-        <v>12.03</v>
       </c>
       <c r="AD19" s="96" t="n">
         <v>12.03</v>
       </c>
       <c r="AE19" s="96" t="n">
-        <v>8.66</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="20">
@@ -8489,94 +8490,94 @@
         </is>
       </c>
       <c r="B20" s="96" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="C20" s="96" t="n">
         <v>44.66</v>
       </c>
-      <c r="C20" s="96" t="n">
+      <c r="D20" s="96" t="n">
         <v>41.56</v>
       </c>
-      <c r="D20" s="96" t="n">
+      <c r="E20" s="96" t="n">
         <v>41.6</v>
       </c>
-      <c r="E20" s="96" t="n">
+      <c r="F20" s="96" t="n">
         <v>56.56</v>
       </c>
-      <c r="F20" s="96" t="n">
+      <c r="G20" s="96" t="n">
         <v>62.36</v>
       </c>
-      <c r="G20" s="96" t="n">
+      <c r="H20" s="96" t="n">
         <v>30</v>
       </c>
-      <c r="H20" s="96" t="n">
+      <c r="I20" s="96" t="n">
         <v>30.88</v>
       </c>
-      <c r="I20" s="96" t="n">
+      <c r="J20" s="96" t="n">
         <v>31.09</v>
       </c>
-      <c r="J20" s="96" t="n">
+      <c r="K20" s="96" t="n">
         <v>37.51</v>
       </c>
-      <c r="K20" s="96" t="n">
+      <c r="L20" s="96" t="n">
         <v>24.17</v>
       </c>
-      <c r="L20" s="96" t="n">
+      <c r="M20" s="96" t="n">
         <v>31.92</v>
-      </c>
-      <c r="M20" s="96" t="n">
-        <v>40.59</v>
       </c>
       <c r="N20" s="96" t="n">
         <v>40.59</v>
       </c>
       <c r="O20" s="96" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="P20" s="96" t="n">
         <v>46.68</v>
       </c>
-      <c r="P20" s="96" t="n">
+      <c r="Q20" s="96" t="n">
         <v>43.34</v>
       </c>
-      <c r="Q20" s="96" t="n">
+      <c r="R20" s="96" t="n">
         <v>44.19</v>
       </c>
-      <c r="R20" s="96" t="n">
+      <c r="S20" s="96" t="n">
         <v>42.15</v>
       </c>
-      <c r="S20" s="96" t="n">
+      <c r="T20" s="96" t="n">
         <v>23.96</v>
       </c>
-      <c r="T20" s="96" t="n">
+      <c r="U20" s="96" t="n">
         <v>27.29</v>
       </c>
-      <c r="U20" s="96" t="n">
+      <c r="V20" s="96" t="n">
         <v>33.69</v>
       </c>
-      <c r="V20" s="96" t="n">
+      <c r="W20" s="96" t="n">
         <v>46.29</v>
       </c>
-      <c r="W20" s="96" t="n">
+      <c r="X20" s="96" t="n">
         <v>46.55</v>
       </c>
-      <c r="X20" s="96" t="n">
+      <c r="Y20" s="96" t="n">
         <v>35.92</v>
       </c>
-      <c r="Y20" s="96" t="n">
+      <c r="Z20" s="96" t="n">
         <v>44.74</v>
       </c>
-      <c r="Z20" s="96" t="n">
+      <c r="AA20" s="96" t="n">
         <v>60.23</v>
       </c>
-      <c r="AA20" s="96" t="n">
+      <c r="AB20" s="96" t="n">
         <v>61.59</v>
       </c>
-      <c r="AB20" s="96" t="n">
+      <c r="AC20" s="96" t="n">
         <v>89.59999999999999</v>
-      </c>
-      <c r="AC20" s="96" t="n">
-        <v>88.75</v>
       </c>
       <c r="AD20" s="96" t="n">
         <v>88.75</v>
       </c>
       <c r="AE20" s="96" t="n">
-        <v>86.84</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="21">
@@ -8586,94 +8587,94 @@
         </is>
       </c>
       <c r="B21" s="96" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="C21" s="96" t="n">
         <v>48.66</v>
       </c>
-      <c r="C21" s="96" t="n">
+      <c r="D21" s="96" t="n">
         <v>47.92</v>
       </c>
-      <c r="D21" s="96" t="n">
+      <c r="E21" s="96" t="n">
         <v>47.93</v>
       </c>
-      <c r="E21" s="96" t="n">
+      <c r="F21" s="96" t="n">
         <v>52.51</v>
       </c>
-      <c r="F21" s="96" t="n">
+      <c r="G21" s="96" t="n">
         <v>54.03</v>
       </c>
-      <c r="G21" s="96" t="n">
+      <c r="H21" s="96" t="n">
         <v>46.04</v>
       </c>
-      <c r="H21" s="96" t="n">
+      <c r="I21" s="96" t="n">
         <v>46.34</v>
       </c>
-      <c r="I21" s="96" t="n">
+      <c r="J21" s="96" t="n">
         <v>46.42</v>
       </c>
-      <c r="J21" s="96" t="n">
+      <c r="K21" s="96" t="n">
         <v>48.84</v>
       </c>
-      <c r="K21" s="96" t="n">
+      <c r="L21" s="96" t="n">
         <v>46.12</v>
       </c>
-      <c r="L21" s="96" t="n">
+      <c r="M21" s="96" t="n">
         <v>49.52</v>
-      </c>
-      <c r="M21" s="96" t="n">
-        <v>52.45</v>
       </c>
       <c r="N21" s="96" t="n">
         <v>52.45</v>
       </c>
       <c r="O21" s="96" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="P21" s="96" t="n">
         <v>54.2</v>
       </c>
-      <c r="P21" s="96" t="n">
+      <c r="Q21" s="96" t="n">
         <v>53.51</v>
       </c>
-      <c r="Q21" s="96" t="n">
+      <c r="R21" s="96" t="n">
         <v>53.79</v>
       </c>
-      <c r="R21" s="96" t="n">
+      <c r="S21" s="96" t="n">
         <v>53.28</v>
       </c>
-      <c r="S21" s="96" t="n">
+      <c r="T21" s="96" t="n">
         <v>49.13</v>
       </c>
-      <c r="T21" s="96" t="n">
+      <c r="U21" s="96" t="n">
         <v>51.14</v>
       </c>
-      <c r="U21" s="96" t="n">
+      <c r="V21" s="96" t="n">
         <v>54.6</v>
       </c>
-      <c r="V21" s="96" t="n">
+      <c r="W21" s="96" t="n">
         <v>59.95</v>
       </c>
-      <c r="W21" s="96" t="n">
+      <c r="X21" s="96" t="n">
         <v>60.05</v>
       </c>
-      <c r="X21" s="96" t="n">
+      <c r="Y21" s="96" t="n">
         <v>57.68</v>
       </c>
-      <c r="Y21" s="96" t="n">
+      <c r="Z21" s="96" t="n">
         <v>61.81</v>
       </c>
-      <c r="Z21" s="96" t="n">
+      <c r="AA21" s="96" t="n">
         <v>67.58</v>
       </c>
-      <c r="AA21" s="96" t="n">
+      <c r="AB21" s="96" t="n">
         <v>68.04000000000001</v>
       </c>
-      <c r="AB21" s="96" t="n">
+      <c r="AC21" s="96" t="n">
         <v>76.20999999999999</v>
-      </c>
-      <c r="AC21" s="96" t="n">
-        <v>75.66</v>
       </c>
       <c r="AD21" s="96" t="n">
         <v>75.66</v>
       </c>
       <c r="AE21" s="96" t="n">
-        <v>74.45999999999999</v>
+        <v>75.66</v>
       </c>
     </row>
     <row r="22">
@@ -8702,89 +8703,89 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="F22" s="95" t="inlineStr">
+      <c r="F22" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G22" s="95" t="inlineStr">
+      <c r="H22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H22" s="95" t="inlineStr">
+      <c r="I22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I22" s="95" t="inlineStr">
+      <c r="J22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J22" s="95" t="inlineStr">
+      <c r="K22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K22" s="95" t="inlineStr">
+      <c r="L22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L22" s="95" t="inlineStr">
+      <c r="M22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M22" s="95" t="inlineStr">
+      <c r="N22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N22" s="95" t="inlineStr">
+      <c r="O22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O22" s="95" t="inlineStr">
+      <c r="P22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P22" s="95" t="inlineStr">
+      <c r="Q22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q22" s="95" t="inlineStr">
+      <c r="R22" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R22" s="94" t="inlineStr">
+      <c r="S22" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S22" s="94" t="inlineStr">
+      <c r="T22" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="93" t="inlineStr">
+      <c r="U22" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U22" s="93" t="inlineStr">
+      <c r="V22" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="V22" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="W22" s="94" t="inlineStr">
@@ -8843,91 +8844,91 @@
         <v>4.09</v>
       </c>
       <c r="C23" s="96" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="D23" s="96" t="n">
         <v>3.8</v>
       </c>
-      <c r="D23" s="96" t="n">
+      <c r="E23" s="96" t="n">
         <v>5.02</v>
       </c>
-      <c r="E23" s="96" t="n">
+      <c r="F23" s="96" t="n">
         <v>4.89</v>
-      </c>
-      <c r="F23" s="96" t="n">
-        <v>4.83</v>
       </c>
       <c r="G23" s="96" t="n">
         <v>4.83</v>
       </c>
       <c r="H23" s="96" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I23" s="96" t="n">
         <v>4.42</v>
       </c>
-      <c r="I23" s="96" t="n">
+      <c r="J23" s="96" t="n">
         <v>3.96</v>
       </c>
-      <c r="J23" s="96" t="n">
+      <c r="K23" s="96" t="n">
         <v>4.93</v>
       </c>
-      <c r="K23" s="96" t="n">
+      <c r="L23" s="96" t="n">
         <v>5.27</v>
       </c>
-      <c r="L23" s="96" t="n">
+      <c r="M23" s="96" t="n">
         <v>5.05</v>
       </c>
-      <c r="M23" s="96" t="n">
+      <c r="N23" s="96" t="n">
         <v>4.08</v>
       </c>
-      <c r="N23" s="96" t="n">
+      <c r="O23" s="96" t="n">
         <v>3.52</v>
       </c>
-      <c r="O23" s="96" t="n">
+      <c r="P23" s="96" t="n">
         <v>3.43</v>
       </c>
-      <c r="P23" s="96" t="n">
+      <c r="Q23" s="96" t="n">
         <v>4.61</v>
       </c>
-      <c r="Q23" s="96" t="n">
+      <c r="R23" s="96" t="n">
         <v>3.27</v>
       </c>
-      <c r="R23" s="96" t="n">
+      <c r="S23" s="96" t="n">
         <v>2.44</v>
       </c>
-      <c r="S23" s="96" t="n">
+      <c r="T23" s="96" t="n">
         <v>3.38</v>
       </c>
-      <c r="T23" s="96" t="n">
+      <c r="U23" s="96" t="n">
         <v>3.09</v>
       </c>
-      <c r="U23" s="96" t="n">
+      <c r="V23" s="96" t="n">
         <v>2.65</v>
       </c>
-      <c r="V23" s="96" t="n">
+      <c r="W23" s="96" t="n">
         <v>3.29</v>
-      </c>
-      <c r="W23" s="96" t="n">
-        <v>4.09</v>
       </c>
       <c r="X23" s="96" t="n">
         <v>4.09</v>
       </c>
       <c r="Y23" s="96" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Z23" s="96" t="n">
         <v>3.91</v>
       </c>
-      <c r="Z23" s="96" t="n">
+      <c r="AA23" s="96" t="n">
         <v>4.51</v>
       </c>
-      <c r="AA23" s="96" t="n">
+      <c r="AB23" s="96" t="n">
         <v>4.97</v>
       </c>
-      <c r="AB23" s="96" t="n">
+      <c r="AC23" s="96" t="n">
         <v>4.31</v>
-      </c>
-      <c r="AC23" s="96" t="n">
-        <v>4.25</v>
       </c>
       <c r="AD23" s="96" t="n">
         <v>4.25</v>
       </c>
       <c r="AE23" s="96" t="n">
-        <v>6.33</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="24">
@@ -8940,91 +8941,91 @@
         <v>15.32</v>
       </c>
       <c r="C24" s="96" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="D24" s="96" t="n">
         <v>14.22</v>
       </c>
-      <c r="D24" s="96" t="n">
+      <c r="E24" s="96" t="n">
         <v>14.24</v>
       </c>
-      <c r="E24" s="96" t="n">
+      <c r="F24" s="96" t="n">
         <v>14.46</v>
-      </c>
-      <c r="F24" s="96" t="n">
-        <v>14.92</v>
       </c>
       <c r="G24" s="96" t="n">
         <v>14.92</v>
       </c>
       <c r="H24" s="96" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="I24" s="96" t="n">
         <v>15.11</v>
       </c>
-      <c r="I24" s="96" t="n">
+      <c r="J24" s="96" t="n">
         <v>14.43</v>
       </c>
-      <c r="J24" s="96" t="n">
+      <c r="K24" s="96" t="n">
         <v>15.65</v>
       </c>
-      <c r="K24" s="96" t="n">
+      <c r="L24" s="96" t="n">
         <v>13.69</v>
       </c>
-      <c r="L24" s="96" t="n">
+      <c r="M24" s="96" t="n">
         <v>13.39</v>
       </c>
-      <c r="M24" s="96" t="n">
+      <c r="N24" s="96" t="n">
         <v>13.6</v>
       </c>
-      <c r="N24" s="96" t="n">
+      <c r="O24" s="96" t="n">
         <v>13.29</v>
       </c>
-      <c r="O24" s="96" t="n">
+      <c r="P24" s="96" t="n">
         <v>13.72</v>
       </c>
-      <c r="P24" s="96" t="n">
+      <c r="Q24" s="96" t="n">
         <v>15.3</v>
       </c>
-      <c r="Q24" s="96" t="n">
+      <c r="R24" s="96" t="n">
         <v>14.47</v>
       </c>
-      <c r="R24" s="96" t="n">
+      <c r="S24" s="96" t="n">
         <v>14.75</v>
       </c>
-      <c r="S24" s="96" t="n">
+      <c r="T24" s="96" t="n">
         <v>15.09</v>
       </c>
-      <c r="T24" s="96" t="n">
+      <c r="U24" s="96" t="n">
         <v>15.08</v>
       </c>
-      <c r="U24" s="96" t="n">
+      <c r="V24" s="96" t="n">
         <v>15.32</v>
       </c>
-      <c r="V24" s="96" t="n">
+      <c r="W24" s="96" t="n">
         <v>16.11</v>
-      </c>
-      <c r="W24" s="96" t="n">
-        <v>15.45</v>
       </c>
       <c r="X24" s="96" t="n">
         <v>15.45</v>
       </c>
       <c r="Y24" s="96" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="Z24" s="96" t="n">
         <v>15.33</v>
       </c>
-      <c r="Z24" s="96" t="n">
+      <c r="AA24" s="96" t="n">
         <v>16.62</v>
       </c>
-      <c r="AA24" s="96" t="n">
+      <c r="AB24" s="96" t="n">
         <v>16.83</v>
       </c>
-      <c r="AB24" s="96" t="n">
+      <c r="AC24" s="96" t="n">
         <v>16.65</v>
-      </c>
-      <c r="AC24" s="96" t="n">
-        <v>16.32</v>
       </c>
       <c r="AD24" s="96" t="n">
         <v>16.32</v>
       </c>
       <c r="AE24" s="96" t="n">
-        <v>16.25</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="25">
@@ -9037,91 +9038,91 @@
         <v>66.08</v>
       </c>
       <c r="C25" s="96" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="D25" s="96" t="n">
         <v>16.87</v>
       </c>
-      <c r="D25" s="96" t="n">
+      <c r="E25" s="96" t="n">
         <v>38.94</v>
       </c>
-      <c r="E25" s="96" t="n">
+      <c r="F25" s="96" t="n">
         <v>58.48</v>
-      </c>
-      <c r="F25" s="96" t="n">
-        <v>98.54000000000001</v>
       </c>
       <c r="G25" s="96" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="H25" s="96" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="I25" s="96" t="n">
         <v>97.78</v>
       </c>
-      <c r="I25" s="96" t="n">
+      <c r="J25" s="96" t="n">
         <v>89.88</v>
       </c>
-      <c r="J25" s="96" t="n">
+      <c r="K25" s="96" t="n">
         <v>98.92</v>
       </c>
-      <c r="K25" s="96" t="n">
+      <c r="L25" s="96" t="n">
         <v>98.45999999999999</v>
       </c>
-      <c r="L25" s="96" t="n">
+      <c r="M25" s="96" t="n">
         <v>93.41</v>
       </c>
-      <c r="M25" s="96" t="n">
+      <c r="N25" s="96" t="n">
         <v>86.23</v>
       </c>
-      <c r="N25" s="96" t="n">
+      <c r="O25" s="96" t="n">
         <v>71.5</v>
       </c>
-      <c r="O25" s="96" t="n">
+      <c r="P25" s="96" t="n">
         <v>93.04000000000001</v>
       </c>
-      <c r="P25" s="96" t="n">
+      <c r="Q25" s="96" t="n">
         <v>95.63</v>
       </c>
-      <c r="Q25" s="96" t="n">
+      <c r="R25" s="96" t="n">
         <v>76.59</v>
       </c>
-      <c r="R25" s="96" t="n">
+      <c r="S25" s="96" t="n">
         <v>67.67</v>
       </c>
-      <c r="S25" s="96" t="n">
+      <c r="T25" s="96" t="n">
         <v>62.36</v>
       </c>
-      <c r="T25" s="96" t="n">
+      <c r="U25" s="96" t="n">
         <v>8.93</v>
       </c>
-      <c r="U25" s="96" t="n">
+      <c r="V25" s="96" t="n">
         <v>19.05</v>
       </c>
-      <c r="V25" s="96" t="n">
+      <c r="W25" s="96" t="n">
         <v>64.41</v>
-      </c>
-      <c r="W25" s="96" t="n">
-        <v>62.92</v>
       </c>
       <c r="X25" s="96" t="n">
         <v>62.92</v>
       </c>
       <c r="Y25" s="96" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="Z25" s="96" t="n">
         <v>10.58</v>
       </c>
-      <c r="Z25" s="96" t="n">
+      <c r="AA25" s="96" t="n">
         <v>42.26</v>
       </c>
-      <c r="AA25" s="96" t="n">
+      <c r="AB25" s="96" t="n">
         <v>94.03</v>
       </c>
-      <c r="AB25" s="96" t="n">
+      <c r="AC25" s="96" t="n">
         <v>86.27</v>
-      </c>
-      <c r="AC25" s="96" t="n">
-        <v>82</v>
       </c>
       <c r="AD25" s="96" t="n">
         <v>82</v>
       </c>
       <c r="AE25" s="96" t="n">
-        <v>77.56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
@@ -9134,91 +9135,91 @@
         <v>66.08</v>
       </c>
       <c r="C26" s="96" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="D26" s="96" t="n">
         <v>16.87</v>
       </c>
-      <c r="D26" s="96" t="n">
+      <c r="E26" s="96" t="n">
         <v>38.94</v>
       </c>
-      <c r="E26" s="96" t="n">
+      <c r="F26" s="96" t="n">
         <v>58.48</v>
-      </c>
-      <c r="F26" s="96" t="n">
-        <v>98.54000000000001</v>
       </c>
       <c r="G26" s="96" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="H26" s="96" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="I26" s="96" t="n">
         <v>97.78</v>
       </c>
-      <c r="I26" s="96" t="n">
+      <c r="J26" s="96" t="n">
         <v>89.88</v>
       </c>
-      <c r="J26" s="96" t="n">
+      <c r="K26" s="96" t="n">
         <v>98.92</v>
       </c>
-      <c r="K26" s="96" t="n">
+      <c r="L26" s="96" t="n">
         <v>98.45999999999999</v>
       </c>
-      <c r="L26" s="96" t="n">
+      <c r="M26" s="96" t="n">
         <v>93.41</v>
       </c>
-      <c r="M26" s="96" t="n">
+      <c r="N26" s="96" t="n">
         <v>86.23</v>
       </c>
-      <c r="N26" s="96" t="n">
+      <c r="O26" s="96" t="n">
         <v>71.5</v>
       </c>
-      <c r="O26" s="96" t="n">
+      <c r="P26" s="96" t="n">
         <v>93.04000000000001</v>
       </c>
-      <c r="P26" s="96" t="n">
+      <c r="Q26" s="96" t="n">
         <v>95.63</v>
       </c>
-      <c r="Q26" s="96" t="n">
+      <c r="R26" s="96" t="n">
         <v>76.59</v>
       </c>
-      <c r="R26" s="96" t="n">
+      <c r="S26" s="96" t="n">
         <v>67.67</v>
       </c>
-      <c r="S26" s="96" t="n">
+      <c r="T26" s="96" t="n">
         <v>62.36</v>
       </c>
-      <c r="T26" s="96" t="n">
+      <c r="U26" s="96" t="n">
         <v>8.93</v>
       </c>
-      <c r="U26" s="96" t="n">
+      <c r="V26" s="96" t="n">
         <v>19.05</v>
       </c>
-      <c r="V26" s="96" t="n">
+      <c r="W26" s="96" t="n">
         <v>64.41</v>
-      </c>
-      <c r="W26" s="96" t="n">
-        <v>62.92</v>
       </c>
       <c r="X26" s="96" t="n">
         <v>62.92</v>
       </c>
       <c r="Y26" s="96" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="Z26" s="96" t="n">
         <v>10.58</v>
       </c>
-      <c r="Z26" s="96" t="n">
+      <c r="AA26" s="96" t="n">
         <v>42.26</v>
       </c>
-      <c r="AA26" s="96" t="n">
+      <c r="AB26" s="96" t="n">
         <v>94.03</v>
       </c>
-      <c r="AB26" s="96" t="n">
+      <c r="AC26" s="96" t="n">
         <v>86.27</v>
-      </c>
-      <c r="AC26" s="96" t="n">
-        <v>82</v>
       </c>
       <c r="AD26" s="96" t="n">
         <v>82</v>
       </c>
       <c r="AE26" s="96" t="n">
-        <v>77.56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
@@ -9232,124 +9233,124 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C27" s="95" t="inlineStr">
+      <c r="C27" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D27" s="95" t="inlineStr">
+      <c r="E27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E27" s="95" t="inlineStr">
+      <c r="F27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F27" s="95" t="inlineStr">
+      <c r="G27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G27" s="95" t="inlineStr">
+      <c r="H27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H27" s="95" t="inlineStr">
+      <c r="I27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I27" s="93" t="inlineStr">
+      <c r="J27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J27" s="94" t="inlineStr">
+      <c r="K27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K27" s="94" t="inlineStr">
+      <c r="L27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L27" s="94" t="inlineStr">
+      <c r="M27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M27" s="95" t="inlineStr">
+      <c r="N27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N27" s="94" t="inlineStr">
+      <c r="O27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O27" s="95" t="inlineStr">
+      <c r="P27" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P27" s="94" t="inlineStr">
+      <c r="Q27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q27" s="94" t="inlineStr">
+      <c r="R27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R27" s="94" t="inlineStr">
+      <c r="S27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S27" s="94" t="inlineStr">
+      <c r="T27" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="93" t="inlineStr">
+      <c r="U27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U27" s="93" t="inlineStr">
+      <c r="V27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V27" s="93" t="inlineStr">
+      <c r="W27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W27" s="93" t="inlineStr">
+      <c r="X27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X27" s="93" t="inlineStr">
+      <c r="Y27" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y27" s="93" t="inlineStr">
+      <c r="Z27" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="Z27" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AA27" s="94" t="inlineStr">
@@ -9388,91 +9389,91 @@
         <v>-1.75</v>
       </c>
       <c r="C28" s="96" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="D28" s="96" t="n">
         <v>-0.88</v>
       </c>
-      <c r="D28" s="96" t="n">
+      <c r="E28" s="96" t="n">
         <v>-0.34</v>
       </c>
-      <c r="E28" s="96" t="n">
+      <c r="F28" s="96" t="n">
         <v>-0.46</v>
-      </c>
-      <c r="F28" s="96" t="n">
-        <v>-1.62</v>
       </c>
       <c r="G28" s="96" t="n">
         <v>-1.62</v>
       </c>
       <c r="H28" s="96" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="I28" s="96" t="n">
         <v>-2.52</v>
       </c>
-      <c r="I28" s="96" t="n">
+      <c r="J28" s="96" t="n">
         <v>-2.34</v>
       </c>
-      <c r="J28" s="96" t="n">
+      <c r="K28" s="96" t="n">
         <v>-1.19</v>
       </c>
-      <c r="K28" s="96" t="n">
+      <c r="L28" s="96" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L28" s="96" t="n">
+      <c r="M28" s="96" t="n">
         <v>0.08</v>
       </c>
-      <c r="M28" s="96" t="n">
+      <c r="N28" s="96" t="n">
         <v>-0.1</v>
       </c>
-      <c r="N28" s="96" t="n">
+      <c r="O28" s="96" t="n">
         <v>-0.63</v>
       </c>
-      <c r="O28" s="96" t="n">
+      <c r="P28" s="96" t="n">
         <v>-0.31</v>
       </c>
-      <c r="P28" s="96" t="n">
+      <c r="Q28" s="96" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="96" t="n">
+      <c r="R28" s="96" t="n">
         <v>-0.03</v>
       </c>
-      <c r="R28" s="96" t="n">
+      <c r="S28" s="96" t="n">
         <v>-0.57</v>
       </c>
-      <c r="S28" s="96" t="n">
+      <c r="T28" s="96" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="T28" s="96" t="n">
+      <c r="U28" s="96" t="n">
         <v>-1.23</v>
       </c>
-      <c r="U28" s="96" t="n">
+      <c r="V28" s="96" t="n">
         <v>-1.41</v>
       </c>
-      <c r="V28" s="96" t="n">
+      <c r="W28" s="96" t="n">
         <v>-0.6</v>
-      </c>
-      <c r="W28" s="96" t="n">
-        <v>0.19</v>
       </c>
       <c r="X28" s="96" t="n">
         <v>0.19</v>
       </c>
       <c r="Y28" s="96" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Z28" s="96" t="n">
         <v>0.3</v>
       </c>
-      <c r="Z28" s="96" t="n">
+      <c r="AA28" s="96" t="n">
         <v>1.79</v>
       </c>
-      <c r="AA28" s="96" t="n">
+      <c r="AB28" s="96" t="n">
         <v>2.06</v>
       </c>
-      <c r="AB28" s="96" t="n">
+      <c r="AC28" s="96" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC28" s="96" t="n">
-        <v>2.39</v>
       </c>
       <c r="AD28" s="96" t="n">
         <v>2.39</v>
       </c>
       <c r="AE28" s="96" t="n">
-        <v>3.26</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="29">
@@ -9485,91 +9486,91 @@
         <v>3.7</v>
       </c>
       <c r="C29" s="96" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D29" s="96" t="n">
         <v>4.57</v>
       </c>
-      <c r="D29" s="96" t="n">
+      <c r="E29" s="96" t="n">
         <v>3.82</v>
       </c>
-      <c r="E29" s="96" t="n">
+      <c r="F29" s="96" t="n">
         <v>3.93</v>
-      </c>
-      <c r="F29" s="96" t="n">
-        <v>3.43</v>
       </c>
       <c r="G29" s="96" t="n">
         <v>3.43</v>
       </c>
       <c r="H29" s="96" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I29" s="96" t="n">
         <v>3.72</v>
       </c>
-      <c r="I29" s="96" t="n">
+      <c r="J29" s="96" t="n">
         <v>3.17</v>
       </c>
-      <c r="J29" s="96" t="n">
+      <c r="K29" s="96" t="n">
         <v>4.22</v>
       </c>
-      <c r="K29" s="96" t="n">
+      <c r="L29" s="96" t="n">
         <v>3.07</v>
       </c>
-      <c r="L29" s="96" t="n">
+      <c r="M29" s="96" t="n">
         <v>3.86</v>
       </c>
-      <c r="M29" s="96" t="n">
+      <c r="N29" s="96" t="n">
         <v>4.19</v>
       </c>
-      <c r="N29" s="96" t="n">
+      <c r="O29" s="96" t="n">
         <v>4.16</v>
       </c>
-      <c r="O29" s="96" t="n">
+      <c r="P29" s="96" t="n">
         <v>4.84</v>
       </c>
-      <c r="P29" s="96" t="n">
+      <c r="Q29" s="96" t="n">
         <v>6.09</v>
       </c>
-      <c r="Q29" s="96" t="n">
+      <c r="R29" s="96" t="n">
         <v>6.34</v>
       </c>
-      <c r="R29" s="96" t="n">
+      <c r="S29" s="96" t="n">
         <v>6.41</v>
       </c>
-      <c r="S29" s="96" t="n">
+      <c r="T29" s="96" t="n">
         <v>7.11</v>
       </c>
-      <c r="T29" s="96" t="n">
+      <c r="U29" s="96" t="n">
         <v>5.71</v>
       </c>
-      <c r="U29" s="96" t="n">
+      <c r="V29" s="96" t="n">
         <v>6.41</v>
       </c>
-      <c r="V29" s="96" t="n">
+      <c r="W29" s="96" t="n">
         <v>7.32</v>
-      </c>
-      <c r="W29" s="96" t="n">
-        <v>7.79</v>
       </c>
       <c r="X29" s="96" t="n">
         <v>7.79</v>
       </c>
       <c r="Y29" s="96" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="Z29" s="96" t="n">
         <v>8.66</v>
       </c>
-      <c r="Z29" s="96" t="n">
+      <c r="AA29" s="96" t="n">
         <v>11.97</v>
       </c>
-      <c r="AA29" s="96" t="n">
+      <c r="AB29" s="96" t="n">
         <v>12.58</v>
       </c>
-      <c r="AB29" s="96" t="n">
+      <c r="AC29" s="96" t="n">
         <v>12.66</v>
-      </c>
-      <c r="AC29" s="96" t="n">
-        <v>13.04</v>
       </c>
       <c r="AD29" s="96" t="n">
         <v>13.04</v>
       </c>
       <c r="AE29" s="96" t="n">
-        <v>13.03</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="30">
@@ -9582,91 +9583,91 @@
         <v>49.59</v>
       </c>
       <c r="C30" s="96" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="D30" s="96" t="n">
         <v>95.22</v>
       </c>
-      <c r="D30" s="96" t="n">
+      <c r="E30" s="96" t="n">
         <v>89.70999999999999</v>
       </c>
-      <c r="E30" s="96" t="n">
+      <c r="F30" s="96" t="n">
         <v>89.20999999999999</v>
-      </c>
-      <c r="F30" s="96" t="n">
-        <v>71.89</v>
       </c>
       <c r="G30" s="96" t="n">
         <v>71.89</v>
       </c>
       <c r="H30" s="96" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="I30" s="96" t="n">
         <v>64.73999999999999</v>
       </c>
-      <c r="I30" s="96" t="n">
+      <c r="J30" s="96" t="n">
         <v>19.12</v>
       </c>
-      <c r="J30" s="96" t="n">
+      <c r="K30" s="96" t="n">
         <v>26</v>
       </c>
-      <c r="K30" s="96" t="n">
+      <c r="L30" s="96" t="n">
         <v>35.59</v>
       </c>
-      <c r="L30" s="96" t="n">
+      <c r="M30" s="96" t="n">
         <v>41.04</v>
       </c>
-      <c r="M30" s="96" t="n">
+      <c r="N30" s="96" t="n">
         <v>63.17</v>
       </c>
-      <c r="N30" s="96" t="n">
+      <c r="O30" s="96" t="n">
         <v>53.63</v>
       </c>
-      <c r="O30" s="96" t="n">
+      <c r="P30" s="96" t="n">
         <v>68.58</v>
       </c>
-      <c r="P30" s="96" t="n">
+      <c r="Q30" s="96" t="n">
         <v>62.23</v>
       </c>
-      <c r="Q30" s="96" t="n">
+      <c r="R30" s="96" t="n">
         <v>54.82</v>
       </c>
-      <c r="R30" s="96" t="n">
+      <c r="S30" s="96" t="n">
         <v>44.15</v>
       </c>
-      <c r="S30" s="96" t="n">
+      <c r="T30" s="96" t="n">
         <v>50.71</v>
       </c>
-      <c r="T30" s="96" t="n">
+      <c r="U30" s="96" t="n">
         <v>2.58</v>
       </c>
-      <c r="U30" s="96" t="n">
+      <c r="V30" s="96" t="n">
         <v>4.12</v>
       </c>
-      <c r="V30" s="96" t="n">
+      <c r="W30" s="96" t="n">
         <v>8.18</v>
-      </c>
-      <c r="W30" s="96" t="n">
-        <v>12.5</v>
       </c>
       <c r="X30" s="96" t="n">
         <v>12.5</v>
       </c>
       <c r="Y30" s="96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z30" s="96" t="n">
         <v>11.88</v>
       </c>
-      <c r="Z30" s="96" t="n">
+      <c r="AA30" s="96" t="n">
         <v>35.03</v>
       </c>
-      <c r="AA30" s="96" t="n">
+      <c r="AB30" s="96" t="n">
         <v>61.8</v>
       </c>
-      <c r="AB30" s="96" t="n">
+      <c r="AC30" s="96" t="n">
         <v>54.14</v>
-      </c>
-      <c r="AC30" s="96" t="n">
-        <v>89.84999999999999</v>
       </c>
       <c r="AD30" s="96" t="n">
         <v>89.84999999999999</v>
       </c>
       <c r="AE30" s="96" t="n">
-        <v>85.51000000000001</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -9679,91 +9680,91 @@
         <v>56.36</v>
       </c>
       <c r="C31" s="96" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="D31" s="96" t="n">
         <v>84.93000000000001</v>
       </c>
-      <c r="D31" s="96" t="n">
+      <c r="E31" s="96" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="E31" s="96" t="n">
+      <c r="F31" s="96" t="n">
         <v>76.06</v>
-      </c>
-      <c r="F31" s="96" t="n">
-        <v>59.17</v>
       </c>
       <c r="G31" s="96" t="n">
         <v>59.17</v>
       </c>
       <c r="H31" s="96" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="I31" s="96" t="n">
         <v>54.28</v>
       </c>
-      <c r="I31" s="96" t="n">
+      <c r="J31" s="96" t="n">
         <v>32.92</v>
       </c>
-      <c r="J31" s="96" t="n">
+      <c r="K31" s="96" t="n">
         <v>37.19</v>
       </c>
-      <c r="K31" s="96" t="n">
+      <c r="L31" s="96" t="n">
         <v>42.08</v>
       </c>
-      <c r="L31" s="96" t="n">
+      <c r="M31" s="96" t="n">
         <v>44.63</v>
       </c>
-      <c r="M31" s="96" t="n">
+      <c r="N31" s="96" t="n">
         <v>53.49</v>
       </c>
-      <c r="N31" s="96" t="n">
+      <c r="O31" s="96" t="n">
         <v>48.84</v>
       </c>
-      <c r="O31" s="96" t="n">
+      <c r="P31" s="96" t="n">
         <v>54.32</v>
       </c>
-      <c r="P31" s="96" t="n">
+      <c r="Q31" s="96" t="n">
         <v>50.28</v>
       </c>
-      <c r="Q31" s="96" t="n">
+      <c r="R31" s="96" t="n">
         <v>45.59</v>
       </c>
-      <c r="R31" s="96" t="n">
+      <c r="S31" s="96" t="n">
         <v>38.85</v>
       </c>
-      <c r="S31" s="96" t="n">
+      <c r="T31" s="96" t="n">
         <v>42.3</v>
       </c>
-      <c r="T31" s="96" t="n">
+      <c r="U31" s="96" t="n">
         <v>10.72</v>
       </c>
-      <c r="U31" s="96" t="n">
+      <c r="V31" s="96" t="n">
         <v>14.31</v>
       </c>
-      <c r="V31" s="96" t="n">
+      <c r="W31" s="96" t="n">
         <v>21.52</v>
-      </c>
-      <c r="W31" s="96" t="n">
-        <v>27.31</v>
       </c>
       <c r="X31" s="96" t="n">
         <v>27.31</v>
       </c>
       <c r="Y31" s="96" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="Z31" s="96" t="n">
         <v>27</v>
       </c>
-      <c r="Z31" s="96" t="n">
+      <c r="AA31" s="96" t="n">
         <v>52.3</v>
       </c>
-      <c r="AA31" s="96" t="n">
+      <c r="AB31" s="96" t="n">
         <v>69.72</v>
       </c>
-      <c r="AB31" s="96" t="n">
+      <c r="AC31" s="96" t="n">
         <v>66.81999999999999</v>
-      </c>
-      <c r="AC31" s="96" t="n">
-        <v>86.52</v>
       </c>
       <c r="AD31" s="96" t="n">
         <v>86.52</v>
       </c>
       <c r="AE31" s="96" t="n">
-        <v>83.94</v>
+        <v>86.52</v>
       </c>
     </row>
     <row r="32">
@@ -9802,84 +9803,84 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H32" s="95" t="inlineStr">
+      <c r="H32" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I32" s="95" t="inlineStr">
+      <c r="J32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J32" s="95" t="inlineStr">
+      <c r="K32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K32" s="95" t="inlineStr">
+      <c r="L32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L32" s="95" t="inlineStr">
+      <c r="M32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M32" s="95" t="inlineStr">
+      <c r="N32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N32" s="94" t="inlineStr">
+      <c r="O32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O32" s="95" t="inlineStr">
+      <c r="P32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P32" s="95" t="inlineStr">
+      <c r="Q32" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q32" s="94" t="inlineStr">
+      <c r="R32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R32" s="94" t="inlineStr">
+      <c r="S32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="94" t="inlineStr">
+      <c r="T32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T32" s="94" t="inlineStr">
+      <c r="U32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U32" s="94" t="inlineStr">
+      <c r="V32" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V32" s="95" t="inlineStr">
+      <c r="W32" s="95" t="inlineStr">
         <is>
           <t>red</t>
-        </is>
-      </c>
-      <c r="W32" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="X32" s="94" t="inlineStr">
@@ -9933,91 +9934,91 @@
         <v>8.17</v>
       </c>
       <c r="C33" s="96" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="D33" s="96" t="n">
         <v>6.69</v>
       </c>
-      <c r="D33" s="96" t="n">
+      <c r="E33" s="96" t="n">
         <v>8.42</v>
       </c>
-      <c r="E33" s="96" t="n">
+      <c r="F33" s="96" t="n">
         <v>8.16</v>
-      </c>
-      <c r="F33" s="96" t="n">
-        <v>8.720000000000001</v>
       </c>
       <c r="G33" s="96" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="H33" s="96" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="I33" s="96" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="I33" s="96" t="n">
+      <c r="J33" s="96" t="n">
         <v>8.06</v>
       </c>
-      <c r="J33" s="96" t="n">
+      <c r="K33" s="96" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="K33" s="96" t="n">
+      <c r="L33" s="96" t="n">
         <v>9.35</v>
       </c>
-      <c r="L33" s="96" t="n">
+      <c r="M33" s="96" t="n">
         <v>8.58</v>
       </c>
-      <c r="M33" s="96" t="n">
+      <c r="N33" s="96" t="n">
         <v>6.6</v>
       </c>
-      <c r="N33" s="96" t="n">
+      <c r="O33" s="96" t="n">
         <v>5.91</v>
       </c>
-      <c r="O33" s="96" t="n">
+      <c r="P33" s="96" t="n">
         <v>5.58</v>
       </c>
-      <c r="P33" s="96" t="n">
+      <c r="Q33" s="96" t="n">
         <v>7.3</v>
       </c>
-      <c r="Q33" s="96" t="n">
+      <c r="R33" s="96" t="n">
         <v>4.8</v>
       </c>
-      <c r="R33" s="96" t="n">
+      <c r="S33" s="96" t="n">
         <v>3.41</v>
       </c>
-      <c r="S33" s="96" t="n">
+      <c r="T33" s="96" t="n">
         <v>4.39</v>
       </c>
-      <c r="T33" s="96" t="n">
+      <c r="U33" s="96" t="n">
         <v>5</v>
       </c>
-      <c r="U33" s="96" t="n">
+      <c r="V33" s="96" t="n">
         <v>4.4</v>
       </c>
-      <c r="V33" s="96" t="n">
+      <c r="W33" s="96" t="n">
         <v>4.58</v>
-      </c>
-      <c r="W33" s="96" t="n">
-        <v>5.15</v>
       </c>
       <c r="X33" s="96" t="n">
         <v>5.15</v>
       </c>
       <c r="Y33" s="96" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Z33" s="96" t="n">
         <v>4.94</v>
       </c>
-      <c r="Z33" s="96" t="n">
+      <c r="AA33" s="96" t="n">
         <v>4.78</v>
       </c>
-      <c r="AA33" s="96" t="n">
+      <c r="AB33" s="96" t="n">
         <v>5.36</v>
       </c>
-      <c r="AB33" s="96" t="n">
+      <c r="AC33" s="96" t="n">
         <v>4.99</v>
-      </c>
-      <c r="AC33" s="96" t="n">
-        <v>4.02</v>
       </c>
       <c r="AD33" s="96" t="n">
         <v>4.02</v>
       </c>
       <c r="AE33" s="96" t="n">
-        <v>7.17</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="34">
@@ -10030,91 +10031,91 @@
         <v>19.99</v>
       </c>
       <c r="C34" s="96" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D34" s="96" t="n">
         <v>16.56</v>
       </c>
-      <c r="D34" s="96" t="n">
+      <c r="E34" s="96" t="n">
         <v>17.19</v>
       </c>
-      <c r="E34" s="96" t="n">
+      <c r="F34" s="96" t="n">
         <v>17.37</v>
-      </c>
-      <c r="F34" s="96" t="n">
-        <v>18.49</v>
       </c>
       <c r="G34" s="96" t="n">
         <v>18.49</v>
       </c>
       <c r="H34" s="96" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="I34" s="96" t="n">
         <v>19.1</v>
       </c>
-      <c r="I34" s="96" t="n">
+      <c r="J34" s="96" t="n">
         <v>18.21</v>
       </c>
-      <c r="J34" s="96" t="n">
+      <c r="K34" s="96" t="n">
         <v>19.55</v>
       </c>
-      <c r="K34" s="96" t="n">
+      <c r="L34" s="96" t="n">
         <v>17.36</v>
       </c>
-      <c r="L34" s="96" t="n">
+      <c r="M34" s="96" t="n">
         <v>16.36</v>
       </c>
-      <c r="M34" s="96" t="n">
+      <c r="N34" s="96" t="n">
         <v>16.06</v>
       </c>
-      <c r="N34" s="96" t="n">
+      <c r="O34" s="96" t="n">
         <v>16.07</v>
       </c>
-      <c r="O34" s="96" t="n">
+      <c r="P34" s="96" t="n">
         <v>16.55</v>
       </c>
-      <c r="P34" s="96" t="n">
+      <c r="Q34" s="96" t="n">
         <v>18.26</v>
       </c>
-      <c r="Q34" s="96" t="n">
+      <c r="R34" s="96" t="n">
         <v>16.8</v>
       </c>
-      <c r="R34" s="96" t="n">
+      <c r="S34" s="96" t="n">
         <v>16.83</v>
       </c>
-      <c r="S34" s="96" t="n">
+      <c r="T34" s="96" t="n">
         <v>16.7</v>
       </c>
-      <c r="T34" s="96" t="n">
+      <c r="U34" s="96" t="n">
         <v>18.31</v>
       </c>
-      <c r="U34" s="96" t="n">
+      <c r="V34" s="96" t="n">
         <v>18.91</v>
       </c>
-      <c r="V34" s="96" t="n">
+      <c r="W34" s="96" t="n">
         <v>19.98</v>
-      </c>
-      <c r="W34" s="96" t="n">
-        <v>18.29</v>
       </c>
       <c r="X34" s="96" t="n">
         <v>18.29</v>
       </c>
       <c r="Y34" s="96" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Z34" s="96" t="n">
         <v>17.64</v>
       </c>
-      <c r="Z34" s="96" t="n">
+      <c r="AA34" s="96" t="n">
         <v>17.84</v>
       </c>
-      <c r="AA34" s="96" t="n">
+      <c r="AB34" s="96" t="n">
         <v>17.86</v>
       </c>
-      <c r="AB34" s="96" t="n">
+      <c r="AC34" s="96" t="n">
         <v>17.93</v>
-      </c>
-      <c r="AC34" s="96" t="n">
-        <v>17.09</v>
       </c>
       <c r="AD34" s="96" t="n">
         <v>17.09</v>
       </c>
       <c r="AE34" s="96" t="n">
-        <v>17.05</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="35">
@@ -10127,91 +10128,91 @@
         <v>65.22</v>
       </c>
       <c r="C35" s="96" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="D35" s="96" t="n">
         <v>6.02</v>
       </c>
-      <c r="D35" s="96" t="n">
+      <c r="E35" s="96" t="n">
         <v>23.33</v>
       </c>
-      <c r="E35" s="96" t="n">
+      <c r="F35" s="96" t="n">
         <v>30.72</v>
-      </c>
-      <c r="F35" s="96" t="n">
-        <v>99.68000000000001</v>
       </c>
       <c r="G35" s="96" t="n">
         <v>99.68000000000001</v>
       </c>
       <c r="H35" s="96" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="I35" s="96" t="n">
         <v>99.67</v>
       </c>
-      <c r="I35" s="96" t="n">
+      <c r="J35" s="96" t="n">
         <v>98.89</v>
       </c>
-      <c r="J35" s="96" t="n">
+      <c r="K35" s="96" t="n">
         <v>98.7</v>
       </c>
-      <c r="K35" s="96" t="n">
+      <c r="L35" s="96" t="n">
         <v>98.29000000000001</v>
       </c>
-      <c r="L35" s="96" t="n">
+      <c r="M35" s="96" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="M35" s="96" t="n">
+      <c r="N35" s="96" t="n">
         <v>80.53</v>
       </c>
-      <c r="N35" s="96" t="n">
+      <c r="O35" s="96" t="n">
         <v>64.48</v>
       </c>
-      <c r="O35" s="96" t="n">
+      <c r="P35" s="96" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="P35" s="96" t="n">
+      <c r="Q35" s="96" t="n">
         <v>96.08</v>
       </c>
-      <c r="Q35" s="96" t="n">
+      <c r="R35" s="96" t="n">
         <v>72.87</v>
       </c>
-      <c r="R35" s="96" t="n">
+      <c r="S35" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="S35" s="96" t="n">
+      <c r="T35" s="96" t="n">
         <v>16.98</v>
       </c>
-      <c r="T35" s="96" t="n">
+      <c r="U35" s="96" t="n">
         <v>17.23</v>
       </c>
-      <c r="U35" s="96" t="n">
+      <c r="V35" s="96" t="n">
         <v>47.49</v>
       </c>
-      <c r="V35" s="96" t="n">
+      <c r="W35" s="96" t="n">
         <v>90.51000000000001</v>
-      </c>
-      <c r="W35" s="96" t="n">
-        <v>82.68000000000001</v>
       </c>
       <c r="X35" s="96" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="Y35" s="96" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="Z35" s="96" t="n">
         <v>25.11</v>
       </c>
-      <c r="Z35" s="96" t="n">
+      <c r="AA35" s="96" t="n">
         <v>61.16</v>
       </c>
-      <c r="AA35" s="96" t="n">
+      <c r="AB35" s="96" t="n">
         <v>92.75</v>
       </c>
-      <c r="AB35" s="96" t="n">
+      <c r="AC35" s="96" t="n">
         <v>89.43000000000001</v>
-      </c>
-      <c r="AC35" s="96" t="n">
-        <v>68.98</v>
       </c>
       <c r="AD35" s="96" t="n">
         <v>68.98</v>
       </c>
       <c r="AE35" s="96" t="n">
-        <v>77.48</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="36">
@@ -10224,91 +10225,91 @@
         <v>65.22</v>
       </c>
       <c r="C36" s="96" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="D36" s="96" t="n">
         <v>6.02</v>
       </c>
-      <c r="D36" s="96" t="n">
+      <c r="E36" s="96" t="n">
         <v>23.33</v>
       </c>
-      <c r="E36" s="96" t="n">
+      <c r="F36" s="96" t="n">
         <v>30.72</v>
-      </c>
-      <c r="F36" s="96" t="n">
-        <v>99.68000000000001</v>
       </c>
       <c r="G36" s="96" t="n">
         <v>99.68000000000001</v>
       </c>
       <c r="H36" s="96" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="I36" s="96" t="n">
         <v>99.67</v>
       </c>
-      <c r="I36" s="96" t="n">
+      <c r="J36" s="96" t="n">
         <v>98.89</v>
       </c>
-      <c r="J36" s="96" t="n">
+      <c r="K36" s="96" t="n">
         <v>98.7</v>
       </c>
-      <c r="K36" s="96" t="n">
+      <c r="L36" s="96" t="n">
         <v>98.29000000000001</v>
       </c>
-      <c r="L36" s="96" t="n">
+      <c r="M36" s="96" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="M36" s="96" t="n">
+      <c r="N36" s="96" t="n">
         <v>80.53</v>
       </c>
-      <c r="N36" s="96" t="n">
+      <c r="O36" s="96" t="n">
         <v>64.48</v>
       </c>
-      <c r="O36" s="96" t="n">
+      <c r="P36" s="96" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="P36" s="96" t="n">
+      <c r="Q36" s="96" t="n">
         <v>96.08</v>
       </c>
-      <c r="Q36" s="96" t="n">
+      <c r="R36" s="96" t="n">
         <v>72.87</v>
       </c>
-      <c r="R36" s="96" t="n">
+      <c r="S36" s="96" t="n">
         <v>63.63</v>
       </c>
-      <c r="S36" s="96" t="n">
+      <c r="T36" s="96" t="n">
         <v>16.98</v>
       </c>
-      <c r="T36" s="96" t="n">
+      <c r="U36" s="96" t="n">
         <v>17.23</v>
       </c>
-      <c r="U36" s="96" t="n">
+      <c r="V36" s="96" t="n">
         <v>47.49</v>
       </c>
-      <c r="V36" s="96" t="n">
+      <c r="W36" s="96" t="n">
         <v>90.51000000000001</v>
-      </c>
-      <c r="W36" s="96" t="n">
-        <v>82.68000000000001</v>
       </c>
       <c r="X36" s="96" t="n">
         <v>82.68000000000001</v>
       </c>
       <c r="Y36" s="96" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="Z36" s="96" t="n">
         <v>25.11</v>
       </c>
-      <c r="Z36" s="96" t="n">
+      <c r="AA36" s="96" t="n">
         <v>61.16</v>
       </c>
-      <c r="AA36" s="96" t="n">
+      <c r="AB36" s="96" t="n">
         <v>92.75</v>
       </c>
-      <c r="AB36" s="96" t="n">
+      <c r="AC36" s="96" t="n">
         <v>89.43000000000001</v>
-      </c>
-      <c r="AC36" s="96" t="n">
-        <v>68.98</v>
       </c>
       <c r="AD36" s="96" t="n">
         <v>68.98</v>
       </c>
       <c r="AE36" s="96" t="n">
-        <v>77.48</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="37">
@@ -10327,124 +10328,124 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D37" s="94" t="inlineStr">
+      <c r="D37" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E37" s="94" t="inlineStr">
+      <c r="F37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F37" s="94" t="inlineStr">
+      <c r="G37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G37" s="93" t="inlineStr">
+      <c r="H37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H37" s="93" t="inlineStr">
+      <c r="I37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I37" s="94" t="inlineStr">
+      <c r="J37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J37" s="93" t="inlineStr">
+      <c r="K37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K37" s="94" t="inlineStr">
+      <c r="L37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L37" s="95" t="inlineStr">
+      <c r="M37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M37" s="95" t="inlineStr">
+      <c r="N37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N37" s="95" t="inlineStr">
+      <c r="O37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O37" s="95" t="inlineStr">
+      <c r="P37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P37" s="93" t="inlineStr">
+      <c r="Q37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q37" s="95" t="inlineStr">
+      <c r="R37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R37" s="95" t="inlineStr">
+      <c r="S37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S37" s="93" t="inlineStr">
+      <c r="T37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T37" s="93" t="inlineStr">
+      <c r="U37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U37" s="93" t="inlineStr">
+      <c r="V37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V37" s="94" t="inlineStr">
+      <c r="W37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W37" s="94" t="inlineStr">
+      <c r="X37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X37" s="93" t="inlineStr">
+      <c r="Y37" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y37" s="95" t="inlineStr">
+      <c r="Z37" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z37" s="94" t="inlineStr">
+      <c r="AA37" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AA37" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AB37" s="95" t="inlineStr">
@@ -10478,91 +10479,91 @@
         <v>-2.4</v>
       </c>
       <c r="C38" s="96" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="D38" s="96" t="n">
         <v>-4.8</v>
       </c>
-      <c r="D38" s="96" t="n">
+      <c r="E38" s="96" t="n">
         <v>-4.46</v>
       </c>
-      <c r="E38" s="96" t="n">
+      <c r="F38" s="96" t="n">
         <v>-4.41</v>
       </c>
-      <c r="F38" s="96" t="n">
+      <c r="G38" s="96" t="n">
         <v>-5.67</v>
       </c>
-      <c r="G38" s="96" t="n">
+      <c r="H38" s="96" t="n">
         <v>-5.72</v>
       </c>
-      <c r="H38" s="96" t="n">
+      <c r="I38" s="96" t="n">
         <v>-4.75</v>
       </c>
-      <c r="I38" s="96" t="n">
+      <c r="J38" s="96" t="n">
         <v>-2.33</v>
       </c>
-      <c r="J38" s="96" t="n">
+      <c r="K38" s="96" t="n">
         <v>0.03</v>
       </c>
-      <c r="K38" s="96" t="n">
+      <c r="L38" s="96" t="n">
         <v>0.18</v>
       </c>
-      <c r="L38" s="96" t="n">
+      <c r="M38" s="96" t="n">
         <v>1.13</v>
       </c>
-      <c r="M38" s="96" t="n">
+      <c r="N38" s="96" t="n">
         <v>0.62</v>
       </c>
-      <c r="N38" s="96" t="n">
+      <c r="O38" s="96" t="n">
         <v>-0.35</v>
       </c>
-      <c r="O38" s="96" t="n">
+      <c r="P38" s="96" t="n">
         <v>-2.48</v>
       </c>
-      <c r="P38" s="96" t="n">
+      <c r="Q38" s="96" t="n">
         <v>-2.8</v>
       </c>
-      <c r="Q38" s="96" t="n">
+      <c r="R38" s="96" t="n">
         <v>-3.13</v>
       </c>
-      <c r="R38" s="96" t="n">
+      <c r="S38" s="96" t="n">
         <v>-2.93</v>
       </c>
-      <c r="S38" s="96" t="n">
+      <c r="T38" s="96" t="n">
         <v>-4.04</v>
       </c>
-      <c r="T38" s="96" t="n">
+      <c r="U38" s="96" t="n">
         <v>-4.65</v>
       </c>
-      <c r="U38" s="96" t="n">
+      <c r="V38" s="96" t="n">
         <v>-1.56</v>
       </c>
-      <c r="V38" s="96" t="n">
+      <c r="W38" s="96" t="n">
         <v>-0.9</v>
       </c>
-      <c r="W38" s="96" t="n">
+      <c r="X38" s="96" t="n">
         <v>-0.87</v>
       </c>
-      <c r="X38" s="96" t="n">
+      <c r="Y38" s="96" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Y38" s="96" t="n">
+      <c r="Z38" s="96" t="n">
         <v>0.01</v>
       </c>
-      <c r="Z38" s="96" t="n">
+      <c r="AA38" s="96" t="n">
         <v>0.93</v>
       </c>
-      <c r="AA38" s="96" t="n">
+      <c r="AB38" s="96" t="n">
         <v>1.52</v>
       </c>
-      <c r="AB38" s="96" t="n">
+      <c r="AC38" s="96" t="n">
         <v>1.56</v>
-      </c>
-      <c r="AC38" s="96" t="n">
-        <v>0.78</v>
       </c>
       <c r="AD38" s="96" t="n">
         <v>0.78</v>
       </c>
       <c r="AE38" s="96" t="n">
-        <v>2</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="39">
@@ -10572,191 +10573,191 @@
         </is>
       </c>
       <c r="B39" s="96" t="n">
-        <v>17.71</v>
+        <v>16.98</v>
       </c>
       <c r="C39" s="96" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="D39" s="96" t="n">
         <v>16.69</v>
       </c>
-      <c r="D39" s="96" t="n">
+      <c r="E39" s="96" t="n">
         <v>16.36</v>
       </c>
-      <c r="E39" s="96" t="n">
+      <c r="F39" s="96" t="n">
         <v>16.57</v>
       </c>
-      <c r="F39" s="96" t="n">
+      <c r="G39" s="96" t="n">
         <v>14.54</v>
       </c>
-      <c r="G39" s="96" t="n">
+      <c r="H39" s="96" t="n">
         <v>15.84</v>
       </c>
-      <c r="H39" s="96" t="n">
+      <c r="I39" s="96" t="n">
         <v>16.31</v>
       </c>
-      <c r="I39" s="96" t="n">
+      <c r="J39" s="96" t="n">
         <v>17.72</v>
       </c>
-      <c r="J39" s="96" t="n">
+      <c r="K39" s="96" t="n">
         <v>18.46</v>
       </c>
-      <c r="K39" s="96" t="n">
+      <c r="L39" s="96" t="n">
         <v>18.07</v>
       </c>
-      <c r="L39" s="96" t="n">
+      <c r="M39" s="96" t="n">
         <v>19.15</v>
       </c>
-      <c r="M39" s="96" t="n">
+      <c r="N39" s="96" t="n">
         <v>19.05</v>
       </c>
-      <c r="N39" s="96" t="n">
+      <c r="O39" s="96" t="n">
         <v>19.74</v>
       </c>
-      <c r="O39" s="96" t="n">
+      <c r="P39" s="96" t="n">
         <v>17.79</v>
       </c>
-      <c r="P39" s="96" t="n">
+      <c r="Q39" s="96" t="n">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="96" t="n">
+      <c r="R39" s="96" t="n">
         <v>18.49</v>
       </c>
-      <c r="R39" s="96" t="n">
+      <c r="S39" s="96" t="n">
         <v>17.13</v>
       </c>
-      <c r="S39" s="96" t="n">
+      <c r="T39" s="96" t="n">
         <v>15.12</v>
       </c>
-      <c r="T39" s="96" t="n">
+      <c r="U39" s="96" t="n">
         <v>13.64</v>
       </c>
-      <c r="U39" s="96" t="n">
+      <c r="V39" s="96" t="n">
         <v>15.71</v>
-      </c>
-      <c r="V39" s="96" t="n">
-        <v>16.3</v>
       </c>
       <c r="W39" s="96" t="n">
         <v>16.3</v>
       </c>
       <c r="X39" s="96" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y39" s="96" t="n">
         <v>14.93</v>
       </c>
-      <c r="Y39" s="96" t="n">
+      <c r="Z39" s="96" t="n">
         <v>16.89</v>
       </c>
-      <c r="Z39" s="96" t="n">
+      <c r="AA39" s="96" t="n">
         <v>15.78</v>
       </c>
-      <c r="AA39" s="96" t="n">
+      <c r="AB39" s="96" t="n">
         <v>16.65</v>
       </c>
-      <c r="AB39" s="96" t="n">
+      <c r="AC39" s="96" t="n">
         <v>16.33</v>
-      </c>
-      <c r="AC39" s="96" t="n">
-        <v>16.05</v>
       </c>
       <c r="AD39" s="96" t="n">
         <v>16.05</v>
       </c>
       <c r="AE39" s="96" t="n">
-        <v>16.11</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="inlineStr">
+      <c r="A40" s="98" t="inlineStr">
         <is>
           <t>jp225:RSI5</t>
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>73.5</v>
+        <v>78.16</v>
       </c>
       <c r="C40" s="96" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="D40" s="96" t="n">
         <v>59.75</v>
       </c>
-      <c r="D40" s="96" t="n">
+      <c r="E40" s="96" t="n">
         <v>48.68</v>
       </c>
-      <c r="E40" s="96" t="n">
+      <c r="F40" s="96" t="n">
         <v>50.64</v>
       </c>
-      <c r="F40" s="96" t="n">
+      <c r="G40" s="96" t="n">
         <v>47.78</v>
       </c>
-      <c r="G40" s="96" t="n">
+      <c r="H40" s="96" t="n">
         <v>44.09</v>
       </c>
-      <c r="H40" s="96" t="n">
+      <c r="I40" s="96" t="n">
         <v>26.25</v>
       </c>
-      <c r="I40" s="96" t="n">
+      <c r="J40" s="96" t="n">
         <v>50.37</v>
       </c>
-      <c r="J40" s="96" t="n">
+      <c r="K40" s="96" t="n">
         <v>45.03</v>
       </c>
-      <c r="K40" s="96" t="n">
+      <c r="L40" s="96" t="n">
         <v>52.54</v>
       </c>
-      <c r="L40" s="96" t="n">
+      <c r="M40" s="96" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="M40" s="96" t="n">
+      <c r="N40" s="96" t="n">
         <v>64.38</v>
       </c>
-      <c r="N40" s="96" t="n">
+      <c r="O40" s="96" t="n">
         <v>51.12</v>
       </c>
-      <c r="O40" s="96" t="n">
+      <c r="P40" s="96" t="n">
         <v>51.98</v>
       </c>
-      <c r="P40" s="96" t="n">
+      <c r="Q40" s="96" t="n">
         <v>43.77</v>
       </c>
-      <c r="Q40" s="96" t="n">
+      <c r="R40" s="96" t="n">
         <v>56.3</v>
       </c>
-      <c r="R40" s="96" t="n">
+      <c r="S40" s="96" t="n">
         <v>59.66</v>
       </c>
-      <c r="S40" s="96" t="n">
+      <c r="T40" s="96" t="n">
         <v>46.7</v>
       </c>
-      <c r="T40" s="96" t="n">
+      <c r="U40" s="96" t="n">
         <v>28.32</v>
       </c>
-      <c r="U40" s="96" t="n">
+      <c r="V40" s="96" t="n">
         <v>41.63</v>
       </c>
-      <c r="V40" s="96" t="n">
+      <c r="W40" s="96" t="n">
         <v>53.58</v>
       </c>
-      <c r="W40" s="96" t="n">
+      <c r="X40" s="96" t="n">
         <v>55.49</v>
       </c>
-      <c r="X40" s="96" t="n">
+      <c r="Y40" s="96" t="n">
         <v>46.89</v>
       </c>
-      <c r="Y40" s="96" t="n">
+      <c r="Z40" s="96" t="n">
         <v>64.97</v>
       </c>
-      <c r="Z40" s="96" t="n">
+      <c r="AA40" s="96" t="n">
         <v>47.87</v>
       </c>
-      <c r="AA40" s="96" t="n">
+      <c r="AB40" s="96" t="n">
         <v>65.12</v>
       </c>
-      <c r="AB40" s="96" t="n">
+      <c r="AC40" s="96" t="n">
         <v>72.95999999999999</v>
-      </c>
-      <c r="AC40" s="96" t="n">
-        <v>65.27</v>
       </c>
       <c r="AD40" s="96" t="n">
         <v>65.27</v>
       </c>
       <c r="AE40" s="96" t="n">
-        <v>73.09</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="41">
@@ -10766,94 +10767,94 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>62.44</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C41" s="96" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="D41" s="96" t="n">
         <v>54</v>
       </c>
-      <c r="D41" s="96" t="n">
+      <c r="E41" s="96" t="n">
         <v>48.68</v>
       </c>
-      <c r="E41" s="96" t="n">
+      <c r="F41" s="96" t="n">
         <v>49.58</v>
       </c>
-      <c r="F41" s="96" t="n">
+      <c r="G41" s="96" t="n">
         <v>48.13</v>
       </c>
-      <c r="G41" s="96" t="n">
+      <c r="H41" s="96" t="n">
         <v>46.18</v>
       </c>
-      <c r="H41" s="96" t="n">
+      <c r="I41" s="96" t="n">
         <v>37.18</v>
       </c>
-      <c r="I41" s="96" t="n">
+      <c r="J41" s="96" t="n">
         <v>51.55</v>
       </c>
-      <c r="J41" s="96" t="n">
+      <c r="K41" s="96" t="n">
         <v>49.25</v>
       </c>
-      <c r="K41" s="96" t="n">
+      <c r="L41" s="96" t="n">
         <v>52.97</v>
       </c>
-      <c r="L41" s="96" t="n">
+      <c r="M41" s="96" t="n">
         <v>59.57</v>
       </c>
-      <c r="M41" s="96" t="n">
+      <c r="N41" s="96" t="n">
         <v>57.82</v>
       </c>
-      <c r="N41" s="96" t="n">
+      <c r="O41" s="96" t="n">
         <v>50.89</v>
       </c>
-      <c r="O41" s="96" t="n">
+      <c r="P41" s="96" t="n">
         <v>51.31</v>
       </c>
-      <c r="P41" s="96" t="n">
+      <c r="Q41" s="96" t="n">
         <v>47.14</v>
       </c>
-      <c r="Q41" s="96" t="n">
+      <c r="R41" s="96" t="n">
         <v>53.8</v>
       </c>
-      <c r="R41" s="96" t="n">
+      <c r="S41" s="96" t="n">
         <v>55.52</v>
       </c>
-      <c r="S41" s="96" t="n">
+      <c r="T41" s="96" t="n">
         <v>48.02</v>
       </c>
-      <c r="T41" s="96" t="n">
+      <c r="U41" s="96" t="n">
         <v>38.89</v>
       </c>
-      <c r="U41" s="96" t="n">
+      <c r="V41" s="96" t="n">
         <v>47.48</v>
       </c>
-      <c r="V41" s="96" t="n">
+      <c r="W41" s="96" t="n">
         <v>53.74</v>
       </c>
-      <c r="W41" s="96" t="n">
+      <c r="X41" s="96" t="n">
         <v>54.7</v>
       </c>
-      <c r="X41" s="96" t="n">
+      <c r="Y41" s="96" t="n">
         <v>50.21</v>
       </c>
-      <c r="Y41" s="96" t="n">
+      <c r="Z41" s="96" t="n">
         <v>59.68</v>
       </c>
-      <c r="Z41" s="96" t="n">
+      <c r="AA41" s="96" t="n">
         <v>50.93</v>
       </c>
-      <c r="AA41" s="96" t="n">
+      <c r="AB41" s="96" t="n">
         <v>58.6</v>
       </c>
-      <c r="AB41" s="96" t="n">
+      <c r="AC41" s="96" t="n">
         <v>61.68</v>
-      </c>
-      <c r="AC41" s="96" t="n">
-        <v>57.08</v>
       </c>
       <c r="AD41" s="96" t="n">
         <v>57.08</v>
       </c>
       <c r="AE41" s="96" t="n">
-        <v>60.1</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="42">
@@ -10872,129 +10873,129 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="94" t="inlineStr">
+      <c r="D42" s="93" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E42" s="94" t="inlineStr">
+      <c r="F42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F42" s="93" t="inlineStr">
+      <c r="G42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G42" s="93" t="inlineStr">
+      <c r="H42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="I42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="J42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="95" t="inlineStr">
+      <c r="K42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K42" s="95" t="inlineStr">
+      <c r="L42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L42" s="94" t="inlineStr">
+      <c r="M42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M42" s="95" t="inlineStr">
+      <c r="N42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N42" s="95" t="inlineStr">
+      <c r="O42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O42" s="94" t="inlineStr">
+      <c r="P42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P42" s="95" t="inlineStr">
+      <c r="Q42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q42" s="95" t="inlineStr">
+      <c r="R42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R42" s="95" t="inlineStr">
+      <c r="S42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S42" s="93" t="inlineStr">
+      <c r="T42" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T42" s="94" t="inlineStr">
+      <c r="U42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U42" s="94" t="inlineStr">
+      <c r="V42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="95" t="inlineStr">
+      <c r="W42" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W42" s="94" t="inlineStr">
+      <c r="X42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X42" s="94" t="inlineStr">
+      <c r="Y42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="94" t="inlineStr">
+      <c r="Z42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="94" t="inlineStr">
+      <c r="AA42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="94" t="inlineStr">
+      <c r="AB42" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="AB42" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="AC42" s="95" t="inlineStr">
@@ -11020,94 +11021,94 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="C43" s="96" t="n">
         <v>-2.07</v>
       </c>
-      <c r="C43" s="96" t="n">
+      <c r="D43" s="96" t="n">
         <v>-2.19</v>
       </c>
-      <c r="D43" s="96" t="n">
+      <c r="E43" s="96" t="n">
         <v>1.12</v>
       </c>
-      <c r="E43" s="96" t="n">
+      <c r="F43" s="96" t="n">
         <v>0.04</v>
       </c>
-      <c r="F43" s="96" t="n">
+      <c r="G43" s="96" t="n">
         <v>0.26</v>
       </c>
-      <c r="G43" s="96" t="n">
+      <c r="H43" s="96" t="n">
         <v>1.54</v>
       </c>
-      <c r="H43" s="96" t="n">
+      <c r="I43" s="96" t="n">
         <v>2.6</v>
       </c>
-      <c r="I43" s="96" t="n">
+      <c r="J43" s="96" t="n">
         <v>2.92</v>
       </c>
-      <c r="J43" s="96" t="n">
+      <c r="K43" s="96" t="n">
         <v>2.99</v>
       </c>
-      <c r="K43" s="96" t="n">
+      <c r="L43" s="96" t="n">
         <v>2.84</v>
       </c>
-      <c r="L43" s="96" t="n">
+      <c r="M43" s="96" t="n">
         <v>1.09</v>
       </c>
-      <c r="M43" s="96" t="n">
+      <c r="N43" s="96" t="n">
         <v>3.67</v>
       </c>
-      <c r="N43" s="96" t="n">
+      <c r="O43" s="96" t="n">
         <v>4.22</v>
       </c>
-      <c r="O43" s="96" t="n">
+      <c r="P43" s="96" t="n">
         <v>2.9</v>
       </c>
-      <c r="P43" s="96" t="n">
+      <c r="Q43" s="96" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q43" s="96" t="n">
+      <c r="R43" s="96" t="n">
         <v>1.65</v>
       </c>
-      <c r="R43" s="96" t="n">
+      <c r="S43" s="96" t="n">
         <v>0.79</v>
       </c>
-      <c r="S43" s="96" t="n">
+      <c r="T43" s="96" t="n">
         <v>0.02</v>
       </c>
-      <c r="T43" s="96" t="n">
+      <c r="U43" s="96" t="n">
         <v>0.64</v>
       </c>
-      <c r="U43" s="96" t="n">
+      <c r="V43" s="96" t="n">
         <v>1.59</v>
       </c>
-      <c r="V43" s="96" t="n">
+      <c r="W43" s="96" t="n">
         <v>2.17</v>
       </c>
-      <c r="W43" s="96" t="n">
+      <c r="X43" s="96" t="n">
         <v>2.44</v>
       </c>
-      <c r="X43" s="96" t="n">
+      <c r="Y43" s="96" t="n">
         <v>3.08</v>
       </c>
-      <c r="Y43" s="96" t="n">
+      <c r="Z43" s="96" t="n">
         <v>5.7</v>
       </c>
-      <c r="Z43" s="96" t="n">
+      <c r="AA43" s="96" t="n">
         <v>3.23</v>
       </c>
-      <c r="AA43" s="96" t="n">
+      <c r="AB43" s="96" t="n">
         <v>3.83</v>
       </c>
-      <c r="AB43" s="96" t="n">
+      <c r="AC43" s="96" t="n">
         <v>3.86</v>
-      </c>
-      <c r="AC43" s="96" t="n">
-        <v>3.93</v>
       </c>
       <c r="AD43" s="96" t="n">
         <v>3.93</v>
       </c>
       <c r="AE43" s="96" t="n">
-        <v>4.88</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="44">
@@ -11117,94 +11118,94 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="C44" s="96" t="n">
         <v>11.97</v>
       </c>
-      <c r="C44" s="96" t="n">
+      <c r="D44" s="96" t="n">
         <v>12.21</v>
       </c>
-      <c r="D44" s="96" t="n">
+      <c r="E44" s="96" t="n">
         <v>16.22</v>
       </c>
-      <c r="E44" s="96" t="n">
+      <c r="F44" s="96" t="n">
         <v>16.32</v>
       </c>
-      <c r="F44" s="96" t="n">
+      <c r="G44" s="96" t="n">
         <v>16.26</v>
       </c>
-      <c r="G44" s="96" t="n">
+      <c r="H44" s="96" t="n">
         <v>16.71</v>
       </c>
-      <c r="H44" s="96" t="n">
+      <c r="I44" s="96" t="n">
         <v>16.75</v>
       </c>
-      <c r="I44" s="96" t="n">
+      <c r="J44" s="96" t="n">
         <v>16.11</v>
       </c>
-      <c r="J44" s="96" t="n">
+      <c r="K44" s="96" t="n">
         <v>17.24</v>
       </c>
-      <c r="K44" s="96" t="n">
+      <c r="L44" s="96" t="n">
         <v>16.69</v>
       </c>
-      <c r="L44" s="96" t="n">
+      <c r="M44" s="96" t="n">
         <v>13.9</v>
       </c>
-      <c r="M44" s="96" t="n">
+      <c r="N44" s="96" t="n">
         <v>14.68</v>
       </c>
-      <c r="N44" s="96" t="n">
+      <c r="O44" s="96" t="n">
         <v>14.51</v>
       </c>
-      <c r="O44" s="96" t="n">
+      <c r="P44" s="96" t="n">
         <v>14.45</v>
       </c>
-      <c r="P44" s="96" t="n">
+      <c r="Q44" s="96" t="n">
         <v>14.02</v>
       </c>
-      <c r="Q44" s="96" t="n">
+      <c r="R44" s="96" t="n">
         <v>15.01</v>
       </c>
-      <c r="R44" s="96" t="n">
+      <c r="S44" s="96" t="n">
         <v>14.24</v>
       </c>
-      <c r="S44" s="96" t="n">
+      <c r="T44" s="96" t="n">
         <v>14.48</v>
       </c>
-      <c r="T44" s="96" t="n">
+      <c r="U44" s="96" t="n">
         <v>15.74</v>
       </c>
-      <c r="U44" s="96" t="n">
+      <c r="V44" s="96" t="n">
         <v>15.4</v>
       </c>
-      <c r="V44" s="96" t="n">
+      <c r="W44" s="96" t="n">
         <v>17.01</v>
       </c>
-      <c r="W44" s="96" t="n">
+      <c r="X44" s="96" t="n">
         <v>16.51</v>
       </c>
-      <c r="X44" s="96" t="n">
+      <c r="Y44" s="96" t="n">
         <v>15.18</v>
       </c>
-      <c r="Y44" s="96" t="n">
+      <c r="Z44" s="96" t="n">
         <v>17.69</v>
       </c>
-      <c r="Z44" s="96" t="n">
+      <c r="AA44" s="96" t="n">
         <v>13.74</v>
       </c>
-      <c r="AA44" s="96" t="n">
+      <c r="AB44" s="96" t="n">
         <v>15.01</v>
       </c>
-      <c r="AB44" s="96" t="n">
+      <c r="AC44" s="96" t="n">
         <v>15.76</v>
-      </c>
-      <c r="AC44" s="96" t="n">
-        <v>15.61</v>
       </c>
       <c r="AD44" s="96" t="n">
         <v>15.61</v>
       </c>
       <c r="AE44" s="96" t="n">
-        <v>12.73</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="45">
@@ -11217,91 +11218,91 @@
         <v>17.75</v>
       </c>
       <c r="C45" s="96" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D45" s="96" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="D45" s="96" t="n">
+      <c r="E45" s="96" t="n">
         <v>50.37</v>
       </c>
-      <c r="E45" s="96" t="n">
+      <c r="F45" s="96" t="n">
         <v>52</v>
       </c>
-      <c r="F45" s="96" t="n">
+      <c r="G45" s="96" t="n">
         <v>40.49</v>
       </c>
-      <c r="G45" s="96" t="n">
+      <c r="H45" s="96" t="n">
         <v>39.37</v>
       </c>
-      <c r="H45" s="96" t="n">
+      <c r="I45" s="96" t="n">
         <v>23.75</v>
       </c>
-      <c r="I45" s="96" t="n">
+      <c r="J45" s="96" t="n">
         <v>29.2</v>
       </c>
-      <c r="J45" s="96" t="n">
+      <c r="K45" s="96" t="n">
         <v>81.68000000000001</v>
       </c>
-      <c r="K45" s="96" t="n">
+      <c r="L45" s="96" t="n">
         <v>80.23</v>
       </c>
-      <c r="L45" s="96" t="n">
+      <c r="M45" s="96" t="n">
         <v>46.62</v>
       </c>
-      <c r="M45" s="96" t="n">
+      <c r="N45" s="96" t="n">
         <v>84.70999999999999</v>
       </c>
-      <c r="N45" s="96" t="n">
+      <c r="O45" s="96" t="n">
         <v>79.09</v>
       </c>
-      <c r="O45" s="96" t="n">
+      <c r="P45" s="96" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="P45" s="96" t="n">
+      <c r="Q45" s="96" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="Q45" s="96" t="n">
+      <c r="R45" s="96" t="n">
         <v>72.56999999999999</v>
       </c>
-      <c r="R45" s="96" t="n">
+      <c r="S45" s="96" t="n">
         <v>68.26000000000001</v>
       </c>
-      <c r="S45" s="96" t="n">
+      <c r="T45" s="96" t="n">
         <v>30.48</v>
       </c>
-      <c r="T45" s="96" t="n">
+      <c r="U45" s="96" t="n">
         <v>38.08</v>
       </c>
-      <c r="U45" s="96" t="n">
+      <c r="V45" s="96" t="n">
         <v>49.36</v>
       </c>
-      <c r="V45" s="96" t="n">
+      <c r="W45" s="96" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="W45" s="96" t="n">
+      <c r="X45" s="96" t="n">
         <v>47.48</v>
       </c>
-      <c r="X45" s="96" t="n">
+      <c r="Y45" s="96" t="n">
         <v>35.25</v>
       </c>
-      <c r="Y45" s="96" t="n">
+      <c r="Z45" s="96" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="Z45" s="96" t="n">
+      <c r="AA45" s="96" t="n">
         <v>42.72</v>
       </c>
-      <c r="AA45" s="96" t="n">
+      <c r="AB45" s="96" t="n">
         <v>91.28</v>
       </c>
-      <c r="AB45" s="96" t="n">
+      <c r="AC45" s="96" t="n">
         <v>94.36</v>
-      </c>
-      <c r="AC45" s="96" t="n">
-        <v>92.69</v>
       </c>
       <c r="AD45" s="96" t="n">
         <v>92.69</v>
       </c>
       <c r="AE45" s="96" t="n">
-        <v>90.95999999999999</v>
+        <v>92.69</v>
       </c>
     </row>
     <row r="46">
@@ -11314,91 +11315,91 @@
         <v>23.96</v>
       </c>
       <c r="C46" s="96" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="D46" s="96" t="n">
         <v>18.88</v>
       </c>
-      <c r="D46" s="96" t="n">
+      <c r="E46" s="96" t="n">
         <v>48.5</v>
       </c>
-      <c r="E46" s="96" t="n">
+      <c r="F46" s="96" t="n">
         <v>49.12</v>
       </c>
-      <c r="F46" s="96" t="n">
+      <c r="G46" s="96" t="n">
         <v>44</v>
       </c>
-      <c r="G46" s="96" t="n">
+      <c r="H46" s="96" t="n">
         <v>43.47</v>
       </c>
-      <c r="H46" s="96" t="n">
+      <c r="I46" s="96" t="n">
         <v>35.57</v>
       </c>
-      <c r="I46" s="96" t="n">
+      <c r="J46" s="96" t="n">
         <v>40.49</v>
       </c>
-      <c r="J46" s="96" t="n">
+      <c r="K46" s="96" t="n">
         <v>75.67</v>
       </c>
-      <c r="K46" s="96" t="n">
+      <c r="L46" s="96" t="n">
         <v>74.59</v>
       </c>
-      <c r="L46" s="96" t="n">
+      <c r="M46" s="96" t="n">
         <v>55.87</v>
       </c>
-      <c r="M46" s="96" t="n">
+      <c r="N46" s="96" t="n">
         <v>72.91</v>
       </c>
-      <c r="N46" s="96" t="n">
+      <c r="O46" s="96" t="n">
         <v>69.2</v>
       </c>
-      <c r="O46" s="96" t="n">
+      <c r="P46" s="96" t="n">
         <v>64.08</v>
       </c>
-      <c r="P46" s="96" t="n">
+      <c r="Q46" s="96" t="n">
         <v>65.8</v>
       </c>
-      <c r="Q46" s="96" t="n">
+      <c r="R46" s="96" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="R46" s="96" t="n">
+      <c r="S46" s="96" t="n">
         <v>62.04</v>
       </c>
-      <c r="S46" s="96" t="n">
+      <c r="T46" s="96" t="n">
         <v>41.33</v>
       </c>
-      <c r="T46" s="96" t="n">
+      <c r="U46" s="96" t="n">
         <v>46.43</v>
       </c>
-      <c r="U46" s="96" t="n">
+      <c r="V46" s="96" t="n">
         <v>53.71</v>
       </c>
-      <c r="V46" s="96" t="n">
+      <c r="W46" s="96" t="n">
         <v>65.55</v>
       </c>
-      <c r="W46" s="96" t="n">
+      <c r="X46" s="96" t="n">
         <v>52.65</v>
       </c>
-      <c r="X46" s="96" t="n">
+      <c r="Y46" s="96" t="n">
         <v>46.03</v>
       </c>
-      <c r="Y46" s="96" t="n">
+      <c r="Z46" s="96" t="n">
         <v>73.20999999999999</v>
       </c>
-      <c r="Z46" s="96" t="n">
+      <c r="AA46" s="96" t="n">
         <v>58.84</v>
       </c>
-      <c r="AA46" s="96" t="n">
+      <c r="AB46" s="96" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="AB46" s="96" t="n">
+      <c r="AC46" s="96" t="n">
         <v>86.75</v>
-      </c>
-      <c r="AC46" s="96" t="n">
-        <v>84.8</v>
       </c>
       <c r="AD46" s="96" t="n">
         <v>84.8</v>
       </c>
       <c r="AE46" s="96" t="n">
-        <v>82.84999999999999</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="47">
@@ -11412,109 +11413,109 @@
           <t>red</t>
         </is>
       </c>
-      <c r="C47" s="94" t="inlineStr">
+      <c r="C47" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D47" s="94" t="inlineStr">
+      <c r="E47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E47" s="94" t="inlineStr">
+      <c r="F47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F47" s="94" t="inlineStr">
+      <c r="G47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G47" s="95" t="inlineStr">
+      <c r="H47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H47" s="94" t="inlineStr">
+      <c r="I47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I47" s="94" t="inlineStr">
+      <c r="J47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J47" s="95" t="inlineStr">
+      <c r="K47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="K47" s="95" t="inlineStr">
+      <c r="L47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L47" s="95" t="inlineStr">
+      <c r="M47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M47" s="95" t="inlineStr">
+      <c r="N47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N47" s="95" t="inlineStr">
+      <c r="O47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O47" s="95" t="inlineStr">
+      <c r="P47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P47" s="95" t="inlineStr">
+      <c r="Q47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q47" s="93" t="inlineStr">
+      <c r="R47" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R47" s="95" t="inlineStr">
+      <c r="S47" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S47" s="93" t="inlineStr">
+      <c r="T47" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T47" s="93" t="inlineStr">
+      <c r="U47" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U47" s="94" t="inlineStr">
+      <c r="V47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V47" s="94" t="inlineStr">
+      <c r="W47" s="94" t="inlineStr">
         <is>
           <t>blue</t>
-        </is>
-      </c>
-      <c r="W47" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
         </is>
       </c>
       <c r="X47" s="95" t="inlineStr">
@@ -11568,91 +11569,91 @@
         <v>7.7</v>
       </c>
       <c r="C48" s="96" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D48" s="96" t="n">
         <v>6.19</v>
       </c>
-      <c r="D48" s="96" t="n">
+      <c r="E48" s="96" t="n">
         <v>6.29</v>
       </c>
-      <c r="E48" s="96" t="n">
+      <c r="F48" s="96" t="n">
         <v>7.46</v>
       </c>
-      <c r="F48" s="96" t="n">
+      <c r="G48" s="96" t="n">
         <v>7.4</v>
       </c>
-      <c r="G48" s="96" t="n">
+      <c r="H48" s="96" t="n">
         <v>6.26</v>
-      </c>
-      <c r="H48" s="96" t="n">
-        <v>5.99</v>
       </c>
       <c r="I48" s="96" t="n">
         <v>5.99</v>
       </c>
       <c r="J48" s="96" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K48" s="96" t="n">
         <v>5.08</v>
       </c>
-      <c r="K48" s="96" t="n">
+      <c r="L48" s="96" t="n">
         <v>5.28</v>
       </c>
-      <c r="L48" s="96" t="n">
+      <c r="M48" s="96" t="n">
         <v>3.79</v>
       </c>
-      <c r="M48" s="96" t="n">
+      <c r="N48" s="96" t="n">
         <v>4.06</v>
       </c>
-      <c r="N48" s="96" t="n">
+      <c r="O48" s="96" t="n">
         <v>3.47</v>
       </c>
-      <c r="O48" s="96" t="n">
+      <c r="P48" s="96" t="n">
         <v>1.33</v>
       </c>
-      <c r="P48" s="96" t="n">
+      <c r="Q48" s="96" t="n">
         <v>0.96</v>
       </c>
-      <c r="Q48" s="96" t="n">
+      <c r="R48" s="96" t="n">
         <v>-2.43</v>
       </c>
-      <c r="R48" s="96" t="n">
+      <c r="S48" s="96" t="n">
         <v>3.61</v>
       </c>
-      <c r="S48" s="96" t="n">
+      <c r="T48" s="96" t="n">
         <v>0.29</v>
       </c>
-      <c r="T48" s="96" t="n">
+      <c r="U48" s="96" t="n">
         <v>1.91</v>
       </c>
-      <c r="U48" s="96" t="n">
+      <c r="V48" s="96" t="n">
         <v>3.04</v>
       </c>
-      <c r="V48" s="96" t="n">
+      <c r="W48" s="96" t="n">
         <v>2.84</v>
       </c>
-      <c r="W48" s="96" t="n">
+      <c r="X48" s="96" t="n">
         <v>3.57</v>
       </c>
-      <c r="X48" s="96" t="n">
+      <c r="Y48" s="96" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y48" s="96" t="n">
+      <c r="Z48" s="96" t="n">
         <v>3.09</v>
       </c>
-      <c r="Z48" s="96" t="n">
+      <c r="AA48" s="96" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA48" s="96" t="n">
+      <c r="AB48" s="96" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AB48" s="96" t="n">
-        <v>1.78</v>
       </c>
       <c r="AC48" s="96" t="n">
         <v>1.78</v>
       </c>
       <c r="AD48" s="96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE48" s="96" t="n">
         <v>2.06</v>
-      </c>
-      <c r="AE48" s="96" t="n">
-        <v>2.24</v>
       </c>
     </row>
     <row r="49">
@@ -11665,91 +11666,91 @@
         <v>8.050000000000001</v>
       </c>
       <c r="C49" s="96" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="D49" s="96" t="n">
         <v>6.81</v>
       </c>
-      <c r="D49" s="96" t="n">
+      <c r="E49" s="96" t="n">
         <v>7.18</v>
       </c>
-      <c r="E49" s="96" t="n">
+      <c r="F49" s="96" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="F49" s="96" t="n">
+      <c r="G49" s="96" t="n">
         <v>8.76</v>
       </c>
-      <c r="G49" s="96" t="n">
+      <c r="H49" s="96" t="n">
         <v>9.08</v>
-      </c>
-      <c r="H49" s="96" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="I49" s="96" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J49" s="96" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K49" s="96" t="n">
         <v>7.52</v>
       </c>
-      <c r="K49" s="96" t="n">
+      <c r="L49" s="96" t="n">
         <v>7.42</v>
       </c>
-      <c r="L49" s="96" t="n">
+      <c r="M49" s="96" t="n">
         <v>6.96</v>
       </c>
-      <c r="M49" s="96" t="n">
+      <c r="N49" s="96" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="N49" s="96" t="n">
+      <c r="O49" s="96" t="n">
         <v>10.22</v>
       </c>
-      <c r="O49" s="96" t="n">
+      <c r="P49" s="96" t="n">
         <v>7.94</v>
       </c>
-      <c r="P49" s="96" t="n">
+      <c r="Q49" s="96" t="n">
         <v>6.37</v>
       </c>
-      <c r="Q49" s="96" t="n">
+      <c r="R49" s="96" t="n">
         <v>3.23</v>
       </c>
-      <c r="R49" s="96" t="n">
+      <c r="S49" s="96" t="n">
         <v>9.99</v>
       </c>
-      <c r="S49" s="96" t="n">
+      <c r="T49" s="96" t="n">
         <v>6.18</v>
       </c>
-      <c r="T49" s="96" t="n">
+      <c r="U49" s="96" t="n">
         <v>6.62</v>
       </c>
-      <c r="U49" s="96" t="n">
+      <c r="V49" s="96" t="n">
         <v>8.19</v>
       </c>
-      <c r="V49" s="96" t="n">
+      <c r="W49" s="96" t="n">
         <v>11.39</v>
       </c>
-      <c r="W49" s="96" t="n">
+      <c r="X49" s="96" t="n">
         <v>12.54</v>
       </c>
-      <c r="X49" s="96" t="n">
+      <c r="Y49" s="96" t="n">
         <v>12.72</v>
       </c>
-      <c r="Y49" s="96" t="n">
+      <c r="Z49" s="96" t="n">
         <v>13.97</v>
       </c>
-      <c r="Z49" s="96" t="n">
+      <c r="AA49" s="96" t="n">
         <v>12.51</v>
       </c>
-      <c r="AA49" s="96" t="n">
+      <c r="AB49" s="96" t="n">
         <v>12.02</v>
-      </c>
-      <c r="AB49" s="96" t="n">
-        <v>12.09</v>
       </c>
       <c r="AC49" s="96" t="n">
         <v>12.09</v>
       </c>
       <c r="AD49" s="96" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="AE49" s="96" t="n">
         <v>12.11</v>
-      </c>
-      <c r="AE49" s="96" t="n">
-        <v>12.2</v>
       </c>
     </row>
     <row r="50">
@@ -11762,91 +11763,91 @@
         <v>72.52</v>
       </c>
       <c r="C50" s="96" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="D50" s="96" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="D50" s="96" t="n">
+      <c r="E50" s="96" t="n">
         <v>62.92</v>
       </c>
-      <c r="E50" s="96" t="n">
+      <c r="F50" s="96" t="n">
         <v>68.67</v>
       </c>
-      <c r="F50" s="96" t="n">
+      <c r="G50" s="96" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="G50" s="96" t="n">
+      <c r="H50" s="96" t="n">
         <v>67.01000000000001</v>
-      </c>
-      <c r="H50" s="96" t="n">
-        <v>64.55</v>
       </c>
       <c r="I50" s="96" t="n">
         <v>64.55</v>
       </c>
       <c r="J50" s="96" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="K50" s="96" t="n">
         <v>63.16</v>
       </c>
-      <c r="K50" s="96" t="n">
+      <c r="L50" s="96" t="n">
         <v>61.72</v>
       </c>
-      <c r="L50" s="96" t="n">
+      <c r="M50" s="96" t="n">
         <v>60.75</v>
       </c>
-      <c r="M50" s="96" t="n">
+      <c r="N50" s="96" t="n">
         <v>61.04</v>
       </c>
-      <c r="N50" s="96" t="n">
+      <c r="O50" s="96" t="n">
         <v>62.63</v>
       </c>
-      <c r="O50" s="96" t="n">
+      <c r="P50" s="96" t="n">
         <v>54.57</v>
       </c>
-      <c r="P50" s="96" t="n">
+      <c r="Q50" s="96" t="n">
         <v>50.68</v>
       </c>
-      <c r="Q50" s="96" t="n">
+      <c r="R50" s="96" t="n">
         <v>34.71</v>
       </c>
-      <c r="R50" s="96" t="n">
+      <c r="S50" s="96" t="n">
         <v>73.68000000000001</v>
       </c>
-      <c r="S50" s="96" t="n">
+      <c r="T50" s="96" t="n">
         <v>41.54</v>
       </c>
-      <c r="T50" s="96" t="n">
+      <c r="U50" s="96" t="n">
         <v>39.63</v>
       </c>
-      <c r="U50" s="96" t="n">
+      <c r="V50" s="96" t="n">
         <v>51.34</v>
       </c>
-      <c r="V50" s="96" t="n">
+      <c r="W50" s="96" t="n">
         <v>70.72</v>
       </c>
-      <c r="W50" s="96" t="n">
+      <c r="X50" s="96" t="n">
         <v>79.16</v>
       </c>
-      <c r="X50" s="96" t="n">
+      <c r="Y50" s="96" t="n">
         <v>79.89</v>
       </c>
-      <c r="Y50" s="96" t="n">
+      <c r="Z50" s="96" t="n">
         <v>80.14</v>
       </c>
-      <c r="Z50" s="96" t="n">
+      <c r="AA50" s="96" t="n">
         <v>66.11</v>
       </c>
-      <c r="AA50" s="96" t="n">
+      <c r="AB50" s="96" t="n">
         <v>60.8</v>
-      </c>
-      <c r="AB50" s="96" t="n">
-        <v>62.45</v>
       </c>
       <c r="AC50" s="96" t="n">
         <v>62.45</v>
       </c>
       <c r="AD50" s="96" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="AE50" s="96" t="n">
         <v>60.92</v>
-      </c>
-      <c r="AE50" s="96" t="n">
-        <v>56.59</v>
       </c>
     </row>
     <row r="51">
@@ -11859,91 +11860,91 @@
         <v>63.55</v>
       </c>
       <c r="C51" s="96" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="D51" s="96" t="n">
         <v>60.54</v>
       </c>
-      <c r="D51" s="96" t="n">
+      <c r="E51" s="96" t="n">
         <v>59.97</v>
       </c>
-      <c r="E51" s="96" t="n">
+      <c r="F51" s="96" t="n">
         <v>61.7</v>
       </c>
-      <c r="F51" s="96" t="n">
+      <c r="G51" s="96" t="n">
         <v>61.14</v>
       </c>
-      <c r="G51" s="96" t="n">
+      <c r="H51" s="96" t="n">
         <v>61</v>
-      </c>
-      <c r="H51" s="96" t="n">
-        <v>59.88</v>
       </c>
       <c r="I51" s="96" t="n">
         <v>59.88</v>
       </c>
       <c r="J51" s="96" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="K51" s="96" t="n">
         <v>59.23</v>
       </c>
-      <c r="K51" s="96" t="n">
+      <c r="L51" s="96" t="n">
         <v>58.51</v>
       </c>
-      <c r="L51" s="96" t="n">
+      <c r="M51" s="96" t="n">
         <v>58</v>
       </c>
-      <c r="M51" s="96" t="n">
+      <c r="N51" s="96" t="n">
         <v>58.15</v>
       </c>
-      <c r="N51" s="96" t="n">
+      <c r="O51" s="96" t="n">
         <v>59.02</v>
       </c>
-      <c r="O51" s="96" t="n">
+      <c r="P51" s="96" t="n">
         <v>53.85</v>
       </c>
-      <c r="P51" s="96" t="n">
+      <c r="Q51" s="96" t="n">
         <v>51.37</v>
       </c>
-      <c r="Q51" s="96" t="n">
+      <c r="R51" s="96" t="n">
         <v>41.57</v>
       </c>
-      <c r="R51" s="96" t="n">
+      <c r="S51" s="96" t="n">
         <v>65.12</v>
       </c>
-      <c r="S51" s="96" t="n">
+      <c r="T51" s="96" t="n">
         <v>49.84</v>
       </c>
-      <c r="T51" s="96" t="n">
+      <c r="U51" s="96" t="n">
         <v>49.21</v>
       </c>
-      <c r="U51" s="96" t="n">
+      <c r="V51" s="96" t="n">
         <v>54.48</v>
       </c>
-      <c r="V51" s="96" t="n">
+      <c r="W51" s="96" t="n">
         <v>61.14</v>
       </c>
-      <c r="W51" s="96" t="n">
+      <c r="X51" s="96" t="n">
         <v>63.56</v>
       </c>
-      <c r="X51" s="96" t="n">
+      <c r="Y51" s="96" t="n">
         <v>63.77</v>
       </c>
-      <c r="Y51" s="96" t="n">
+      <c r="Z51" s="96" t="n">
         <v>63.85</v>
       </c>
-      <c r="Z51" s="96" t="n">
+      <c r="AA51" s="96" t="n">
         <v>55.93</v>
       </c>
-      <c r="AA51" s="96" t="n">
+      <c r="AB51" s="96" t="n">
         <v>53.8</v>
-      </c>
-      <c r="AB51" s="96" t="n">
-        <v>54.28</v>
       </c>
       <c r="AC51" s="96" t="n">
         <v>54.28</v>
       </c>
       <c r="AD51" s="96" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AE51" s="96" t="n">
         <v>53.62</v>
-      </c>
-      <c r="AE51" s="96" t="n">
-        <v>51.73</v>
       </c>
     </row>
     <row r="52">
@@ -11982,109 +11983,109 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="93" t="inlineStr">
+      <c r="H52" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I52" s="93" t="inlineStr">
+      <c r="J52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J52" s="93" t="inlineStr">
+      <c r="K52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K52" s="94" t="inlineStr">
+      <c r="L52" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L52" s="93" t="inlineStr">
+      <c r="M52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M52" s="93" t="inlineStr">
+      <c r="N52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N52" s="94" t="inlineStr">
+      <c r="O52" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O52" s="95" t="inlineStr">
+      <c r="P52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P52" s="94" t="inlineStr">
+      <c r="Q52" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q52" s="93" t="inlineStr">
+      <c r="R52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R52" s="94" t="inlineStr">
+      <c r="S52" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S52" s="94" t="inlineStr">
+      <c r="T52" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T52" s="93" t="inlineStr">
+      <c r="U52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U52" s="93" t="inlineStr">
+      <c r="V52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V52" s="93" t="inlineStr">
+      <c r="W52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W52" s="95" t="inlineStr">
+      <c r="X52" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X52" s="93" t="inlineStr">
+      <c r="Y52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y52" s="93" t="inlineStr">
+      <c r="Z52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z52" s="93" t="inlineStr">
+      <c r="AA52" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA52" s="93" t="inlineStr">
+      <c r="AB52" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="AB52" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="AC52" s="94" t="inlineStr">
@@ -12113,91 +12114,91 @@
         <v>-6.62</v>
       </c>
       <c r="C53" s="96" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="D53" s="96" t="n">
         <v>-6.07</v>
       </c>
-      <c r="D53" s="96" t="n">
+      <c r="E53" s="96" t="n">
         <v>-6.8</v>
       </c>
-      <c r="E53" s="96" t="n">
+      <c r="F53" s="96" t="n">
         <v>-5.89</v>
       </c>
-      <c r="F53" s="96" t="n">
+      <c r="G53" s="96" t="n">
         <v>-7.14</v>
       </c>
-      <c r="G53" s="96" t="n">
+      <c r="H53" s="96" t="n">
         <v>-6.74</v>
       </c>
-      <c r="H53" s="96" t="n">
+      <c r="I53" s="96" t="n">
         <v>-7.23</v>
       </c>
-      <c r="I53" s="96" t="n">
+      <c r="J53" s="96" t="n">
         <v>-8.51</v>
       </c>
-      <c r="J53" s="96" t="n">
+      <c r="K53" s="96" t="n">
         <v>-5.4</v>
       </c>
-      <c r="K53" s="96" t="n">
+      <c r="L53" s="96" t="n">
         <v>-3.67</v>
       </c>
-      <c r="L53" s="96" t="n">
+      <c r="M53" s="96" t="n">
         <v>-4.56</v>
       </c>
-      <c r="M53" s="96" t="n">
+      <c r="N53" s="96" t="n">
         <v>-2.99</v>
       </c>
-      <c r="N53" s="96" t="n">
+      <c r="O53" s="96" t="n">
         <v>-1.06</v>
       </c>
-      <c r="O53" s="96" t="n">
+      <c r="P53" s="96" t="n">
         <v>0.25</v>
       </c>
-      <c r="P53" s="96" t="n">
+      <c r="Q53" s="96" t="n">
         <v>-0.27</v>
       </c>
-      <c r="Q53" s="96" t="n">
+      <c r="R53" s="96" t="n">
         <v>-0.98</v>
       </c>
-      <c r="R53" s="96" t="n">
+      <c r="S53" s="96" t="n">
         <v>0.54</v>
       </c>
-      <c r="S53" s="96" t="n">
+      <c r="T53" s="96" t="n">
         <v>0.76</v>
       </c>
-      <c r="T53" s="96" t="n">
+      <c r="U53" s="96" t="n">
         <v>0.28</v>
       </c>
-      <c r="U53" s="96" t="n">
+      <c r="V53" s="96" t="n">
         <v>0.01</v>
       </c>
-      <c r="V53" s="96" t="n">
+      <c r="W53" s="96" t="n">
         <v>1.64</v>
       </c>
-      <c r="W53" s="96" t="n">
+      <c r="X53" s="96" t="n">
         <v>2.24</v>
       </c>
-      <c r="X53" s="96" t="n">
+      <c r="Y53" s="96" t="n">
         <v>1.84</v>
       </c>
-      <c r="Y53" s="96" t="n">
+      <c r="Z53" s="96" t="n">
         <v>2.18</v>
       </c>
-      <c r="Z53" s="96" t="n">
+      <c r="AA53" s="96" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA53" s="96" t="n">
+      <c r="AB53" s="96" t="n">
         <v>2.91</v>
       </c>
-      <c r="AB53" s="96" t="n">
+      <c r="AC53" s="96" t="n">
         <v>4.91</v>
-      </c>
-      <c r="AC53" s="96" t="n">
-        <v>4.78</v>
       </c>
       <c r="AD53" s="96" t="n">
         <v>4.78</v>
       </c>
       <c r="AE53" s="96" t="n">
-        <v>5.41</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="54">
@@ -12210,91 +12211,91 @@
         <v>2.84</v>
       </c>
       <c r="C54" s="96" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="D54" s="96" t="n">
         <v>3.98</v>
       </c>
-      <c r="D54" s="96" t="n">
+      <c r="E54" s="96" t="n">
         <v>1.3</v>
       </c>
-      <c r="E54" s="96" t="n">
+      <c r="F54" s="96" t="n">
         <v>1.7</v>
       </c>
-      <c r="F54" s="96" t="n">
+      <c r="G54" s="96" t="n">
         <v>0.47</v>
       </c>
-      <c r="G54" s="96" t="n">
+      <c r="H54" s="96" t="n">
         <v>0.75</v>
       </c>
-      <c r="H54" s="96" t="n">
+      <c r="I54" s="96" t="n">
         <v>0.04</v>
       </c>
-      <c r="I54" s="96" t="n">
+      <c r="J54" s="96" t="n">
         <v>-0.9</v>
       </c>
-      <c r="J54" s="96" t="n">
+      <c r="K54" s="96" t="n">
         <v>1.64</v>
       </c>
-      <c r="K54" s="96" t="n">
+      <c r="L54" s="96" t="n">
         <v>3.83</v>
       </c>
-      <c r="L54" s="96" t="n">
+      <c r="M54" s="96" t="n">
         <v>2.91</v>
       </c>
-      <c r="M54" s="96" t="n">
+      <c r="N54" s="96" t="n">
         <v>3.91</v>
       </c>
-      <c r="N54" s="96" t="n">
+      <c r="O54" s="96" t="n">
         <v>5.62</v>
       </c>
-      <c r="O54" s="96" t="n">
+      <c r="P54" s="96" t="n">
         <v>6.76</v>
       </c>
-      <c r="P54" s="96" t="n">
+      <c r="Q54" s="96" t="n">
         <v>6.14</v>
       </c>
-      <c r="Q54" s="96" t="n">
+      <c r="R54" s="96" t="n">
         <v>5.12</v>
       </c>
-      <c r="R54" s="96" t="n">
+      <c r="S54" s="96" t="n">
         <v>6.26</v>
       </c>
-      <c r="S54" s="96" t="n">
+      <c r="T54" s="96" t="n">
         <v>7.6</v>
       </c>
-      <c r="T54" s="96" t="n">
+      <c r="U54" s="96" t="n">
         <v>7.3</v>
       </c>
-      <c r="U54" s="96" t="n">
+      <c r="V54" s="96" t="n">
         <v>7.42</v>
       </c>
-      <c r="V54" s="96" t="n">
+      <c r="W54" s="96" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="W54" s="96" t="n">
+      <c r="X54" s="96" t="n">
         <v>10.7</v>
       </c>
-      <c r="X54" s="96" t="n">
+      <c r="Y54" s="96" t="n">
         <v>10.73</v>
       </c>
-      <c r="Y54" s="96" t="n">
+      <c r="Z54" s="96" t="n">
         <v>11.49</v>
       </c>
-      <c r="Z54" s="96" t="n">
+      <c r="AA54" s="96" t="n">
         <v>11.61</v>
       </c>
-      <c r="AA54" s="96" t="n">
+      <c r="AB54" s="96" t="n">
         <v>12.06</v>
       </c>
-      <c r="AB54" s="96" t="n">
+      <c r="AC54" s="96" t="n">
         <v>12.38</v>
-      </c>
-      <c r="AC54" s="96" t="n">
-        <v>12.22</v>
       </c>
       <c r="AD54" s="96" t="n">
         <v>12.22</v>
       </c>
       <c r="AE54" s="96" t="n">
-        <v>12.78</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="55">
@@ -12307,91 +12308,91 @@
         <v>50.33</v>
       </c>
       <c r="C55" s="96" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="D55" s="96" t="n">
         <v>65.25</v>
       </c>
-      <c r="D55" s="96" t="n">
+      <c r="E55" s="96" t="n">
         <v>46.78</v>
       </c>
-      <c r="E55" s="96" t="n">
+      <c r="F55" s="96" t="n">
         <v>58.01</v>
       </c>
-      <c r="F55" s="96" t="n">
+      <c r="G55" s="96" t="n">
         <v>32.44</v>
       </c>
-      <c r="G55" s="96" t="n">
+      <c r="H55" s="96" t="n">
         <v>42.41</v>
       </c>
-      <c r="H55" s="96" t="n">
+      <c r="I55" s="96" t="n">
         <v>28</v>
       </c>
-      <c r="I55" s="96" t="n">
+      <c r="J55" s="96" t="n">
         <v>10.09</v>
       </c>
-      <c r="J55" s="96" t="n">
+      <c r="K55" s="96" t="n">
         <v>20.06</v>
       </c>
-      <c r="K55" s="96" t="n">
+      <c r="L55" s="96" t="n">
         <v>40.45</v>
       </c>
-      <c r="L55" s="96" t="n">
+      <c r="M55" s="96" t="n">
         <v>11.58</v>
       </c>
-      <c r="M55" s="96" t="n">
+      <c r="N55" s="96" t="n">
         <v>21.01</v>
       </c>
-      <c r="N55" s="96" t="n">
+      <c r="O55" s="96" t="n">
         <v>47.54</v>
       </c>
-      <c r="O55" s="96" t="n">
+      <c r="P55" s="96" t="n">
         <v>67.86</v>
       </c>
-      <c r="P55" s="96" t="n">
+      <c r="Q55" s="96" t="n">
         <v>57.18</v>
       </c>
-      <c r="Q55" s="96" t="n">
+      <c r="R55" s="96" t="n">
         <v>21.68</v>
       </c>
-      <c r="R55" s="96" t="n">
+      <c r="S55" s="96" t="n">
         <v>42</v>
       </c>
-      <c r="S55" s="96" t="n">
+      <c r="T55" s="96" t="n">
         <v>38.72</v>
       </c>
-      <c r="T55" s="96" t="n">
+      <c r="U55" s="96" t="n">
         <v>31.52</v>
       </c>
-      <c r="U55" s="96" t="n">
+      <c r="V55" s="96" t="n">
         <v>10.24</v>
       </c>
-      <c r="V55" s="96" t="n">
+      <c r="W55" s="96" t="n">
         <v>24.68</v>
       </c>
-      <c r="W55" s="96" t="n">
+      <c r="X55" s="96" t="n">
         <v>57.67</v>
       </c>
-      <c r="X55" s="96" t="n">
+      <c r="Y55" s="96" t="n">
         <v>23.36</v>
       </c>
-      <c r="Y55" s="96" t="n">
+      <c r="Z55" s="96" t="n">
         <v>26.13</v>
       </c>
-      <c r="Z55" s="96" t="n">
+      <c r="AA55" s="96" t="n">
         <v>17.02</v>
       </c>
-      <c r="AA55" s="96" t="n">
+      <c r="AB55" s="96" t="n">
         <v>28.23</v>
       </c>
-      <c r="AB55" s="96" t="n">
+      <c r="AC55" s="96" t="n">
         <v>54.76</v>
-      </c>
-      <c r="AC55" s="96" t="n">
-        <v>32.74</v>
       </c>
       <c r="AD55" s="96" t="n">
         <v>32.74</v>
       </c>
       <c r="AE55" s="96" t="n">
-        <v>43.04</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="56">
@@ -12404,91 +12405,91 @@
         <v>46.44</v>
       </c>
       <c r="C56" s="96" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="D56" s="96" t="n">
         <v>52.97</v>
       </c>
-      <c r="D56" s="96" t="n">
+      <c r="E56" s="96" t="n">
         <v>41.4</v>
       </c>
-      <c r="E56" s="96" t="n">
+      <c r="F56" s="96" t="n">
         <v>46.38</v>
       </c>
-      <c r="F56" s="96" t="n">
+      <c r="G56" s="96" t="n">
         <v>30.56</v>
       </c>
-      <c r="G56" s="96" t="n">
+      <c r="H56" s="96" t="n">
         <v>35.4</v>
       </c>
-      <c r="H56" s="96" t="n">
+      <c r="I56" s="96" t="n">
         <v>26.27</v>
       </c>
-      <c r="I56" s="96" t="n">
+      <c r="J56" s="96" t="n">
         <v>14.76</v>
       </c>
-      <c r="J56" s="96" t="n">
+      <c r="K56" s="96" t="n">
         <v>23.59</v>
       </c>
-      <c r="K56" s="96" t="n">
+      <c r="L56" s="96" t="n">
         <v>37.21</v>
       </c>
-      <c r="L56" s="96" t="n">
+      <c r="M56" s="96" t="n">
         <v>19.24</v>
       </c>
-      <c r="M56" s="96" t="n">
+      <c r="N56" s="96" t="n">
         <v>28.21</v>
       </c>
-      <c r="N56" s="96" t="n">
+      <c r="O56" s="96" t="n">
         <v>45.76</v>
       </c>
-      <c r="O56" s="96" t="n">
+      <c r="P56" s="96" t="n">
         <v>55.59</v>
       </c>
-      <c r="P56" s="96" t="n">
+      <c r="Q56" s="96" t="n">
         <v>47.72</v>
       </c>
-      <c r="Q56" s="96" t="n">
+      <c r="R56" s="96" t="n">
         <v>26.35</v>
       </c>
-      <c r="R56" s="96" t="n">
+      <c r="S56" s="96" t="n">
         <v>36.92</v>
       </c>
-      <c r="S56" s="96" t="n">
+      <c r="T56" s="96" t="n">
         <v>35.14</v>
       </c>
-      <c r="T56" s="96" t="n">
+      <c r="U56" s="96" t="n">
         <v>30.77</v>
       </c>
-      <c r="U56" s="96" t="n">
+      <c r="V56" s="96" t="n">
         <v>17.28</v>
       </c>
-      <c r="V56" s="96" t="n">
+      <c r="W56" s="96" t="n">
         <v>30.86</v>
       </c>
-      <c r="W56" s="96" t="n">
+      <c r="X56" s="96" t="n">
         <v>49.99</v>
       </c>
-      <c r="X56" s="96" t="n">
+      <c r="Y56" s="96" t="n">
         <v>33.4</v>
       </c>
-      <c r="Y56" s="96" t="n">
+      <c r="Z56" s="96" t="n">
         <v>35.24</v>
       </c>
-      <c r="Z56" s="96" t="n">
+      <c r="AA56" s="96" t="n">
         <v>31.03</v>
       </c>
-      <c r="AA56" s="96" t="n">
+      <c r="AB56" s="96" t="n">
         <v>41.42</v>
       </c>
-      <c r="AB56" s="96" t="n">
+      <c r="AC56" s="96" t="n">
         <v>58.82</v>
-      </c>
-      <c r="AC56" s="96" t="n">
-        <v>50.06</v>
       </c>
       <c r="AD56" s="96" t="n">
         <v>50.06</v>
       </c>
       <c r="AE56" s="96" t="n">
-        <v>57.25</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="57">
@@ -12502,104 +12503,104 @@
           <t>blue</t>
         </is>
       </c>
-      <c r="C57" s="95" t="inlineStr">
+      <c r="C57" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D57" s="94" t="inlineStr">
+      <c r="E57" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E57" s="94" t="inlineStr">
+      <c r="F57" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F57" s="94" t="inlineStr">
+      <c r="G57" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G57" s="94" t="inlineStr">
+      <c r="H57" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H57" s="93" t="inlineStr">
+      <c r="I57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I57" s="93" t="inlineStr">
+      <c r="J57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J57" s="93" t="inlineStr">
+      <c r="K57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K57" s="95" t="inlineStr">
+      <c r="L57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L57" s="93" t="inlineStr">
+      <c r="M57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M57" s="93" t="inlineStr">
+      <c r="N57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N57" s="94" t="inlineStr">
+      <c r="O57" s="94" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O57" s="95" t="inlineStr">
+      <c r="P57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P57" s="95" t="inlineStr">
+      <c r="Q57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q57" s="93" t="inlineStr">
+      <c r="R57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R57" s="95" t="inlineStr">
+      <c r="S57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S57" s="93" t="inlineStr">
+      <c r="T57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T57" s="93" t="inlineStr">
+      <c r="U57" s="93" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U57" s="93" t="inlineStr">
+      <c r="V57" s="93" t="inlineStr">
         <is>
           <t>green</t>
-        </is>
-      </c>
-      <c r="V57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
         </is>
       </c>
       <c r="W57" s="94" t="inlineStr">
@@ -12658,91 +12659,91 @@
         <v>-1.78</v>
       </c>
       <c r="C58" s="96" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="D58" s="96" t="n">
         <v>-0.82</v>
       </c>
-      <c r="D58" s="96" t="n">
+      <c r="E58" s="96" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E58" s="96" t="n">
+      <c r="F58" s="96" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F58" s="96" t="n">
+      <c r="G58" s="96" t="n">
         <v>-0.76</v>
       </c>
-      <c r="G58" s="96" t="n">
+      <c r="H58" s="96" t="n">
         <v>-0.26</v>
       </c>
-      <c r="H58" s="96" t="n">
+      <c r="I58" s="96" t="n">
         <v>0.29</v>
       </c>
-      <c r="I58" s="96" t="n">
+      <c r="J58" s="96" t="n">
         <v>0.08</v>
       </c>
-      <c r="J58" s="96" t="n">
+      <c r="K58" s="96" t="n">
         <v>1.86</v>
       </c>
-      <c r="K58" s="96" t="n">
+      <c r="L58" s="96" t="n">
         <v>3.87</v>
       </c>
-      <c r="L58" s="96" t="n">
+      <c r="M58" s="96" t="n">
         <v>2.38</v>
       </c>
-      <c r="M58" s="96" t="n">
+      <c r="N58" s="96" t="n">
         <v>2.97</v>
       </c>
-      <c r="N58" s="96" t="n">
+      <c r="O58" s="96" t="n">
         <v>3.3</v>
       </c>
-      <c r="O58" s="96" t="n">
+      <c r="P58" s="96" t="n">
         <v>5.11</v>
       </c>
-      <c r="P58" s="96" t="n">
+      <c r="Q58" s="96" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q58" s="96" t="n">
+      <c r="R58" s="96" t="n">
         <v>3.15</v>
       </c>
-      <c r="R58" s="96" t="n">
+      <c r="S58" s="96" t="n">
         <v>5.03</v>
       </c>
-      <c r="S58" s="96" t="n">
+      <c r="T58" s="96" t="n">
         <v>4.52</v>
       </c>
-      <c r="T58" s="96" t="n">
+      <c r="U58" s="96" t="n">
         <v>4.41</v>
       </c>
-      <c r="U58" s="96" t="n">
+      <c r="V58" s="96" t="n">
         <v>4.16</v>
       </c>
-      <c r="V58" s="96" t="n">
+      <c r="W58" s="96" t="n">
         <v>5.65</v>
       </c>
-      <c r="W58" s="96" t="n">
+      <c r="X58" s="96" t="n">
         <v>6.67</v>
       </c>
-      <c r="X58" s="96" t="n">
+      <c r="Y58" s="96" t="n">
         <v>6.48</v>
       </c>
-      <c r="Y58" s="96" t="n">
+      <c r="Z58" s="96" t="n">
         <v>7.28</v>
       </c>
-      <c r="Z58" s="96" t="n">
+      <c r="AA58" s="96" t="n">
         <v>7.24</v>
       </c>
-      <c r="AA58" s="96" t="n">
+      <c r="AB58" s="96" t="n">
         <v>7.81</v>
       </c>
-      <c r="AB58" s="96" t="n">
+      <c r="AC58" s="96" t="n">
         <v>9.640000000000001</v>
-      </c>
-      <c r="AC58" s="96" t="n">
-        <v>9.58</v>
       </c>
       <c r="AD58" s="96" t="n">
         <v>9.58</v>
       </c>
       <c r="AE58" s="96" t="n">
-        <v>9.630000000000001</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="59">
@@ -12755,91 +12756,91 @@
         <v>9.300000000000001</v>
       </c>
       <c r="C59" s="96" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D59" s="96" t="n">
         <v>10.81</v>
       </c>
-      <c r="D59" s="96" t="n">
+      <c r="E59" s="96" t="n">
         <v>8.31</v>
       </c>
-      <c r="E59" s="96" t="n">
+      <c r="F59" s="96" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="F59" s="96" t="n">
+      <c r="G59" s="96" t="n">
         <v>8.18</v>
       </c>
-      <c r="G59" s="96" t="n">
+      <c r="H59" s="96" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H59" s="96" t="n">
+      <c r="I59" s="96" t="n">
         <v>8.15</v>
       </c>
-      <c r="I59" s="96" t="n">
+      <c r="J59" s="96" t="n">
         <v>7.88</v>
       </c>
-      <c r="J59" s="96" t="n">
+      <c r="K59" s="96" t="n">
         <v>9.16</v>
       </c>
-      <c r="K59" s="96" t="n">
+      <c r="L59" s="96" t="n">
         <v>11.27</v>
       </c>
-      <c r="L59" s="96" t="n">
+      <c r="M59" s="96" t="n">
         <v>10.33</v>
       </c>
-      <c r="M59" s="96" t="n">
+      <c r="N59" s="96" t="n">
         <v>10.41</v>
       </c>
-      <c r="N59" s="96" t="n">
+      <c r="O59" s="96" t="n">
         <v>10.77</v>
       </c>
-      <c r="O59" s="96" t="n">
+      <c r="P59" s="96" t="n">
         <v>11.25</v>
       </c>
-      <c r="P59" s="96" t="n">
+      <c r="Q59" s="96" t="n">
         <v>10.63</v>
       </c>
-      <c r="Q59" s="96" t="n">
+      <c r="R59" s="96" t="n">
         <v>9.59</v>
       </c>
-      <c r="R59" s="96" t="n">
+      <c r="S59" s="96" t="n">
         <v>11.03</v>
       </c>
-      <c r="S59" s="96" t="n">
+      <c r="T59" s="96" t="n">
         <v>11.24</v>
       </c>
-      <c r="T59" s="96" t="n">
+      <c r="U59" s="96" t="n">
         <v>11.05</v>
       </c>
-      <c r="U59" s="96" t="n">
+      <c r="V59" s="96" t="n">
         <v>11.74</v>
       </c>
-      <c r="V59" s="96" t="n">
+      <c r="W59" s="96" t="n">
         <v>13.86</v>
       </c>
-      <c r="W59" s="96" t="n">
+      <c r="X59" s="96" t="n">
         <v>14.5</v>
       </c>
-      <c r="X59" s="96" t="n">
+      <c r="Y59" s="96" t="n">
         <v>15.28</v>
       </c>
-      <c r="Y59" s="96" t="n">
+      <c r="Z59" s="96" t="n">
         <v>15.62</v>
       </c>
-      <c r="Z59" s="96" t="n">
+      <c r="AA59" s="96" t="n">
         <v>16.8</v>
       </c>
-      <c r="AA59" s="96" t="n">
+      <c r="AB59" s="96" t="n">
         <v>17.29</v>
       </c>
-      <c r="AB59" s="96" t="n">
+      <c r="AC59" s="96" t="n">
         <v>17.09</v>
-      </c>
-      <c r="AC59" s="96" t="n">
-        <v>16.94</v>
       </c>
       <c r="AD59" s="96" t="n">
         <v>16.94</v>
       </c>
       <c r="AE59" s="96" t="n">
-        <v>17.43</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="60">
@@ -12852,91 +12853,91 @@
         <v>43.95</v>
       </c>
       <c r="C60" s="96" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="D60" s="96" t="n">
         <v>61.3</v>
       </c>
-      <c r="D60" s="96" t="n">
+      <c r="E60" s="96" t="n">
         <v>45.16</v>
       </c>
-      <c r="E60" s="96" t="n">
+      <c r="F60" s="96" t="n">
         <v>54.74</v>
       </c>
-      <c r="F60" s="96" t="n">
+      <c r="G60" s="96" t="n">
         <v>32.74</v>
       </c>
-      <c r="G60" s="96" t="n">
+      <c r="H60" s="96" t="n">
         <v>37.44</v>
       </c>
-      <c r="H60" s="96" t="n">
+      <c r="I60" s="96" t="n">
         <v>29.94</v>
       </c>
-      <c r="I60" s="96" t="n">
+      <c r="J60" s="96" t="n">
         <v>22.73</v>
       </c>
-      <c r="J60" s="96" t="n">
+      <c r="K60" s="96" t="n">
         <v>32.82</v>
       </c>
-      <c r="K60" s="96" t="n">
+      <c r="L60" s="96" t="n">
         <v>60.89</v>
       </c>
-      <c r="L60" s="96" t="n">
+      <c r="M60" s="96" t="n">
         <v>27.8</v>
       </c>
-      <c r="M60" s="96" t="n">
+      <c r="N60" s="96" t="n">
         <v>39.93</v>
       </c>
-      <c r="N60" s="96" t="n">
+      <c r="O60" s="96" t="n">
         <v>47.73</v>
       </c>
-      <c r="O60" s="96" t="n">
+      <c r="P60" s="96" t="n">
         <v>61.52</v>
       </c>
-      <c r="P60" s="96" t="n">
+      <c r="Q60" s="96" t="n">
         <v>53.4</v>
       </c>
-      <c r="Q60" s="96" t="n">
+      <c r="R60" s="96" t="n">
         <v>28.17</v>
       </c>
-      <c r="R60" s="96" t="n">
+      <c r="S60" s="96" t="n">
         <v>54.46</v>
       </c>
-      <c r="S60" s="96" t="n">
+      <c r="T60" s="96" t="n">
         <v>26.44</v>
       </c>
-      <c r="T60" s="96" t="n">
+      <c r="U60" s="96" t="n">
         <v>26.09</v>
       </c>
-      <c r="U60" s="96" t="n">
+      <c r="V60" s="96" t="n">
         <v>20.17</v>
       </c>
-      <c r="V60" s="96" t="n">
+      <c r="W60" s="96" t="n">
         <v>42.28</v>
       </c>
-      <c r="W60" s="96" t="n">
+      <c r="X60" s="96" t="n">
         <v>69.20999999999999</v>
       </c>
-      <c r="X60" s="96" t="n">
+      <c r="Y60" s="96" t="n">
         <v>48.57</v>
       </c>
-      <c r="Y60" s="96" t="n">
+      <c r="Z60" s="96" t="n">
         <v>47.91</v>
       </c>
-      <c r="Z60" s="96" t="n">
+      <c r="AA60" s="96" t="n">
         <v>45.04</v>
       </c>
-      <c r="AA60" s="96" t="n">
+      <c r="AB60" s="96" t="n">
         <v>54.46</v>
       </c>
-      <c r="AB60" s="96" t="n">
+      <c r="AC60" s="96" t="n">
         <v>63.48</v>
-      </c>
-      <c r="AC60" s="96" t="n">
-        <v>54.91</v>
       </c>
       <c r="AD60" s="96" t="n">
         <v>54.91</v>
       </c>
       <c r="AE60" s="96" t="n">
-        <v>60.6</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="61">
@@ -12949,104 +12950,104 @@
         <v>43.81</v>
       </c>
       <c r="C61" s="96" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="D61" s="96" t="n">
         <v>54.16</v>
       </c>
-      <c r="D61" s="96" t="n">
+      <c r="E61" s="96" t="n">
         <v>43.01</v>
       </c>
-      <c r="E61" s="96" t="n">
+      <c r="F61" s="96" t="n">
         <v>48.51</v>
       </c>
-      <c r="F61" s="96" t="n">
+      <c r="G61" s="96" t="n">
         <v>34.07</v>
       </c>
-      <c r="G61" s="96" t="n">
+      <c r="H61" s="96" t="n">
         <v>37.04</v>
       </c>
-      <c r="H61" s="96" t="n">
+      <c r="I61" s="96" t="n">
         <v>32.12</v>
       </c>
-      <c r="I61" s="96" t="n">
+      <c r="J61" s="96" t="n">
         <v>27.2</v>
       </c>
-      <c r="J61" s="96" t="n">
+      <c r="K61" s="96" t="n">
         <v>35.83</v>
       </c>
-      <c r="K61" s="96" t="n">
+      <c r="L61" s="96" t="n">
         <v>56.49</v>
       </c>
-      <c r="L61" s="96" t="n">
+      <c r="M61" s="96" t="n">
         <v>33.73</v>
       </c>
-      <c r="M61" s="96" t="n">
+      <c r="N61" s="96" t="n">
         <v>42.63</v>
       </c>
-      <c r="N61" s="96" t="n">
+      <c r="O61" s="96" t="n">
         <v>47.89</v>
       </c>
-      <c r="O61" s="96" t="n">
+      <c r="P61" s="96" t="n">
         <v>56.82</v>
       </c>
-      <c r="P61" s="96" t="n">
+      <c r="Q61" s="96" t="n">
         <v>50.65</v>
       </c>
-      <c r="Q61" s="96" t="n">
+      <c r="R61" s="96" t="n">
         <v>32.93</v>
       </c>
-      <c r="R61" s="96" t="n">
+      <c r="S61" s="96" t="n">
         <v>51.12</v>
       </c>
-      <c r="S61" s="96" t="n">
+      <c r="T61" s="96" t="n">
         <v>34.78</v>
       </c>
-      <c r="T61" s="96" t="n">
+      <c r="U61" s="96" t="n">
         <v>34.59</v>
       </c>
-      <c r="U61" s="96" t="n">
+      <c r="V61" s="96" t="n">
         <v>31.17</v>
       </c>
-      <c r="V61" s="96" t="n">
+      <c r="W61" s="96" t="n">
         <v>50.2</v>
       </c>
-      <c r="W61" s="96" t="n">
+      <c r="X61" s="96" t="n">
         <v>66.11</v>
       </c>
-      <c r="X61" s="96" t="n">
+      <c r="Y61" s="96" t="n">
         <v>56.44</v>
       </c>
-      <c r="Y61" s="96" t="n">
+      <c r="Z61" s="96" t="n">
         <v>56.18</v>
       </c>
-      <c r="Z61" s="96" t="n">
+      <c r="AA61" s="96" t="n">
         <v>54.96</v>
       </c>
-      <c r="AA61" s="96" t="n">
+      <c r="AB61" s="96" t="n">
         <v>60.91</v>
       </c>
-      <c r="AB61" s="96" t="n">
+      <c r="AC61" s="96" t="n">
         <v>66.34</v>
-      </c>
-      <c r="AC61" s="96" t="n">
-        <v>62.02</v>
       </c>
       <c r="AD61" s="96" t="n">
         <v>62.02</v>
       </c>
       <c r="AE61" s="96" t="n">
-        <v>65.76000000000001</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI11:21.95&lt;=27;sh:RSI2:1.4&lt;=7;kc:RSI5:16.13&lt;=21;vn:RSI3:17.75&lt;=25</t>
+          <t>今日买报：sh:RSI11:20.66&lt;=27;sh:RSI2:0.92&lt;=7;kc:RSI5:15.25&lt;=21;vn:RSI3:17.75&lt;=25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：</t>
+          <t>今日卖报：jp225:RSI5:78.16&gt;=74</t>
         </is>
       </c>
     </row>
@@ -16702,13 +16703,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="98" t="n">
+      <c r="H2" s="99" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="99">
+      <c r="J2" s="100">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16739,13 +16740,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="98" t="n">
+      <c r="H3" s="99" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="99">
+      <c r="J3" s="100">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16776,13 +16777,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="98" t="n">
+      <c r="H4" s="99" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="99">
+      <c r="J4" s="100">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16813,13 +16814,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="98" t="n">
+      <c r="H5" s="99" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="100">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16850,13 +16851,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="100" t="n">
+      <c r="H6" s="101" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="99">
+      <c r="J6" s="100">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16887,13 +16888,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="98" t="n">
+      <c r="H7" s="99" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="99">
+      <c r="J7" s="100">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16924,13 +16925,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="100" t="n">
+      <c r="H8" s="101" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="99">
+      <c r="J8" s="100">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16961,13 +16962,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="100" t="n">
+      <c r="H9" s="101" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="100">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16998,13 +16999,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="100" t="n">
+      <c r="H10" s="101" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17035,13 +17036,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="102" t="n">
+      <c r="H11" s="103" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="104">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17072,13 +17073,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="100" t="n">
+      <c r="H12" s="101" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="101">
+      <c r="J12" s="102">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17109,13 +17110,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="102" t="n">
+      <c r="H13" s="103" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="104">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17146,13 +17147,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="100" t="n">
+      <c r="H14" s="101" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="101">
+      <c r="J14" s="102">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17183,13 +17184,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="102" t="n">
+      <c r="H15" s="103" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="104">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17220,13 +17221,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="100" t="n">
+      <c r="H16" s="101" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="101">
+      <c r="J16" s="102">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17257,13 +17258,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="102" t="n">
+      <c r="H17" s="103" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="104">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17294,13 +17295,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="100" t="n">
+      <c r="H18" s="101" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="101">
+      <c r="J18" s="102">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17331,13 +17332,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="102" t="n">
+      <c r="H19" s="103" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="104">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17368,13 +17369,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="100" t="n">
+      <c r="H20" s="101" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="101">
+      <c r="J20" s="102">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17405,13 +17406,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="102" t="n">
+      <c r="H21" s="103" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="103">
+      <c r="J21" s="104">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17440,13 +17441,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="104" t="n">
+      <c r="H22" s="105" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="102">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17475,13 +17476,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="105" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="102">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17510,13 +17511,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="100" t="n">
+      <c r="H24" s="101" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="101">
+      <c r="J24" s="102">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17545,13 +17546,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="100" t="n">
+      <c r="H25" s="101" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="101">
+      <c r="J25" s="102">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17580,13 +17581,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="100" t="n">
+      <c r="H26" s="101" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="101">
+      <c r="J26" s="102">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17615,13 +17616,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="100" t="n">
+      <c r="H27" s="101" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="101">
+      <c r="J27" s="102">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17650,13 +17651,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="104" t="n">
+      <c r="H28" s="105" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="101">
+      <c r="J28" s="102">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17685,13 +17686,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="105" t="n">
+      <c r="H29" s="106" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="103">
+      <c r="J29" s="104">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17720,13 +17721,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="104" t="n">
+      <c r="H30" s="105" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="101">
+      <c r="J30" s="102">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17755,13 +17756,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="105" t="n">
+      <c r="H31" s="106" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="103">
+      <c r="J31" s="104">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17790,13 +17791,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="104" t="n">
+      <c r="H32" s="105" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="101">
+      <c r="J32" s="102">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17825,13 +17826,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="105" t="n">
+      <c r="H33" s="106" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="103">
+      <c r="J33" s="104">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17860,13 +17861,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="105" t="n">
+      <c r="H34" s="106" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="103">
+      <c r="J34" s="104">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17895,13 +17896,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="104" t="n">
+      <c r="H35" s="105" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="101">
+      <c r="J35" s="102">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17930,13 +17931,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="105" t="n">
+      <c r="H36" s="106" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="103">
+      <c r="J36" s="104">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17965,13 +17966,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="104" t="n">
+      <c r="H37" s="105" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="101">
+      <c r="J37" s="102">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18000,13 +18001,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="104" t="n">
+      <c r="H38" s="105" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="101">
+      <c r="J38" s="102">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18035,13 +18036,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="105" t="n">
+      <c r="H39" s="106" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="103">
+      <c r="J39" s="104">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -480,12 +480,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000ff00"/>
+        <fgColor rgb="000000ff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000ff"/>
+        <fgColor rgb="0000ff00"/>
       </patternFill>
     </fill>
     <fill>
@@ -794,7 +794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,8 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1450,152 +1449,152 @@
       </c>
       <c r="B1" s="79" t="inlineStr">
         <is>
+          <t>240626</t>
+        </is>
+      </c>
+      <c r="C1" s="79" t="inlineStr">
+        <is>
           <t>240625</t>
         </is>
       </c>
-      <c r="C1" s="79" t="inlineStr">
+      <c r="D1" s="79" t="inlineStr">
         <is>
           <t>240624</t>
         </is>
       </c>
-      <c r="D1" s="79" t="inlineStr">
+      <c r="E1" s="79" t="inlineStr">
         <is>
           <t>240621</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="F1" s="79" t="inlineStr">
         <is>
           <t>240620</t>
         </is>
       </c>
-      <c r="F1" s="79" t="inlineStr">
+      <c r="G1" s="79" t="inlineStr">
         <is>
           <t>240619</t>
         </is>
       </c>
-      <c r="G1" s="79" t="inlineStr">
+      <c r="H1" s="79" t="inlineStr">
         <is>
           <t>240618</t>
         </is>
       </c>
-      <c r="H1" s="79" t="inlineStr">
+      <c r="I1" s="79" t="inlineStr">
         <is>
           <t>240617</t>
         </is>
       </c>
-      <c r="I1" s="79" t="inlineStr">
+      <c r="J1" s="79" t="inlineStr">
         <is>
           <t>240614</t>
         </is>
       </c>
-      <c r="J1" s="79" t="inlineStr">
+      <c r="K1" s="79" t="inlineStr">
         <is>
           <t>240613</t>
         </is>
       </c>
-      <c r="K1" s="79" t="inlineStr">
+      <c r="L1" s="79" t="inlineStr">
         <is>
           <t>240612</t>
         </is>
       </c>
-      <c r="L1" s="79" t="inlineStr">
+      <c r="M1" s="79" t="inlineStr">
         <is>
           <t>240611</t>
         </is>
       </c>
-      <c r="M1" s="79" t="inlineStr">
+      <c r="N1" s="79" t="inlineStr">
         <is>
           <t>240607</t>
         </is>
       </c>
-      <c r="N1" s="79" t="inlineStr">
+      <c r="O1" s="79" t="inlineStr">
         <is>
           <t>240606</t>
         </is>
       </c>
-      <c r="O1" s="79" t="inlineStr">
+      <c r="P1" s="79" t="inlineStr">
         <is>
           <t>240605</t>
         </is>
       </c>
-      <c r="P1" s="79" t="inlineStr">
+      <c r="Q1" s="79" t="inlineStr">
         <is>
           <t>240604</t>
         </is>
       </c>
-      <c r="Q1" s="79" t="inlineStr">
+      <c r="R1" s="79" t="inlineStr">
         <is>
           <t>240603</t>
         </is>
       </c>
-      <c r="R1" s="79" t="inlineStr">
+      <c r="S1" s="79" t="inlineStr">
         <is>
           <t>240531</t>
         </is>
       </c>
-      <c r="S1" s="79" t="inlineStr">
+      <c r="T1" s="79" t="inlineStr">
         <is>
           <t>240530</t>
         </is>
       </c>
-      <c r="T1" s="79" t="inlineStr">
+      <c r="U1" s="79" t="inlineStr">
         <is>
           <t>240529</t>
         </is>
       </c>
-      <c r="U1" s="79" t="inlineStr">
+      <c r="V1" s="79" t="inlineStr">
         <is>
           <t>240528</t>
         </is>
       </c>
-      <c r="V1" s="79" t="inlineStr">
+      <c r="W1" s="79" t="inlineStr">
         <is>
           <t>240527</t>
         </is>
       </c>
-      <c r="W1" s="79" t="inlineStr">
+      <c r="X1" s="79" t="inlineStr">
         <is>
           <t>240524</t>
         </is>
       </c>
-      <c r="X1" s="79" t="inlineStr">
+      <c r="Y1" s="79" t="inlineStr">
         <is>
           <t>240523</t>
         </is>
       </c>
-      <c r="Y1" s="79" t="inlineStr">
+      <c r="Z1" s="79" t="inlineStr">
         <is>
           <t>240522</t>
         </is>
       </c>
-      <c r="Z1" s="79" t="inlineStr">
+      <c r="AA1" s="79" t="inlineStr">
         <is>
           <t>240521</t>
         </is>
       </c>
-      <c r="AA1" s="79" t="inlineStr">
+      <c r="AB1" s="79" t="inlineStr">
         <is>
           <t>240520</t>
         </is>
       </c>
-      <c r="AB1" s="79" t="inlineStr">
+      <c r="AC1" s="79" t="inlineStr">
         <is>
           <t>240517</t>
         </is>
       </c>
-      <c r="AC1" s="79" t="inlineStr">
+      <c r="AD1" s="79" t="inlineStr">
         <is>
           <t>240516</t>
         </is>
       </c>
-      <c r="AD1" s="79" t="inlineStr">
+      <c r="AE1" s="79" t="inlineStr">
         <is>
           <t>240515</t>
-        </is>
-      </c>
-      <c r="AE1" s="79" t="inlineStr">
-        <is>
-          <t>240514</t>
         </is>
       </c>
     </row>
@@ -1606,94 +1605,94 @@
         </is>
       </c>
       <c r="B2" s="80" t="n">
+        <v>2972.53</v>
+      </c>
+      <c r="C2" s="80" t="n">
         <v>2950</v>
       </c>
-      <c r="C2" s="80" t="n">
+      <c r="D2" s="80" t="n">
         <v>2963.1</v>
       </c>
-      <c r="D2" s="80" t="n">
+      <c r="E2" s="80" t="n">
         <v>2998.14</v>
       </c>
-      <c r="E2" s="80" t="n">
+      <c r="F2" s="80" t="n">
         <v>3005.44</v>
       </c>
-      <c r="F2" s="80" t="n">
+      <c r="G2" s="80" t="n">
         <v>3018.05</v>
       </c>
-      <c r="G2" s="80" t="n">
+      <c r="H2" s="80" t="n">
         <v>3030.25</v>
       </c>
-      <c r="H2" s="80" t="n">
+      <c r="I2" s="80" t="n">
         <v>3015.89</v>
       </c>
-      <c r="I2" s="80" t="n">
+      <c r="J2" s="80" t="n">
         <v>3032.63</v>
       </c>
-      <c r="J2" s="80" t="n">
+      <c r="K2" s="80" t="n">
         <v>3028.92</v>
       </c>
-      <c r="K2" s="80" t="n">
+      <c r="L2" s="80" t="n">
         <v>3037.47</v>
       </c>
-      <c r="L2" s="80" t="n">
+      <c r="M2" s="80" t="n">
         <v>3028.05</v>
       </c>
-      <c r="M2" s="80" t="n">
+      <c r="N2" s="80" t="n">
         <v>3051.28</v>
       </c>
-      <c r="N2" s="80" t="n">
+      <c r="O2" s="80" t="n">
         <v>3048.79</v>
       </c>
-      <c r="O2" s="80" t="n">
+      <c r="P2" s="80" t="n">
         <v>3065.4</v>
       </c>
-      <c r="P2" s="80" t="n">
+      <c r="Q2" s="80" t="n">
         <v>3091.2</v>
       </c>
-      <c r="Q2" s="80" t="n">
+      <c r="R2" s="80" t="n">
         <v>3078.49</v>
       </c>
-      <c r="R2" s="80" t="n">
+      <c r="S2" s="80" t="n">
         <v>3086.81</v>
       </c>
-      <c r="S2" s="80" t="n">
+      <c r="T2" s="80" t="n">
         <v>3091.68</v>
       </c>
-      <c r="T2" s="80" t="n">
+      <c r="U2" s="80" t="n">
         <v>3111.02</v>
       </c>
-      <c r="U2" s="80" t="n">
+      <c r="V2" s="80" t="n">
         <v>3109.57</v>
       </c>
-      <c r="V2" s="80" t="n">
+      <c r="W2" s="80" t="n">
         <v>3124.04</v>
       </c>
-      <c r="W2" s="80" t="n">
+      <c r="X2" s="80" t="n">
         <v>3088.87</v>
       </c>
-      <c r="X2" s="80" t="n">
+      <c r="Y2" s="80" t="n">
         <v>3116.39</v>
       </c>
-      <c r="Y2" s="80" t="n">
+      <c r="Z2" s="80" t="n">
         <v>3158.54</v>
       </c>
-      <c r="Z2" s="80" t="n">
+      <c r="AA2" s="80" t="n">
         <v>3157.97</v>
       </c>
-      <c r="AA2" s="80" t="n">
+      <c r="AB2" s="80" t="n">
         <v>3171.15</v>
       </c>
-      <c r="AB2" s="80" t="n">
+      <c r="AC2" s="80" t="n">
         <v>3154.03</v>
       </c>
-      <c r="AC2" s="80" t="n">
+      <c r="AD2" s="80" t="n">
         <v>3122.4</v>
       </c>
-      <c r="AD2" s="80" t="n">
+      <c r="AE2" s="80" t="n">
         <v>3119.9</v>
-      </c>
-      <c r="AE2" s="80" t="n">
-        <v>3145.77</v>
       </c>
     </row>
     <row r="3">
@@ -1704,150 +1703,150 @@
       </c>
       <c r="B3" s="81" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C3" s="82" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="D3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D3" s="82" t="inlineStr">
+      <c r="E3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E3" s="82" t="inlineStr">
+      <c r="F3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F3" s="82" t="inlineStr">
+      <c r="G3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G3" s="82" t="inlineStr">
+      <c r="H3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H3" s="82" t="inlineStr">
+      <c r="I3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I3" s="82" t="inlineStr">
+      <c r="J3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J3" s="82" t="inlineStr">
+      <c r="K3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K3" s="82" t="inlineStr">
+      <c r="L3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L3" s="81" t="inlineStr">
+      <c r="M3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M3" s="82" t="inlineStr">
+      <c r="N3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N3" s="81" t="inlineStr">
+      <c r="O3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O3" s="81" t="inlineStr">
+      <c r="P3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P3" s="82" t="inlineStr">
+      <c r="Q3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q3" s="81" t="inlineStr">
+      <c r="R3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R3" s="81" t="inlineStr">
+      <c r="S3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S3" s="81" t="inlineStr">
+      <c r="T3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="T3" s="81" t="inlineStr">
+      <c r="U3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U3" s="81" t="inlineStr">
+      <c r="V3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V3" s="81" t="inlineStr">
+      <c r="W3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W3" s="81" t="inlineStr">
+      <c r="X3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X3" s="81" t="inlineStr">
+      <c r="Y3" s="82" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y3" s="82" t="inlineStr">
+      <c r="Z3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z3" s="82" t="inlineStr">
+      <c r="AA3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA3" s="83" t="inlineStr">
+      <c r="AB3" s="83" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB3" s="83" t="inlineStr">
+      <c r="AC3" s="83" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC3" s="82" t="inlineStr">
+      <c r="AD3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD3" s="82" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE3" s="82" t="inlineStr">
+      <c r="AE3" s="81" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -1860,94 +1859,94 @@
         </is>
       </c>
       <c r="B4" s="80" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C4" s="80" t="n">
         <v>-0.44</v>
       </c>
-      <c r="C4" s="80" t="n">
+      <c r="D4" s="80" t="n">
         <v>-1.17</v>
       </c>
-      <c r="D4" s="80" t="n">
+      <c r="E4" s="80" t="n">
         <v>-0.24</v>
       </c>
-      <c r="E4" s="80" t="n">
+      <c r="F4" s="80" t="n">
         <v>-0.42</v>
       </c>
-      <c r="F4" s="80" t="n">
+      <c r="G4" s="80" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G4" s="80" t="n">
+      <c r="H4" s="80" t="n">
         <v>0.48</v>
       </c>
-      <c r="H4" s="80" t="n">
+      <c r="I4" s="80" t="n">
         <v>-0.55</v>
       </c>
-      <c r="I4" s="80" t="n">
+      <c r="J4" s="80" t="n">
         <v>0.12</v>
       </c>
-      <c r="J4" s="80" t="n">
+      <c r="K4" s="80" t="n">
         <v>-0.28</v>
       </c>
-      <c r="K4" s="80" t="n">
+      <c r="L4" s="80" t="n">
         <v>0.31</v>
       </c>
-      <c r="L4" s="80" t="n">
+      <c r="M4" s="80" t="n">
         <v>-0.76</v>
       </c>
-      <c r="M4" s="80" t="n">
+      <c r="N4" s="80" t="n">
         <v>0.08</v>
       </c>
-      <c r="N4" s="80" t="n">
+      <c r="O4" s="80" t="n">
         <v>-0.54</v>
       </c>
-      <c r="O4" s="80" t="n">
+      <c r="P4" s="80" t="n">
         <v>-0.83</v>
       </c>
-      <c r="P4" s="80" t="n">
+      <c r="Q4" s="80" t="n">
         <v>0.41</v>
       </c>
-      <c r="Q4" s="80" t="n">
+      <c r="R4" s="80" t="n">
         <v>-0.27</v>
       </c>
-      <c r="R4" s="80" t="n">
+      <c r="S4" s="80" t="n">
         <v>-0.16</v>
       </c>
-      <c r="S4" s="80" t="n">
+      <c r="T4" s="80" t="n">
         <v>-0.62</v>
       </c>
-      <c r="T4" s="80" t="n">
+      <c r="U4" s="80" t="n">
         <v>0.05</v>
       </c>
-      <c r="U4" s="80" t="n">
+      <c r="V4" s="80" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V4" s="80" t="n">
+      <c r="W4" s="80" t="n">
         <v>1.14</v>
       </c>
-      <c r="W4" s="80" t="n">
+      <c r="X4" s="80" t="n">
         <v>-0.88</v>
       </c>
-      <c r="X4" s="80" t="n">
+      <c r="Y4" s="80" t="n">
         <v>-1.33</v>
       </c>
-      <c r="Y4" s="80" t="n">
+      <c r="Z4" s="80" t="n">
         <v>0.02</v>
       </c>
-      <c r="Z4" s="80" t="n">
+      <c r="AA4" s="80" t="n">
         <v>-0.42</v>
       </c>
-      <c r="AA4" s="80" t="n">
+      <c r="AB4" s="80" t="n">
         <v>0.54</v>
       </c>
-      <c r="AB4" s="80" t="n">
+      <c r="AC4" s="80" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC4" s="80" t="n">
+      <c r="AD4" s="80" t="n">
         <v>0.08</v>
       </c>
-      <c r="AD4" s="80" t="n">
+      <c r="AE4" s="80" t="n">
         <v>-0.82</v>
-      </c>
-      <c r="AE4" s="80" t="n">
-        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1957,94 +1956,94 @@
         </is>
       </c>
       <c r="B5" s="80" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="C5" s="80" t="n">
         <v>-2.52</v>
       </c>
-      <c r="C5" s="80" t="n">
+      <c r="D5" s="80" t="n">
         <v>-2.79</v>
       </c>
-      <c r="D5" s="80" t="n">
+      <c r="E5" s="80" t="n">
         <v>-2.57</v>
       </c>
-      <c r="E5" s="80" t="n">
+      <c r="F5" s="80" t="n">
         <v>-2.41</v>
       </c>
-      <c r="F5" s="80" t="n">
+      <c r="G5" s="80" t="n">
         <v>-1.46</v>
       </c>
-      <c r="G5" s="80" t="n">
+      <c r="H5" s="80" t="n">
         <v>-1.77</v>
       </c>
-      <c r="H5" s="80" t="n">
+      <c r="I5" s="80" t="n">
         <v>-1.27</v>
       </c>
-      <c r="I5" s="80" t="n">
+      <c r="J5" s="80" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J5" s="80" t="n">
+      <c r="K5" s="80" t="n">
         <v>-0.49</v>
       </c>
-      <c r="K5" s="80" t="n">
+      <c r="L5" s="80" t="n">
         <v>-0.6</v>
       </c>
-      <c r="L5" s="80" t="n">
+      <c r="M5" s="80" t="n">
         <v>-1.32</v>
       </c>
-      <c r="M5" s="80" t="n">
+      <c r="N5" s="80" t="n">
         <v>0.17</v>
       </c>
-      <c r="N5" s="80" t="n">
+      <c r="O5" s="80" t="n">
         <v>0.71</v>
       </c>
-      <c r="O5" s="80" t="n">
+      <c r="P5" s="80" t="n">
         <v>0.84</v>
       </c>
-      <c r="P5" s="80" t="n">
+      <c r="Q5" s="80" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q5" s="80" t="n">
+      <c r="R5" s="80" t="n">
         <v>1.29</v>
       </c>
-      <c r="R5" s="80" t="n">
+      <c r="S5" s="80" t="n">
         <v>1.98</v>
       </c>
-      <c r="S5" s="80" t="n">
+      <c r="T5" s="80" t="n">
         <v>2.54</v>
       </c>
-      <c r="T5" s="80" t="n">
+      <c r="U5" s="80" t="n">
         <v>5.18</v>
       </c>
-      <c r="U5" s="80" t="n">
+      <c r="V5" s="80" t="n">
         <v>3.12</v>
       </c>
-      <c r="V5" s="80" t="n">
+      <c r="W5" s="80" t="n">
         <v>4.94</v>
       </c>
-      <c r="W5" s="80" t="n">
+      <c r="X5" s="80" t="n">
         <v>2.8</v>
       </c>
-      <c r="X5" s="80" t="n">
+      <c r="Y5" s="80" t="n">
         <v>4.28</v>
       </c>
-      <c r="Y5" s="80" t="n">
+      <c r="Z5" s="80" t="n">
         <v>7.03</v>
       </c>
-      <c r="Z5" s="80" t="n">
+      <c r="AA5" s="80" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="AA5" s="80" t="n">
+      <c r="AB5" s="80" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="AB5" s="80" t="n">
+      <c r="AC5" s="80" t="n">
         <v>10.05</v>
       </c>
-      <c r="AC5" s="80" t="n">
+      <c r="AD5" s="80" t="n">
         <v>10.34</v>
       </c>
-      <c r="AD5" s="80" t="n">
+      <c r="AE5" s="80" t="n">
         <v>11.84</v>
-      </c>
-      <c r="AE5" s="80" t="n">
-        <v>16.42</v>
       </c>
     </row>
     <row r="6">
@@ -2054,94 +2053,94 @@
         </is>
       </c>
       <c r="B6" s="80" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C6" s="80" t="n">
         <v>1.07</v>
       </c>
-      <c r="C6" s="80" t="n">
+      <c r="D6" s="80" t="n">
         <v>2.1</v>
       </c>
-      <c r="D6" s="80" t="n">
+      <c r="E6" s="80" t="n">
         <v>2.24</v>
       </c>
-      <c r="E6" s="80" t="n">
+      <c r="F6" s="80" t="n">
         <v>2.55</v>
       </c>
-      <c r="F6" s="80" t="n">
+      <c r="G6" s="80" t="n">
         <v>2.57</v>
       </c>
-      <c r="G6" s="80" t="n">
+      <c r="H6" s="80" t="n">
         <v>2.41</v>
       </c>
-      <c r="H6" s="80" t="n">
+      <c r="I6" s="80" t="n">
         <v>1.59</v>
       </c>
-      <c r="I6" s="80" t="n">
+      <c r="J6" s="80" t="n">
         <v>0.97</v>
       </c>
-      <c r="J6" s="80" t="n">
+      <c r="K6" s="80" t="n">
         <v>1.25</v>
       </c>
-      <c r="K6" s="80" t="n">
+      <c r="L6" s="80" t="n">
         <v>2.29</v>
       </c>
-      <c r="L6" s="80" t="n">
+      <c r="M6" s="80" t="n">
         <v>2.08</v>
       </c>
-      <c r="M6" s="80" t="n">
+      <c r="N6" s="80" t="n">
         <v>2.77</v>
       </c>
-      <c r="N6" s="80" t="n">
+      <c r="O6" s="80" t="n">
         <v>2.57</v>
       </c>
-      <c r="O6" s="80" t="n">
+      <c r="P6" s="80" t="n">
         <v>1.41</v>
       </c>
-      <c r="P6" s="80" t="n">
+      <c r="Q6" s="80" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q6" s="80" t="n">
+      <c r="R6" s="80" t="n">
         <v>1.61</v>
       </c>
-      <c r="R6" s="80" t="n">
+      <c r="S6" s="80" t="n">
         <v>2.16</v>
       </c>
-      <c r="S6" s="80" t="n">
+      <c r="T6" s="80" t="n">
         <v>1.75</v>
       </c>
-      <c r="T6" s="80" t="n">
+      <c r="U6" s="80" t="n">
         <v>2.62</v>
       </c>
-      <c r="U6" s="80" t="n">
+      <c r="V6" s="80" t="n">
         <v>2.26</v>
       </c>
-      <c r="V6" s="80" t="n">
+      <c r="W6" s="80" t="n">
         <v>2.03</v>
       </c>
-      <c r="W6" s="80" t="n">
+      <c r="X6" s="80" t="n">
         <v>1.49</v>
       </c>
-      <c r="X6" s="80" t="n">
+      <c r="Y6" s="80" t="n">
         <v>1.58</v>
       </c>
-      <c r="Y6" s="80" t="n">
+      <c r="Z6" s="80" t="n">
         <v>2.94</v>
       </c>
-      <c r="Z6" s="80" t="n">
+      <c r="AA6" s="80" t="n">
         <v>3.39</v>
       </c>
-      <c r="AA6" s="80" t="n">
+      <c r="AB6" s="80" t="n">
         <v>3.94</v>
       </c>
-      <c r="AB6" s="80" t="n">
+      <c r="AC6" s="80" t="n">
         <v>2.64</v>
       </c>
-      <c r="AC6" s="80" t="n">
+      <c r="AD6" s="80" t="n">
         <v>2.17</v>
       </c>
-      <c r="AD6" s="80" t="n">
+      <c r="AE6" s="80" t="n">
         <v>2.41</v>
-      </c>
-      <c r="AE6" s="80" t="n">
-        <v>3.51</v>
       </c>
     </row>
     <row r="7">
@@ -2151,94 +2150,94 @@
         </is>
       </c>
       <c r="B7" s="80" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C7" s="80" t="n">
         <v>0.99</v>
       </c>
-      <c r="C7" s="80" t="n">
+      <c r="D7" s="80" t="n">
         <v>1.06</v>
       </c>
-      <c r="D7" s="80" t="n">
+      <c r="E7" s="80" t="n">
         <v>0.93</v>
       </c>
-      <c r="E7" s="80" t="n">
+      <c r="F7" s="80" t="n">
         <v>1.09</v>
       </c>
-      <c r="F7" s="80" t="n">
+      <c r="G7" s="80" t="n">
         <v>1.05</v>
       </c>
-      <c r="G7" s="80" t="n">
+      <c r="H7" s="80" t="n">
         <v>1.09</v>
       </c>
-      <c r="H7" s="80" t="n">
+      <c r="I7" s="80" t="n">
         <v>1.12</v>
       </c>
-      <c r="I7" s="80" t="n">
+      <c r="J7" s="80" t="n">
         <v>1.26</v>
       </c>
-      <c r="J7" s="80" t="n">
+      <c r="K7" s="80" t="n">
         <v>1.12</v>
       </c>
-      <c r="K7" s="80" t="n">
+      <c r="L7" s="80" t="n">
         <v>1.03</v>
       </c>
-      <c r="L7" s="80" t="n">
+      <c r="M7" s="80" t="n">
         <v>1.05</v>
       </c>
-      <c r="M7" s="80" t="n">
+      <c r="N7" s="80" t="n">
         <v>1.07</v>
       </c>
-      <c r="N7" s="80" t="n">
+      <c r="O7" s="80" t="n">
         <v>1.26</v>
       </c>
-      <c r="O7" s="80" t="n">
+      <c r="P7" s="80" t="n">
         <v>1.02</v>
       </c>
-      <c r="P7" s="80" t="n">
+      <c r="Q7" s="80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R7" s="80" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S7" s="80" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T7" s="80" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U7" s="80" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V7" s="80" t="n">
         <v>1.09</v>
       </c>
-      <c r="Q7" s="80" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R7" s="80" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S7" s="80" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="T7" s="80" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U7" s="80" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V7" s="80" t="n">
+      <c r="W7" s="80" t="n">
         <v>1.13</v>
       </c>
-      <c r="W7" s="80" t="n">
+      <c r="X7" s="80" t="n">
         <v>1.12</v>
       </c>
-      <c r="X7" s="80" t="n">
+      <c r="Y7" s="80" t="n">
         <v>1.24</v>
       </c>
-      <c r="Y7" s="80" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z7" s="80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA7" s="80" t="n">
         <v>1.15</v>
       </c>
-      <c r="AA7" s="80" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AB7" s="80" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC7" s="80" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC7" s="80" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AD7" s="80" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" s="80" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AE7" s="80" t="n">
-        <v>1.19</v>
       </c>
     </row>
     <row r="8">
@@ -2248,94 +2247,94 @@
         </is>
       </c>
       <c r="B8" s="80" t="n">
+        <v>6433.85</v>
+      </c>
+      <c r="C8" s="80" t="n">
         <v>6481.95</v>
       </c>
-      <c r="C8" s="80" t="n">
+      <c r="D8" s="80" t="n">
         <v>6956.13</v>
       </c>
-      <c r="D8" s="80" t="n">
+      <c r="E8" s="80" t="n">
         <v>6195.98</v>
       </c>
-      <c r="E8" s="80" t="n">
+      <c r="F8" s="80" t="n">
         <v>7243.93</v>
       </c>
-      <c r="F8" s="80" t="n">
+      <c r="G8" s="80" t="n">
         <v>7047.49</v>
       </c>
-      <c r="G8" s="80" t="n">
+      <c r="H8" s="80" t="n">
         <v>7370.33</v>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="I8" s="80" t="n">
         <v>7516.07</v>
       </c>
-      <c r="I8" s="80" t="n">
+      <c r="J8" s="80" t="n">
         <v>8480.950000000001</v>
       </c>
-      <c r="J8" s="80" t="n">
+      <c r="K8" s="80" t="n">
         <v>7524.83</v>
       </c>
-      <c r="K8" s="80" t="n">
+      <c r="L8" s="80" t="n">
         <v>6919.21</v>
       </c>
-      <c r="L8" s="80" t="n">
+      <c r="M8" s="80" t="n">
         <v>7029.28</v>
       </c>
-      <c r="M8" s="80" t="n">
+      <c r="N8" s="80" t="n">
         <v>7168.32</v>
       </c>
-      <c r="N8" s="80" t="n">
+      <c r="O8" s="80" t="n">
         <v>8459.32</v>
       </c>
-      <c r="O8" s="80" t="n">
+      <c r="P8" s="80" t="n">
         <v>6885.79</v>
       </c>
-      <c r="P8" s="80" t="n">
+      <c r="Q8" s="80" t="n">
         <v>7457.13</v>
       </c>
-      <c r="Q8" s="80" t="n">
+      <c r="R8" s="80" t="n">
         <v>8306.99</v>
       </c>
-      <c r="R8" s="80" t="n">
+      <c r="S8" s="80" t="n">
         <v>7149.59</v>
       </c>
-      <c r="S8" s="80" t="n">
+      <c r="T8" s="80" t="n">
         <v>7232.88</v>
       </c>
-      <c r="T8" s="80" t="n">
+      <c r="U8" s="80" t="n">
         <v>7083.91</v>
       </c>
-      <c r="U8" s="80" t="n">
+      <c r="V8" s="80" t="n">
         <v>7417.25</v>
       </c>
-      <c r="V8" s="80" t="n">
+      <c r="W8" s="80" t="n">
         <v>7748.07</v>
       </c>
-      <c r="W8" s="80" t="n">
+      <c r="X8" s="80" t="n">
         <v>7639.24</v>
       </c>
-      <c r="X8" s="80" t="n">
+      <c r="Y8" s="80" t="n">
         <v>8477.030000000001</v>
       </c>
-      <c r="Y8" s="80" t="n">
+      <c r="Z8" s="80" t="n">
         <v>8312.84</v>
       </c>
-      <c r="Z8" s="80" t="n">
+      <c r="AA8" s="80" t="n">
         <v>7992.46</v>
       </c>
-      <c r="AA8" s="80" t="n">
+      <c r="AB8" s="80" t="n">
         <v>9954.440000000001</v>
       </c>
-      <c r="AB8" s="80" t="n">
+      <c r="AC8" s="80" t="n">
         <v>8873.639999999999</v>
       </c>
-      <c r="AC8" s="80" t="n">
+      <c r="AD8" s="80" t="n">
         <v>8477.879999999999</v>
       </c>
-      <c r="AD8" s="80" t="n">
+      <c r="AE8" s="80" t="n">
         <v>7610.71</v>
-      </c>
-      <c r="AE8" s="80" t="n">
-        <v>8245.620000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2345,94 +2344,94 @@
         </is>
       </c>
       <c r="B9" s="84" t="n">
-        <v>0.4151</v>
+        <v>0.4413</v>
       </c>
       <c r="C9" s="84" t="n">
-        <v>0.4232</v>
+        <v>0.4144</v>
       </c>
       <c r="D9" s="84" t="n">
-        <v>0.4494</v>
+        <v>0.4224</v>
       </c>
       <c r="E9" s="84" t="n">
-        <v>0.4575</v>
+        <v>0.4485</v>
       </c>
       <c r="F9" s="84" t="n">
-        <v>0.4807</v>
+        <v>0.4568</v>
       </c>
       <c r="G9" s="84" t="n">
-        <v>0.4952</v>
+        <v>0.4799</v>
       </c>
       <c r="H9" s="84" t="n">
-        <v>0.4772</v>
+        <v>0.4944</v>
       </c>
       <c r="I9" s="84" t="n">
-        <v>0.4885</v>
+        <v>0.4764</v>
       </c>
       <c r="J9" s="84" t="n">
-        <v>0.477</v>
+        <v>0.4878</v>
       </c>
       <c r="K9" s="84" t="n">
-        <v>0.4881</v>
+        <v>0.4763</v>
       </c>
       <c r="L9" s="84" t="n">
-        <v>0.469</v>
+        <v>0.4872</v>
       </c>
       <c r="M9" s="84" t="n">
-        <v>0.4909</v>
+        <v>0.4682</v>
       </c>
       <c r="N9" s="84" t="n">
-        <v>0.4847</v>
+        <v>0.4901</v>
       </c>
       <c r="O9" s="84" t="n">
-        <v>0.4942</v>
+        <v>0.4838</v>
       </c>
       <c r="P9" s="84" t="n">
-        <v>0.5327</v>
+        <v>0.4933</v>
       </c>
       <c r="Q9" s="84" t="n">
-        <v>0.5044</v>
+        <v>0.5319</v>
       </c>
       <c r="R9" s="84" t="n">
-        <v>0.513</v>
+        <v>0.5037</v>
       </c>
       <c r="S9" s="84" t="n">
-        <v>0.5171</v>
+        <v>0.5123</v>
       </c>
       <c r="T9" s="84" t="n">
-        <v>0.5397</v>
+        <v>0.5165</v>
       </c>
       <c r="U9" s="84" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5392</v>
       </c>
       <c r="V9" s="84" t="n">
-        <v>0.5629</v>
+        <v>0.5333</v>
       </c>
       <c r="W9" s="84" t="n">
-        <v>0.521</v>
+        <v>0.5623</v>
       </c>
       <c r="X9" s="84" t="n">
-        <v>0.5568</v>
+        <v>0.5201</v>
       </c>
       <c r="Y9" s="84" t="n">
-        <v>0.6169</v>
+        <v>0.556</v>
       </c>
       <c r="Z9" s="84" t="n">
-        <v>0.6152</v>
+        <v>0.6161</v>
       </c>
       <c r="AA9" s="84" t="n">
-        <v>0.6381</v>
+        <v>0.6145</v>
       </c>
       <c r="AB9" s="84" t="n">
-        <v>0.6188</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="AC9" s="84" t="n">
-        <v>0.5769</v>
+        <v>0.6179</v>
       </c>
       <c r="AD9" s="84" t="n">
-        <v>0.5747</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="AE9" s="84" t="n">
-        <v>0.6083</v>
+        <v>0.5738</v>
       </c>
     </row>
     <row r="10">
@@ -2442,94 +2441,94 @@
         </is>
       </c>
       <c r="B10" s="84" t="n">
+        <v>0.400067</v>
+      </c>
+      <c r="C10" s="84" t="n">
         <v>0.347822</v>
       </c>
-      <c r="C10" s="84" t="n">
+      <c r="D10" s="84" t="n">
         <v>0.370858</v>
       </c>
-      <c r="D10" s="84" t="n">
+      <c r="E10" s="84" t="n">
         <v>0.444546</v>
       </c>
-      <c r="E10" s="84" t="n">
+      <c r="F10" s="84" t="n">
         <v>0.463565</v>
       </c>
-      <c r="F10" s="84" t="n">
+      <c r="G10" s="84" t="n">
         <v>0.529099</v>
       </c>
-      <c r="G10" s="84" t="n">
+      <c r="H10" s="84" t="n">
         <v>0.6094580000000001</v>
       </c>
-      <c r="H10" s="84" t="n">
+      <c r="I10" s="84" t="n">
         <v>0.519536</v>
       </c>
-      <c r="I10" s="84" t="n">
+      <c r="J10" s="84" t="n">
         <v>0.622049</v>
       </c>
-      <c r="J10" s="84" t="n">
+      <c r="K10" s="84" t="n">
         <v>0.599158</v>
       </c>
-      <c r="K10" s="84" t="n">
+      <c r="L10" s="84" t="n">
         <v>0.651015</v>
       </c>
-      <c r="L10" s="84" t="n">
+      <c r="M10" s="84" t="n">
         <v>0.597652</v>
       </c>
-      <c r="M10" s="84" t="n">
+      <c r="N10" s="84" t="n">
         <v>0.71348</v>
       </c>
-      <c r="N10" s="84" t="n">
+      <c r="O10" s="84" t="n">
         <v>0.702858</v>
       </c>
-      <c r="O10" s="84" t="n">
+      <c r="P10" s="84" t="n">
         <v>0.778069</v>
       </c>
-      <c r="P10" s="84" t="n">
+      <c r="Q10" s="84" t="n">
         <v>0.855721</v>
       </c>
-      <c r="Q10" s="84" t="n">
+      <c r="R10" s="84" t="n">
         <v>0.829256</v>
       </c>
-      <c r="R10" s="84" t="n">
+      <c r="S10" s="84" t="n">
         <v>0.845056</v>
       </c>
-      <c r="S10" s="84" t="n">
+      <c r="T10" s="84" t="n">
         <v>0.85697</v>
       </c>
-      <c r="T10" s="84" t="n">
+      <c r="U10" s="84" t="n">
         <v>0.893103</v>
       </c>
-      <c r="U10" s="84" t="n">
+      <c r="V10" s="84" t="n">
         <v>0.891944</v>
       </c>
-      <c r="V10" s="84" t="n">
+      <c r="W10" s="84" t="n">
         <v>0.92065</v>
       </c>
-      <c r="W10" s="84" t="n">
+      <c r="X10" s="84" t="n">
         <v>0.8739130000000001</v>
       </c>
-      <c r="X10" s="84" t="n">
+      <c r="Y10" s="84" t="n">
         <v>0.90562</v>
       </c>
-      <c r="Y10" s="84" t="n">
+      <c r="Z10" s="84" t="n">
         <v>0.9932029999999999</v>
       </c>
-      <c r="Z10" s="84" t="n">
+      <c r="AA10" s="84" t="n">
         <v>0.993279</v>
       </c>
-      <c r="AA10" s="84" t="n">
+      <c r="AB10" s="84" t="n">
         <v>0.999889</v>
       </c>
-      <c r="AB10" s="84" t="n">
+      <c r="AC10" s="84" t="n">
         <v>0.99874</v>
       </c>
-      <c r="AC10" s="84" t="n">
+      <c r="AD10" s="84" t="n">
         <v>0.944308</v>
       </c>
-      <c r="AD10" s="84" t="n">
+      <c r="AE10" s="84" t="n">
         <v>0.945653</v>
-      </c>
-      <c r="AE10" s="84" t="n">
-        <v>0.992076</v>
       </c>
     </row>
     <row r="11" ht="19" customFormat="1" customHeight="1" s="30">
@@ -2539,94 +2538,94 @@
         </is>
       </c>
       <c r="B11" s="86" t="n">
-        <v>-0.01959999999999998</v>
+        <v>-0.0224</v>
       </c>
       <c r="C11" s="86" t="n">
-        <v>-0.02120000000000002</v>
+        <v>-0.01730000000000001</v>
       </c>
       <c r="D11" s="86" t="n">
-        <v>-0.02540000000000001</v>
+        <v>-0.01879999999999998</v>
       </c>
       <c r="E11" s="86" t="n">
-        <v>-0.02549999999999999</v>
+        <v>-0.02289999999999998</v>
       </c>
       <c r="F11" s="86" t="n">
-        <v>-0.02670000000000003</v>
+        <v>-0.02310000000000001</v>
       </c>
       <c r="G11" s="86" t="n">
-        <v>-0.02880000000000002</v>
+        <v>-0.0242</v>
       </c>
       <c r="H11" s="86" t="n">
-        <v>-0.0285</v>
+        <v>-0.02639999999999998</v>
       </c>
       <c r="I11" s="86" t="n">
-        <v>-0.028</v>
+        <v>-0.02590000000000003</v>
       </c>
       <c r="J11" s="86" t="n">
-        <v>-0.03400000000000003</v>
+        <v>-0.02520000000000003</v>
       </c>
       <c r="K11" s="86" t="n">
-        <v>-0.03469999999999998</v>
+        <v>-0.03110000000000002</v>
       </c>
       <c r="L11" s="86" t="n">
-        <v>-0.0275</v>
+        <v>-0.03159999999999999</v>
       </c>
       <c r="M11" s="86" t="n">
-        <v>-0.02740000000000001</v>
+        <v>-0.02449999999999999</v>
       </c>
       <c r="N11" s="86" t="n">
-        <v>-0.02740000000000004</v>
+        <v>-0.0242</v>
       </c>
       <c r="O11" s="86" t="n">
-        <v>-0.02820000000000003</v>
+        <v>-0.02450000000000002</v>
       </c>
       <c r="P11" s="86" t="n">
-        <v>-0.03130000000000002</v>
+        <v>-0.02459999999999998</v>
       </c>
       <c r="Q11" s="86" t="n">
-        <v>-0.03190000000000001</v>
+        <v>-0.02809999999999999</v>
       </c>
       <c r="R11" s="86" t="n">
-        <v>-0.03289999999999998</v>
+        <v>-0.02860000000000001</v>
       </c>
       <c r="S11" s="86" t="n">
-        <v>-0.03339999999999999</v>
+        <v>-0.0297</v>
       </c>
       <c r="T11" s="86" t="n">
-        <v>-0.03379999999999997</v>
+        <v>-0.03009999999999999</v>
       </c>
       <c r="U11" s="86" t="n">
-        <v>-0.0343</v>
+        <v>-0.03039999999999998</v>
       </c>
       <c r="V11" s="86" t="n">
-        <v>-0.03459999999999999</v>
+        <v>-0.03070000000000001</v>
       </c>
       <c r="W11" s="86" t="n">
-        <v>-0.03790000000000002</v>
+        <v>-0.03129999999999999</v>
       </c>
       <c r="X11" s="86" t="n">
-        <v>-0.0411</v>
+        <v>-0.03420000000000001</v>
       </c>
       <c r="Y11" s="86" t="n">
-        <v>-0.04289999999999999</v>
+        <v>-0.03740000000000002</v>
       </c>
       <c r="Z11" s="86" t="n">
-        <v>-0.04190000000000002</v>
+        <v>-0.03929999999999997</v>
       </c>
       <c r="AA11" s="86" t="n">
-        <v>-0.0449</v>
+        <v>-0.03809999999999999</v>
       </c>
       <c r="AB11" s="86" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.04120000000000001</v>
       </c>
       <c r="AC11" s="86" t="n">
-        <v>-0.05249999999999999</v>
+        <v>-0.04719999999999999</v>
       </c>
       <c r="AD11" s="86" t="n">
-        <v>-0.0519</v>
+        <v>-0.04869999999999999</v>
       </c>
       <c r="AE11" s="86" t="n">
-        <v>-0.04920000000000002</v>
+        <v>-0.04799999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2636,94 +2635,94 @@
         </is>
       </c>
       <c r="B12" s="80" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="C12" s="80" t="n">
         <v>76.58</v>
       </c>
-      <c r="C12" s="80" t="n">
+      <c r="D12" s="80" t="n">
         <v>70.66</v>
       </c>
-      <c r="D12" s="80" t="n">
+      <c r="E12" s="80" t="n">
         <v>63.35</v>
       </c>
-      <c r="E12" s="80" t="n">
+      <c r="F12" s="80" t="n">
         <v>56.17</v>
       </c>
-      <c r="F12" s="80" t="n">
+      <c r="G12" s="80" t="n">
         <v>51.28</v>
       </c>
-      <c r="G12" s="80" t="n">
+      <c r="H12" s="80" t="n">
         <v>46.71</v>
       </c>
-      <c r="H12" s="80" t="n">
+      <c r="I12" s="80" t="n">
         <v>42.47</v>
       </c>
-      <c r="I12" s="80" t="n">
+      <c r="J12" s="80" t="n">
         <v>36.79</v>
       </c>
-      <c r="J12" s="80" t="n">
+      <c r="K12" s="80" t="n">
         <v>31.64</v>
       </c>
-      <c r="K12" s="80" t="n">
+      <c r="L12" s="80" t="n">
         <v>25.69</v>
       </c>
-      <c r="L12" s="80" t="n">
+      <c r="M12" s="80" t="n">
         <v>21.25</v>
       </c>
-      <c r="M12" s="80" t="n">
+      <c r="N12" s="80" t="n">
         <v>16.12</v>
       </c>
-      <c r="N12" s="80" t="n">
+      <c r="O12" s="80" t="n">
         <v>12.18</v>
       </c>
-      <c r="O12" s="80" t="n">
+      <c r="P12" s="80" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="P12" s="80" t="n">
+      <c r="Q12" s="80" t="n">
         <v>5.83</v>
       </c>
-      <c r="Q12" s="80" t="n">
+      <c r="R12" s="80" t="n">
         <v>4.59</v>
       </c>
-      <c r="R12" s="80" t="n">
+      <c r="S12" s="80" t="n">
         <v>3.05</v>
       </c>
-      <c r="S12" s="80" t="n">
+      <c r="T12" s="80" t="n">
         <v>1.6</v>
       </c>
-      <c r="T12" s="80" t="n">
+      <c r="U12" s="80" t="n">
         <v>0.16</v>
       </c>
-      <c r="U12" s="80" t="n">
+      <c r="V12" s="80" t="n">
         <v>-0.83</v>
       </c>
-      <c r="V12" s="80" t="n">
+      <c r="W12" s="80" t="n">
         <v>-1.95</v>
       </c>
-      <c r="W12" s="80" t="n">
+      <c r="X12" s="80" t="n">
         <v>-2.74</v>
       </c>
-      <c r="X12" s="80" t="n">
+      <c r="Y12" s="80" t="n">
         <v>-4.61</v>
       </c>
-      <c r="Y12" s="80" t="n">
+      <c r="Z12" s="80" t="n">
         <v>-5.83</v>
       </c>
-      <c r="Z12" s="80" t="n">
+      <c r="AA12" s="80" t="n">
         <v>-5.92</v>
       </c>
-      <c r="AA12" s="80" t="n">
+      <c r="AB12" s="80" t="n">
         <v>-6</v>
       </c>
-      <c r="AB12" s="80" t="n">
+      <c r="AC12" s="80" t="n">
         <v>-5.67</v>
       </c>
-      <c r="AC12" s="80" t="n">
+      <c r="AD12" s="80" t="n">
         <v>-5.46</v>
       </c>
-      <c r="AD12" s="80" t="n">
+      <c r="AE12" s="80" t="n">
         <v>-6.13</v>
-      </c>
-      <c r="AE12" s="80" t="n">
-        <v>-6.92</v>
       </c>
     </row>
     <row r="13">
@@ -2733,94 +2732,94 @@
         </is>
       </c>
       <c r="B13" s="87" t="n">
+        <v>-19.82</v>
+      </c>
+      <c r="C13" s="87" t="n">
         <v>-33.67</v>
       </c>
-      <c r="C13" s="87" t="n">
+      <c r="D13" s="87" t="n">
         <v>-4.03</v>
       </c>
-      <c r="D13" s="87" t="n">
+      <c r="E13" s="87" t="n">
         <v>0.04</v>
       </c>
-      <c r="E13" s="87" t="n">
+      <c r="F13" s="87" t="n">
         <v>-32.7</v>
       </c>
-      <c r="F13" s="87" t="n">
+      <c r="G13" s="87" t="n">
         <v>-72.36</v>
       </c>
-      <c r="G13" s="87" t="n">
+      <c r="H13" s="87" t="n">
         <v>-23.12</v>
       </c>
-      <c r="H13" s="87" t="n">
+      <c r="I13" s="87" t="n">
         <v>-33.01</v>
       </c>
-      <c r="I13" s="87" t="n">
+      <c r="J13" s="87" t="n">
         <v>-47.35</v>
       </c>
-      <c r="J13" s="87" t="n">
+      <c r="K13" s="87" t="n">
         <v>-63.06</v>
       </c>
-      <c r="K13" s="87" t="n">
+      <c r="L13" s="87" t="n">
         <v>-33.35</v>
       </c>
-      <c r="L13" s="87" t="n">
+      <c r="M13" s="87" t="n">
         <v>-74.97</v>
       </c>
-      <c r="M13" s="87" t="n">
+      <c r="N13" s="87" t="n">
         <v>-7.05</v>
       </c>
-      <c r="N13" s="87" t="n">
+      <c r="O13" s="87" t="n">
         <v>67.73</v>
       </c>
-      <c r="O13" s="87" t="n">
+      <c r="P13" s="87" t="n">
         <v>-56.8</v>
       </c>
-      <c r="P13" s="87" t="n">
+      <c r="Q13" s="87" t="n">
         <v>33.78</v>
       </c>
-      <c r="Q13" s="87" t="n">
+      <c r="R13" s="87" t="n">
         <v>15.39</v>
       </c>
-      <c r="R13" s="87" t="n">
+      <c r="S13" s="87" t="n">
         <v>-77.98</v>
       </c>
-      <c r="S13" s="87" t="n">
+      <c r="T13" s="87" t="n">
         <v>10.45</v>
       </c>
-      <c r="T13" s="87" t="n">
+      <c r="U13" s="87" t="n">
         <v>33.99</v>
       </c>
-      <c r="U13" s="87" t="n">
+      <c r="V13" s="87" t="n">
         <v>-50.55</v>
       </c>
-      <c r="V13" s="87" t="n">
+      <c r="W13" s="87" t="n">
         <v>27.48</v>
       </c>
-      <c r="W13" s="87" t="n">
+      <c r="X13" s="87" t="n">
         <v>-40.39</v>
       </c>
-      <c r="X13" s="87" t="n">
+      <c r="Y13" s="87" t="n">
         <v>-32.66</v>
       </c>
-      <c r="Y13" s="87" t="n">
+      <c r="Z13" s="87" t="n">
         <v>47.76</v>
       </c>
-      <c r="Z13" s="87" t="n">
+      <c r="AA13" s="87" t="n">
         <v>-19.67</v>
       </c>
-      <c r="AA13" s="87" t="n">
+      <c r="AB13" s="87" t="n">
         <v>53.33</v>
       </c>
-      <c r="AB13" s="87" t="n">
+      <c r="AC13" s="87" t="n">
         <v>139.56</v>
       </c>
-      <c r="AC13" s="87" t="n">
+      <c r="AD13" s="87" t="n">
         <v>60.67</v>
       </c>
-      <c r="AD13" s="87" t="n">
+      <c r="AE13" s="87" t="n">
         <v>0</v>
-      </c>
-      <c r="AE13" s="87" t="n">
-        <v>-66.7</v>
       </c>
     </row>
     <row r="14">
@@ -2830,73 +2829,73 @@
         </is>
       </c>
       <c r="B14" s="88" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="87" t="n">
+      <c r="D14" s="87" t="n">
         <v>17</v>
       </c>
-      <c r="D14" s="87" t="n">
+      <c r="E14" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="87" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="87" t="n">
+      <c r="J14" s="87" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="87" t="n">
+        <v>35</v>
+      </c>
+      <c r="N14" s="87" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="87" t="n">
+        <v>17</v>
+      </c>
+      <c r="R14" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="S14" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="87" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="87" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" s="87" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" s="87" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="87" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="87" t="n">
-        <v>37</v>
-      </c>
-      <c r="M14" s="87" t="n">
-        <v>22</v>
-      </c>
-      <c r="N14" s="87" t="n">
+      <c r="T14" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="O14" s="87" t="n">
+      <c r="W14" s="87" t="n">
+        <v>84</v>
+      </c>
+      <c r="X14" s="87" t="n">
         <v>2</v>
-      </c>
-      <c r="P14" s="87" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q14" s="87" t="n">
-        <v>9</v>
-      </c>
-      <c r="R14" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="87" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="87" t="n">
-        <v>88</v>
-      </c>
-      <c r="W14" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" s="87" t="n">
-        <v>1</v>
       </c>
       <c r="Y14" s="87" t="n">
         <v>1</v>
@@ -2905,10 +2904,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="87" t="n">
         <v>5</v>
-      </c>
-      <c r="AB14" s="87" t="n">
-        <v>1</v>
       </c>
       <c r="AC14" s="87" t="n">
         <v>1</v>
@@ -2917,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="AE14" s="87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2927,55 +2926,55 @@
         </is>
       </c>
       <c r="B15" s="88" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C15" s="87" t="n">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="D15" s="87" t="n">
+        <v>97</v>
+      </c>
+      <c r="E15" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="87" t="n">
+      <c r="F15" s="87" t="n">
         <v>38</v>
       </c>
-      <c r="F15" s="87" t="n">
-        <v>21</v>
-      </c>
       <c r="G15" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="87" t="n">
+      <c r="I15" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="I15" s="87" t="n">
+      <c r="J15" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="87" t="n">
+      <c r="K15" s="87" t="n">
         <v>18</v>
       </c>
-      <c r="K15" s="87" t="n">
+      <c r="L15" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="87" t="n">
+      <c r="M15" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="87" t="n">
+      <c r="N15" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="87" t="n">
+      <c r="O15" s="87" t="n">
         <v>26</v>
       </c>
-      <c r="O15" s="87" t="n">
+      <c r="P15" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="P15" s="87" t="n">
+      <c r="Q15" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" s="87" t="n">
+      <c r="R15" s="87" t="n">
         <v>4</v>
-      </c>
-      <c r="R15" s="87" t="n">
-        <v>0</v>
       </c>
       <c r="S15" s="87" t="n">
         <v>0</v>
@@ -3024,58 +3023,58 @@
         </is>
       </c>
       <c r="B16" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="87" t="n">
         <v>45</v>
       </c>
-      <c r="C16" s="87" t="n">
+      <c r="D16" s="87" t="n">
         <v>224</v>
       </c>
-      <c r="D16" s="87" t="n">
+      <c r="E16" s="87" t="n">
         <v>23</v>
       </c>
-      <c r="E16" s="87" t="n">
+      <c r="F16" s="87" t="n">
         <v>106</v>
       </c>
-      <c r="F16" s="87" t="n">
+      <c r="G16" s="87" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="87" t="n">
+      <c r="H16" s="87" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="87" t="n">
+      <c r="I16" s="87" t="n">
         <v>26</v>
       </c>
-      <c r="I16" s="87" t="n">
+      <c r="J16" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="87" t="n">
+      <c r="K16" s="87" t="n">
         <v>32</v>
       </c>
-      <c r="K16" s="87" t="n">
+      <c r="L16" s="87" t="n">
         <v>20</v>
       </c>
-      <c r="L16" s="87" t="n">
+      <c r="M16" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="87" t="n">
+      <c r="N16" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="N16" s="87" t="n">
+      <c r="O16" s="87" t="n">
         <v>84</v>
       </c>
-      <c r="O16" s="87" t="n">
+      <c r="P16" s="87" t="n">
         <v>43</v>
       </c>
-      <c r="P16" s="87" t="n">
+      <c r="Q16" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="Q16" s="87" t="n">
+      <c r="R16" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="R16" s="87" t="n">
+      <c r="S16" s="87" t="n">
         <v>2</v>
-      </c>
-      <c r="S16" s="87" t="n">
-        <v>0</v>
       </c>
       <c r="T16" s="87" t="n">
         <v>0</v>
@@ -3121,94 +3120,94 @@
         </is>
       </c>
       <c r="B17" s="87" t="n">
-        <v>45</v>
+        <v>367</v>
       </c>
       <c r="C17" s="87" t="n">
+        <v>46</v>
+      </c>
+      <c r="D17" s="87" t="n">
         <v>80</v>
-      </c>
-      <c r="D17" s="87" t="n">
-        <v>66</v>
       </c>
       <c r="E17" s="87" t="n">
         <v>66</v>
       </c>
       <c r="F17" s="87" t="n">
+        <v>66</v>
+      </c>
+      <c r="G17" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="G17" s="87" t="n">
+      <c r="H17" s="87" t="n">
         <v>59</v>
       </c>
-      <c r="H17" s="87" t="n">
+      <c r="I17" s="87" t="n">
         <v>155</v>
       </c>
-      <c r="I17" s="87" t="n">
+      <c r="J17" s="87" t="n">
         <v>607</v>
       </c>
-      <c r="J17" s="87" t="n">
+      <c r="K17" s="87" t="n">
         <v>41</v>
       </c>
-      <c r="K17" s="87" t="n">
+      <c r="L17" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="L17" s="87" t="n">
+      <c r="M17" s="87" t="n">
         <v>313</v>
       </c>
-      <c r="M17" s="87" t="n">
+      <c r="N17" s="87" t="n">
         <v>100</v>
       </c>
-      <c r="N17" s="87" t="n">
+      <c r="O17" s="87" t="n">
         <v>96</v>
       </c>
-      <c r="O17" s="87" t="n">
+      <c r="P17" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="P17" s="87" t="n">
+      <c r="Q17" s="87" t="n">
         <v>151</v>
       </c>
-      <c r="Q17" s="87" t="n">
+      <c r="R17" s="87" t="n">
         <v>46</v>
       </c>
-      <c r="R17" s="87" t="n">
+      <c r="S17" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="S17" s="87" t="n">
+      <c r="T17" s="87" t="n">
         <v>32</v>
       </c>
-      <c r="T17" s="87" t="n">
+      <c r="U17" s="87" t="n">
         <v>17</v>
       </c>
-      <c r="U17" s="87" t="n">
+      <c r="V17" s="87" t="n">
         <v>18</v>
       </c>
-      <c r="V17" s="87" t="n">
-        <v>462</v>
-      </c>
       <c r="W17" s="87" t="n">
+        <v>463</v>
+      </c>
+      <c r="X17" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="X17" s="87" t="n">
+      <c r="Y17" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="Y17" s="87" t="n">
+      <c r="Z17" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="Z17" s="87" t="n">
+      <c r="AA17" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="AA17" s="87" t="n">
+      <c r="AB17" s="87" t="n">
         <v>40</v>
       </c>
-      <c r="AB17" s="87" t="n">
+      <c r="AC17" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="AC17" s="87" t="n">
+      <c r="AD17" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="AD17" s="87" t="n">
+      <c r="AE17" s="87" t="n">
         <v>3</v>
-      </c>
-      <c r="AE17" s="87" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3218,94 +3217,94 @@
         </is>
       </c>
       <c r="B18" s="87" t="n">
-        <v>916</v>
+        <v>664</v>
       </c>
       <c r="C18" s="87" t="n">
-        <v>1301</v>
+        <v>917</v>
       </c>
       <c r="D18" s="87" t="n">
-        <v>977</v>
+        <v>1302</v>
       </c>
       <c r="E18" s="87" t="n">
+        <v>978</v>
+      </c>
+      <c r="F18" s="87" t="n">
         <v>719</v>
       </c>
-      <c r="F18" s="87" t="n">
-        <v>276</v>
-      </c>
       <c r="G18" s="87" t="n">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="H18" s="87" t="n">
+        <v>212</v>
+      </c>
+      <c r="I18" s="87" t="n">
         <v>453</v>
       </c>
-      <c r="I18" s="87" t="n">
-        <v>658</v>
-      </c>
       <c r="J18" s="87" t="n">
-        <v>496</v>
+        <v>659</v>
       </c>
       <c r="K18" s="87" t="n">
-        <v>166</v>
+        <v>497</v>
       </c>
       <c r="L18" s="87" t="n">
+        <v>167</v>
+      </c>
+      <c r="M18" s="87" t="n">
         <v>704</v>
       </c>
-      <c r="M18" s="87" t="n">
+      <c r="N18" s="87" t="n">
         <v>550</v>
       </c>
-      <c r="N18" s="87" t="n">
+      <c r="O18" s="87" t="n">
         <v>666</v>
       </c>
-      <c r="O18" s="87" t="n">
+      <c r="P18" s="87" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q18" s="87" t="n">
+        <v>325</v>
+      </c>
+      <c r="R18" s="87" t="n">
+        <v>362</v>
+      </c>
+      <c r="S18" s="87" t="n">
+        <v>88</v>
+      </c>
+      <c r="T18" s="87" t="n">
         <v>209</v>
       </c>
-      <c r="P18" s="87" t="n">
-        <v>325</v>
-      </c>
-      <c r="Q18" s="87" t="n">
-        <v>362</v>
-      </c>
-      <c r="R18" s="87" t="n">
-        <v>88</v>
-      </c>
-      <c r="S18" s="87" t="n">
-        <v>209</v>
-      </c>
-      <c r="T18" s="87" t="n">
-        <v>169</v>
-      </c>
       <c r="U18" s="87" t="n">
+        <v>170</v>
+      </c>
+      <c r="V18" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="V18" s="87" t="n">
-        <v>318</v>
-      </c>
       <c r="W18" s="87" t="n">
+        <v>319</v>
+      </c>
+      <c r="X18" s="87" t="n">
         <v>194</v>
       </c>
-      <c r="X18" s="87" t="n">
+      <c r="Y18" s="87" t="n">
         <v>111</v>
       </c>
-      <c r="Y18" s="87" t="n">
+      <c r="Z18" s="87" t="n">
         <v>34</v>
       </c>
-      <c r="Z18" s="87" t="n">
+      <c r="AA18" s="87" t="n">
         <v>53</v>
       </c>
-      <c r="AA18" s="87" t="n">
+      <c r="AB18" s="87" t="n">
         <v>28</v>
       </c>
-      <c r="AB18" s="87" t="n">
+      <c r="AC18" s="87" t="n">
         <v>62</v>
       </c>
-      <c r="AC18" s="87" t="n">
+      <c r="AD18" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="AD18" s="87" t="n">
+      <c r="AE18" s="87" t="n">
         <v>31</v>
-      </c>
-      <c r="AE18" s="87" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -3315,94 +3314,94 @@
         </is>
       </c>
       <c r="B19" s="87" t="n">
+        <v>74</v>
+      </c>
+      <c r="C19" s="87" t="n">
         <v>1036</v>
       </c>
-      <c r="C19" s="87" t="n">
+      <c r="D19" s="87" t="n">
         <v>2168</v>
       </c>
-      <c r="D19" s="87" t="n">
+      <c r="E19" s="87" t="n">
         <v>708</v>
       </c>
-      <c r="E19" s="87" t="n">
+      <c r="F19" s="87" t="n">
         <v>1081</v>
       </c>
-      <c r="F19" s="87" t="n">
+      <c r="G19" s="87" t="n">
         <v>469</v>
       </c>
-      <c r="G19" s="87" t="n">
+      <c r="H19" s="87" t="n">
         <v>184</v>
       </c>
-      <c r="H19" s="87" t="n">
+      <c r="I19" s="87" t="n">
         <v>454</v>
       </c>
-      <c r="I19" s="87" t="n">
+      <c r="J19" s="87" t="n">
         <v>242</v>
       </c>
-      <c r="J19" s="87" t="n">
+      <c r="K19" s="87" t="n">
         <v>386</v>
       </c>
-      <c r="K19" s="87" t="n">
+      <c r="L19" s="87" t="n">
         <v>152</v>
       </c>
-      <c r="L19" s="87" t="n">
+      <c r="M19" s="87" t="n">
         <v>207</v>
       </c>
-      <c r="M19" s="87" t="n">
+      <c r="N19" s="87" t="n">
         <v>286</v>
       </c>
-      <c r="N19" s="87" t="n">
+      <c r="O19" s="87" t="n">
         <v>1883</v>
       </c>
-      <c r="O19" s="87" t="n">
+      <c r="P19" s="87" t="n">
         <v>1032</v>
       </c>
-      <c r="P19" s="87" t="n">
+      <c r="Q19" s="87" t="n">
         <v>658</v>
       </c>
-      <c r="Q19" s="87" t="n">
+      <c r="R19" s="87" t="n">
         <v>641</v>
       </c>
-      <c r="R19" s="87" t="n">
+      <c r="S19" s="87" t="n">
         <v>191</v>
       </c>
-      <c r="S19" s="87" t="n">
+      <c r="T19" s="87" t="n">
         <v>335</v>
       </c>
-      <c r="T19" s="87" t="n">
+      <c r="U19" s="87" t="n">
         <v>312</v>
       </c>
-      <c r="U19" s="87" t="n">
+      <c r="V19" s="87" t="n">
         <v>409</v>
       </c>
-      <c r="V19" s="87" t="n">
+      <c r="W19" s="87" t="n">
         <v>215</v>
       </c>
-      <c r="W19" s="87" t="n">
+      <c r="X19" s="87" t="n">
         <v>370</v>
       </c>
-      <c r="X19" s="87" t="n">
+      <c r="Y19" s="87" t="n">
         <v>272</v>
       </c>
-      <c r="Y19" s="87" t="n">
+      <c r="Z19" s="87" t="n">
         <v>78</v>
       </c>
-      <c r="Z19" s="87" t="n">
+      <c r="AA19" s="87" t="n">
         <v>153</v>
       </c>
-      <c r="AA19" s="87" t="n">
+      <c r="AB19" s="87" t="n">
         <v>74</v>
       </c>
-      <c r="AB19" s="87" t="n">
+      <c r="AC19" s="87" t="n">
         <v>51</v>
       </c>
-      <c r="AC19" s="87" t="n">
+      <c r="AD19" s="87" t="n">
         <v>114</v>
       </c>
-      <c r="AD19" s="87" t="n">
+      <c r="AE19" s="87" t="n">
         <v>111</v>
-      </c>
-      <c r="AE19" s="87" t="n">
-        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -3412,94 +3411,94 @@
         </is>
       </c>
       <c r="B20" s="87" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" s="87" t="n">
         <v>174</v>
       </c>
-      <c r="C20" s="87" t="n">
+      <c r="D20" s="87" t="n">
         <v>222</v>
       </c>
-      <c r="D20" s="87" t="n">
+      <c r="E20" s="87" t="n">
         <v>101</v>
       </c>
-      <c r="E20" s="87" t="n">
+      <c r="F20" s="87" t="n">
         <v>167</v>
       </c>
-      <c r="F20" s="87" t="n">
+      <c r="G20" s="87" t="n">
         <v>95</v>
       </c>
-      <c r="G20" s="87" t="n">
+      <c r="H20" s="87" t="n">
         <v>35</v>
       </c>
-      <c r="H20" s="87" t="n">
+      <c r="I20" s="87" t="n">
         <v>68</v>
       </c>
-      <c r="I20" s="87" t="n">
+      <c r="J20" s="87" t="n">
         <v>38</v>
       </c>
-      <c r="J20" s="87" t="n">
+      <c r="K20" s="87" t="n">
         <v>101</v>
-      </c>
-      <c r="K20" s="87" t="n">
-        <v>44</v>
       </c>
       <c r="L20" s="87" t="n">
         <v>44</v>
       </c>
       <c r="M20" s="87" t="n">
+        <v>44</v>
+      </c>
+      <c r="N20" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="N20" s="87" t="n">
+      <c r="O20" s="87" t="n">
         <v>145</v>
       </c>
-      <c r="O20" s="87" t="n">
+      <c r="P20" s="87" t="n">
         <v>89</v>
       </c>
-      <c r="P20" s="87" t="n">
+      <c r="Q20" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="Q20" s="87" t="n">
+      <c r="R20" s="87" t="n">
         <v>97</v>
       </c>
-      <c r="R20" s="87" t="n">
+      <c r="S20" s="87" t="n">
         <v>35</v>
       </c>
-      <c r="S20" s="87" t="n">
+      <c r="T20" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="T20" s="87" t="n">
+      <c r="U20" s="87" t="n">
         <v>55</v>
       </c>
-      <c r="U20" s="87" t="n">
+      <c r="V20" s="87" t="n">
         <v>71</v>
       </c>
-      <c r="V20" s="87" t="n">
+      <c r="W20" s="87" t="n">
         <v>35</v>
       </c>
-      <c r="W20" s="87" t="n">
+      <c r="X20" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="X20" s="87" t="n">
+      <c r="Y20" s="87" t="n">
         <v>60</v>
       </c>
-      <c r="Y20" s="87" t="n">
+      <c r="Z20" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="Z20" s="87" t="n">
+      <c r="AA20" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="AA20" s="87" t="n">
+      <c r="AB20" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="AB20" s="87" t="n">
+      <c r="AC20" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="AC20" s="87" t="n">
+      <c r="AD20" s="87" t="n">
         <v>27</v>
       </c>
-      <c r="AD20" s="87" t="n">
+      <c r="AE20" s="87" t="n">
         <v>29</v>
-      </c>
-      <c r="AE20" s="87" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -3509,94 +3508,94 @@
         </is>
       </c>
       <c r="B21" s="87" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C21" s="87" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D21" s="87" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E21" s="87" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F21" s="87" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>36</v>
       </c>
       <c r="H21" s="87" t="n">
+        <v>35</v>
+      </c>
+      <c r="I21" s="87" t="n">
         <v>54</v>
       </c>
-      <c r="I21" s="87" t="n">
-        <v>36</v>
-      </c>
       <c r="J21" s="87" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="K21" s="87" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L21" s="87" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M21" s="87" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="N21" s="87" t="n">
+        <v>33</v>
+      </c>
+      <c r="O21" s="87" t="n">
+        <v>42</v>
+      </c>
+      <c r="P21" s="87" t="n">
         <v>43</v>
       </c>
-      <c r="O21" s="87" t="n">
-        <v>44</v>
-      </c>
-      <c r="P21" s="87" t="n">
+      <c r="Q21" s="87" t="n">
+        <v>22</v>
+      </c>
+      <c r="R21" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="S21" s="87" t="n">
         <v>21</v>
-      </c>
-      <c r="Q21" s="87" t="n">
-        <v>25</v>
-      </c>
-      <c r="R21" s="87" t="n">
-        <v>22</v>
-      </c>
-      <c r="S21" s="87" t="n">
-        <v>30</v>
       </c>
       <c r="T21" s="87" t="n">
         <v>28</v>
       </c>
       <c r="U21" s="87" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="V21" s="87" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="W21" s="87" t="n">
+        <v>29</v>
+      </c>
+      <c r="X21" s="87" t="n">
         <v>32</v>
       </c>
-      <c r="X21" s="87" t="n">
+      <c r="Y21" s="87" t="n">
         <v>23</v>
-      </c>
-      <c r="Y21" s="87" t="n">
-        <v>73</v>
       </c>
       <c r="Z21" s="87" t="n">
         <v>73</v>
       </c>
       <c r="AA21" s="87" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB21" s="87" t="n">
         <v>115</v>
       </c>
-      <c r="AB21" s="87" t="n">
-        <v>86</v>
-      </c>
       <c r="AC21" s="87" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD21" s="87" t="n">
         <v>80</v>
       </c>
-      <c r="AD21" s="87" t="n">
+      <c r="AE21" s="87" t="n">
         <v>98</v>
-      </c>
-      <c r="AE21" s="87" t="n">
-        <v>160</v>
       </c>
     </row>
     <row r="22">
@@ -3606,94 +3605,94 @@
         </is>
       </c>
       <c r="B22" s="87" t="n">
+        <v>161</v>
+      </c>
+      <c r="C22" s="87" t="n">
         <v>34</v>
       </c>
-      <c r="C22" s="87" t="n">
-        <v>178</v>
-      </c>
       <c r="D22" s="87" t="n">
+        <v>179</v>
+      </c>
+      <c r="E22" s="87" t="n">
         <v>62</v>
       </c>
-      <c r="E22" s="87" t="n">
+      <c r="F22" s="87" t="n">
         <v>103</v>
       </c>
-      <c r="F22" s="87" t="n">
-        <v>150</v>
-      </c>
       <c r="G22" s="87" t="n">
+        <v>151</v>
+      </c>
+      <c r="H22" s="87" t="n">
         <v>185</v>
       </c>
-      <c r="H22" s="87" t="n">
+      <c r="I22" s="87" t="n">
         <v>254</v>
       </c>
-      <c r="I22" s="87" t="n">
-        <v>212</v>
-      </c>
       <c r="J22" s="87" t="n">
+        <v>213</v>
+      </c>
+      <c r="K22" s="87" t="n">
         <v>371</v>
       </c>
-      <c r="K22" s="87" t="n">
+      <c r="L22" s="87" t="n">
         <v>292</v>
       </c>
-      <c r="L22" s="87" t="n">
+      <c r="M22" s="87" t="n">
         <v>248</v>
       </c>
-      <c r="M22" s="87" t="n">
+      <c r="N22" s="87" t="n">
         <v>161</v>
       </c>
-      <c r="N22" s="87" t="n">
+      <c r="O22" s="87" t="n">
         <v>330</v>
       </c>
-      <c r="O22" s="87" t="n">
-        <v>287</v>
-      </c>
       <c r="P22" s="87" t="n">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="Q22" s="87" t="n">
+        <v>187</v>
+      </c>
+      <c r="R22" s="87" t="n">
         <v>199</v>
       </c>
-      <c r="R22" s="87" t="n">
+      <c r="S22" s="87" t="n">
         <v>122</v>
       </c>
-      <c r="S22" s="87" t="n">
+      <c r="T22" s="87" t="n">
         <v>224</v>
       </c>
-      <c r="T22" s="87" t="n">
+      <c r="U22" s="87" t="n">
         <v>140</v>
       </c>
-      <c r="U22" s="87" t="n">
-        <v>388</v>
-      </c>
       <c r="V22" s="87" t="n">
-        <v>255</v>
+        <v>389</v>
       </c>
       <c r="W22" s="87" t="n">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="X22" s="87" t="n">
+        <v>149</v>
+      </c>
+      <c r="Y22" s="87" t="n">
         <v>155</v>
       </c>
-      <c r="Y22" s="87" t="n">
+      <c r="Z22" s="87" t="n">
         <v>412</v>
       </c>
-      <c r="Z22" s="87" t="n">
+      <c r="AA22" s="87" t="n">
         <v>315</v>
       </c>
-      <c r="AA22" s="87" t="n">
-        <v>674</v>
-      </c>
       <c r="AB22" s="87" t="n">
-        <v>465</v>
+        <v>675</v>
       </c>
       <c r="AC22" s="87" t="n">
-        <v>396</v>
+        <v>466</v>
       </c>
       <c r="AD22" s="87" t="n">
+        <v>397</v>
+      </c>
+      <c r="AE22" s="87" t="n">
         <v>274</v>
-      </c>
-      <c r="AE22" s="87" t="n">
-        <v>520</v>
       </c>
     </row>
     <row r="23">
@@ -3703,94 +3702,94 @@
         </is>
       </c>
       <c r="B23" s="87" t="n">
+        <v>44</v>
+      </c>
+      <c r="C23" s="87" t="n">
         <v>30</v>
       </c>
-      <c r="C23" s="87" t="n">
+      <c r="D23" s="87" t="n">
         <v>39</v>
       </c>
-      <c r="D23" s="87" t="n">
+      <c r="E23" s="87" t="n">
         <v>69</v>
-      </c>
-      <c r="E23" s="87" t="n">
-        <v>76</v>
       </c>
       <c r="F23" s="87" t="n">
         <v>76</v>
       </c>
       <c r="G23" s="87" t="n">
+        <v>76</v>
+      </c>
+      <c r="H23" s="87" t="n">
         <v>115</v>
       </c>
-      <c r="H23" s="87" t="n">
+      <c r="I23" s="87" t="n">
         <v>129</v>
       </c>
-      <c r="I23" s="87" t="n">
+      <c r="J23" s="87" t="n">
         <v>85</v>
       </c>
-      <c r="J23" s="87" t="n">
+      <c r="K23" s="87" t="n">
         <v>96</v>
       </c>
-      <c r="K23" s="87" t="n">
+      <c r="L23" s="87" t="n">
         <v>82</v>
       </c>
-      <c r="L23" s="87" t="n">
+      <c r="M23" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="M23" s="87" t="n">
+      <c r="N23" s="87" t="n">
         <v>65</v>
       </c>
-      <c r="N23" s="87" t="n">
+      <c r="O23" s="87" t="n">
         <v>58</v>
       </c>
-      <c r="O23" s="87" t="n">
+      <c r="P23" s="87" t="n">
         <v>61</v>
       </c>
-      <c r="P23" s="87" t="n">
+      <c r="Q23" s="87" t="n">
         <v>103</v>
       </c>
-      <c r="Q23" s="87" t="n">
+      <c r="R23" s="87" t="n">
         <v>81</v>
       </c>
-      <c r="R23" s="87" t="n">
+      <c r="S23" s="87" t="n">
         <v>91</v>
       </c>
-      <c r="S23" s="87" t="n">
+      <c r="T23" s="87" t="n">
         <v>72</v>
       </c>
-      <c r="T23" s="87" t="n">
+      <c r="U23" s="87" t="n">
         <v>118</v>
       </c>
-      <c r="U23" s="87" t="n">
+      <c r="V23" s="87" t="n">
         <v>126</v>
       </c>
-      <c r="V23" s="87" t="n">
+      <c r="W23" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="W23" s="87" t="n">
+      <c r="X23" s="87" t="n">
         <v>86</v>
       </c>
-      <c r="X23" s="87" t="n">
+      <c r="Y23" s="87" t="n">
         <v>75</v>
       </c>
-      <c r="Y23" s="87" t="n">
+      <c r="Z23" s="87" t="n">
         <v>201</v>
       </c>
-      <c r="Z23" s="87" t="n">
+      <c r="AA23" s="87" t="n">
         <v>202</v>
       </c>
-      <c r="AA23" s="87" t="n">
+      <c r="AB23" s="87" t="n">
         <v>328</v>
       </c>
-      <c r="AB23" s="87" t="n">
+      <c r="AC23" s="87" t="n">
         <v>332</v>
       </c>
-      <c r="AC23" s="87" t="n">
+      <c r="AD23" s="87" t="n">
         <v>196</v>
       </c>
-      <c r="AD23" s="87" t="n">
+      <c r="AE23" s="87" t="n">
         <v>172</v>
-      </c>
-      <c r="AE23" s="87" t="n">
-        <v>356</v>
       </c>
     </row>
     <row r="24">
@@ -3800,94 +3799,94 @@
         </is>
       </c>
       <c r="B24" s="87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" s="87" t="n">
         <v>4</v>
       </c>
       <c r="D24" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="E24" s="87" t="n">
+      <c r="F24" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="87" t="n">
+      <c r="G24" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="87" t="n">
+      <c r="H24" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="H24" s="87" t="n">
+      <c r="I24" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="I24" s="87" t="n">
+      <c r="J24" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="J24" s="87" t="n">
+      <c r="K24" s="87" t="n">
         <v>16</v>
       </c>
-      <c r="K24" s="87" t="n">
+      <c r="L24" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="L24" s="87" t="n">
+      <c r="M24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="M24" s="87" t="n">
+      <c r="N24" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="N24" s="87" t="n">
+      <c r="O24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="O24" s="87" t="n">
+      <c r="P24" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="P24" s="87" t="n">
+      <c r="Q24" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="Q24" s="87" t="n">
+      <c r="R24" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="87" t="n">
+      <c r="S24" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="S24" s="87" t="n">
+      <c r="T24" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="T24" s="87" t="n">
+      <c r="U24" s="87" t="n">
         <v>15</v>
       </c>
-      <c r="U24" s="87" t="n">
+      <c r="V24" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="87" t="n">
+      <c r="W24" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="W24" s="87" t="n">
+      <c r="X24" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="X24" s="87" t="n">
+      <c r="Y24" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" s="87" t="n">
+      <c r="Z24" s="87" t="n">
         <v>20</v>
       </c>
-      <c r="Z24" s="87" t="n">
+      <c r="AA24" s="87" t="n">
         <v>21</v>
       </c>
-      <c r="AA24" s="87" t="n">
+      <c r="AB24" s="87" t="n">
         <v>33</v>
       </c>
-      <c r="AB24" s="87" t="n">
+      <c r="AC24" s="87" t="n">
         <v>44</v>
       </c>
-      <c r="AC24" s="87" t="n">
+      <c r="AD24" s="87" t="n">
         <v>22</v>
       </c>
-      <c r="AD24" s="87" t="n">
+      <c r="AE24" s="87" t="n">
         <v>17</v>
-      </c>
-      <c r="AE24" s="87" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -3897,22 +3896,22 @@
         </is>
       </c>
       <c r="B25" s="89" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C25" s="89" t="n">
         <v>7.29</v>
       </c>
-      <c r="C25" s="89" t="n">
+      <c r="D25" s="89" t="n">
         <v>7.28</v>
-      </c>
-      <c r="D25" s="89" t="n">
-        <v>7.29</v>
       </c>
       <c r="E25" s="89" t="n">
         <v>7.29</v>
       </c>
       <c r="F25" s="89" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="G25" s="89" t="n">
         <v>7.28</v>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>7.27</v>
       </c>
       <c r="H25" s="89" t="n">
         <v>7.27</v>
@@ -3924,13 +3923,13 @@
         <v>7.27</v>
       </c>
       <c r="K25" s="89" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="L25" s="89" t="n">
         <v>7.26</v>
       </c>
-      <c r="L25" s="89" t="n">
+      <c r="M25" s="89" t="n">
         <v>7.27</v>
-      </c>
-      <c r="M25" s="89" t="n">
-        <v>7.26</v>
       </c>
       <c r="N25" s="89" t="n">
         <v>7.26</v>
@@ -3939,22 +3938,22 @@
         <v>7.26</v>
       </c>
       <c r="P25" s="89" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="Q25" s="89" t="n">
         <v>7.25</v>
       </c>
       <c r="R25" s="89" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S25" s="89" t="n">
         <v>7.26</v>
       </c>
-      <c r="S25" s="89" t="n">
+      <c r="T25" s="89" t="n">
         <v>7.25</v>
       </c>
-      <c r="T25" s="89" t="n">
+      <c r="U25" s="89" t="n">
         <v>7.27</v>
-      </c>
-      <c r="U25" s="89" t="n">
-        <v>7.26</v>
       </c>
       <c r="V25" s="89" t="n">
         <v>7.26</v>
@@ -3966,7 +3965,7 @@
         <v>7.26</v>
       </c>
       <c r="Y25" s="89" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="Z25" s="89" t="n">
         <v>7.25</v>
@@ -3975,16 +3974,16 @@
         <v>7.25</v>
       </c>
       <c r="AB25" s="89" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AC25" s="89" t="n">
         <v>7.23</v>
       </c>
-      <c r="AC25" s="89" t="n">
+      <c r="AD25" s="89" t="n">
         <v>7.22</v>
       </c>
-      <c r="AD25" s="89" t="n">
+      <c r="AE25" s="89" t="n">
         <v>7.21</v>
-      </c>
-      <c r="AE25" s="89" t="n">
-        <v>7.24</v>
       </c>
     </row>
     <row r="26">
@@ -3994,94 +3993,94 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C26" s="90" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C26" s="90" t="n">
+      <c r="D26" s="89" t="n">
         <v>-0.08</v>
       </c>
-      <c r="D26" s="89" t="n">
+      <c r="E26" s="89" t="n">
         <v>-0.03</v>
       </c>
-      <c r="E26" s="89" t="n">
+      <c r="F26" s="89" t="n">
         <v>0.17</v>
       </c>
-      <c r="F26" s="89" t="n">
+      <c r="G26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="G26" s="89" t="n">
+      <c r="H26" s="89" t="n">
         <v>0.04</v>
       </c>
-      <c r="H26" s="89" t="n">
+      <c r="I26" s="89" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I26" s="89" t="n">
+      <c r="J26" s="89" t="n">
         <v>-0</v>
       </c>
-      <c r="J26" s="89" t="n">
+      <c r="K26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="K26" s="89" t="n">
+      <c r="L26" s="89" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L26" s="89" t="n">
+      <c r="M26" s="89" t="n">
         <v>0.14</v>
       </c>
-      <c r="M26" s="89" t="n">
+      <c r="N26" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="N26" s="89" t="n">
+      <c r="O26" s="89" t="n">
         <v>0.05</v>
       </c>
-      <c r="O26" s="89" t="n">
+      <c r="P26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="P26" s="89" t="n">
+      <c r="Q26" s="89" t="n">
         <v>-0.01</v>
       </c>
-      <c r="Q26" s="89" t="n">
+      <c r="R26" s="89" t="n">
         <v>-0.16</v>
       </c>
-      <c r="R26" s="89" t="n">
+      <c r="S26" s="89" t="n">
         <v>0.15</v>
       </c>
-      <c r="S26" s="89" t="n">
+      <c r="T26" s="89" t="n">
         <v>-0.3</v>
       </c>
-      <c r="T26" s="89" t="n">
+      <c r="U26" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="U26" s="89" t="n">
+      <c r="V26" s="89" t="n">
         <v>0.08</v>
       </c>
-      <c r="V26" s="89" t="n">
+      <c r="W26" s="89" t="n">
         <v>-0.04</v>
       </c>
-      <c r="W26" s="89" t="n">
+      <c r="X26" s="89" t="n">
         <v>0.05</v>
-      </c>
-      <c r="X26" s="89" t="n">
-        <v>0.06</v>
       </c>
       <c r="Y26" s="89" t="n">
         <v>0.06</v>
       </c>
       <c r="Z26" s="89" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA26" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="AA26" s="89" t="n">
+      <c r="AB26" s="89" t="n">
         <v>0.19</v>
       </c>
-      <c r="AB26" s="89" t="n">
+      <c r="AC26" s="89" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC26" s="89" t="n">
+      <c r="AD26" s="89" t="n">
         <v>0.18</v>
       </c>
-      <c r="AD26" s="89" t="n">
+      <c r="AE26" s="89" t="n">
         <v>-0.44</v>
-      </c>
-      <c r="AE26" s="89" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="27">
@@ -4091,94 +4090,94 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C27" s="90" t="n">
         <v>0.42</v>
       </c>
-      <c r="C27" s="90" t="n">
+      <c r="D27" s="89" t="n">
         <v>0.31</v>
       </c>
-      <c r="D27" s="89" t="n">
+      <c r="E27" s="89" t="n">
         <v>0.44</v>
       </c>
-      <c r="E27" s="89" t="n">
+      <c r="F27" s="89" t="n">
         <v>0.53</v>
       </c>
-      <c r="F27" s="89" t="n">
+      <c r="G27" s="89" t="n">
         <v>0.43</v>
       </c>
-      <c r="G27" s="89" t="n">
+      <c r="H27" s="89" t="n">
         <v>0.36</v>
       </c>
-      <c r="H27" s="89" t="n">
+      <c r="I27" s="89" t="n">
         <v>0.51</v>
       </c>
-      <c r="I27" s="89" t="n">
+      <c r="J27" s="89" t="n">
         <v>0.65</v>
       </c>
-      <c r="J27" s="89" t="n">
+      <c r="K27" s="89" t="n">
         <v>0.84</v>
       </c>
-      <c r="K27" s="89" t="n">
+      <c r="L27" s="89" t="n">
         <v>0.3</v>
       </c>
-      <c r="L27" s="89" t="n">
+      <c r="M27" s="89" t="n">
         <v>0.46</v>
       </c>
-      <c r="M27" s="89" t="n">
+      <c r="N27" s="89" t="n">
         <v>0.39</v>
       </c>
-      <c r="N27" s="89" t="n">
+      <c r="O27" s="89" t="n">
         <v>0.55</v>
       </c>
-      <c r="O27" s="89" t="n">
+      <c r="P27" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="P27" s="89" t="n">
+      <c r="Q27" s="89" t="n">
         <v>0.32</v>
       </c>
-      <c r="Q27" s="89" t="n">
+      <c r="R27" s="89" t="n">
         <v>0.45</v>
       </c>
-      <c r="R27" s="89" t="n">
+      <c r="S27" s="89" t="n">
         <v>0.11</v>
       </c>
-      <c r="S27" s="89" t="n">
+      <c r="T27" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="T27" s="89" t="n">
+      <c r="U27" s="89" t="n">
         <v>0.06</v>
       </c>
-      <c r="U27" s="89" t="n">
+      <c r="V27" s="89" t="n">
         <v>0.12</v>
       </c>
-      <c r="V27" s="89" t="n">
+      <c r="W27" s="89" t="n">
         <v>-0.2</v>
       </c>
-      <c r="W27" s="89" t="n">
+      <c r="X27" s="89" t="n">
         <v>0.03</v>
       </c>
-      <c r="X27" s="89" t="n">
+      <c r="Y27" s="89" t="n">
         <v>0.09</v>
       </c>
-      <c r="Y27" s="89" t="n">
+      <c r="Z27" s="89" t="n">
         <v>0.04</v>
       </c>
-      <c r="Z27" s="89" t="n">
+      <c r="AA27" s="89" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AA27" s="89" t="n">
+      <c r="AB27" s="89" t="n">
         <v>0.02</v>
       </c>
-      <c r="AB27" s="89" t="n">
+      <c r="AC27" s="89" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AC27" s="89" t="n">
+      <c r="AD27" s="89" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AD27" s="89" t="n">
+      <c r="AE27" s="89" t="n">
         <v>-0.77</v>
-      </c>
-      <c r="AE27" s="89" t="n">
-        <v>-0.16</v>
       </c>
     </row>
     <row r="28">
@@ -4188,94 +4187,94 @@
         </is>
       </c>
       <c r="B28" s="87" t="n">
+        <v>2557</v>
+      </c>
+      <c r="C28" s="87" t="n">
         <v>2517</v>
       </c>
-      <c r="C28" s="87" t="n">
+      <c r="D28" s="87" t="n">
         <v>2535</v>
       </c>
-      <c r="D28" s="87" t="n">
+      <c r="E28" s="87" t="n">
         <v>2579</v>
       </c>
-      <c r="E28" s="87" t="n">
+      <c r="F28" s="87" t="n">
         <v>2583</v>
       </c>
-      <c r="F28" s="87" t="n">
+      <c r="G28" s="87" t="n">
         <v>2617</v>
       </c>
-      <c r="G28" s="87" t="n">
+      <c r="H28" s="87" t="n">
         <v>2640</v>
       </c>
-      <c r="H28" s="87" t="n">
+      <c r="I28" s="87" t="n">
         <v>2624</v>
       </c>
-      <c r="I28" s="87" t="n">
+      <c r="J28" s="87" t="n">
         <v>2629</v>
       </c>
-      <c r="J28" s="87" t="n">
+      <c r="K28" s="87" t="n">
         <v>2614</v>
       </c>
-      <c r="K28" s="87" t="n">
+      <c r="L28" s="87" t="n">
         <v>2629</v>
       </c>
-      <c r="L28" s="87" t="n">
+      <c r="M28" s="87" t="n">
         <v>2628</v>
       </c>
-      <c r="M28" s="87" t="n">
+      <c r="N28" s="87" t="n">
         <v>2624</v>
       </c>
-      <c r="N28" s="87" t="n">
+      <c r="O28" s="87" t="n">
         <v>2634</v>
       </c>
-      <c r="O28" s="87" t="n">
+      <c r="P28" s="87" t="n">
         <v>2656</v>
       </c>
-      <c r="P28" s="87" t="n">
+      <c r="Q28" s="87" t="n">
         <v>2679</v>
       </c>
-      <c r="Q28" s="87" t="n">
+      <c r="R28" s="87" t="n">
         <v>2654</v>
       </c>
-      <c r="R28" s="87" t="n">
+      <c r="S28" s="87" t="n">
         <v>2676</v>
       </c>
-      <c r="S28" s="87" t="n">
+      <c r="T28" s="87" t="n">
         <v>2677</v>
       </c>
-      <c r="T28" s="87" t="n">
+      <c r="U28" s="87" t="n">
         <v>2680</v>
       </c>
-      <c r="U28" s="87" t="n">
+      <c r="V28" s="87" t="n">
         <v>2678</v>
       </c>
-      <c r="V28" s="87" t="n">
+      <c r="W28" s="87" t="n">
         <v>2700</v>
       </c>
-      <c r="W28" s="87" t="n">
+      <c r="X28" s="87" t="n">
         <v>2677</v>
       </c>
-      <c r="X28" s="87" t="n">
+      <c r="Y28" s="87" t="n">
         <v>2709</v>
       </c>
-      <c r="Y28" s="87" t="n">
+      <c r="Z28" s="87" t="n">
         <v>2753</v>
       </c>
-      <c r="Z28" s="87" t="n">
+      <c r="AA28" s="87" t="n">
         <v>2755</v>
       </c>
-      <c r="AA28" s="87" t="n">
+      <c r="AB28" s="87" t="n">
         <v>2773</v>
       </c>
-      <c r="AB28" s="87" t="n">
+      <c r="AC28" s="87" t="n">
         <v>2768</v>
       </c>
-      <c r="AC28" s="87" t="n">
+      <c r="AD28" s="87" t="n">
         <v>2722</v>
       </c>
-      <c r="AD28" s="87" t="n">
+      <c r="AE28" s="87" t="n">
         <v>2725</v>
-      </c>
-      <c r="AE28" s="87" t="n">
-        <v>2748</v>
       </c>
     </row>
     <row r="29">
@@ -4285,94 +4284,94 @@
         </is>
       </c>
       <c r="B29" s="87" t="n">
+        <v>13009.41</v>
+      </c>
+      <c r="C29" s="87" t="n">
         <v>12884.06</v>
       </c>
-      <c r="C29" s="87" t="n">
+      <c r="D29" s="87" t="n">
         <v>13099.14</v>
       </c>
-      <c r="D29" s="87" t="n">
+      <c r="E29" s="87" t="n">
         <v>13076.01</v>
       </c>
-      <c r="E29" s="87" t="n">
+      <c r="F29" s="87" t="n">
         <v>13873.58</v>
       </c>
-      <c r="F29" s="87" t="n">
+      <c r="G29" s="87" t="n">
         <v>13753.52</v>
       </c>
-      <c r="G29" s="87" t="n">
+      <c r="H29" s="87" t="n">
         <v>13974.58</v>
       </c>
-      <c r="H29" s="87" t="n">
+      <c r="I29" s="87" t="n">
         <v>13651.6</v>
       </c>
-      <c r="I29" s="87" t="n">
+      <c r="J29" s="87" t="n">
         <v>14297.64</v>
       </c>
-      <c r="J29" s="87" t="n">
+      <c r="K29" s="87" t="n">
         <v>13887.31</v>
       </c>
-      <c r="K29" s="87" t="n">
+      <c r="L29" s="87" t="n">
         <v>13676.26</v>
       </c>
-      <c r="L29" s="87" t="n">
+      <c r="M29" s="87" t="n">
         <v>14085.55</v>
       </c>
-      <c r="M29" s="87" t="n">
+      <c r="N29" s="87" t="n">
         <v>13874.95</v>
       </c>
-      <c r="N29" s="87" t="n">
+      <c r="O29" s="87" t="n">
         <v>14300.01</v>
       </c>
-      <c r="O29" s="87" t="n">
+      <c r="P29" s="87" t="n">
         <v>13513.73</v>
       </c>
-      <c r="P29" s="87" t="n">
+      <c r="Q29" s="87" t="n">
         <v>13855.46</v>
       </c>
-      <c r="Q29" s="87" t="n">
+      <c r="R29" s="87" t="n">
         <v>13994.74</v>
       </c>
-      <c r="R29" s="87" t="n">
+      <c r="S29" s="87" t="n">
         <v>13436.37</v>
       </c>
-      <c r="S29" s="87" t="n">
+      <c r="T29" s="87" t="n">
         <v>13431.28</v>
       </c>
-      <c r="T29" s="87" t="n">
+      <c r="U29" s="87" t="n">
         <v>13315.67</v>
       </c>
-      <c r="U29" s="87" t="n">
+      <c r="V29" s="87" t="n">
         <v>12995.34</v>
       </c>
-      <c r="V29" s="87" t="n">
+      <c r="W29" s="87" t="n">
         <v>13417.35</v>
       </c>
-      <c r="W29" s="87" t="n">
+      <c r="X29" s="87" t="n">
         <v>13400.53</v>
       </c>
-      <c r="X29" s="87" t="n">
+      <c r="Y29" s="87" t="n">
         <v>13682.26</v>
       </c>
-      <c r="Y29" s="87" t="n">
+      <c r="Z29" s="87" t="n">
         <v>13684.07</v>
       </c>
-      <c r="Z29" s="87" t="n">
+      <c r="AA29" s="87" t="n">
         <v>13695.7</v>
       </c>
-      <c r="AA29" s="87" t="n">
+      <c r="AB29" s="87" t="n">
         <v>14009.49</v>
       </c>
-      <c r="AB29" s="87" t="n">
+      <c r="AC29" s="87" t="n">
         <v>14200.74</v>
       </c>
-      <c r="AC29" s="87" t="n">
+      <c r="AD29" s="87" t="n">
         <v>14644.3</v>
       </c>
-      <c r="AD29" s="87" t="n">
+      <c r="AE29" s="87" t="n">
         <v>14427.61</v>
-      </c>
-      <c r="AE29" s="87" t="n">
-        <v>14647.14</v>
       </c>
     </row>
     <row r="30">
@@ -4382,43 +4381,43 @@
         </is>
       </c>
       <c r="B30" s="91" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="C30" s="91" t="n">
         <v>46.82</v>
       </c>
-      <c r="C30" s="91" t="n">
+      <c r="D30" s="91" t="n">
         <v>46.89</v>
       </c>
-      <c r="D30" s="91" t="n">
+      <c r="E30" s="91" t="n">
         <v>46.93</v>
       </c>
-      <c r="E30" s="91" t="n">
+      <c r="F30" s="91" t="n">
         <v>47.08</v>
       </c>
-      <c r="F30" s="91" t="n">
+      <c r="G30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="G30" s="91" t="n">
+      <c r="H30" s="91" t="n">
         <v>46.95</v>
       </c>
-      <c r="H30" s="91" t="n">
+      <c r="I30" s="91" t="n">
         <v>47.06</v>
       </c>
-      <c r="I30" s="91" t="n">
+      <c r="J30" s="91" t="n">
         <v>47.11</v>
       </c>
-      <c r="J30" s="91" t="n">
+      <c r="K30" s="91" t="n">
         <v>47.16</v>
       </c>
-      <c r="K30" s="91" t="n">
+      <c r="L30" s="91" t="n">
         <v>47.19</v>
       </c>
-      <c r="L30" s="91" t="n">
+      <c r="M30" s="91" t="n">
         <v>47.2</v>
       </c>
-      <c r="M30" s="91" t="n">
+      <c r="N30" s="91" t="n">
         <v>47.23</v>
-      </c>
-      <c r="N30" s="91" t="n">
-        <v>47.31</v>
       </c>
       <c r="O30" s="91" t="n">
         <v>47.31</v>
@@ -4427,49 +4426,49 @@
         <v>47.31</v>
       </c>
       <c r="Q30" s="91" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="R30" s="91" t="n">
         <v>47.32</v>
       </c>
-      <c r="R30" s="91" t="n">
+      <c r="S30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="S30" s="91" t="n">
+      <c r="T30" s="91" t="n">
         <v>47.16</v>
       </c>
-      <c r="T30" s="91" t="n">
+      <c r="U30" s="91" t="n">
         <v>47.24</v>
       </c>
-      <c r="U30" s="91" t="n">
+      <c r="V30" s="91" t="n">
         <v>47.3</v>
       </c>
-      <c r="V30" s="91" t="n">
+      <c r="W30" s="91" t="n">
         <v>47.27</v>
       </c>
-      <c r="W30" s="91" t="n">
+      <c r="X30" s="91" t="n">
         <v>47.19</v>
       </c>
-      <c r="X30" s="91" t="n">
+      <c r="Y30" s="91" t="n">
         <v>47.25</v>
       </c>
-      <c r="Y30" s="91" t="n">
+      <c r="Z30" s="91" t="n">
         <v>47.08</v>
       </c>
-      <c r="Z30" s="91" t="n">
+      <c r="AA30" s="91" t="n">
         <v>46.99</v>
       </c>
-      <c r="AA30" s="91" t="n">
+      <c r="AB30" s="91" t="n">
         <v>47.01</v>
       </c>
-      <c r="AB30" s="91" t="n">
+      <c r="AC30" s="91" t="n">
         <v>46.92</v>
       </c>
-      <c r="AC30" s="91" t="n">
+      <c r="AD30" s="91" t="n">
         <v>47.16</v>
       </c>
-      <c r="AD30" s="91" t="n">
+      <c r="AE30" s="91" t="n">
         <v>47.13</v>
-      </c>
-      <c r="AE30" s="91" t="n">
-        <v>47.06</v>
       </c>
     </row>
     <row r="31">
@@ -4479,94 +4478,94 @@
         </is>
       </c>
       <c r="B31" s="87" t="n">
+        <v>-825.4299999999999</v>
+      </c>
+      <c r="C31" s="87" t="n">
         <v>-819.33</v>
       </c>
-      <c r="C31" s="87" t="n">
+      <c r="D31" s="87" t="n">
         <v>-814.1799999999999</v>
       </c>
-      <c r="D31" s="87" t="n">
+      <c r="E31" s="87" t="n">
         <v>-803.74</v>
       </c>
-      <c r="E31" s="87" t="n">
+      <c r="F31" s="87" t="n">
         <v>-809.09</v>
       </c>
-      <c r="F31" s="87" t="n">
+      <c r="G31" s="87" t="n">
         <v>-821.67</v>
       </c>
-      <c r="G31" s="87" t="n">
+      <c r="H31" s="87" t="n">
         <v>-851.8099999999999</v>
       </c>
-      <c r="H31" s="87" t="n">
+      <c r="I31" s="87" t="n">
         <v>-803.37</v>
       </c>
-      <c r="I31" s="87" t="n">
+      <c r="J31" s="87" t="n">
         <v>-827.16</v>
       </c>
-      <c r="J31" s="87" t="n">
+      <c r="K31" s="87" t="n">
         <v>-788.48</v>
       </c>
-      <c r="K31" s="87" t="n">
+      <c r="L31" s="87" t="n">
         <v>-768.4</v>
       </c>
-      <c r="L31" s="87" t="n">
+      <c r="M31" s="87" t="n">
         <v>-787.86</v>
       </c>
-      <c r="M31" s="87" t="n">
+      <c r="N31" s="87" t="n">
         <v>-768.96</v>
       </c>
-      <c r="N31" s="87" t="n">
+      <c r="O31" s="87" t="n">
         <v>-770.47</v>
       </c>
-      <c r="O31" s="87" t="n">
+      <c r="P31" s="87" t="n">
         <v>-726.3099999999999</v>
       </c>
-      <c r="P31" s="87" t="n">
+      <c r="Q31" s="87" t="n">
         <v>-746.26</v>
       </c>
-      <c r="Q31" s="87" t="n">
+      <c r="R31" s="87" t="n">
         <v>-749.58</v>
       </c>
-      <c r="R31" s="87" t="n">
+      <c r="S31" s="87" t="n">
         <v>-803.5</v>
       </c>
-      <c r="S31" s="87" t="n">
+      <c r="T31" s="87" t="n">
         <v>-762.4400000000001</v>
       </c>
-      <c r="T31" s="87" t="n">
+      <c r="U31" s="87" t="n">
         <v>-735.5599999999999</v>
       </c>
-      <c r="U31" s="87" t="n">
+      <c r="V31" s="87" t="n">
         <v>-702.0599999999999</v>
       </c>
-      <c r="V31" s="87" t="n">
+      <c r="W31" s="87" t="n">
         <v>-732.28</v>
       </c>
-      <c r="W31" s="87" t="n">
+      <c r="X31" s="87" t="n">
         <v>-753.28</v>
       </c>
-      <c r="X31" s="87" t="n">
+      <c r="Y31" s="87" t="n">
         <v>-753.6799999999999</v>
       </c>
-      <c r="Y31" s="87" t="n">
+      <c r="Z31" s="87" t="n">
         <v>-799.49</v>
       </c>
-      <c r="Z31" s="87" t="n">
+      <c r="AA31" s="87" t="n">
         <v>-824.87</v>
       </c>
-      <c r="AA31" s="87" t="n">
+      <c r="AB31" s="87" t="n">
         <v>-838.41</v>
       </c>
-      <c r="AB31" s="87" t="n">
+      <c r="AC31" s="87" t="n">
         <v>-875.21</v>
       </c>
-      <c r="AC31" s="87" t="n">
+      <c r="AD31" s="87" t="n">
         <v>-833.22</v>
       </c>
-      <c r="AD31" s="87" t="n">
+      <c r="AE31" s="87" t="n">
         <v>-828.75</v>
-      </c>
-      <c r="AE31" s="87" t="n">
-        <v>-861.96</v>
       </c>
     </row>
     <row r="32">
@@ -4576,94 +4575,94 @@
         </is>
       </c>
       <c r="B32" s="87" t="n">
+        <v>-25508</v>
+      </c>
+      <c r="C32" s="87" t="n">
         <v>-19781</v>
       </c>
-      <c r="C32" s="87" t="n">
+      <c r="D32" s="87" t="n">
         <v>-16900</v>
       </c>
-      <c r="D32" s="87" t="n">
+      <c r="E32" s="87" t="n">
         <v>-16002</v>
       </c>
-      <c r="E32" s="87" t="n">
+      <c r="F32" s="87" t="n">
         <v>-33405</v>
       </c>
-      <c r="F32" s="87" t="n">
+      <c r="G32" s="87" t="n">
         <v>-30696</v>
       </c>
-      <c r="G32" s="87" t="n">
+      <c r="H32" s="87" t="n">
         <v>-26217</v>
       </c>
-      <c r="H32" s="87" t="n">
+      <c r="I32" s="87" t="n">
         <v>-16494</v>
       </c>
-      <c r="I32" s="87" t="n">
+      <c r="J32" s="87" t="n">
         <v>-26084</v>
       </c>
-      <c r="J32" s="87" t="n">
+      <c r="K32" s="87" t="n">
         <v>-24283</v>
       </c>
-      <c r="K32" s="87" t="n">
+      <c r="L32" s="87" t="n">
         <v>-24887</v>
       </c>
-      <c r="L32" s="87" t="n">
+      <c r="M32" s="87" t="n">
         <v>-28237</v>
       </c>
-      <c r="M32" s="87" t="n">
+      <c r="N32" s="87" t="n">
         <v>-27204</v>
       </c>
-      <c r="N32" s="87" t="n">
+      <c r="O32" s="87" t="n">
         <v>-29347</v>
       </c>
-      <c r="O32" s="87" t="n">
+      <c r="P32" s="87" t="n">
         <v>-21316</v>
       </c>
-      <c r="P32" s="87" t="n">
+      <c r="Q32" s="87" t="n">
         <v>-27707</v>
       </c>
-      <c r="Q32" s="87" t="n">
+      <c r="R32" s="87" t="n">
         <v>-25723</v>
       </c>
-      <c r="R32" s="87" t="n">
+      <c r="S32" s="87" t="n">
         <v>-30642</v>
       </c>
-      <c r="S32" s="87" t="n">
+      <c r="T32" s="87" t="n">
         <v>-25064</v>
       </c>
-      <c r="T32" s="87" t="n">
+      <c r="U32" s="87" t="n">
         <v>-14410</v>
       </c>
-      <c r="U32" s="87" t="n">
+      <c r="V32" s="87" t="n">
         <v>-17749</v>
       </c>
-      <c r="V32" s="87" t="n">
+      <c r="W32" s="87" t="n">
         <v>-22631</v>
       </c>
-      <c r="W32" s="87" t="n">
+      <c r="X32" s="87" t="n">
         <v>-24009</v>
       </c>
-      <c r="X32" s="87" t="n">
+      <c r="Y32" s="87" t="n">
         <v>-21715</v>
       </c>
-      <c r="Y32" s="87" t="n">
+      <c r="Z32" s="87" t="n">
         <v>-19175</v>
       </c>
-      <c r="Z32" s="87" t="n">
+      <c r="AA32" s="87" t="n">
         <v>-17642</v>
       </c>
-      <c r="AA32" s="87" t="n">
+      <c r="AB32" s="87" t="n">
         <v>-22961</v>
       </c>
-      <c r="AB32" s="87" t="n">
+      <c r="AC32" s="87" t="n">
         <v>-30279</v>
       </c>
-      <c r="AC32" s="87" t="n">
+      <c r="AD32" s="87" t="n">
         <v>-35761</v>
       </c>
-      <c r="AD32" s="87" t="n">
+      <c r="AE32" s="87" t="n">
         <v>-31934</v>
-      </c>
-      <c r="AE32" s="87" t="n">
-        <v>-24510</v>
       </c>
     </row>
     <row r="33">
@@ -4673,94 +4672,94 @@
         </is>
       </c>
       <c r="B33" s="87" t="n">
+        <v>4801</v>
+      </c>
+      <c r="C33" s="87" t="n">
         <v>5573</v>
       </c>
-      <c r="C33" s="87" t="n">
+      <c r="D33" s="87" t="n">
         <v>9176</v>
       </c>
-      <c r="D33" s="87" t="n">
+      <c r="E33" s="87" t="n">
         <v>8193</v>
       </c>
-      <c r="E33" s="87" t="n">
+      <c r="F33" s="87" t="n">
         <v>8093</v>
       </c>
-      <c r="F33" s="87" t="n">
+      <c r="G33" s="87" t="n">
         <v>8585</v>
       </c>
-      <c r="G33" s="87" t="n">
+      <c r="H33" s="87" t="n">
         <v>7465</v>
       </c>
-      <c r="H33" s="87" t="n">
+      <c r="I33" s="87" t="n">
         <v>6232</v>
       </c>
-      <c r="I33" s="87" t="n">
+      <c r="J33" s="87" t="n">
         <v>7286</v>
       </c>
-      <c r="J33" s="87" t="n">
+      <c r="K33" s="87" t="n">
         <v>7615</v>
       </c>
-      <c r="K33" s="87" t="n">
+      <c r="L33" s="87" t="n">
         <v>7344</v>
       </c>
-      <c r="L33" s="87" t="n">
+      <c r="M33" s="87" t="n">
         <v>8297</v>
       </c>
-      <c r="M33" s="87" t="n">
+      <c r="N33" s="87" t="n">
         <v>8757</v>
       </c>
-      <c r="N33" s="87" t="n">
+      <c r="O33" s="87" t="n">
         <v>6268</v>
       </c>
-      <c r="O33" s="87" t="n">
+      <c r="P33" s="87" t="n">
         <v>7513</v>
       </c>
-      <c r="P33" s="87" t="n">
+      <c r="Q33" s="87" t="n">
         <v>7055</v>
       </c>
-      <c r="Q33" s="87" t="n">
+      <c r="R33" s="87" t="n">
         <v>4167</v>
       </c>
-      <c r="R33" s="87" t="n">
+      <c r="S33" s="87" t="n">
         <v>825</v>
       </c>
-      <c r="S33" s="87" t="n">
+      <c r="T33" s="87" t="n">
         <v>1656</v>
       </c>
-      <c r="T33" s="87" t="n">
+      <c r="U33" s="87" t="n">
         <v>4911</v>
       </c>
-      <c r="U33" s="87" t="n">
+      <c r="V33" s="87" t="n">
         <v>10067</v>
       </c>
-      <c r="V33" s="87" t="n">
+      <c r="W33" s="87" t="n">
         <v>7777</v>
       </c>
-      <c r="W33" s="87" t="n">
+      <c r="X33" s="87" t="n">
         <v>5332</v>
       </c>
-      <c r="X33" s="87" t="n">
+      <c r="Y33" s="87" t="n">
         <v>7800</v>
       </c>
-      <c r="Y33" s="87" t="n">
+      <c r="Z33" s="87" t="n">
         <v>5405</v>
       </c>
-      <c r="Z33" s="87" t="n">
+      <c r="AA33" s="87" t="n">
         <v>6378</v>
       </c>
-      <c r="AA33" s="87" t="n">
+      <c r="AB33" s="87" t="n">
         <v>3153</v>
       </c>
-      <c r="AB33" s="87" t="n">
+      <c r="AC33" s="87" t="n">
         <v>729</v>
       </c>
-      <c r="AC33" s="87" t="n">
+      <c r="AD33" s="87" t="n">
         <v>2667</v>
       </c>
-      <c r="AD33" s="87" t="n">
+      <c r="AE33" s="87" t="n">
         <v>13776</v>
-      </c>
-      <c r="AE33" s="87" t="n">
-        <v>15956</v>
       </c>
     </row>
     <row r="34">
@@ -4770,94 +4769,94 @@
         </is>
       </c>
       <c r="B34" s="87" t="n">
+        <v>-26486</v>
+      </c>
+      <c r="C34" s="87" t="n">
         <v>-25184</v>
       </c>
-      <c r="C34" s="87" t="n">
+      <c r="D34" s="87" t="n">
         <v>-25403</v>
       </c>
-      <c r="D34" s="87" t="n">
+      <c r="E34" s="87" t="n">
         <v>-25696</v>
       </c>
-      <c r="E34" s="87" t="n">
+      <c r="F34" s="87" t="n">
         <v>-32225</v>
       </c>
-      <c r="F34" s="87" t="n">
+      <c r="G34" s="87" t="n">
         <v>-24676</v>
       </c>
-      <c r="G34" s="87" t="n">
+      <c r="H34" s="87" t="n">
         <v>-24901</v>
       </c>
-      <c r="H34" s="87" t="n">
+      <c r="I34" s="87" t="n">
         <v>-23194</v>
       </c>
-      <c r="I34" s="87" t="n">
+      <c r="J34" s="87" t="n">
         <v>-31837</v>
       </c>
-      <c r="J34" s="87" t="n">
+      <c r="K34" s="87" t="n">
         <v>-32622</v>
       </c>
-      <c r="K34" s="87" t="n">
+      <c r="L34" s="87" t="n">
         <v>-32469</v>
       </c>
-      <c r="L34" s="87" t="n">
+      <c r="M34" s="87" t="n">
         <v>-33076</v>
       </c>
-      <c r="M34" s="87" t="n">
+      <c r="N34" s="87" t="n">
         <v>-30361</v>
       </c>
-      <c r="N34" s="87" t="n">
+      <c r="O34" s="87" t="n">
         <v>-28635</v>
       </c>
-      <c r="O34" s="87" t="n">
+      <c r="P34" s="87" t="n">
         <v>-26241</v>
       </c>
-      <c r="P34" s="87" t="n">
+      <c r="Q34" s="87" t="n">
         <v>-26360</v>
       </c>
-      <c r="Q34" s="87" t="n">
+      <c r="R34" s="87" t="n">
         <v>-29373</v>
       </c>
-      <c r="R34" s="87" t="n">
+      <c r="S34" s="87" t="n">
         <v>-31844</v>
       </c>
-      <c r="S34" s="87" t="n">
+      <c r="T34" s="87" t="n">
         <v>-30383</v>
       </c>
-      <c r="T34" s="87" t="n">
+      <c r="U34" s="87" t="n">
         <v>-21910</v>
       </c>
-      <c r="U34" s="87" t="n">
+      <c r="V34" s="87" t="n">
         <v>-21975</v>
       </c>
-      <c r="V34" s="87" t="n">
+      <c r="W34" s="87" t="n">
         <v>-21240</v>
       </c>
-      <c r="W34" s="87" t="n">
+      <c r="X34" s="87" t="n">
         <v>-21904</v>
       </c>
-      <c r="X34" s="87" t="n">
+      <c r="Y34" s="87" t="n">
         <v>-22144</v>
       </c>
-      <c r="Y34" s="87" t="n">
+      <c r="Z34" s="87" t="n">
         <v>-21833</v>
       </c>
-      <c r="Z34" s="87" t="n">
+      <c r="AA34" s="87" t="n">
         <v>-23667</v>
       </c>
-      <c r="AA34" s="87" t="n">
+      <c r="AB34" s="87" t="n">
         <v>-23027</v>
       </c>
-      <c r="AB34" s="87" t="n">
+      <c r="AC34" s="87" t="n">
         <v>-22034</v>
       </c>
-      <c r="AC34" s="87" t="n">
+      <c r="AD34" s="87" t="n">
         <v>-33664</v>
       </c>
-      <c r="AD34" s="87" t="n">
+      <c r="AE34" s="87" t="n">
         <v>-32281</v>
-      </c>
-      <c r="AE34" s="87" t="n">
-        <v>-29115</v>
       </c>
     </row>
     <row r="35">
@@ -4867,94 +4866,94 @@
         </is>
       </c>
       <c r="B35" s="87" t="n">
+        <v>-2833</v>
+      </c>
+      <c r="C35" s="87" t="n">
         <v>-2254</v>
       </c>
-      <c r="C35" s="87" t="n">
+      <c r="D35" s="87" t="n">
         <v>-2410</v>
       </c>
-      <c r="D35" s="87" t="n">
+      <c r="E35" s="87" t="n">
         <v>-2872</v>
       </c>
-      <c r="E35" s="87" t="n">
+      <c r="F35" s="87" t="n">
         <v>-3539</v>
       </c>
-      <c r="F35" s="87" t="n">
+      <c r="G35" s="87" t="n">
         <v>-156</v>
       </c>
-      <c r="G35" s="87" t="n">
+      <c r="H35" s="87" t="n">
         <v>-372</v>
       </c>
-      <c r="H35" s="87" t="n">
+      <c r="I35" s="87" t="n">
         <v>-156</v>
       </c>
-      <c r="I35" s="87" t="n">
+      <c r="J35" s="87" t="n">
         <v>-1628</v>
       </c>
-      <c r="J35" s="87" t="n">
+      <c r="K35" s="87" t="n">
         <v>-3979</v>
       </c>
-      <c r="K35" s="87" t="n">
+      <c r="L35" s="87" t="n">
         <v>-3829</v>
       </c>
-      <c r="L35" s="87" t="n">
+      <c r="M35" s="87" t="n">
         <v>-4389</v>
       </c>
-      <c r="M35" s="87" t="n">
+      <c r="N35" s="87" t="n">
         <v>-3228</v>
       </c>
-      <c r="N35" s="87" t="n">
+      <c r="O35" s="87" t="n">
         <v>-3925</v>
       </c>
-      <c r="O35" s="87" t="n">
+      <c r="P35" s="87" t="n">
         <v>-4189</v>
       </c>
-      <c r="P35" s="87" t="n">
+      <c r="Q35" s="87" t="n">
         <v>-3693</v>
       </c>
-      <c r="Q35" s="87" t="n">
+      <c r="R35" s="87" t="n">
         <v>-5291</v>
       </c>
-      <c r="R35" s="87" t="n">
+      <c r="S35" s="87" t="n">
         <v>-7949</v>
       </c>
-      <c r="S35" s="87" t="n">
+      <c r="T35" s="87" t="n">
         <v>-7149</v>
       </c>
-      <c r="T35" s="87" t="n">
+      <c r="U35" s="87" t="n">
         <v>-5836</v>
       </c>
-      <c r="U35" s="87" t="n">
+      <c r="V35" s="87" t="n">
         <v>-5763</v>
       </c>
-      <c r="V35" s="87" t="n">
+      <c r="W35" s="87" t="n">
         <v>-6288</v>
       </c>
-      <c r="W35" s="87" t="n">
+      <c r="X35" s="87" t="n">
         <v>-7760</v>
       </c>
-      <c r="X35" s="87" t="n">
+      <c r="Y35" s="87" t="n">
         <v>-6647</v>
       </c>
-      <c r="Y35" s="87" t="n">
+      <c r="Z35" s="87" t="n">
         <v>-5501</v>
       </c>
-      <c r="Z35" s="87" t="n">
+      <c r="AA35" s="87" t="n">
         <v>-6893</v>
       </c>
-      <c r="AA35" s="87" t="n">
+      <c r="AB35" s="87" t="n">
         <v>-6178</v>
       </c>
-      <c r="AB35" s="87" t="n">
+      <c r="AC35" s="87" t="n">
         <v>-7857</v>
       </c>
-      <c r="AC35" s="87" t="n">
+      <c r="AD35" s="87" t="n">
         <v>-7778</v>
       </c>
-      <c r="AD35" s="87" t="n">
+      <c r="AE35" s="87" t="n">
         <v>3316</v>
-      </c>
-      <c r="AE35" s="87" t="n">
-        <v>3068</v>
       </c>
     </row>
     <row r="36">
@@ -4964,94 +4963,94 @@
         </is>
       </c>
       <c r="B36" s="87" t="n">
+        <v>46963</v>
+      </c>
+      <c r="C36" s="87" t="n">
         <v>49904</v>
       </c>
-      <c r="C36" s="87" t="n">
+      <c r="D36" s="87" t="n">
         <v>51531</v>
       </c>
-      <c r="D36" s="87" t="n">
+      <c r="E36" s="87" t="n">
         <v>46708</v>
       </c>
-      <c r="E36" s="87" t="n">
+      <c r="F36" s="87" t="n">
         <v>39550</v>
       </c>
-      <c r="F36" s="87" t="n">
+      <c r="G36" s="87" t="n">
         <v>28850</v>
       </c>
-      <c r="G36" s="87" t="n">
+      <c r="H36" s="87" t="n">
         <v>40733</v>
       </c>
-      <c r="H36" s="87" t="n">
+      <c r="I36" s="87" t="n">
         <v>48297</v>
       </c>
-      <c r="I36" s="87" t="n">
+      <c r="J36" s="87" t="n">
         <v>52439</v>
       </c>
-      <c r="J36" s="87" t="n">
+      <c r="K36" s="87" t="n">
         <v>53889</v>
       </c>
-      <c r="K36" s="87" t="n">
+      <c r="L36" s="87" t="n">
         <v>53101</v>
       </c>
-      <c r="L36" s="87" t="n">
+      <c r="M36" s="87" t="n">
         <v>58839</v>
       </c>
-      <c r="M36" s="87" t="n">
+      <c r="N36" s="87" t="n">
         <v>65212</v>
       </c>
-      <c r="N36" s="87" t="n">
+      <c r="O36" s="87" t="n">
         <v>62949</v>
       </c>
-      <c r="O36" s="87" t="n">
+      <c r="P36" s="87" t="n">
         <v>66197</v>
       </c>
-      <c r="P36" s="87" t="n">
+      <c r="Q36" s="87" t="n">
         <v>68838</v>
       </c>
-      <c r="Q36" s="87" t="n">
+      <c r="R36" s="87" t="n">
         <v>66373</v>
       </c>
-      <c r="R36" s="87" t="n">
+      <c r="S36" s="87" t="n">
         <v>76163</v>
       </c>
-      <c r="S36" s="87" t="n">
+      <c r="T36" s="87" t="n">
         <v>70604</v>
       </c>
-      <c r="T36" s="87" t="n">
+      <c r="U36" s="87" t="n">
         <v>76315</v>
       </c>
-      <c r="U36" s="87" t="n">
+      <c r="V36" s="87" t="n">
         <v>72620</v>
       </c>
-      <c r="V36" s="87" t="n">
+      <c r="W36" s="87" t="n">
         <v>77671</v>
       </c>
-      <c r="W36" s="87" t="n">
+      <c r="X36" s="87" t="n">
         <v>82025</v>
       </c>
-      <c r="X36" s="87" t="n">
+      <c r="Y36" s="87" t="n">
         <v>84772</v>
       </c>
-      <c r="Y36" s="87" t="n">
+      <c r="Z36" s="87" t="n">
         <v>86448</v>
       </c>
-      <c r="Z36" s="87" t="n">
+      <c r="AA36" s="87" t="n">
         <v>89869</v>
       </c>
-      <c r="AA36" s="87" t="n">
+      <c r="AB36" s="87" t="n">
         <v>90418</v>
       </c>
-      <c r="AB36" s="87" t="n">
+      <c r="AC36" s="87" t="n">
         <v>93250</v>
       </c>
-      <c r="AC36" s="87" t="n">
+      <c r="AD36" s="87" t="n">
         <v>89993</v>
       </c>
-      <c r="AD36" s="87" t="n">
+      <c r="AE36" s="87" t="n">
         <v>14143</v>
-      </c>
-      <c r="AE36" s="87" t="n">
-        <v>15877</v>
       </c>
     </row>
     <row r="37">
@@ -5061,94 +5060,94 @@
         </is>
       </c>
       <c r="B37" s="87" t="n">
+        <v>132578</v>
+      </c>
+      <c r="C37" s="87" t="n">
         <v>140575</v>
       </c>
-      <c r="C37" s="87" t="n">
+      <c r="D37" s="87" t="n">
         <v>139141</v>
       </c>
-      <c r="D37" s="87" t="n">
+      <c r="E37" s="87" t="n">
         <v>142963</v>
       </c>
-      <c r="E37" s="87" t="n">
+      <c r="F37" s="87" t="n">
         <v>133783</v>
       </c>
-      <c r="F37" s="87" t="n">
+      <c r="G37" s="87" t="n">
         <v>125847</v>
       </c>
-      <c r="G37" s="87" t="n">
+      <c r="H37" s="87" t="n">
         <v>125426</v>
       </c>
-      <c r="H37" s="87" t="n">
+      <c r="I37" s="87" t="n">
         <v>124797</v>
       </c>
-      <c r="I37" s="87" t="n">
+      <c r="J37" s="87" t="n">
         <v>132489</v>
       </c>
-      <c r="J37" s="87" t="n">
+      <c r="K37" s="87" t="n">
         <v>128991</v>
       </c>
-      <c r="K37" s="87" t="n">
+      <c r="L37" s="87" t="n">
         <v>125498</v>
       </c>
-      <c r="L37" s="87" t="n">
+      <c r="M37" s="87" t="n">
         <v>126825</v>
       </c>
-      <c r="M37" s="87" t="n">
+      <c r="N37" s="87" t="n">
         <v>122035</v>
       </c>
-      <c r="N37" s="87" t="n">
+      <c r="O37" s="87" t="n">
         <v>125656</v>
       </c>
-      <c r="O37" s="87" t="n">
+      <c r="P37" s="87" t="n">
         <v>118142</v>
       </c>
-      <c r="P37" s="87" t="n">
+      <c r="Q37" s="87" t="n">
         <v>118235</v>
       </c>
-      <c r="Q37" s="87" t="n">
+      <c r="R37" s="87" t="n">
         <v>110786</v>
       </c>
-      <c r="R37" s="87" t="n">
+      <c r="S37" s="87" t="n">
         <v>122924</v>
       </c>
-      <c r="S37" s="87" t="n">
+      <c r="T37" s="87" t="n">
         <v>117927</v>
       </c>
-      <c r="T37" s="87" t="n">
+      <c r="U37" s="87" t="n">
         <v>116647</v>
       </c>
-      <c r="U37" s="87" t="n">
+      <c r="V37" s="87" t="n">
         <v>115300</v>
       </c>
-      <c r="V37" s="87" t="n">
+      <c r="W37" s="87" t="n">
         <v>115552</v>
       </c>
-      <c r="W37" s="87" t="n">
+      <c r="X37" s="87" t="n">
         <v>119400</v>
       </c>
-      <c r="X37" s="87" t="n">
+      <c r="Y37" s="87" t="n">
         <v>121852</v>
       </c>
-      <c r="Y37" s="87" t="n">
+      <c r="Z37" s="87" t="n">
         <v>129562</v>
       </c>
-      <c r="Z37" s="87" t="n">
+      <c r="AA37" s="87" t="n">
         <v>125109</v>
       </c>
-      <c r="AA37" s="87" t="n">
+      <c r="AB37" s="87" t="n">
         <v>135159</v>
       </c>
-      <c r="AB37" s="87" t="n">
+      <c r="AC37" s="87" t="n">
         <v>143826</v>
       </c>
-      <c r="AC37" s="87" t="n">
+      <c r="AD37" s="87" t="n">
         <v>128738</v>
       </c>
-      <c r="AD37" s="87" t="n">
+      <c r="AE37" s="87" t="n">
         <v>130829</v>
-      </c>
-      <c r="AE37" s="87" t="n">
-        <v>131214</v>
       </c>
     </row>
     <row r="38">
@@ -5158,94 +5157,94 @@
         </is>
       </c>
       <c r="B38" s="87" t="n">
+        <v>64086</v>
+      </c>
+      <c r="C38" s="87" t="n">
         <v>63937</v>
       </c>
-      <c r="C38" s="87" t="n">
+      <c r="D38" s="87" t="n">
         <v>64236</v>
       </c>
-      <c r="D38" s="87" t="n">
+      <c r="E38" s="87" t="n">
         <v>69431</v>
       </c>
-      <c r="E38" s="87" t="n">
+      <c r="F38" s="87" t="n">
         <v>63697</v>
       </c>
-      <c r="F38" s="87" t="n">
+      <c r="G38" s="87" t="n">
         <v>61173</v>
       </c>
-      <c r="G38" s="87" t="n">
+      <c r="H38" s="87" t="n">
         <v>62910</v>
       </c>
-      <c r="H38" s="87" t="n">
+      <c r="I38" s="87" t="n">
         <v>61723</v>
       </c>
-      <c r="I38" s="87" t="n">
+      <c r="J38" s="87" t="n">
         <v>64111</v>
       </c>
-      <c r="J38" s="87" t="n">
+      <c r="K38" s="87" t="n">
         <v>63463</v>
       </c>
-      <c r="K38" s="87" t="n">
+      <c r="L38" s="87" t="n">
         <v>58169</v>
       </c>
-      <c r="L38" s="87" t="n">
+      <c r="M38" s="87" t="n">
         <v>59356</v>
       </c>
-      <c r="M38" s="87" t="n">
+      <c r="N38" s="87" t="n">
         <v>55425</v>
       </c>
-      <c r="N38" s="87" t="n">
+      <c r="O38" s="87" t="n">
         <v>54843</v>
       </c>
-      <c r="O38" s="87" t="n">
+      <c r="P38" s="87" t="n">
         <v>52920</v>
       </c>
-      <c r="P38" s="87" t="n">
+      <c r="Q38" s="87" t="n">
         <v>53807</v>
       </c>
-      <c r="Q38" s="87" t="n">
+      <c r="R38" s="87" t="n">
         <v>53539</v>
       </c>
-      <c r="R38" s="87" t="n">
+      <c r="S38" s="87" t="n">
         <v>53866</v>
       </c>
-      <c r="S38" s="87" t="n">
+      <c r="T38" s="87" t="n">
         <v>53868</v>
       </c>
-      <c r="T38" s="87" t="n">
+      <c r="U38" s="87" t="n">
         <v>52372</v>
       </c>
-      <c r="U38" s="87" t="n">
+      <c r="V38" s="87" t="n">
         <v>51020</v>
       </c>
-      <c r="V38" s="87" t="n">
+      <c r="W38" s="87" t="n">
         <v>53738</v>
       </c>
-      <c r="W38" s="87" t="n">
+      <c r="X38" s="87" t="n">
         <v>56388</v>
       </c>
-      <c r="X38" s="87" t="n">
+      <c r="Y38" s="87" t="n">
         <v>54848</v>
       </c>
-      <c r="Y38" s="87" t="n">
+      <c r="Z38" s="87" t="n">
         <v>58393</v>
       </c>
-      <c r="Z38" s="87" t="n">
+      <c r="AA38" s="87" t="n">
         <v>56777</v>
       </c>
-      <c r="AA38" s="87" t="n">
+      <c r="AB38" s="87" t="n">
         <v>57602</v>
       </c>
-      <c r="AB38" s="87" t="n">
+      <c r="AC38" s="87" t="n">
         <v>60702</v>
       </c>
-      <c r="AC38" s="87" t="n">
+      <c r="AD38" s="87" t="n">
         <v>58706</v>
       </c>
-      <c r="AD38" s="87" t="n">
+      <c r="AE38" s="87" t="n">
         <v>59655</v>
-      </c>
-      <c r="AE38" s="87" t="n">
-        <v>60384</v>
       </c>
     </row>
     <row r="39">
@@ -5255,94 +5254,94 @@
         </is>
       </c>
       <c r="B39" s="87" t="n">
+        <v>16680</v>
+      </c>
+      <c r="C39" s="87" t="n">
         <v>16604</v>
       </c>
-      <c r="C39" s="87" t="n">
+      <c r="D39" s="87" t="n">
         <v>16985</v>
       </c>
-      <c r="D39" s="87" t="n">
+      <c r="E39" s="87" t="n">
         <v>19142</v>
       </c>
-      <c r="E39" s="87" t="n">
+      <c r="F39" s="87" t="n">
         <v>14808</v>
       </c>
-      <c r="F39" s="87" t="n">
+      <c r="G39" s="87" t="n">
         <v>9827</v>
       </c>
-      <c r="G39" s="87" t="n">
+      <c r="H39" s="87" t="n">
         <v>14015</v>
       </c>
-      <c r="H39" s="87" t="n">
+      <c r="I39" s="87" t="n">
         <v>19775</v>
       </c>
-      <c r="I39" s="87" t="n">
+      <c r="J39" s="87" t="n">
         <v>22819</v>
       </c>
-      <c r="J39" s="87" t="n">
+      <c r="K39" s="87" t="n">
         <v>21302</v>
       </c>
-      <c r="K39" s="87" t="n">
+      <c r="L39" s="87" t="n">
         <v>21844</v>
       </c>
-      <c r="L39" s="87" t="n">
+      <c r="M39" s="87" t="n">
         <v>23440</v>
       </c>
-      <c r="M39" s="87" t="n">
+      <c r="N39" s="87" t="n">
         <v>26714</v>
       </c>
-      <c r="N39" s="87" t="n">
+      <c r="O39" s="87" t="n">
         <v>23548</v>
       </c>
-      <c r="O39" s="87" t="n">
+      <c r="P39" s="87" t="n">
         <v>23276</v>
       </c>
-      <c r="P39" s="87" t="n">
+      <c r="Q39" s="87" t="n">
         <v>23891</v>
       </c>
-      <c r="Q39" s="87" t="n">
+      <c r="R39" s="87" t="n">
         <v>25503</v>
       </c>
-      <c r="R39" s="87" t="n">
+      <c r="S39" s="87" t="n">
         <v>27367</v>
       </c>
-      <c r="S39" s="87" t="n">
+      <c r="T39" s="87" t="n">
         <v>26882</v>
       </c>
-      <c r="T39" s="87" t="n">
+      <c r="U39" s="87" t="n">
         <v>26314</v>
       </c>
-      <c r="U39" s="87" t="n">
+      <c r="V39" s="87" t="n">
         <v>26343</v>
       </c>
-      <c r="V39" s="87" t="n">
+      <c r="W39" s="87" t="n">
         <v>27611</v>
       </c>
-      <c r="W39" s="87" t="n">
+      <c r="X39" s="87" t="n">
         <v>30360</v>
       </c>
-      <c r="X39" s="87" t="n">
+      <c r="Y39" s="87" t="n">
         <v>30957</v>
       </c>
-      <c r="Y39" s="87" t="n">
+      <c r="Z39" s="87" t="n">
         <v>30447</v>
       </c>
-      <c r="Z39" s="87" t="n">
+      <c r="AA39" s="87" t="n">
         <v>32090</v>
       </c>
-      <c r="AA39" s="87" t="n">
+      <c r="AB39" s="87" t="n">
         <v>31857</v>
       </c>
-      <c r="AB39" s="87" t="n">
+      <c r="AC39" s="87" t="n">
         <v>33458</v>
       </c>
-      <c r="AC39" s="87" t="n">
+      <c r="AD39" s="87" t="n">
         <v>38662</v>
       </c>
-      <c r="AD39" s="87" t="n">
+      <c r="AE39" s="87" t="n">
         <v>3733</v>
-      </c>
-      <c r="AE39" s="87" t="n">
-        <v>4401</v>
       </c>
     </row>
     <row r="41">
@@ -6505,135 +6504,135 @@
       </c>
       <c r="B2" s="93" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C2" s="94" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C2" s="93" t="inlineStr">
+      <c r="D2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D2" s="93" t="inlineStr">
+      <c r="E2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="J2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L2" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M2" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E2" s="94" t="inlineStr">
+      <c r="N2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="94" t="inlineStr">
+      <c r="O2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="94" t="inlineStr">
+      <c r="P2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="R2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="94" t="inlineStr">
+      <c r="S2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="T2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="X2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z2" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="J2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="K2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="L2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Q2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="R2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="T2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z2" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA2" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB2" s="94" t="inlineStr">
+      <c r="AB2" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -6661,7 +6660,7 @@
         </is>
       </c>
       <c r="B3" s="96" t="n">
-        <v>-3</v>
+        <v>-1.94</v>
       </c>
       <c r="C3" s="96" t="n">
         <v>-2.52</v>
@@ -6758,7 +6757,7 @@
         </is>
       </c>
       <c r="B4" s="96" t="n">
-        <v>0.89</v>
+        <v>1.98</v>
       </c>
       <c r="C4" s="96" t="n">
         <v>1.07</v>
@@ -6849,13 +6848,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="97" t="inlineStr">
+      <c r="A5" s="78" t="inlineStr">
         <is>
           <t>sh:RSI11</t>
         </is>
       </c>
       <c r="B5" s="96" t="n">
-        <v>20.66</v>
+        <v>32.09</v>
       </c>
       <c r="C5" s="96" t="n">
         <v>21.95</v>
@@ -6946,13 +6945,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="97" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>sh:RSI2</t>
         </is>
       </c>
       <c r="B6" s="96" t="n">
-        <v>0.92</v>
+        <v>56.48</v>
       </c>
       <c r="C6" s="96" t="n">
         <v>1.4</v>
@@ -7048,17 +7047,17 @@
           <t>kc:EIDE</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C7" s="93" t="inlineStr">
+      <c r="C7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D7" s="93" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7068,17 +7067,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="F7" s="94" t="inlineStr">
+      <c r="F7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G7" s="93" t="inlineStr">
+      <c r="G7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H7" s="94" t="inlineStr">
+      <c r="H7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7088,7 +7087,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J7" s="94" t="inlineStr">
+      <c r="J7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7108,17 +7107,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="N7" s="93" t="inlineStr">
+      <c r="N7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O7" s="93" t="inlineStr">
+      <c r="O7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P7" s="93" t="inlineStr">
+      <c r="P7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7138,62 +7137,62 @@
           <t>red</t>
         </is>
       </c>
-      <c r="T7" s="94" t="inlineStr">
+      <c r="T7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U7" s="94" t="inlineStr">
+      <c r="U7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V7" s="94" t="inlineStr">
+      <c r="V7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W7" s="93" t="inlineStr">
+      <c r="W7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X7" s="94" t="inlineStr">
+      <c r="X7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y7" s="93" t="inlineStr">
+      <c r="Y7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z7" s="93" t="inlineStr">
+      <c r="Z7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA7" s="94" t="inlineStr">
+      <c r="AA7" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB7" s="93" t="inlineStr">
+      <c r="AB7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC7" s="93" t="inlineStr">
+      <c r="AC7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AD7" s="93" t="inlineStr">
+      <c r="AD7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AE7" s="93" t="inlineStr">
+      <c r="AE7" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -7206,7 +7205,7 @@
         </is>
       </c>
       <c r="B8" s="96" t="n">
-        <v>-7.34</v>
+        <v>-5.5</v>
       </c>
       <c r="C8" s="96" t="n">
         <v>-8.18</v>
@@ -7303,7 +7302,7 @@
         </is>
       </c>
       <c r="B9" s="96" t="n">
-        <v>-15.16</v>
+        <v>-13.48</v>
       </c>
       <c r="C9" s="96" t="n">
         <v>-15.34</v>
@@ -7400,7 +7399,7 @@
         </is>
       </c>
       <c r="B10" s="96" t="n">
-        <v>28.18</v>
+        <v>39.18</v>
       </c>
       <c r="C10" s="96" t="n">
         <v>29.08</v>
@@ -7491,13 +7490,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="97" t="inlineStr">
+      <c r="A11" s="78" t="inlineStr">
         <is>
           <t>kc:RSI5</t>
         </is>
       </c>
       <c r="B11" s="96" t="n">
-        <v>15.25</v>
+        <v>35.46</v>
       </c>
       <c r="C11" s="96" t="n">
         <v>16.13</v>
@@ -7595,150 +7594,150 @@
       </c>
       <c r="B12" s="93" t="inlineStr">
         <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D12" s="93" t="inlineStr">
+      <c r="E12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E12" s="93" t="inlineStr">
+      <c r="F12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F12" s="93" t="inlineStr">
+      <c r="G12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G12" s="93" t="inlineStr">
+      <c r="H12" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="I12" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="J12" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H12" s="95" t="inlineStr">
+      <c r="L12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="P12" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I12" s="95" t="inlineStr">
+      <c r="R12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="J12" s="94" t="inlineStr">
+      <c r="S12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K12" s="93" t="inlineStr">
+      <c r="T12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L12" s="93" t="inlineStr">
+      <c r="U12" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M12" s="93" t="inlineStr">
+      <c r="W12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N12" s="93" t="inlineStr">
+      <c r="X12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O12" s="93" t="inlineStr">
+      <c r="Y12" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="P12" s="94" t="inlineStr">
+      <c r="Z12" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA12" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AB12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q12" s="95" t="inlineStr">
+      <c r="AC12" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S12" s="94" t="inlineStr">
+      <c r="AD12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U12" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z12" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AB12" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC12" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AD12" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE12" s="94" t="inlineStr">
+      <c r="AE12" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7751,7 +7750,7 @@
         </is>
       </c>
       <c r="B13" s="96" t="n">
-        <v>-7.27</v>
+        <v>-6.02</v>
       </c>
       <c r="C13" s="96" t="n">
         <v>-7.28</v>
@@ -7848,7 +7847,7 @@
         </is>
       </c>
       <c r="B14" s="96" t="n">
-        <v>-6.47</v>
+        <v>-5.21</v>
       </c>
       <c r="C14" s="96" t="n">
         <v>-7.24</v>
@@ -7945,7 +7944,7 @@
         </is>
       </c>
       <c r="B15" s="96" t="n">
-        <v>26.83</v>
+        <v>35.81</v>
       </c>
       <c r="C15" s="96" t="n">
         <v>23.23</v>
@@ -8042,7 +8041,7 @@
         </is>
       </c>
       <c r="B16" s="96" t="n">
-        <v>25.47</v>
+        <v>35.49</v>
       </c>
       <c r="C16" s="96" t="n">
         <v>21.37</v>
@@ -8138,22 +8137,22 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
+      <c r="C17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D17" s="94" t="inlineStr">
+      <c r="D17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E17" s="93" t="inlineStr">
+      <c r="E17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -8168,122 +8167,122 @@
           <t>red</t>
         </is>
       </c>
-      <c r="H17" s="94" t="inlineStr">
+      <c r="H17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I17" s="94" t="inlineStr">
+      <c r="I17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J17" s="94" t="inlineStr">
+      <c r="J17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K17" s="94" t="inlineStr">
+      <c r="K17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L17" s="93" t="inlineStr">
+      <c r="L17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M17" s="93" t="inlineStr">
+      <c r="M17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N17" s="94" t="inlineStr">
+      <c r="N17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O17" s="94" t="inlineStr">
+      <c r="O17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P17" s="94" t="inlineStr">
+      <c r="P17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q17" s="94" t="inlineStr">
+      <c r="Q17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R17" s="94" t="inlineStr">
+      <c r="R17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S17" s="94" t="inlineStr">
+      <c r="S17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T17" s="93" t="inlineStr">
+      <c r="T17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U17" s="93" t="inlineStr">
+      <c r="U17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V17" s="93" t="inlineStr">
+      <c r="V17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W17" s="93" t="inlineStr">
+      <c r="W17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X17" s="93" t="inlineStr">
+      <c r="X17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y17" s="93" t="inlineStr">
+      <c r="Y17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z17" s="93" t="inlineStr">
+      <c r="Z17" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA17" s="94" t="inlineStr">
+      <c r="AA17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB17" s="94" t="inlineStr">
+      <c r="AB17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC17" s="94" t="inlineStr">
+      <c r="AC17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD17" s="94" t="inlineStr">
+      <c r="AD17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE17" s="94" t="inlineStr">
+      <c r="AE17" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8296,7 +8295,7 @@
         </is>
       </c>
       <c r="B18" s="96" t="n">
-        <v>8.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C18" s="96" t="n">
         <v>9.710000000000001</v>
@@ -8393,7 +8392,7 @@
         </is>
       </c>
       <c r="B19" s="96" t="n">
-        <v>6.03</v>
+        <v>6.14</v>
       </c>
       <c r="C19" s="96" t="n">
         <v>8.710000000000001</v>
@@ -8490,7 +8489,7 @@
         </is>
       </c>
       <c r="B20" s="96" t="n">
-        <v>44.6</v>
+        <v>45.96</v>
       </c>
       <c r="C20" s="96" t="n">
         <v>44.66</v>
@@ -8587,7 +8586,7 @@
         </is>
       </c>
       <c r="B21" s="96" t="n">
-        <v>48.64</v>
+        <v>48.94</v>
       </c>
       <c r="C21" s="96" t="n">
         <v>48.66</v>
@@ -8683,27 +8682,27 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D22" s="94" t="inlineStr">
+      <c r="D22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E22" s="94" t="inlineStr">
+      <c r="E22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F22" s="94" t="inlineStr">
+      <c r="F22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8768,67 +8767,67 @@
           <t>red</t>
         </is>
       </c>
-      <c r="S22" s="94" t="inlineStr">
+      <c r="S22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T22" s="94" t="inlineStr">
+      <c r="T22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U22" s="93" t="inlineStr">
+      <c r="U22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V22" s="93" t="inlineStr">
+      <c r="V22" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W22" s="94" t="inlineStr">
+      <c r="W22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="94" t="inlineStr">
+      <c r="X22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y22" s="94" t="inlineStr">
+      <c r="Y22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z22" s="94" t="inlineStr">
+      <c r="Z22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA22" s="94" t="inlineStr">
+      <c r="AA22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB22" s="94" t="inlineStr">
+      <c r="AB22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC22" s="94" t="inlineStr">
+      <c r="AC22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD22" s="94" t="inlineStr">
+      <c r="AD22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE22" s="94" t="inlineStr">
+      <c r="AE22" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9228,12 +9227,12 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
+      <c r="C27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9268,22 +9267,22 @@
           <t>red</t>
         </is>
       </c>
-      <c r="J27" s="93" t="inlineStr">
+      <c r="J27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K27" s="94" t="inlineStr">
+      <c r="K27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L27" s="94" t="inlineStr">
+      <c r="L27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M27" s="94" t="inlineStr">
+      <c r="M27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9293,7 +9292,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="O27" s="94" t="inlineStr">
+      <c r="O27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9303,77 +9302,77 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q27" s="94" t="inlineStr">
+      <c r="Q27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R27" s="94" t="inlineStr">
+      <c r="R27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S27" s="94" t="inlineStr">
+      <c r="S27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T27" s="94" t="inlineStr">
+      <c r="T27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U27" s="93" t="inlineStr">
+      <c r="U27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V27" s="93" t="inlineStr">
+      <c r="V27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W27" s="93" t="inlineStr">
+      <c r="W27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="X27" s="93" t="inlineStr">
+      <c r="X27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Y27" s="93" t="inlineStr">
+      <c r="Y27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z27" s="93" t="inlineStr">
+      <c r="Z27" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA27" s="94" t="inlineStr">
+      <c r="AA27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB27" s="94" t="inlineStr">
+      <c r="AB27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC27" s="94" t="inlineStr">
+      <c r="AC27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD27" s="94" t="inlineStr">
+      <c r="AD27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE27" s="94" t="inlineStr">
+      <c r="AE27" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9773,37 +9772,37 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="C32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D32" s="94" t="inlineStr">
+      <c r="D32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E32" s="94" t="inlineStr">
+      <c r="E32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F32" s="94" t="inlineStr">
+      <c r="F32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G32" s="94" t="inlineStr">
+      <c r="G32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H32" s="94" t="inlineStr">
+      <c r="H32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9838,7 +9837,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="O32" s="94" t="inlineStr">
+      <c r="O32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9853,27 +9852,27 @@
           <t>red</t>
         </is>
       </c>
-      <c r="R32" s="94" t="inlineStr">
+      <c r="R32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S32" s="94" t="inlineStr">
+      <c r="S32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T32" s="94" t="inlineStr">
+      <c r="T32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U32" s="94" t="inlineStr">
+      <c r="U32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V32" s="94" t="inlineStr">
+      <c r="V32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9883,42 +9882,42 @@
           <t>red</t>
         </is>
       </c>
-      <c r="X32" s="94" t="inlineStr">
+      <c r="X32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y32" s="94" t="inlineStr">
+      <c r="Y32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z32" s="94" t="inlineStr">
+      <c r="Z32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA32" s="94" t="inlineStr">
+      <c r="AA32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB32" s="94" t="inlineStr">
+      <c r="AB32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC32" s="94" t="inlineStr">
+      <c r="AC32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD32" s="94" t="inlineStr">
+      <c r="AD32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE32" s="94" t="inlineStr">
+      <c r="AE32" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10333,42 +10332,42 @@
           <t>red</t>
         </is>
       </c>
-      <c r="E37" s="94" t="inlineStr">
+      <c r="E37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F37" s="94" t="inlineStr">
+      <c r="F37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G37" s="94" t="inlineStr">
+      <c r="G37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H37" s="93" t="inlineStr">
+      <c r="H37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I37" s="93" t="inlineStr">
+      <c r="I37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J37" s="94" t="inlineStr">
+      <c r="J37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K37" s="93" t="inlineStr">
+      <c r="K37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L37" s="94" t="inlineStr">
+      <c r="L37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10393,7 +10392,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q37" s="93" t="inlineStr">
+      <c r="Q37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10408,32 +10407,32 @@
           <t>red</t>
         </is>
       </c>
-      <c r="T37" s="93" t="inlineStr">
+      <c r="T37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U37" s="93" t="inlineStr">
+      <c r="U37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V37" s="93" t="inlineStr">
+      <c r="V37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W37" s="94" t="inlineStr">
+      <c r="W37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X37" s="94" t="inlineStr">
+      <c r="X37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y37" s="93" t="inlineStr">
+      <c r="Y37" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10443,7 +10442,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="AA37" s="94" t="inlineStr">
+      <c r="AA37" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10476,7 +10475,7 @@
         </is>
       </c>
       <c r="B38" s="96" t="n">
-        <v>-2.4</v>
+        <v>-1.66</v>
       </c>
       <c r="C38" s="96" t="n">
         <v>-2.48</v>
@@ -10573,7 +10572,7 @@
         </is>
       </c>
       <c r="B39" s="96" t="n">
-        <v>16.98</v>
+        <v>17.87</v>
       </c>
       <c r="C39" s="96" t="n">
         <v>17.62</v>
@@ -10664,13 +10663,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="98" t="inlineStr">
+      <c r="A40" s="97" t="inlineStr">
         <is>
           <t>jp225:RSI5</t>
         </is>
       </c>
       <c r="B40" s="96" t="n">
-        <v>78.16</v>
+        <v>82.73</v>
       </c>
       <c r="C40" s="96" t="n">
         <v>72.75</v>
@@ -10767,7 +10766,7 @@
         </is>
       </c>
       <c r="B41" s="96" t="n">
-        <v>65.90000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="C41" s="96" t="n">
         <v>61.88</v>
@@ -10863,47 +10862,47 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
+      <c r="B42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="93" t="inlineStr">
+      <c r="C42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="93" t="inlineStr">
+      <c r="D42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="94" t="inlineStr">
+      <c r="E42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F42" s="94" t="inlineStr">
+      <c r="F42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G42" s="93" t="inlineStr">
+      <c r="G42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="93" t="inlineStr">
+      <c r="H42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="93" t="inlineStr">
+      <c r="I42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="93" t="inlineStr">
+      <c r="J42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -10918,7 +10917,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="M42" s="94" t="inlineStr">
+      <c r="M42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10933,7 +10932,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="P42" s="94" t="inlineStr">
+      <c r="P42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10953,17 +10952,17 @@
           <t>red</t>
         </is>
       </c>
-      <c r="T42" s="93" t="inlineStr">
+      <c r="T42" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U42" s="94" t="inlineStr">
+      <c r="U42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V42" s="94" t="inlineStr">
+      <c r="V42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10973,27 +10972,27 @@
           <t>red</t>
         </is>
       </c>
-      <c r="X42" s="94" t="inlineStr">
+      <c r="X42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y42" s="94" t="inlineStr">
+      <c r="Y42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z42" s="94" t="inlineStr">
+      <c r="Z42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA42" s="94" t="inlineStr">
+      <c r="AA42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB42" s="94" t="inlineStr">
+      <c r="AB42" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11021,7 +11020,7 @@
         </is>
       </c>
       <c r="B43" s="96" t="n">
-        <v>-2.61</v>
+        <v>-2.24</v>
       </c>
       <c r="C43" s="96" t="n">
         <v>-2.07</v>
@@ -11118,7 +11117,7 @@
         </is>
       </c>
       <c r="B44" s="96" t="n">
-        <v>11.99</v>
+        <v>12.41</v>
       </c>
       <c r="C44" s="96" t="n">
         <v>11.97</v>
@@ -11209,13 +11208,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="97" t="inlineStr">
+      <c r="A45" s="78" t="inlineStr">
         <is>
           <t>vn:RSI3</t>
         </is>
       </c>
       <c r="B45" s="96" t="n">
-        <v>17.75</v>
+        <v>35.78</v>
       </c>
       <c r="C45" s="96" t="n">
         <v>17.75</v>
@@ -11312,7 +11311,7 @@
         </is>
       </c>
       <c r="B46" s="96" t="n">
-        <v>23.96</v>
+        <v>33.88</v>
       </c>
       <c r="C46" s="96" t="n">
         <v>23.96</v>
@@ -11418,22 +11417,22 @@
           <t>red</t>
         </is>
       </c>
-      <c r="D47" s="94" t="inlineStr">
+      <c r="D47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E47" s="94" t="inlineStr">
+      <c r="E47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F47" s="94" t="inlineStr">
+      <c r="F47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G47" s="94" t="inlineStr">
+      <c r="G47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11443,12 +11442,12 @@
           <t>red</t>
         </is>
       </c>
-      <c r="I47" s="94" t="inlineStr">
+      <c r="I47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J47" s="94" t="inlineStr">
+      <c r="J47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11488,7 +11487,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="R47" s="93" t="inlineStr">
+      <c r="R47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -11498,22 +11497,22 @@
           <t>red</t>
         </is>
       </c>
-      <c r="T47" s="93" t="inlineStr">
+      <c r="T47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="U47" s="93" t="inlineStr">
+      <c r="U47" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V47" s="94" t="inlineStr">
+      <c r="V47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W47" s="94" t="inlineStr">
+      <c r="W47" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11566,7 +11565,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>7.7</v>
@@ -11663,7 +11662,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>8.050000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>8.050000000000001</v>
@@ -11760,7 +11759,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>72.52</v>
+        <v>77.69</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>72.52</v>
@@ -11857,7 +11856,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>63.55</v>
+        <v>66</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>63.55</v>
@@ -11953,72 +11952,72 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B52" s="94" t="inlineStr">
+      <c r="B52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C52" s="94" t="inlineStr">
+      <c r="C52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D52" s="94" t="inlineStr">
+      <c r="D52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E52" s="94" t="inlineStr">
+      <c r="E52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F52" s="94" t="inlineStr">
+      <c r="F52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G52" s="94" t="inlineStr">
+      <c r="G52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H52" s="94" t="inlineStr">
+      <c r="H52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I52" s="93" t="inlineStr">
+      <c r="I52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J52" s="93" t="inlineStr">
+      <c r="J52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K52" s="93" t="inlineStr">
+      <c r="K52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L52" s="94" t="inlineStr">
+      <c r="L52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M52" s="93" t="inlineStr">
+      <c r="M52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="N52" s="93" t="inlineStr">
+      <c r="N52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O52" s="94" t="inlineStr">
+      <c r="O52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12028,37 +12027,37 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q52" s="94" t="inlineStr">
+      <c r="Q52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R52" s="93" t="inlineStr">
+      <c r="R52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="S52" s="94" t="inlineStr">
+      <c r="S52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T52" s="94" t="inlineStr">
+      <c r="T52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U52" s="93" t="inlineStr">
+      <c r="U52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V52" s="93" t="inlineStr">
+      <c r="V52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="W52" s="93" t="inlineStr">
+      <c r="W52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -12068,37 +12067,37 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Y52" s="93" t="inlineStr">
+      <c r="Y52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Z52" s="93" t="inlineStr">
+      <c r="Z52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AA52" s="93" t="inlineStr">
+      <c r="AA52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AB52" s="93" t="inlineStr">
+      <c r="AB52" s="94" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="AC52" s="94" t="inlineStr">
+      <c r="AC52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD52" s="94" t="inlineStr">
+      <c r="AD52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE52" s="94" t="inlineStr">
+      <c r="AE52" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12111,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.62</v>
+        <v>-6.28</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-6.62</v>
@@ -12208,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>2.84</v>
@@ -12305,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>50.33</v>
+        <v>37.81</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>50.33</v>
@@ -12402,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>46.44</v>
+        <v>40.43</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>46.44</v>
@@ -12498,152 +12497,152 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="94" t="inlineStr">
+      <c r="B57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C57" s="94" t="inlineStr">
+      <c r="D57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D57" s="95" t="inlineStr">
+      <c r="F57" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G57" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="H57" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="I57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L57" s="95" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E57" s="94" t="inlineStr">
+      <c r="M57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F57" s="94" t="inlineStr">
+      <c r="P57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="R57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="S57" s="95" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="U57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="V57" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="W57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G57" s="94" t="inlineStr">
+      <c r="X57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H57" s="94" t="inlineStr">
+      <c r="Y57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="J57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L57" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="M57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="N57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O57" s="94" t="inlineStr">
+      <c r="Z57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P57" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q57" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="R57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="S57" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="U57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="V57" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W57" s="94" t="inlineStr">
+      <c r="AA57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X57" s="94" t="inlineStr">
+      <c r="AB57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y57" s="94" t="inlineStr">
+      <c r="AC57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z57" s="94" t="inlineStr">
+      <c r="AD57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD57" s="94" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE57" s="94" t="inlineStr">
+      <c r="AE57" s="93" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -12656,10 +12655,10 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>-1.78</v>
+        <v>0.14</v>
       </c>
       <c r="C58" s="96" t="n">
-        <v>-1.78</v>
+        <v>-1.7</v>
       </c>
       <c r="D58" s="96" t="n">
         <v>-0.82</v>
@@ -12753,10 +12752,10 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>9.300000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="C59" s="96" t="n">
-        <v>9.300000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D59" s="96" t="n">
         <v>10.81</v>
@@ -12850,10 +12849,10 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>43.95</v>
+        <v>58.12</v>
       </c>
       <c r="C60" s="96" t="n">
-        <v>43.95</v>
+        <v>45.13</v>
       </c>
       <c r="D60" s="96" t="n">
         <v>61.3</v>
@@ -12947,10 +12946,10 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>43.81</v>
+        <v>53.32</v>
       </c>
       <c r="C61" s="96" t="n">
-        <v>43.81</v>
+        <v>44.6</v>
       </c>
       <c r="D61" s="96" t="n">
         <v>54.16</v>
@@ -13040,14 +13039,14 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：sh:RSI11:20.66&lt;=27;sh:RSI2:0.92&lt;=7;kc:RSI5:15.25&lt;=21;vn:RSI3:17.75&lt;=25</t>
+          <t>今日买报：</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="92" t="inlineStr">
         <is>
-          <t>今日卖报：jp225:RSI5:78.16&gt;=74</t>
+          <t>今日卖报：jp225:RSI5:82.73&gt;=74</t>
         </is>
       </c>
     </row>
@@ -16703,13 +16702,13 @@
       <c r="G2" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="H2" s="99" t="n">
+      <c r="H2" s="98" t="n">
         <v>23.9310495</v>
       </c>
       <c r="I2" s="35" t="n">
         <v>12.09</v>
       </c>
-      <c r="J2" s="100">
+      <c r="J2" s="99">
         <f>(1+H2/100)^(1/(YEAR(D2)-YEAR(C2)))-1</f>
         <v/>
       </c>
@@ -16740,13 +16739,13 @@
       <c r="G3" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="99" t="n">
+      <c r="H3" s="98" t="n">
         <v>21.61014418</v>
       </c>
       <c r="I3" s="35" t="n">
         <v>-1.9</v>
       </c>
-      <c r="J3" s="100">
+      <c r="J3" s="99">
         <f>(1+H3/100)^(1/(YEAR(D3)-YEAR(C3)))-1</f>
         <v/>
       </c>
@@ -16777,13 +16776,13 @@
       <c r="G4" s="35" t="n">
         <v>76</v>
       </c>
-      <c r="H4" s="99" t="n">
+      <c r="H4" s="98" t="n">
         <v>46.08846392</v>
       </c>
       <c r="I4" s="35" t="n">
         <v>-0.96</v>
       </c>
-      <c r="J4" s="100">
+      <c r="J4" s="99">
         <f>(1+H4/100)^(1/(YEAR(D4)-YEAR(C4)))-1</f>
         <v/>
       </c>
@@ -16814,13 +16813,13 @@
       <c r="G5" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H5" s="99" t="n">
+      <c r="H5" s="98" t="n">
         <v>18.0953083</v>
       </c>
       <c r="I5" s="35" t="n">
         <v>-23.37</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <f>(1+H5/100)^(1/(YEAR(D5)-YEAR(C5)))-1</f>
         <v/>
       </c>
@@ -16851,13 +16850,13 @@
       <c r="G6" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H6" s="101" t="n">
+      <c r="H6" s="100" t="n">
         <v>38.04509628</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>15.85</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <f>(1+H6/100)^(1/(YEAR(D6)-YEAR(C6)))-1</f>
         <v/>
       </c>
@@ -16888,13 +16887,13 @@
       <c r="G7" s="35" t="n">
         <v>65</v>
       </c>
-      <c r="H7" s="99" t="n">
+      <c r="H7" s="98" t="n">
         <v>12.9328046</v>
       </c>
       <c r="I7" s="35" t="n">
         <v>-23.8</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <f>(1+H7/100)^(1/(YEAR(D7)-YEAR(C7)))-1</f>
         <v/>
       </c>
@@ -16925,13 +16924,13 @@
       <c r="G8" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="H8" s="101" t="n">
+      <c r="H8" s="100" t="n">
         <v>17.26300716</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>5.22</v>
       </c>
-      <c r="J8" s="100">
+      <c r="J8" s="99">
         <f>(1+H8/100)^(1/(YEAR(D8)-YEAR(C8)))-1</f>
         <v/>
       </c>
@@ -16962,13 +16961,13 @@
       <c r="G9" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H9" s="101" t="n">
+      <c r="H9" s="100" t="n">
         <v>48.50925168</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="99">
         <f>(1+H9/100)^(1/(YEAR(D9)-YEAR(C9)))-1</f>
         <v/>
       </c>
@@ -16999,13 +16998,13 @@
       <c r="G10" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H10" s="101" t="n">
+      <c r="H10" s="100" t="n">
         <v>702.9984392600001</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>257.05</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="101">
         <f>(1+H10/100)^(1/(YEAR(D10)-YEAR(C10)))-1</f>
         <v/>
       </c>
@@ -17036,13 +17035,13 @@
       <c r="G11" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="103" t="n">
+      <c r="H11" s="102" t="n">
         <v>120.95329264</v>
       </c>
       <c r="I11" s="46" t="n">
         <v>59.58</v>
       </c>
-      <c r="J11" s="104">
+      <c r="J11" s="103">
         <f>(1+H11/100)^(1/(YEAR(D11)-YEAR(C11)))-1</f>
         <v/>
       </c>
@@ -17073,13 +17072,13 @@
       <c r="G12" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H12" s="101" t="n">
+      <c r="H12" s="100" t="n">
         <v>891.19200896</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>675.88</v>
       </c>
-      <c r="J12" s="102">
+      <c r="J12" s="101">
         <f>(1+H12/100)^(1/(YEAR(D12)-YEAR(C12)))-1</f>
         <v/>
       </c>
@@ -17110,13 +17109,13 @@
       <c r="G13" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="103" t="n">
+      <c r="H13" s="102" t="n">
         <v>130.44764824</v>
       </c>
       <c r="I13" s="46" t="n">
         <v>74.70999999999999</v>
       </c>
-      <c r="J13" s="104">
+      <c r="J13" s="103">
         <f>(1+H13/100)^(1/(YEAR(D13)-YEAR(C13)))-1</f>
         <v/>
       </c>
@@ -17147,13 +17146,13 @@
       <c r="G14" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="H14" s="101" t="n">
+      <c r="H14" s="100" t="n">
         <v>612.29988714</v>
       </c>
       <c r="I14" s="23" t="n">
         <v>165.89</v>
       </c>
-      <c r="J14" s="102">
+      <c r="J14" s="101">
         <f>(1+H14/100)^(1/(YEAR(D14)-YEAR(C14)))-1</f>
         <v/>
       </c>
@@ -17184,13 +17183,13 @@
       <c r="G15" s="46" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="103" t="n">
+      <c r="H15" s="102" t="n">
         <v>95.7546074</v>
       </c>
       <c r="I15" s="46" t="n">
         <v>34.09</v>
       </c>
-      <c r="J15" s="104">
+      <c r="J15" s="103">
         <f>(1+H15/100)^(1/(YEAR(D15)-YEAR(C15)))-1</f>
         <v/>
       </c>
@@ -17221,13 +17220,13 @@
       <c r="G16" s="23" t="n">
         <v>74</v>
       </c>
-      <c r="H16" s="101" t="n">
+      <c r="H16" s="100" t="n">
         <v>355.1498973</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>107.56</v>
       </c>
-      <c r="J16" s="102">
+      <c r="J16" s="101">
         <f>(1+H16/100)^(1/(YEAR(D16)-YEAR(C16)))-1</f>
         <v/>
       </c>
@@ -17258,13 +17257,13 @@
       <c r="G17" s="46" t="n">
         <v>86</v>
       </c>
-      <c r="H17" s="103" t="n">
+      <c r="H17" s="102" t="n">
         <v>104.7539962</v>
       </c>
       <c r="I17" s="46" t="n">
         <v>69.98</v>
       </c>
-      <c r="J17" s="104">
+      <c r="J17" s="103">
         <f>(1+H17/100)^(1/(YEAR(D17)-YEAR(C17)))-1</f>
         <v/>
       </c>
@@ -17295,13 +17294,13 @@
       <c r="G18" s="23" t="n">
         <v>73</v>
       </c>
-      <c r="H18" s="101" t="n">
+      <c r="H18" s="100" t="n">
         <v>569.47222364</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>35.51</v>
       </c>
-      <c r="J18" s="102">
+      <c r="J18" s="101">
         <f>(1+H18/100)^(1/(YEAR(D18)-YEAR(C18)))-1</f>
         <v/>
       </c>
@@ -17332,13 +17331,13 @@
       <c r="G19" s="46" t="n">
         <v>87</v>
       </c>
-      <c r="H19" s="103" t="n">
+      <c r="H19" s="102" t="n">
         <v>81.41461922000001</v>
       </c>
       <c r="I19" s="46" t="n">
         <v>32.72</v>
       </c>
-      <c r="J19" s="104">
+      <c r="J19" s="103">
         <f>(1+H19/100)^(1/(YEAR(D19)-YEAR(C19)))-1</f>
         <v/>
       </c>
@@ -17369,13 +17368,13 @@
       <c r="G20" s="23" t="n">
         <v>90</v>
       </c>
-      <c r="H20" s="101" t="n">
+      <c r="H20" s="100" t="n">
         <v>117.80657762</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>81.66</v>
       </c>
-      <c r="J20" s="102">
+      <c r="J20" s="101">
         <f>(1+H20/100)^(1/(YEAR(D20)-YEAR(C20)))-1</f>
         <v/>
       </c>
@@ -17406,13 +17405,13 @@
       <c r="G21" s="46" t="n">
         <v>79</v>
       </c>
-      <c r="H21" s="103" t="n">
+      <c r="H21" s="102" t="n">
         <v>30.24021844</v>
       </c>
       <c r="I21" s="46" t="n">
         <v>22.68</v>
       </c>
-      <c r="J21" s="104">
+      <c r="J21" s="103">
         <f>(1+H21/100)^(1/(YEAR(D21)-YEAR(C21)))-1</f>
         <v/>
       </c>
@@ -17441,13 +17440,13 @@
       <c r="G22" s="66" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="105" t="n">
+      <c r="H22" s="104" t="n">
         <v>104.79727432</v>
       </c>
       <c r="I22" s="66" t="n">
         <v>21.86</v>
       </c>
-      <c r="J22" s="102">
+      <c r="J22" s="101">
         <f>(1+H22/100)^(1/(YEAR(D22)-YEAR(C22)))-1</f>
         <v/>
       </c>
@@ -17476,13 +17475,13 @@
       <c r="G23" s="66" t="n">
         <v>79</v>
       </c>
-      <c r="H23" s="105" t="n">
+      <c r="H23" s="104" t="n">
         <v>17.27596272</v>
       </c>
       <c r="I23" s="66" t="n">
         <v>4.71</v>
       </c>
-      <c r="J23" s="102">
+      <c r="J23" s="101">
         <f>(1+H23/100)^(1/(YEAR(D23)-YEAR(C23)))-1</f>
         <v/>
       </c>
@@ -17511,13 +17510,13 @@
       <c r="G24" s="23" t="n">
         <v>84</v>
       </c>
-      <c r="H24" s="101" t="n">
+      <c r="H24" s="100" t="n">
         <v>45.8229273</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>-1.84</v>
       </c>
-      <c r="J24" s="102">
+      <c r="J24" s="101">
         <f>(1+H24/100)^(1/(YEAR(D24)-YEAR(C24)))-1</f>
         <v/>
       </c>
@@ -17546,13 +17545,13 @@
       <c r="G25" s="23" t="n">
         <v>81</v>
       </c>
-      <c r="H25" s="101" t="n">
+      <c r="H25" s="100" t="n">
         <v>17.93032122</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>-23.26</v>
       </c>
-      <c r="J25" s="102">
+      <c r="J25" s="101">
         <f>(1+H25/100)^(1/(YEAR(D25)-YEAR(C25)))-1</f>
         <v/>
       </c>
@@ -17581,13 +17580,13 @@
       <c r="G26" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H26" s="101" t="n">
+      <c r="H26" s="100" t="n">
         <v>34.98312112</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>3.48</v>
       </c>
-      <c r="J26" s="102">
+      <c r="J26" s="101">
         <f>(1+H26/100)^(1/(YEAR(D26)-YEAR(C26)))-1</f>
         <v/>
       </c>
@@ -17616,13 +17615,13 @@
       <c r="G27" s="23" t="n">
         <v>67</v>
       </c>
-      <c r="H27" s="101" t="n">
+      <c r="H27" s="100" t="n">
         <v>26.27988584</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>-11.98</v>
       </c>
-      <c r="J27" s="102">
+      <c r="J27" s="101">
         <f>(1+H27/100)^(1/(YEAR(D27)-YEAR(C27)))-1</f>
         <v/>
       </c>
@@ -17651,13 +17650,13 @@
       <c r="G28" s="66" t="n">
         <v>81</v>
       </c>
-      <c r="H28" s="105" t="n">
+      <c r="H28" s="104" t="n">
         <v>369.32255078</v>
       </c>
       <c r="I28" s="66" t="n">
         <v>243.55</v>
       </c>
-      <c r="J28" s="102">
+      <c r="J28" s="101">
         <f>(1+H28/100)^(1/(YEAR(D28)-YEAR(C28)))-1</f>
         <v/>
       </c>
@@ -17686,13 +17685,13 @@
       <c r="G29" s="43" t="n">
         <v>79</v>
       </c>
-      <c r="H29" s="106" t="n">
+      <c r="H29" s="105" t="n">
         <v>114.17578458</v>
       </c>
       <c r="I29" s="43" t="n">
         <v>67.42</v>
       </c>
-      <c r="J29" s="104">
+      <c r="J29" s="103">
         <f>(1+H29/100)^(1/(YEAR(D29)-YEAR(C29)))-1</f>
         <v/>
       </c>
@@ -17721,13 +17720,13 @@
       <c r="G30" s="66" t="n">
         <v>90</v>
       </c>
-      <c r="H30" s="105" t="n">
+      <c r="H30" s="104" t="n">
         <v>507.04997572</v>
       </c>
       <c r="I30" s="66" t="n">
         <v>312.81</v>
       </c>
-      <c r="J30" s="102">
+      <c r="J30" s="101">
         <f>(1+H30/100)^(1/(YEAR(D30)-YEAR(C30)))-1</f>
         <v/>
       </c>
@@ -17756,13 +17755,13 @@
       <c r="G31" s="43" t="n">
         <v>74</v>
       </c>
-      <c r="H31" s="106" t="n">
+      <c r="H31" s="105" t="n">
         <v>167.78781912</v>
       </c>
       <c r="I31" s="43" t="n">
         <v>102.23</v>
       </c>
-      <c r="J31" s="104">
+      <c r="J31" s="103">
         <f>(1+H31/100)^(1/(YEAR(D31)-YEAR(C31)))-1</f>
         <v/>
       </c>
@@ -17791,13 +17790,13 @@
       <c r="G32" s="66" t="n">
         <v>92</v>
       </c>
-      <c r="H32" s="105" t="n">
+      <c r="H32" s="104" t="n">
         <v>136.38694796</v>
       </c>
       <c r="I32" s="66" t="n">
         <v>36.93</v>
       </c>
-      <c r="J32" s="102">
+      <c r="J32" s="101">
         <f>(1+H32/100)^(1/(YEAR(D32)-YEAR(C32)))-1</f>
         <v/>
       </c>
@@ -17826,13 +17825,13 @@
       <c r="G33" s="43" t="n">
         <v>96</v>
       </c>
-      <c r="H33" s="106" t="n">
+      <c r="H33" s="105" t="n">
         <v>95.06948973999999</v>
       </c>
       <c r="I33" s="43" t="n">
         <v>21.38</v>
       </c>
-      <c r="J33" s="104">
+      <c r="J33" s="103">
         <f>(1+H33/100)^(1/(YEAR(D33)-YEAR(C33)))-1</f>
         <v/>
       </c>
@@ -17861,13 +17860,13 @@
       <c r="G34" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H34" s="106" t="n">
+      <c r="H34" s="105" t="n">
         <v>81.73439344000001</v>
       </c>
       <c r="I34" s="43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J34" s="104">
+      <c r="J34" s="103">
         <f>(1+H34/100)^(1/(YEAR(D34)-YEAR(C34)))-1</f>
         <v/>
       </c>
@@ -17896,13 +17895,13 @@
       <c r="G35" s="66" t="n">
         <v>83</v>
       </c>
-      <c r="H35" s="105" t="n">
+      <c r="H35" s="104" t="n">
         <v>53.7012105</v>
       </c>
       <c r="I35" s="66" t="n">
         <v>12.79</v>
       </c>
-      <c r="J35" s="102">
+      <c r="J35" s="101">
         <f>(1+H35/100)^(1/(YEAR(D35)-YEAR(C35)))-1</f>
         <v/>
       </c>
@@ -17931,13 +17930,13 @@
       <c r="G36" s="43" t="n">
         <v>83</v>
       </c>
-      <c r="H36" s="106" t="n">
+      <c r="H36" s="105" t="n">
         <v>35.30009596</v>
       </c>
       <c r="I36" s="43" t="n">
         <v>28.95</v>
       </c>
-      <c r="J36" s="104">
+      <c r="J36" s="103">
         <f>(1+H36/100)^(1/(YEAR(D36)-YEAR(C36)))-1</f>
         <v/>
       </c>
@@ -17966,13 +17965,13 @@
       <c r="G37" s="66" t="n">
         <v>93</v>
       </c>
-      <c r="H37" s="105" t="n">
+      <c r="H37" s="104" t="n">
         <v>72.02704692</v>
       </c>
       <c r="I37" s="66" t="n">
         <v>63.75</v>
       </c>
-      <c r="J37" s="102">
+      <c r="J37" s="101">
         <f>(1+H37/100)^(1/(YEAR(D37)-YEAR(C37)))-1</f>
         <v/>
       </c>
@@ -18001,13 +18000,13 @@
       <c r="G38" s="66" t="n">
         <v>99</v>
       </c>
-      <c r="H38" s="105" t="n">
+      <c r="H38" s="104" t="n">
         <v>89.93269322</v>
       </c>
       <c r="I38" s="66" t="n">
         <v>60.24</v>
       </c>
-      <c r="J38" s="102">
+      <c r="J38" s="101">
         <f>(1+H38/100)^(1/(YEAR(D38)-YEAR(C38)))-1</f>
         <v/>
       </c>
@@ -18036,13 +18035,13 @@
       <c r="G39" s="43" t="n">
         <v>98</v>
       </c>
-      <c r="H39" s="106" t="n">
+      <c r="H39" s="105" t="n">
         <v>51.30245932</v>
       </c>
       <c r="I39" s="43" t="n">
         <v>30.26</v>
       </c>
-      <c r="J39" s="104">
+      <c r="J39" s="103">
         <f>(1+H39/100)^(1/(YEAR(D39)-YEAR(C39)))-1</f>
         <v/>
       </c>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.07000000000000001</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.42</v>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>0.07000000000000001</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.42</v>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>4.09</v>
+        <v>4.46</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>4.09</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>15.32</v>
+        <v>16.43</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>15.32</v>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>66.08</v>
+        <v>77</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>66.08</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>66.08</v>
+        <v>77</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>66.08</v>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-1.75</v>
+        <v>-1.11</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-1.75</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>3.7</v>
+        <v>4.54</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>3.7</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>49.59</v>
+        <v>51.42</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>49.59</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>56.36</v>
+        <v>57.3</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>56.36</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>8.17</v>
+        <v>8.59</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>8.17</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>19.99</v>
+        <v>22.02</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>19.99</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>65.22</v>
+        <v>76.8</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>65.22</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>65.22</v>
+        <v>76.8</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>65.22</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B48" s="96" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="C48" s="96" t="n">
         <v>7.7</v>
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="B49" s="96" t="n">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="C49" s="96" t="n">
         <v>8.050000000000001</v>
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="B50" s="96" t="n">
-        <v>77.69</v>
+        <v>77.61</v>
       </c>
       <c r="C50" s="96" t="n">
         <v>72.52</v>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="B51" s="96" t="n">
-        <v>66</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="C51" s="96" t="n">
         <v>63.55</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-6.28</v>
+        <v>-6.41</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-6.62</v>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>2.84</v>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>37.81</v>
+        <v>35.72</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>50.33</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>40.43</v>
+        <v>39.24</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>46.44</v>
@@ -12497,9 +12497,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B57" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B57" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C57" s="93" t="inlineStr">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>0.14</v>
+        <v>-0.65</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>-1.7</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>10.33</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>9.390000000000001</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>58.12</v>
+        <v>43.7</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>45.13</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>53.32</v>
+        <v>43.74</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>44.6</v>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="B26" s="91" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="91" t="n">
         <v>0.14</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="B27" s="91" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="C27" s="91" t="n">
         <v>0.48</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="B23" s="97" t="n">
-        <v>4.46</v>
+        <v>5.32</v>
       </c>
       <c r="C23" s="97" t="n">
         <v>4.46</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="B24" s="97" t="n">
-        <v>16.43</v>
+        <v>16.94</v>
       </c>
       <c r="C24" s="97" t="n">
         <v>16.43</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="B25" s="97" t="n">
-        <v>77</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="C25" s="97" t="n">
         <v>77</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="B26" s="97" t="n">
-        <v>77</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="C26" s="97" t="n">
         <v>77</v>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="B28" s="97" t="n">
-        <v>-1.11</v>
+        <v>-0.02</v>
       </c>
       <c r="C28" s="97" t="n">
         <v>-1.11</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="B29" s="97" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="C29" s="97" t="n">
         <v>4.54</v>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="B30" s="97" t="n">
-        <v>51.42</v>
+        <v>56.85</v>
       </c>
       <c r="C30" s="97" t="n">
         <v>51.42</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="B31" s="97" t="n">
-        <v>57.3</v>
+        <v>59.81</v>
       </c>
       <c r="C31" s="97" t="n">
         <v>57.3</v>
@@ -9761,9 +9761,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="95" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B32" s="96" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C32" s="95" t="inlineStr">
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B33" s="97" t="n">
-        <v>8.59</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="C33" s="97" t="n">
         <v>8.59</v>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="B34" s="97" t="n">
-        <v>22.02</v>
+        <v>23.08</v>
       </c>
       <c r="C34" s="97" t="n">
         <v>22.02</v>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="B35" s="97" t="n">
-        <v>76.8</v>
+        <v>83.52</v>
       </c>
       <c r="C35" s="97" t="n">
         <v>76.8</v>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="B36" s="97" t="n">
-        <v>76.8</v>
+        <v>83.52</v>
       </c>
       <c r="C36" s="97" t="n">
         <v>76.8</v>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="B53" s="97" t="n">
-        <v>-7.13</v>
+        <v>-7.64</v>
       </c>
       <c r="C53" s="97" t="n">
         <v>-6.41</v>
@@ -12188,7 +12188,7 @@
         </is>
       </c>
       <c r="B54" s="97" t="n">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="C54" s="97" t="n">
         <v>2.54</v>
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="B55" s="97" t="n">
-        <v>27.36</v>
+        <v>21.75</v>
       </c>
       <c r="C55" s="97" t="n">
         <v>35.72</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="B56" s="97" t="n">
-        <v>34.53</v>
+        <v>30.51</v>
       </c>
       <c r="C56" s="97" t="n">
         <v>39.24</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B58" s="97" t="n">
-        <v>-0.78</v>
+        <v>-0.88</v>
       </c>
       <c r="C58" s="97" t="n">
         <v>-0.7</v>
@@ -12731,7 +12731,7 @@
         </is>
       </c>
       <c r="B59" s="97" t="n">
-        <v>9.02</v>
+        <v>8.91</v>
       </c>
       <c r="C59" s="97" t="n">
         <v>9.41</v>
@@ -12828,7 +12828,7 @@
         </is>
       </c>
       <c r="B60" s="97" t="n">
-        <v>52.76</v>
+        <v>50.34</v>
       </c>
       <c r="C60" s="97" t="n">
         <v>42.85</v>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="B61" s="97" t="n">
-        <v>49.12</v>
+        <v>47.59</v>
       </c>
       <c r="C61" s="97" t="n">
         <v>43.21</v>
@@ -13018,7 +13018,7 @@
     <row r="63">
       <c r="A63" s="93" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RSI6:28.42&lt;=30;fr40:RSI3:27.36&lt;=28</t>
+          <t>今日买报：hk50:RSI6:28.42&lt;=30;fr40:RSI3:21.75&lt;=28</t>
         </is>
       </c>
     </row>

--- a/report_2406.xlsx
+++ b/report_2406.xlsx
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.44</v>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>5.32</v>
+        <v>4.78</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>5.32</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>16.94</v>
+        <v>16.25</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>16.94</v>
@@ -9028,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="inlineStr">
+      <c r="A25" s="97" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>83.23999999999999</v>
+        <v>24.17</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>83.23999999999999</v>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>83.23999999999999</v>
+        <v>24.17</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>83.23999999999999</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>4.6</v>
+        <v>4.41</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>4.6</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>56.85</v>
+        <v>47.02</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>56.85</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>59.81</v>
+        <v>54.79</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>59.81</v>
@@ -9772,9 +9772,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B32" s="95" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C32" s="95" t="inlineStr">
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>9.960000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>9.960000000000001</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>23.08</v>
+        <v>22.09</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>23.08</v>
@@ -10118,13 +10118,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="78" t="inlineStr">
+      <c r="A35" s="97" t="inlineStr">
         <is>
           <t>ixic:RSI2</t>
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>83.52</v>
+        <v>35.33</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>83.52</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>83.52</v>
+        <v>35.33</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>83.52</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>-8.390000000000001</v>
+        <v>-8.25</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>-7.64</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>1.08</v>
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>14.81</v>
+        <v>15.72</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>21.75</v>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>24.96</v>
+        <v>25.81</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>30.51</v>
@@ -13037,7 +13037,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RSI6:28.61&lt;=30;vn:RSI3:13.75&lt;=25;fr40:RSI3:14.81&lt;=28</t>
+          <t>今日买报：hk50:RSI6:28.61&lt;=30;us500:RSI2:24.17&lt;=28;ixic:RSI2:35.33&lt;=36;vn:RSI3:13.75&lt;=25;fr40:RSI3:15.72&lt;=28</t>
         </is>
       </c>
     </row>
